--- a/data/computational_data_processed/quencher_properties_calc.xlsx
+++ b/data/computational_data_processed/quencher_properties_calc.xlsx
@@ -795,7 +795,7 @@
         <v>144.5</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="L3" s="19" t="n">
         <v>4.5</v>
@@ -807,7 +807,7 @@
         <v>49.9</v>
       </c>
       <c r="P3" s="19" t="n">
-        <v>-2.28</v>
+        <v>-2.26</v>
       </c>
       <c r="Q3" s="19" t="n">
         <v>4.9</v>
@@ -896,7 +896,7 @@
         <v>142.9</v>
       </c>
       <c r="K4" s="19" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="L4" s="19" t="n">
         <v>4.4</v>
@@ -908,7 +908,7 @@
         <v>41.4</v>
       </c>
       <c r="P4" s="19" t="n">
-        <v>-2.65</v>
+        <v>-2.62</v>
       </c>
       <c r="Q4" s="19" t="n">
         <v>5.5</v>
@@ -997,7 +997,7 @@
         <v>155.5</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="L5" s="19" t="n">
         <v>5.3</v>
@@ -1009,7 +1009,7 @@
         <v>73</v>
       </c>
       <c r="P5" s="19" t="n">
-        <v>-1.28</v>
+        <v>-1.25</v>
       </c>
       <c r="Q5" s="19" t="n">
         <v>12.9</v>
@@ -1098,7 +1098,7 @@
         <v>139.5</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="L6" s="19" t="n">
         <v>3.9</v>
@@ -1110,7 +1110,7 @@
         <v>35.4</v>
       </c>
       <c r="P6" s="19" t="n">
-        <v>-2.91</v>
+        <v>-2.88</v>
       </c>
       <c r="Q6" s="19" t="n">
         <v>5.1</v>
@@ -1199,7 +1199,7 @@
         <v>158.8</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="L7" s="19" t="n">
         <v>10.1</v>
@@ -1211,7 +1211,7 @@
         <v>63.9</v>
       </c>
       <c r="P7" s="19" t="n">
-        <v>-1.67</v>
+        <v>-1.65</v>
       </c>
       <c r="Q7" s="19" t="n">
         <v>4.8</v>
@@ -1300,7 +1300,7 @@
         <v>145.5</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="L8" s="19" t="n">
         <v>3.4</v>
@@ -1312,7 +1312,7 @@
         <v>49.6</v>
       </c>
       <c r="P8" s="19" t="n">
-        <v>-2.29</v>
+        <v>-2.27</v>
       </c>
       <c r="Q8" s="19" t="n">
         <v>4.7</v>
@@ -1401,7 +1401,7 @@
         <v>151.3</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="L9" s="19" t="n">
         <v>3.8</v>
@@ -1413,7 +1413,7 @@
         <v>60.3</v>
       </c>
       <c r="P9" s="19" t="n">
-        <v>-1.83</v>
+        <v>-1.81</v>
       </c>
       <c r="Q9" s="19" t="n">
         <v>6.7</v>
@@ -1502,7 +1502,7 @@
         <v>158.2</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="L10" s="19" t="n">
         <v>24.4</v>
@@ -1514,7 +1514,7 @@
         <v>54.8</v>
       </c>
       <c r="P10" s="19" t="n">
-        <v>-2.07</v>
+        <v>-2.04</v>
       </c>
       <c r="Q10" s="19" t="n">
         <v>11.3</v>
@@ -1603,7 +1603,7 @@
         <v>134.8</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="L11" s="19" t="n">
         <v>6</v>
@@ -1615,7 +1615,7 @@
         <v>39.1</v>
       </c>
       <c r="P11" s="19" t="n">
-        <v>-2.75</v>
+        <v>-2.72</v>
       </c>
       <c r="Q11" s="19" t="n">
         <v>7.4</v>
@@ -1704,7 +1704,7 @@
         <v>137.6</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="L12" s="19" t="n">
         <v>10.5</v>
@@ -1797,7 +1797,7 @@
         <v>136.7</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="L13" s="19" t="n">
         <v>9.300000000000001</v>
@@ -1890,7 +1890,7 @@
         <v>140.9</v>
       </c>
       <c r="K14" s="19" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="L14" s="19" t="n">
         <v>4.6</v>
@@ -1902,7 +1902,7 @@
         <v>44.5</v>
       </c>
       <c r="P14" s="19" t="n">
-        <v>-2.51</v>
+        <v>-2.49</v>
       </c>
       <c r="Q14" s="19" t="n">
         <v>5.1</v>
@@ -1991,7 +1991,7 @@
         <v>172.2</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="L15" s="19" t="n">
         <v>8.9</v>
@@ -2003,7 +2003,7 @@
         <v>76.09999999999999</v>
       </c>
       <c r="P15" s="19" t="n">
-        <v>-1.14</v>
+        <v>-1.12</v>
       </c>
       <c r="Q15" s="19" t="n">
         <v>9.300000000000001</v>
@@ -2092,7 +2092,7 @@
         <v>159</v>
       </c>
       <c r="K16" s="19" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="L16" s="19" t="n">
         <v>90.90000000000001</v>
@@ -2104,7 +2104,7 @@
         <v>48</v>
       </c>
       <c r="P16" s="19" t="n">
-        <v>-2.36</v>
+        <v>-2.34</v>
       </c>
       <c r="Q16" s="19" t="n">
         <v>11</v>
@@ -2193,7 +2193,7 @@
         <v>136.3</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="L17" s="19" t="n">
         <v>4.3</v>
@@ -2205,7 +2205,7 @@
         <v>32.7</v>
       </c>
       <c r="P17" s="19" t="n">
-        <v>-3.02</v>
+        <v>-3</v>
       </c>
       <c r="Q17" s="19" t="n">
         <v>5.9</v>
@@ -2294,7 +2294,7 @@
         <v>134.5</v>
       </c>
       <c r="K18" s="19" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="L18" s="19" t="n">
         <v>5.5</v>
@@ -2306,7 +2306,7 @@
         <v>45.5</v>
       </c>
       <c r="P18" s="19" t="n">
-        <v>-2.47</v>
+        <v>-2.45</v>
       </c>
       <c r="Q18" s="19" t="n">
         <v>6.3</v>
@@ -2395,7 +2395,7 @@
         <v>132.9</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="L19" s="19" t="n">
         <v>7.5</v>
@@ -2407,7 +2407,7 @@
         <v>54.2</v>
       </c>
       <c r="P19" s="19" t="n">
-        <v>-2.09</v>
+        <v>-2.07</v>
       </c>
       <c r="Q19" s="19" t="n">
         <v>119.6</v>
@@ -2496,7 +2496,7 @@
         <v>124.5</v>
       </c>
       <c r="K20" s="19" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="L20" s="19" t="n">
         <v>10.4</v>
@@ -2508,7 +2508,7 @@
         <v>44</v>
       </c>
       <c r="P20" s="19" t="n">
-        <v>-2.53</v>
+        <v>-2.51</v>
       </c>
       <c r="Q20" s="19" t="n">
         <v>7.2</v>
@@ -2597,7 +2597,7 @@
         <v>153</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="L21" s="19" t="n">
         <v>5.5</v>
@@ -2609,7 +2609,7 @@
         <v>57.1</v>
       </c>
       <c r="P21" s="19" t="n">
-        <v>-1.97</v>
+        <v>-1.94</v>
       </c>
       <c r="Q21" s="19" t="n">
         <v>10.6</v>
@@ -2698,7 +2698,7 @@
         <v>138.8</v>
       </c>
       <c r="K22" s="19" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="L22" s="19" t="n">
         <v>3</v>
@@ -2710,7 +2710,7 @@
         <v>41.8</v>
       </c>
       <c r="P22" s="19" t="n">
-        <v>-2.63</v>
+        <v>-2.61</v>
       </c>
       <c r="Q22" s="19" t="n">
         <v>4</v>
@@ -2799,7 +2799,7 @@
         <v>155.8</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="L23" s="19" t="n">
         <v>5</v>
@@ -2811,7 +2811,7 @@
         <v>56.7</v>
       </c>
       <c r="P23" s="19" t="n">
-        <v>-1.98</v>
+        <v>-1.96</v>
       </c>
       <c r="Q23" s="19" t="n">
         <v>7.3</v>
@@ -2900,7 +2900,7 @@
         <v>148.9</v>
       </c>
       <c r="K24" s="19" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="L24" s="19" t="n">
         <v>6</v>
@@ -2912,7 +2912,7 @@
         <v>57.2</v>
       </c>
       <c r="P24" s="19" t="n">
-        <v>-1.96</v>
+        <v>-1.94</v>
       </c>
       <c r="Q24" s="19" t="n">
         <v>12.2</v>
@@ -3001,7 +3001,7 @@
         <v>140.7</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="L25" s="19" t="n">
         <v>3.9</v>
@@ -3013,7 +3013,7 @@
         <v>45.5</v>
       </c>
       <c r="P25" s="19" t="n">
-        <v>-2.47</v>
+        <v>-2.45</v>
       </c>
       <c r="Q25" s="19" t="n">
         <v>6.5</v>
@@ -3102,7 +3102,7 @@
         <v>142.3</v>
       </c>
       <c r="K26" s="19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="L26" s="19" t="n">
         <v>5.3</v>
@@ -3114,7 +3114,7 @@
         <v>42.7</v>
       </c>
       <c r="P26" s="19" t="n">
-        <v>-2.59</v>
+        <v>-2.57</v>
       </c>
       <c r="Q26" s="19" t="n">
         <v>6.9</v>
@@ -3203,7 +3203,7 @@
         <v>141.3</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="L27" s="19" t="n">
         <v>4.6</v>
@@ -3215,7 +3215,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="P27" s="19" t="n">
-        <v>-1.64</v>
+        <v>-1.62</v>
       </c>
       <c r="Q27" s="19" t="n">
         <v>73.09999999999999</v>
@@ -3304,7 +3304,7 @@
         <v>140.8</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="L28" s="19" t="n">
         <v>5.1</v>
@@ -3316,7 +3316,7 @@
         <v>62.2</v>
       </c>
       <c r="P28" s="19" t="n">
-        <v>-1.74</v>
+        <v>-1.72</v>
       </c>
       <c r="Q28" s="19" t="n">
         <v>73.5</v>
@@ -3405,7 +3405,7 @@
         <v>144.2</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="L29" s="19" t="n">
         <v>5.3</v>
@@ -3417,7 +3417,7 @@
         <v>65.3</v>
       </c>
       <c r="P29" s="19" t="n">
-        <v>-1.61</v>
+        <v>-1.59</v>
       </c>
       <c r="Q29" s="19" t="n">
         <v>68</v>
@@ -3506,7 +3506,7 @@
         <v>159.3</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="L30" s="19" t="n">
         <v>6.3</v>
@@ -3518,7 +3518,7 @@
         <v>71</v>
       </c>
       <c r="P30" s="19" t="n">
-        <v>-1.36</v>
+        <v>-1.34</v>
       </c>
       <c r="Q30" s="19" t="n">
         <v>6.6</v>
@@ -3607,7 +3607,7 @@
         <v>154.9</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="L31" s="19" t="n">
         <v>7.9</v>
@@ -3619,7 +3619,7 @@
         <v>55</v>
       </c>
       <c r="P31" s="19" t="n">
-        <v>-2.06</v>
+        <v>-2.04</v>
       </c>
       <c r="Q31" s="19" t="n">
         <v>7</v>
@@ -3708,7 +3708,7 @@
         <v>132.6</v>
       </c>
       <c r="K32" s="19" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="L32" s="19" t="n">
         <v>4.8</v>
@@ -3720,7 +3720,7 @@
         <v>49.3</v>
       </c>
       <c r="P32" s="19" t="n">
-        <v>-2.3</v>
+        <v>-2.28</v>
       </c>
       <c r="Q32" s="19" t="n">
         <v>5.4</v>
@@ -3809,7 +3809,7 @@
         <v>142.4</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="L33" s="19" t="n">
         <v>7.4</v>
@@ -3821,7 +3821,7 @@
         <v>40.2</v>
       </c>
       <c r="P33" s="19" t="n">
-        <v>-2.7</v>
+        <v>-2.68</v>
       </c>
       <c r="Q33" s="19" t="n">
         <v>27.2</v>
@@ -3910,7 +3910,7 @@
         <v>134.1</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="L34" s="19" t="n">
         <v>2.5</v>
@@ -3922,7 +3922,7 @@
         <v>53.8</v>
       </c>
       <c r="P34" s="19" t="n">
-        <v>-2.11</v>
+        <v>-2.09</v>
       </c>
       <c r="Q34" s="19" t="n">
         <v>21.1</v>
@@ -4011,7 +4011,7 @@
         <v>133.5</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="L35" s="19" t="n">
         <v>7.2</v>
@@ -4023,7 +4023,7 @@
         <v>51.3</v>
       </c>
       <c r="P35" s="19" t="n">
-        <v>-2.22</v>
+        <v>-2.2</v>
       </c>
       <c r="Q35" s="19" t="n">
         <v>23.5</v>
@@ -4112,7 +4112,7 @@
         <v>139.8</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="L36" s="19" t="n">
         <v>13.6</v>
@@ -4124,7 +4124,7 @@
         <v>44</v>
       </c>
       <c r="P36" s="19" t="n">
-        <v>-2.53</v>
+        <v>-2.51</v>
       </c>
       <c r="Q36" s="19" t="n">
         <v>8.199999999999999</v>
@@ -4213,7 +4213,7 @@
         <v>135.6</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="L37" s="19" t="n">
         <v>8.6</v>
@@ -4225,7 +4225,7 @@
         <v>52.8</v>
       </c>
       <c r="P37" s="19" t="n">
-        <v>-2.15</v>
+        <v>-2.13</v>
       </c>
       <c r="Q37" s="19" t="n">
         <v>1.9</v>
@@ -4314,7 +4314,7 @@
         <v>138.4</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="L38" s="19" t="n">
         <v>4.6</v>
@@ -4326,7 +4326,7 @@
         <v>44.9</v>
       </c>
       <c r="P38" s="19" t="n">
-        <v>-2.49</v>
+        <v>-2.47</v>
       </c>
       <c r="Q38" s="19" t="n">
         <v>6.9</v>
@@ -4415,7 +4415,7 @@
         <v>143.1</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="L39" s="19" t="n">
         <v>6</v>
@@ -4427,7 +4427,7 @@
         <v>44.7</v>
       </c>
       <c r="P39" s="19" t="n">
-        <v>-2.5</v>
+        <v>-2.48</v>
       </c>
       <c r="Q39" s="19" t="n">
         <v>26.9</v>
@@ -4516,7 +4516,7 @@
         <v>145.6</v>
       </c>
       <c r="K40" s="19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="L40" s="19" t="n">
         <v>4.5</v>
@@ -4528,7 +4528,7 @@
         <v>41.6</v>
       </c>
       <c r="P40" s="19" t="n">
-        <v>-2.64</v>
+        <v>-2.62</v>
       </c>
       <c r="Q40" s="19" t="n">
         <v>8.9</v>
@@ -4617,7 +4617,7 @@
         <v>139</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="L41" s="19" t="n">
         <v>7</v>
@@ -4629,7 +4629,7 @@
         <v>49.9</v>
       </c>
       <c r="P41" s="19" t="n">
-        <v>-2.28</v>
+        <v>-2.26</v>
       </c>
       <c r="Q41" s="19" t="n">
         <v>5.5</v>
@@ -4718,7 +4718,7 @@
         <v>144</v>
       </c>
       <c r="K42" s="19" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="L42" s="19" t="n">
         <v>6.5</v>
@@ -4730,7 +4730,7 @@
         <v>45.7</v>
       </c>
       <c r="P42" s="19" t="n">
-        <v>-2.46</v>
+        <v>-2.44</v>
       </c>
       <c r="Q42" s="19" t="n">
         <v>5.8</v>
@@ -4819,7 +4819,7 @@
         <v>141.3</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="L43" s="19" t="n">
         <v>5.1</v>
@@ -4831,7 +4831,7 @@
         <v>39.5</v>
       </c>
       <c r="P43" s="19" t="n">
-        <v>-2.73</v>
+        <v>-2.71</v>
       </c>
       <c r="Q43" s="19" t="n">
         <v>6.1</v>
@@ -4920,7 +4920,7 @@
         <v>150.9</v>
       </c>
       <c r="K44" s="19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="L44" s="19" t="n">
         <v>7.1</v>
@@ -4932,7 +4932,7 @@
         <v>61.4</v>
       </c>
       <c r="P44" s="19" t="n">
-        <v>-1.78</v>
+        <v>-1.76</v>
       </c>
       <c r="Q44" s="19" t="n">
         <v>7</v>
@@ -5021,7 +5021,7 @@
         <v>147.3</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="L45" s="19" t="n">
         <v>6</v>
@@ -5033,7 +5033,7 @@
         <v>57.1</v>
       </c>
       <c r="P45" s="19" t="n">
-        <v>-1.97</v>
+        <v>-1.94</v>
       </c>
       <c r="Q45" s="19" t="n">
         <v>6.9</v>
@@ -5122,7 +5122,7 @@
         <v>161.4</v>
       </c>
       <c r="K46" s="19" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="L46" s="19" t="n">
         <v>11.4</v>
@@ -5134,7 +5134,7 @@
         <v>60.1</v>
       </c>
       <c r="P46" s="19" t="n">
-        <v>-1.84</v>
+        <v>-1.81</v>
       </c>
       <c r="Q46" s="19" t="n">
         <v>7.8</v>
@@ -5223,7 +5223,7 @@
         <v>152.6</v>
       </c>
       <c r="K47" s="19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="L47" s="19" t="n">
         <v>6</v>
@@ -5235,7 +5235,7 @@
         <v>46.4</v>
       </c>
       <c r="P47" s="19" t="n">
-        <v>-2.43</v>
+        <v>-2.41</v>
       </c>
       <c r="Q47" s="19" t="n">
         <v>12.2</v>
@@ -5324,7 +5324,7 @@
         <v>145.4</v>
       </c>
       <c r="K48" s="19" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="L48" s="19" t="n">
         <v>31.1</v>
@@ -5336,7 +5336,7 @@
         <v>51.7</v>
       </c>
       <c r="P48" s="19" t="n">
-        <v>-2.2</v>
+        <v>-2.18</v>
       </c>
       <c r="Q48" s="19" t="n">
         <v>6.1</v>
@@ -5425,7 +5425,7 @@
         <v>152.7</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="L49" s="19" t="n">
         <v>25.6</v>
@@ -5437,7 +5437,7 @@
         <v>58.2</v>
       </c>
       <c r="P49" s="19" t="n">
-        <v>-1.92</v>
+        <v>-1.9</v>
       </c>
       <c r="Q49" s="19" t="n">
         <v>7.8</v>
@@ -5526,7 +5526,7 @@
         <v>158.9</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="L50" s="19" t="n">
         <v>4</v>
@@ -5538,7 +5538,7 @@
         <v>51.9</v>
       </c>
       <c r="P50" s="19" t="n">
-        <v>-2.19</v>
+        <v>-2.17</v>
       </c>
       <c r="Q50" s="19" t="n">
         <v>8.699999999999999</v>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>dG_Ox / F - 4.442 V.</t>
+          <t>dG_Ox / F - 4.42 V.</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>dG_Red / F - 4.442 V.</t>
+          <t>dG_Red / F - 4.42 V.</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">

--- a/data/computational_data_processed/quencher_properties_calc.xlsx
+++ b/data/computational_data_processed/quencher_properties_calc.xlsx
@@ -513,7 +513,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="2" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -774,7 +774,7 @@
       </c>
       <c r="C3" s="19" t="inlineStr">
         <is>
-          <t>6-Me-quinoline</t>
+          <t>6-methylquinoline</t>
         </is>
       </c>
       <c r="D3" s="19" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>2-Nitro-m-Xylene</t>
+          <t>1,3-dimethyl-2-nitrobenzene</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>Benzothiophene</t>
+          <t>benzo[b]thiophene</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>Quinoxaline</t>
+          <t>quinoxaline</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>Isoquinoline</t>
+          <t>isoquinoline</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>Coumarin</t>
+          <t>coumarin</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>OiPr bifunc</t>
+          <t>benzophenone O-(isopropoxycarbonyl) oxime</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>2-Ph-3-Me-Thiazol</t>
+          <t>3-methyl-2-phenylthiophene</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>Diphenyldisulfide</t>
+          <t>diphenyl disulfide</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>Dibenzyldisulfide</t>
+          <t>dibenzyl disulfide</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>dihydro azaborinine</t>
+          <t>1,2-dihydro-1,2-benzazaborinine</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>maleimide</t>
+          <t>N-methylmaleimide</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>Butyl-Methacrylate</t>
+          <t>butyl methacrylate</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>Inden</t>
+          <t>indene</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>5-Me-Pyridone</t>
+          <t>5-methylpyridin-2(1H)-one</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>(BnSe)2</t>
+          <t>dibenzyl diselenide</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>oxadiazole</t>
+          <t>5,5-dimethyl-3-phenyl-4,5-dihydro-1,2,4-oxadiazole</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>sulfur bifunc</t>
+          <t>benzophenone O-[(benzylsulfanyl)carbonyl] oxime</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>Ethylphenylpropiolat</t>
+          <t>ethyl 3-phenylpropiolate</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>4-Oxo-Quinazolin</t>
+          <t>4-oxo-2-phenylquinazolin-3(4H)-yl 3-phenylpropanoate</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>Bpin-Benzothiophen</t>
+          <t>2-(benzo[b]thiophen-2-yl)-4,4,5,5-tetramethyl-1,3,2-dioxaborolane</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>Bpin-Benzofuran</t>
+          <t>2-(benzofuran-2-yl)-4,4,5,5-tetramethyl-1,3,2-dioxaborolane</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>Br-Benzothiophen</t>
+          <t>2-bromobenzo[b]thiophene</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>Br-Benzofuran</t>
+          <t>2-bromobenzofuran</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>Di-Br-Thiophene</t>
+          <t>2,5-dibromothiophene</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>Benzoyl-Thiazol</t>
+          <t>2-benzoylthiazole</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>Isoxazolon</t>
+          <t>4,4-dimethyl-3-phenylisoxazol-5(4H)-one</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>E-Stilbene</t>
+          <t>(E)-stilbene</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>N-Peroxide</t>
+          <t>6-phenyl-5-oxa-6-azaspiro[2.4]heptane-4,7-dione</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>Thioamide 1</t>
+          <t>1-(thiobenzoyl)pyrrolidine</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>Thioamide 2</t>
+          <t>N-methyl-N-phenylpropanethioamide</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>oxime ether</t>
+          <t>(Z)-3,4-dihydronaphthalen-1(2H)-one O-methyl oxime</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t>Z-Stilbene</t>
+          <t>(Z)-stilbene</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>Ac-Pyrol</t>
+          <t>2-acetyl-1-methylpyrrole</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
-          <t>F-styrene</t>
+          <t>1-bromo-4-(2,2-difluorovinyl)benzene</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>butadiene</t>
+          <t>1,3-butadiene</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t>4-Me-2-Ph-Thiazol</t>
+          <t>4-methyl-2-phenylthiazole</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>Ph-Oxazol</t>
+          <t>2-phenyloxazole</t>
         </is>
       </c>
       <c r="D42" s="19" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t>alpha-Methylstyrol</t>
+          <t>alpha-methylstyrene</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="C44" s="19" t="inlineStr">
         <is>
-          <t>2-Benzoyl-Furan</t>
+          <t>2-benzoylfuran</t>
         </is>
       </c>
       <c r="D44" s="19" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>2-Acetyl-4-Me-Thiophen</t>
+          <t>2-acetyl-4-methylthiophene</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C46" s="19" t="inlineStr">
         <is>
-          <t>2-Acetylpyridine</t>
+          <t>2-acetylpyridine</t>
         </is>
       </c>
       <c r="D46" s="19" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t>vinyl selenoxide</t>
+          <t>phenyl vinyl selenoxide</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C48" s="19" t="inlineStr">
         <is>
-          <t>Azirin-Intermediat</t>
+          <t>2,2-dimethyl-3-phenyl-2H-azirine</t>
         </is>
       </c>
       <c r="D48" s="19" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t>Quinolin-8-Ester</t>
+          <t>methyl quinoline-8-carboxylate</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C50" s="19" t="inlineStr">
         <is>
-          <t>Cyclohexenone</t>
+          <t>cyclohex-2-en-1-one</t>
         </is>
       </c>
       <c r="D50" s="19" t="inlineStr">
@@ -5711,7 +5711,7 @@
       <c r="C4" s="21" t="inlineStr"/>
       <c r="D4" s="22" t="inlineStr">
         <is>
-          <t>Compound, from the experimental record.</t>
+          <t>Name derived from the SMILES, as in the experimental workbook.</t>
         </is>
       </c>
       <c r="E4" s="21" t="inlineStr">

--- a/data/computational_data_processed/quencher_properties_calc.xlsx
+++ b/data/computational_data_processed/quencher_properties_calc.xlsx
@@ -36,7 +36,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -68,11 +68,6 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDE2F6"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -113,10 +108,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -130,9 +121,6 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -508,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ50"/>
+  <dimension ref="A1:AE50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -530,23 +518,18 @@
     <col width="27" customWidth="1" min="17" max="17"/>
     <col width="27" customWidth="1" min="18" max="18"/>
     <col width="2" customWidth="1" min="19" max="19"/>
-    <col width="17" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="2" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="23" customWidth="1" min="28" max="28"/>
-    <col width="25" customWidth="1" min="29" max="29"/>
-    <col width="25" customWidth="1" min="30" max="30"/>
-    <col width="24" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
-    <col width="29" customWidth="1" min="34" max="34"/>
-    <col width="28" customWidth="1" min="35" max="35"/>
-    <col width="29" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="23" customWidth="1" min="23" max="23"/>
+    <col width="25" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="26" max="26"/>
+    <col width="25" customWidth="1" min="27" max="27"/>
+    <col width="29" customWidth="1" min="28" max="28"/>
+    <col width="29" customWidth="1" min="29" max="29"/>
+    <col width="28" customWidth="1" min="30" max="30"/>
+    <col width="29" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -583,5026 +566,4421 @@
       <c r="R1" s="8" t="n"/>
       <c r="T1" s="9" t="inlineStr">
         <is>
-          <t>Conformers</t>
+          <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
       <c r="U1" s="10" t="n"/>
       <c r="V1" s="10" t="n"/>
       <c r="W1" s="10" t="n"/>
-      <c r="Y1" s="11" t="inlineStr">
-        <is>
-          <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="Z1" s="12" t="n"/>
-      <c r="AA1" s="12" t="n"/>
-      <c r="AB1" s="12" t="n"/>
-      <c r="AC1" s="12" t="n"/>
-      <c r="AD1" s="12" t="n"/>
-      <c r="AE1" s="12" t="n"/>
-      <c r="AF1" s="12" t="n"/>
-      <c r="AG1" s="12" t="n"/>
-      <c r="AH1" s="12" t="n"/>
-      <c r="AI1" s="12" t="n"/>
-      <c r="AJ1" s="12" t="n"/>
+      <c r="X1" s="10" t="n"/>
+      <c r="Y1" s="10" t="n"/>
+      <c r="Z1" s="10" t="n"/>
+      <c r="AA1" s="10" t="n"/>
+      <c r="AB1" s="10" t="n"/>
+      <c r="AC1" s="10" t="n"/>
+      <c r="AD1" s="10" t="n"/>
+      <c r="AE1" s="10" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>quencher_id</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>quencher_name</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>compound</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>smiles</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>E_T / kcal mol-1</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>lambda_S_T / kcal mol-1</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>lambda_T_S / kcal mol-1</t>
         </is>
       </c>
-      <c r="J2" s="15" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>dG_Ox / kcal mol-1</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="K2" s="13" t="inlineStr">
         <is>
           <t>E_Ox_vs_SCE_calc / V</t>
         </is>
       </c>
-      <c r="L2" s="15" t="inlineStr">
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>lambda_S0_D+ / kcal mol-1</t>
         </is>
       </c>
-      <c r="M2" s="15" t="inlineStr">
+      <c r="M2" s="13" t="inlineStr">
         <is>
           <t>lambda_D+_S0 / kcal mol-1</t>
         </is>
       </c>
-      <c r="O2" s="16" t="inlineStr">
+      <c r="O2" s="14" t="inlineStr">
         <is>
           <t>dG_Red / kcal mol-1</t>
         </is>
       </c>
-      <c r="P2" s="16" t="inlineStr">
+      <c r="P2" s="14" t="inlineStr">
         <is>
           <t>E_Red_vs_SCE_calc / V</t>
         </is>
       </c>
-      <c r="Q2" s="16" t="inlineStr">
+      <c r="Q2" s="14" t="inlineStr">
         <is>
           <t>lambda_S0_D- / kcal mol-1</t>
         </is>
       </c>
-      <c r="R2" s="16" t="inlineStr">
+      <c r="R2" s="14" t="inlineStr">
         <is>
           <t>lambda_D-_S0 / kcal mol-1</t>
         </is>
       </c>
-      <c r="T2" s="17" t="inlineStr">
-        <is>
-          <t>n_conformers_S0</t>
-        </is>
-      </c>
-      <c r="U2" s="17" t="inlineStr">
-        <is>
-          <t>n_conformers_T1</t>
-        </is>
-      </c>
-      <c r="V2" s="17" t="inlineStr">
-        <is>
-          <t>n_conformers_ox</t>
-        </is>
-      </c>
-      <c r="W2" s="17" t="inlineStr">
-        <is>
-          <t>n_conformers_red</t>
-        </is>
-      </c>
-      <c r="Y2" s="18" t="inlineStr">
+      <c r="T2" s="15" t="inlineStr">
         <is>
           <t>n_samples</t>
         </is>
       </c>
-      <c r="Z2" s="18" t="inlineStr">
+      <c r="U2" s="15" t="inlineStr">
         <is>
           <t>n_trajectories</t>
         </is>
       </c>
-      <c r="AA2" s="18" t="inlineStr">
+      <c r="V2" s="15" t="inlineStr">
         <is>
           <t>dvte_mu / kcal mol-1</t>
         </is>
       </c>
-      <c r="AB2" s="18" t="inlineStr">
+      <c r="W2" s="15" t="inlineStr">
         <is>
           <t>dvte_std / kcal mol-1</t>
         </is>
       </c>
-      <c r="AC2" s="18" t="inlineStr">
+      <c r="X2" s="15" t="inlineStr">
         <is>
           <t>dvte_0.005 / kcal mol-1</t>
         </is>
       </c>
-      <c r="AD2" s="18" t="inlineStr">
+      <c r="Y2" s="15" t="inlineStr">
         <is>
           <t>dvte_0.008 / kcal mol-1</t>
         </is>
       </c>
-      <c r="AE2" s="18" t="inlineStr">
+      <c r="Z2" s="15" t="inlineStr">
         <is>
           <t>dvte_0.01 / kcal mol-1</t>
         </is>
       </c>
-      <c r="AF2" s="18" t="inlineStr">
+      <c r="AA2" s="15" t="inlineStr">
         <is>
           <t>dvte_0.015 / kcal mol-1</t>
         </is>
       </c>
-      <c r="AG2" s="18" t="inlineStr">
+      <c r="AB2" s="15" t="inlineStr">
         <is>
           <t>dvte_0.005_kde / kcal mol-1</t>
         </is>
       </c>
-      <c r="AH2" s="18" t="inlineStr">
+      <c r="AC2" s="15" t="inlineStr">
         <is>
           <t>dvte_0.008_kde / kcal mol-1</t>
         </is>
       </c>
-      <c r="AI2" s="18" t="inlineStr">
+      <c r="AD2" s="15" t="inlineStr">
         <is>
           <t>dvte_0.01_kde / kcal mol-1</t>
         </is>
       </c>
-      <c r="AJ2" s="18" t="inlineStr">
+      <c r="AE2" s="15" t="inlineStr">
         <is>
           <t>dvte_0.015_kde / kcal mol-1</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="n">
+      <c r="A3" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>6-methylquinoline</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>CC1=CC=C2C(C=CC=N2)=C1</t>
         </is>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="16" t="n">
         <v>60.2</v>
       </c>
-      <c r="G3" s="19" t="n">
+      <c r="G3" s="16" t="n">
         <v>14.4</v>
       </c>
-      <c r="H3" s="19" t="n">
+      <c r="H3" s="16" t="n">
         <v>15.8</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="16" t="n">
         <v>144.5</v>
       </c>
-      <c r="K3" s="19" t="n">
+      <c r="K3" s="16" t="n">
         <v>1.85</v>
       </c>
-      <c r="L3" s="19" t="n">
+      <c r="L3" s="16" t="n">
         <v>4.5</v>
       </c>
-      <c r="M3" s="19" t="n">
+      <c r="M3" s="16" t="n">
         <v>4.1</v>
       </c>
-      <c r="O3" s="19" t="n">
+      <c r="O3" s="16" t="n">
         <v>49.9</v>
       </c>
-      <c r="P3" s="19" t="n">
+      <c r="P3" s="16" t="n">
         <v>-2.26</v>
       </c>
-      <c r="Q3" s="19" t="n">
+      <c r="Q3" s="16" t="n">
         <v>4.9</v>
       </c>
-      <c r="R3" s="19" t="n">
+      <c r="R3" s="16" t="n">
         <v>4.5</v>
       </c>
-      <c r="T3" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="19" t="n">
+      <c r="T3" s="16" t="n">
         <v>4865</v>
       </c>
-      <c r="Z3" s="19" t="n">
+      <c r="U3" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA3" s="19" t="n">
+      <c r="V3" s="16" t="n">
         <v>76.1883</v>
       </c>
-      <c r="AB3" s="19" t="n">
+      <c r="W3" s="16" t="n">
         <v>7.14234</v>
       </c>
-      <c r="AC3" s="19" t="n">
+      <c r="X3" s="16" t="n">
         <v>57.7909</v>
       </c>
-      <c r="AD3" s="19" t="n">
+      <c r="Y3" s="16" t="n">
         <v>58.983</v>
       </c>
-      <c r="AE3" s="19" t="n">
+      <c r="Z3" s="16" t="n">
         <v>59.5727</v>
       </c>
-      <c r="AF3" s="19" t="n">
+      <c r="AA3" s="16" t="n">
         <v>60.6888</v>
       </c>
-      <c r="AG3" s="19" t="n">
+      <c r="AB3" s="16" t="n">
         <v>56.925</v>
       </c>
-      <c r="AH3" s="19" t="n">
+      <c r="AC3" s="16" t="n">
         <v>58.1419</v>
       </c>
-      <c r="AI3" s="19" t="n">
+      <c r="AD3" s="16" t="n">
         <v>58.7237</v>
       </c>
-      <c r="AJ3" s="19" t="n">
+      <c r="AE3" s="16" t="n">
         <v>59.848</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="n">
+      <c r="A4" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>styrene</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>C=CC1=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="16" t="n">
         <v>52.2</v>
       </c>
-      <c r="G4" s="19" t="n">
+      <c r="G4" s="16" t="n">
         <v>86</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="H4" s="16" t="n">
         <v>26.7</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="16" t="n">
         <v>142.9</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K4" s="16" t="n">
         <v>1.78</v>
       </c>
-      <c r="L4" s="19" t="n">
+      <c r="L4" s="16" t="n">
         <v>4.4</v>
       </c>
-      <c r="M4" s="19" t="n">
+      <c r="M4" s="16" t="n">
         <v>4.4</v>
       </c>
-      <c r="O4" s="19" t="n">
+      <c r="O4" s="16" t="n">
         <v>41.4</v>
       </c>
-      <c r="P4" s="19" t="n">
+      <c r="P4" s="16" t="n">
         <v>-2.62</v>
       </c>
-      <c r="Q4" s="19" t="n">
+      <c r="Q4" s="16" t="n">
         <v>5.5</v>
       </c>
-      <c r="R4" s="19" t="n">
+      <c r="R4" s="16" t="n">
         <v>5.1</v>
       </c>
-      <c r="T4" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="19" t="n">
+      <c r="T4" s="16" t="n">
         <v>4877</v>
       </c>
-      <c r="Z4" s="19" t="n">
+      <c r="U4" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA4" s="19" t="n">
+      <c r="V4" s="16" t="n">
         <v>81.3467</v>
       </c>
-      <c r="AB4" s="19" t="n">
+      <c r="W4" s="16" t="n">
         <v>9.08047</v>
       </c>
-      <c r="AC4" s="19" t="n">
+      <c r="X4" s="16" t="n">
         <v>57.957</v>
       </c>
-      <c r="AD4" s="19" t="n">
+      <c r="Y4" s="16" t="n">
         <v>59.4726</v>
       </c>
-      <c r="AE4" s="19" t="n">
+      <c r="Z4" s="16" t="n">
         <v>60.2224</v>
       </c>
-      <c r="AF4" s="19" t="n">
+      <c r="AA4" s="16" t="n">
         <v>61.6413</v>
       </c>
-      <c r="AG4" s="19" t="n">
+      <c r="AB4" s="16" t="n">
         <v>56.8652</v>
       </c>
-      <c r="AH4" s="19" t="n">
+      <c r="AC4" s="16" t="n">
         <v>58.3881</v>
       </c>
-      <c r="AI4" s="19" t="n">
+      <c r="AD4" s="16" t="n">
         <v>59.0995</v>
       </c>
-      <c r="AJ4" s="19" t="n">
+      <c r="AE4" s="16" t="n">
         <v>60.3927</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>1,3-dimethyl-2-nitrobenzene</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>CC1=C(C(=CC=C1)C)[N+](=O)[O-]</t>
         </is>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="16" t="n">
         <v>60.8</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="16" t="n">
         <v>32.3</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="16" t="n">
         <v>17.4</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="16" t="n">
         <v>155.5</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="16" t="n">
         <v>2.32</v>
       </c>
-      <c r="L5" s="19" t="n">
+      <c r="L5" s="16" t="n">
         <v>5.3</v>
       </c>
-      <c r="M5" s="19" t="n">
+      <c r="M5" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="O5" s="19" t="n">
+      <c r="O5" s="16" t="n">
         <v>73</v>
       </c>
-      <c r="P5" s="19" t="n">
+      <c r="P5" s="16" t="n">
         <v>-1.25</v>
       </c>
-      <c r="Q5" s="19" t="n">
+      <c r="Q5" s="16" t="n">
         <v>12.9</v>
       </c>
-      <c r="R5" s="19" t="n">
+      <c r="R5" s="16" t="n">
         <v>11.4</v>
       </c>
-      <c r="T5" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W5" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="19" t="n">
+      <c r="T5" s="16" t="n">
         <v>4876</v>
       </c>
-      <c r="Z5" s="19" t="n">
+      <c r="U5" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA5" s="19" t="n">
+      <c r="V5" s="16" t="n">
         <v>78.8339</v>
       </c>
-      <c r="AB5" s="19" t="n">
+      <c r="W5" s="16" t="n">
         <v>7.00378</v>
       </c>
-      <c r="AC5" s="19" t="n">
+      <c r="X5" s="16" t="n">
         <v>60.7934</v>
       </c>
-      <c r="AD5" s="19" t="n">
+      <c r="Y5" s="16" t="n">
         <v>61.9624</v>
       </c>
-      <c r="AE5" s="19" t="n">
+      <c r="Z5" s="16" t="n">
         <v>62.5407</v>
       </c>
-      <c r="AF5" s="19" t="n">
+      <c r="AA5" s="16" t="n">
         <v>63.6351</v>
       </c>
-      <c r="AG5" s="19" t="n">
+      <c r="AB5" s="16" t="n">
         <v>61.1571</v>
       </c>
-      <c r="AH5" s="19" t="n">
+      <c r="AC5" s="16" t="n">
         <v>62.1824</v>
       </c>
-      <c r="AI5" s="19" t="n">
+      <c r="AD5" s="16" t="n">
         <v>62.7172</v>
       </c>
-      <c r="AJ5" s="19" t="n">
+      <c r="AE5" s="16" t="n">
         <v>63.7767</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="n">
+      <c r="A6" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>benzo[b]thiophene</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>C12=CC=CC=C1C=CS2</t>
         </is>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="16" t="n">
         <v>67.8</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="16" t="n">
         <v>19.7</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="16" t="n">
         <v>15.9</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="16" t="n">
         <v>139.5</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="K6" s="16" t="n">
         <v>1.63</v>
       </c>
-      <c r="L6" s="19" t="n">
+      <c r="L6" s="16" t="n">
         <v>3.9</v>
       </c>
-      <c r="M6" s="19" t="n">
+      <c r="M6" s="16" t="n">
         <v>3.6</v>
       </c>
-      <c r="O6" s="19" t="n">
+      <c r="O6" s="16" t="n">
         <v>35.4</v>
       </c>
-      <c r="P6" s="19" t="n">
+      <c r="P6" s="16" t="n">
         <v>-2.88</v>
       </c>
-      <c r="Q6" s="19" t="n">
+      <c r="Q6" s="16" t="n">
         <v>5.1</v>
       </c>
-      <c r="R6" s="19" t="n">
+      <c r="R6" s="16" t="n">
         <v>4.7</v>
       </c>
-      <c r="T6" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="19" t="n">
+      <c r="T6" s="16" t="n">
         <v>4861</v>
       </c>
-      <c r="Z6" s="19" t="n">
+      <c r="U6" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA6" s="19" t="n">
+      <c r="V6" s="16" t="n">
         <v>83.5459</v>
       </c>
-      <c r="AB6" s="19" t="n">
+      <c r="W6" s="16" t="n">
         <v>6.65662</v>
       </c>
-      <c r="AC6" s="19" t="n">
+      <c r="X6" s="16" t="n">
         <v>66.39960000000001</v>
       </c>
-      <c r="AD6" s="19" t="n">
+      <c r="Y6" s="16" t="n">
         <v>67.5107</v>
       </c>
-      <c r="AE6" s="19" t="n">
+      <c r="Z6" s="16" t="n">
         <v>68.0603</v>
       </c>
-      <c r="AF6" s="19" t="n">
+      <c r="AA6" s="16" t="n">
         <v>69.1005</v>
       </c>
-      <c r="AG6" s="19" t="n">
+      <c r="AB6" s="16" t="n">
         <v>65.50749999999999</v>
       </c>
-      <c r="AH6" s="19" t="n">
+      <c r="AC6" s="16" t="n">
         <v>66.64100000000001</v>
       </c>
-      <c r="AI6" s="19" t="n">
+      <c r="AD6" s="16" t="n">
         <v>67.2462</v>
       </c>
-      <c r="AJ6" s="19" t="n">
+      <c r="AE6" s="16" t="n">
         <v>68.4359</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>quinoxaline</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>C12=NC=CN=C1C=CC=C2</t>
         </is>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="16" t="n">
         <v>58.6</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="16" t="n">
         <v>14.1</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="16" t="n">
         <v>14.3</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="16" t="n">
         <v>158.8</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="K7" s="16" t="n">
         <v>2.47</v>
       </c>
-      <c r="L7" s="19" t="n">
+      <c r="L7" s="16" t="n">
         <v>10.1</v>
       </c>
-      <c r="M7" s="19" t="n">
+      <c r="M7" s="16" t="n">
         <v>-1.8</v>
       </c>
-      <c r="O7" s="19" t="n">
+      <c r="O7" s="16" t="n">
         <v>63.9</v>
       </c>
-      <c r="P7" s="19" t="n">
+      <c r="P7" s="16" t="n">
         <v>-1.65</v>
       </c>
-      <c r="Q7" s="19" t="n">
+      <c r="Q7" s="16" t="n">
         <v>4.8</v>
       </c>
-      <c r="R7" s="19" t="n">
+      <c r="R7" s="16" t="n">
         <v>4.7</v>
       </c>
-      <c r="T7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="19" t="n">
+      <c r="T7" s="16" t="n">
         <v>4953</v>
       </c>
-      <c r="Z7" s="19" t="n">
+      <c r="U7" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA7" s="19" t="n">
+      <c r="V7" s="16" t="n">
         <v>72.5236</v>
       </c>
-      <c r="AB7" s="19" t="n">
+      <c r="W7" s="16" t="n">
         <v>5.90317</v>
       </c>
-      <c r="AC7" s="19" t="n">
+      <c r="X7" s="16" t="n">
         <v>57.3181</v>
       </c>
-      <c r="AD7" s="19" t="n">
+      <c r="Y7" s="16" t="n">
         <v>58.3034</v>
       </c>
-      <c r="AE7" s="19" t="n">
+      <c r="Z7" s="16" t="n">
         <v>58.7908</v>
       </c>
-      <c r="AF7" s="19" t="n">
+      <c r="AA7" s="16" t="n">
         <v>59.7132</v>
       </c>
-      <c r="AG7" s="19" t="n">
+      <c r="AB7" s="16" t="n">
         <v>55.6201</v>
       </c>
-      <c r="AH7" s="19" t="n">
+      <c r="AC7" s="16" t="n">
         <v>56.6554</v>
       </c>
-      <c r="AI7" s="19" t="n">
+      <c r="AD7" s="16" t="n">
         <v>57.2407</v>
       </c>
-      <c r="AJ7" s="19" t="n">
+      <c r="AE7" s="16" t="n">
         <v>58.4453</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>isoquinoline</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>C12=CN=CC=C1C=CC=C2</t>
         </is>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="16" t="n">
         <v>60.1</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="16" t="n">
         <v>14.3</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="16" t="n">
         <v>14.5</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="16" t="n">
         <v>145.5</v>
       </c>
-      <c r="K8" s="19" t="n">
+      <c r="K8" s="16" t="n">
         <v>1.89</v>
       </c>
-      <c r="L8" s="19" t="n">
+      <c r="L8" s="16" t="n">
         <v>3.4</v>
       </c>
-      <c r="M8" s="19" t="n">
+      <c r="M8" s="16" t="n">
         <v>3.5</v>
       </c>
-      <c r="O8" s="19" t="n">
+      <c r="O8" s="16" t="n">
         <v>49.6</v>
       </c>
-      <c r="P8" s="19" t="n">
+      <c r="P8" s="16" t="n">
         <v>-2.27</v>
       </c>
-      <c r="Q8" s="19" t="n">
+      <c r="Q8" s="16" t="n">
         <v>4.7</v>
       </c>
-      <c r="R8" s="19" t="n">
+      <c r="R8" s="16" t="n">
         <v>4.5</v>
       </c>
-      <c r="T8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="19" t="n">
+      <c r="T8" s="16" t="n">
         <v>4939</v>
       </c>
-      <c r="Z8" s="19" t="n">
+      <c r="U8" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA8" s="19" t="n">
+      <c r="V8" s="16" t="n">
         <v>75.4422</v>
       </c>
-      <c r="AB8" s="19" t="n">
+      <c r="W8" s="16" t="n">
         <v>7.31194</v>
       </c>
-      <c r="AC8" s="19" t="n">
+      <c r="X8" s="16" t="n">
         <v>56.6079</v>
       </c>
-      <c r="AD8" s="19" t="n">
+      <c r="Y8" s="16" t="n">
         <v>57.8284</v>
       </c>
-      <c r="AE8" s="19" t="n">
+      <c r="Z8" s="16" t="n">
         <v>58.4321</v>
       </c>
-      <c r="AF8" s="19" t="n">
+      <c r="AA8" s="16" t="n">
         <v>59.5746</v>
       </c>
-      <c r="AG8" s="19" t="n">
+      <c r="AB8" s="16" t="n">
         <v>56.8972</v>
       </c>
-      <c r="AH8" s="19" t="n">
+      <c r="AC8" s="16" t="n">
         <v>57.944</v>
       </c>
-      <c r="AI8" s="19" t="n">
+      <c r="AD8" s="16" t="n">
         <v>58.4797</v>
       </c>
-      <c r="AJ8" s="19" t="n">
+      <c r="AE8" s="16" t="n">
         <v>59.516</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Q7</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>coumarin</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>O=C1Oc2ccccc2C=C1</t>
         </is>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="16" t="n">
         <v>12.4</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="16" t="n">
         <v>12.7</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="16" t="n">
         <v>151.3</v>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K9" s="16" t="n">
         <v>2.14</v>
       </c>
-      <c r="L9" s="19" t="n">
+      <c r="L9" s="16" t="n">
         <v>3.8</v>
       </c>
-      <c r="M9" s="19" t="n">
+      <c r="M9" s="16" t="n">
         <v>3.8</v>
       </c>
-      <c r="O9" s="19" t="n">
+      <c r="O9" s="16" t="n">
         <v>60.3</v>
       </c>
-      <c r="P9" s="19" t="n">
+      <c r="P9" s="16" t="n">
         <v>-1.81</v>
       </c>
-      <c r="Q9" s="19" t="n">
+      <c r="Q9" s="16" t="n">
         <v>6.7</v>
       </c>
-      <c r="R9" s="19" t="n">
+      <c r="R9" s="16" t="n">
         <v>6.6</v>
       </c>
-      <c r="T9" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="19" t="n">
+      <c r="T9" s="16" t="n">
         <v>4941</v>
       </c>
-      <c r="Z9" s="19" t="n">
+      <c r="U9" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA9" s="19" t="n">
+      <c r="V9" s="16" t="n">
         <v>75.5534</v>
       </c>
-      <c r="AB9" s="19" t="n">
+      <c r="W9" s="16" t="n">
         <v>7.38718</v>
       </c>
-      <c r="AC9" s="19" t="n">
+      <c r="X9" s="16" t="n">
         <v>56.5252</v>
       </c>
-      <c r="AD9" s="19" t="n">
+      <c r="Y9" s="16" t="n">
         <v>57.7583</v>
       </c>
-      <c r="AE9" s="19" t="n">
+      <c r="Z9" s="16" t="n">
         <v>58.3682</v>
       </c>
-      <c r="AF9" s="19" t="n">
+      <c r="AA9" s="16" t="n">
         <v>59.5225</v>
       </c>
-      <c r="AG9" s="19" t="n">
+      <c r="AB9" s="16" t="n">
         <v>55.4952</v>
       </c>
-      <c r="AH9" s="19" t="n">
+      <c r="AC9" s="16" t="n">
         <v>56.8322</v>
       </c>
-      <c r="AI9" s="19" t="n">
+      <c r="AD9" s="16" t="n">
         <v>57.4607</v>
       </c>
-      <c r="AJ9" s="19" t="n">
+      <c r="AE9" s="16" t="n">
         <v>58.6718</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>benzophenone O-(isopropoxycarbonyl) oxime</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>CC(OC(O/N=C(C1=CC=CC=C1)\C2=CC=CC=C2)=O)C</t>
         </is>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="16" t="n">
         <v>51.8</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="16" t="n">
         <v>53.7</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="16" t="n">
         <v>158.2</v>
       </c>
-      <c r="K10" s="19" t="n">
+      <c r="K10" s="16" t="n">
         <v>2.44</v>
       </c>
-      <c r="L10" s="19" t="n">
+      <c r="L10" s="16" t="n">
         <v>24.4</v>
       </c>
-      <c r="M10" s="19" t="n">
+      <c r="M10" s="16" t="n">
         <v>5.9</v>
       </c>
-      <c r="O10" s="19" t="n">
+      <c r="O10" s="16" t="n">
         <v>54.8</v>
       </c>
-      <c r="P10" s="19" t="n">
+      <c r="P10" s="16" t="n">
         <v>-2.04</v>
       </c>
-      <c r="Q10" s="19" t="n">
+      <c r="Q10" s="16" t="n">
         <v>11.3</v>
       </c>
-      <c r="R10" s="19" t="n">
+      <c r="R10" s="16" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="T10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="19" t="n">
+      <c r="T10" s="16" t="n">
         <v>4744</v>
       </c>
-      <c r="Z10" s="19" t="n">
+      <c r="U10" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA10" s="19" t="n">
+      <c r="V10" s="16" t="n">
         <v>82.666</v>
       </c>
-      <c r="AB10" s="19" t="n">
+      <c r="W10" s="16" t="n">
         <v>7.10289</v>
       </c>
-      <c r="AC10" s="19" t="n">
+      <c r="X10" s="16" t="n">
         <v>64.3702</v>
       </c>
-      <c r="AD10" s="19" t="n">
+      <c r="Y10" s="16" t="n">
         <v>65.5557</v>
       </c>
-      <c r="AE10" s="19" t="n">
+      <c r="Z10" s="16" t="n">
         <v>66.1422</v>
       </c>
-      <c r="AF10" s="19" t="n">
+      <c r="AA10" s="16" t="n">
         <v>67.2521</v>
       </c>
-      <c r="AG10" s="19" t="n">
+      <c r="AB10" s="16" t="n">
         <v>62.7799</v>
       </c>
-      <c r="AH10" s="19" t="n">
+      <c r="AC10" s="16" t="n">
         <v>64.2259</v>
       </c>
-      <c r="AI10" s="19" t="n">
+      <c r="AD10" s="16" t="n">
         <v>64.9298</v>
       </c>
-      <c r="AJ10" s="19" t="n">
+      <c r="AE10" s="16" t="n">
         <v>66.26519999999999</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Q9</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>3-methyl-2-phenylthiophene</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>CC1=C(C2=CC=CC=C2)SC=C1</t>
         </is>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="16" t="n">
         <v>58.5</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="16" t="n">
         <v>16.9</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="16" t="n">
         <v>21.7</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="16" t="n">
         <v>134.8</v>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="K11" s="16" t="n">
         <v>1.43</v>
       </c>
-      <c r="L11" s="19" t="n">
+      <c r="L11" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="M11" s="19" t="n">
+      <c r="M11" s="16" t="n">
         <v>6.9</v>
       </c>
-      <c r="O11" s="19" t="n">
+      <c r="O11" s="16" t="n">
         <v>39.1</v>
       </c>
-      <c r="P11" s="19" t="n">
+      <c r="P11" s="16" t="n">
         <v>-2.72</v>
       </c>
-      <c r="Q11" s="19" t="n">
+      <c r="Q11" s="16" t="n">
         <v>7.4</v>
       </c>
-      <c r="R11" s="19" t="n">
+      <c r="R11" s="16" t="n">
         <v>10.6</v>
       </c>
-      <c r="T11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="19" t="n">
+      <c r="T11" s="16" t="n">
         <v>4907</v>
       </c>
-      <c r="Z11" s="19" t="n">
+      <c r="U11" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA11" s="19" t="n">
+      <c r="V11" s="16" t="n">
         <v>82.15179999999999</v>
       </c>
-      <c r="AB11" s="19" t="n">
+      <c r="W11" s="16" t="n">
         <v>7.57912</v>
       </c>
-      <c r="AC11" s="19" t="n">
+      <c r="X11" s="16" t="n">
         <v>62.6292</v>
       </c>
-      <c r="AD11" s="19" t="n">
+      <c r="Y11" s="16" t="n">
         <v>63.8943</v>
       </c>
-      <c r="AE11" s="19" t="n">
+      <c r="Z11" s="16" t="n">
         <v>64.5201</v>
       </c>
-      <c r="AF11" s="19" t="n">
+      <c r="AA11" s="16" t="n">
         <v>65.70440000000001</v>
       </c>
-      <c r="AG11" s="19" t="n">
+      <c r="AB11" s="16" t="n">
         <v>61.6092</v>
       </c>
-      <c r="AH11" s="19" t="n">
+      <c r="AC11" s="16" t="n">
         <v>62.9839</v>
       </c>
-      <c r="AI11" s="19" t="n">
+      <c r="AD11" s="16" t="n">
         <v>63.6924</v>
       </c>
-      <c r="AJ11" s="19" t="n">
+      <c r="AE11" s="16" t="n">
         <v>65.0989</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>diphenyl disulfide</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>C1(SSC2=CC=CC=C2)=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="16" t="n">
         <v>40.3</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="16" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="16" t="n">
         <v>42.6</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="16" t="n">
         <v>137.6</v>
       </c>
-      <c r="K12" s="19" t="n">
+      <c r="K12" s="16" t="n">
         <v>1.55</v>
       </c>
-      <c r="L12" s="19" t="n">
+      <c r="L12" s="16" t="n">
         <v>10.5</v>
       </c>
-      <c r="M12" s="19" t="n">
+      <c r="M12" s="16" t="n">
         <v>16.6</v>
       </c>
-      <c r="O12" s="19" t="n"/>
-      <c r="P12" s="19" t="n"/>
-      <c r="Q12" s="19" t="n"/>
-      <c r="R12" s="19" t="n"/>
-      <c r="T12" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="19" t="n">
+      <c r="O12" s="16" t="n"/>
+      <c r="P12" s="16" t="n"/>
+      <c r="Q12" s="16" t="n"/>
+      <c r="R12" s="16" t="n"/>
+      <c r="T12" s="16" t="n">
         <v>4924</v>
       </c>
-      <c r="Z12" s="19" t="n">
+      <c r="U12" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA12" s="19" t="n">
+      <c r="V12" s="16" t="n">
         <v>82.056</v>
       </c>
-      <c r="AB12" s="19" t="n">
+      <c r="W12" s="16" t="n">
         <v>7.97085</v>
       </c>
-      <c r="AC12" s="19" t="n">
+      <c r="X12" s="16" t="n">
         <v>61.5245</v>
       </c>
-      <c r="AD12" s="19" t="n">
+      <c r="Y12" s="16" t="n">
         <v>62.8549</v>
       </c>
-      <c r="AE12" s="19" t="n">
+      <c r="Z12" s="16" t="n">
         <v>63.513</v>
       </c>
-      <c r="AF12" s="19" t="n">
+      <c r="AA12" s="16" t="n">
         <v>64.7585</v>
       </c>
-      <c r="AG12" s="19" t="n">
+      <c r="AB12" s="16" t="n">
         <v>57.9689</v>
       </c>
-      <c r="AH12" s="19" t="n">
+      <c r="AC12" s="16" t="n">
         <v>59.6312</v>
       </c>
-      <c r="AI12" s="19" t="n">
+      <c r="AD12" s="16" t="n">
         <v>60.491</v>
       </c>
-      <c r="AJ12" s="19" t="n">
+      <c r="AE12" s="16" t="n">
         <v>62.1933</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>dibenzyl disulfide</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>C1(CSSCC2=CC=CC=C2)=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="16" t="n">
         <v>56.6</v>
       </c>
-      <c r="G13" s="19" t="n">
+      <c r="G13" s="16" t="n">
         <v>45.5</v>
       </c>
-      <c r="H13" s="19" t="n">
+      <c r="H13" s="16" t="n">
         <v>45.1</v>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J13" s="16" t="n">
         <v>136.7</v>
       </c>
-      <c r="K13" s="19" t="n">
+      <c r="K13" s="16" t="n">
         <v>1.51</v>
       </c>
-      <c r="L13" s="19" t="n">
+      <c r="L13" s="16" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="M13" s="19" t="n">
+      <c r="M13" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="O13" s="19" t="n"/>
-      <c r="P13" s="19" t="n"/>
-      <c r="Q13" s="19" t="n"/>
-      <c r="R13" s="19" t="n"/>
-      <c r="T13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="19" t="n">
+      <c r="O13" s="16" t="n"/>
+      <c r="P13" s="16" t="n"/>
+      <c r="Q13" s="16" t="n"/>
+      <c r="R13" s="16" t="n"/>
+      <c r="T13" s="16" t="n">
         <v>4953</v>
       </c>
-      <c r="Z13" s="19" t="n">
+      <c r="U13" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA13" s="19" t="n">
+      <c r="V13" s="16" t="n">
         <v>87.7253</v>
       </c>
-      <c r="AB13" s="19" t="n">
+      <c r="W13" s="16" t="n">
         <v>6.79933</v>
       </c>
-      <c r="AC13" s="19" t="n">
+      <c r="X13" s="16" t="n">
         <v>70.2114</v>
       </c>
-      <c r="AD13" s="19" t="n">
+      <c r="Y13" s="16" t="n">
         <v>71.3463</v>
       </c>
-      <c r="AE13" s="19" t="n">
+      <c r="Z13" s="16" t="n">
         <v>71.90770000000001</v>
       </c>
-      <c r="AF13" s="19" t="n">
+      <c r="AA13" s="16" t="n">
         <v>72.97020000000001</v>
       </c>
-      <c r="AG13" s="19" t="n">
+      <c r="AB13" s="16" t="n">
         <v>70.2144</v>
       </c>
-      <c r="AH13" s="19" t="n">
+      <c r="AC13" s="16" t="n">
         <v>71.40779999999999</v>
       </c>
-      <c r="AI13" s="19" t="n">
+      <c r="AD13" s="16" t="n">
         <v>71.9838</v>
       </c>
-      <c r="AJ13" s="19" t="n">
+      <c r="AE13" s="16" t="n">
         <v>73.0975</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="n">
+      <c r="A14" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Q12</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>1,2-dihydro-1,2-benzazaborinine</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>C12=CC=CC=C1C=CBN2</t>
         </is>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="16" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="16" t="n">
         <v>13.5</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H14" s="16" t="n">
         <v>13.1</v>
       </c>
-      <c r="J14" s="19" t="n">
+      <c r="J14" s="16" t="n">
         <v>140.9</v>
       </c>
-      <c r="K14" s="19" t="n">
+      <c r="K14" s="16" t="n">
         <v>1.69</v>
       </c>
-      <c r="L14" s="19" t="n">
+      <c r="L14" s="16" t="n">
         <v>4.6</v>
       </c>
-      <c r="M14" s="19" t="n">
+      <c r="M14" s="16" t="n">
         <v>4.6</v>
       </c>
-      <c r="O14" s="19" t="n">
+      <c r="O14" s="16" t="n">
         <v>44.5</v>
       </c>
-      <c r="P14" s="19" t="n">
+      <c r="P14" s="16" t="n">
         <v>-2.49</v>
       </c>
-      <c r="Q14" s="19" t="n">
+      <c r="Q14" s="16" t="n">
         <v>5.1</v>
       </c>
-      <c r="R14" s="19" t="n">
+      <c r="R14" s="16" t="n">
         <v>4.7</v>
       </c>
-      <c r="T14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="19" t="n">
+      <c r="T14" s="16" t="n">
         <v>4920</v>
       </c>
-      <c r="Z14" s="19" t="n">
+      <c r="U14" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA14" s="19" t="n">
+      <c r="V14" s="16" t="n">
         <v>79.16759999999999</v>
       </c>
-      <c r="AB14" s="19" t="n">
+      <c r="W14" s="16" t="n">
         <v>6.45295</v>
       </c>
-      <c r="AC14" s="19" t="n">
+      <c r="X14" s="16" t="n">
         <v>62.5459</v>
       </c>
-      <c r="AD14" s="19" t="n">
+      <c r="Y14" s="16" t="n">
         <v>63.623</v>
       </c>
-      <c r="AE14" s="19" t="n">
+      <c r="Z14" s="16" t="n">
         <v>64.1558</v>
       </c>
-      <c r="AF14" s="19" t="n">
+      <c r="AA14" s="16" t="n">
         <v>65.1641</v>
       </c>
-      <c r="AG14" s="19" t="n">
+      <c r="AB14" s="16" t="n">
         <v>60.1854</v>
       </c>
-      <c r="AH14" s="19" t="n">
+      <c r="AC14" s="16" t="n">
         <v>61.4605</v>
       </c>
-      <c r="AI14" s="19" t="n">
+      <c r="AD14" s="16" t="n">
         <v>62.1007</v>
       </c>
-      <c r="AJ14" s="19" t="n">
+      <c r="AE14" s="16" t="n">
         <v>63.3326</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>N-methylmaleimide</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>O=C1C=CC(N1C)=O</t>
         </is>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="16" t="n">
         <v>56.7</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="16" t="n">
         <v>18.9</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="16" t="n">
         <v>18.2</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="16" t="n">
         <v>172.2</v>
       </c>
-      <c r="K15" s="19" t="n">
+      <c r="K15" s="16" t="n">
         <v>3.05</v>
       </c>
-      <c r="L15" s="19" t="n">
+      <c r="L15" s="16" t="n">
         <v>8.9</v>
       </c>
-      <c r="M15" s="19" t="n">
+      <c r="M15" s="16" t="n">
         <v>6.9</v>
       </c>
-      <c r="O15" s="19" t="n">
+      <c r="O15" s="16" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="P15" s="19" t="n">
+      <c r="P15" s="16" t="n">
         <v>-1.12</v>
       </c>
-      <c r="Q15" s="19" t="n">
+      <c r="Q15" s="16" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="R15" s="19" t="n">
+      <c r="R15" s="16" t="n">
         <v>8.9</v>
       </c>
-      <c r="T15" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W15" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="19" t="n">
+      <c r="T15" s="16" t="n">
         <v>4977</v>
       </c>
-      <c r="Z15" s="19" t="n">
+      <c r="U15" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA15" s="19" t="n">
+      <c r="V15" s="16" t="n">
         <v>76.7282</v>
       </c>
-      <c r="AB15" s="19" t="n">
+      <c r="W15" s="16" t="n">
         <v>7.99366</v>
       </c>
-      <c r="AC15" s="19" t="n">
+      <c r="X15" s="16" t="n">
         <v>56.1379</v>
       </c>
-      <c r="AD15" s="19" t="n">
+      <c r="Y15" s="16" t="n">
         <v>57.4722</v>
       </c>
-      <c r="AE15" s="19" t="n">
+      <c r="Z15" s="16" t="n">
         <v>58.1322</v>
       </c>
-      <c r="AF15" s="19" t="n">
+      <c r="AA15" s="16" t="n">
         <v>59.3812</v>
       </c>
-      <c r="AG15" s="19" t="n">
+      <c r="AB15" s="16" t="n">
         <v>55.5665</v>
       </c>
-      <c r="AH15" s="19" t="n">
+      <c r="AC15" s="16" t="n">
         <v>56.8887</v>
       </c>
-      <c r="AI15" s="19" t="n">
+      <c r="AD15" s="16" t="n">
         <v>57.5281</v>
       </c>
-      <c r="AJ15" s="19" t="n">
+      <c r="AE15" s="16" t="n">
         <v>58.7158</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="n">
+      <c r="A16" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>butyl methacrylate</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>CC(C(OCCCC)=O)=C</t>
         </is>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="16" t="n">
         <v>53.6</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G16" s="16" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H16" s="16" t="n">
         <v>30.8</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J16" s="16" t="n">
         <v>159</v>
       </c>
-      <c r="K16" s="19" t="n">
+      <c r="K16" s="16" t="n">
         <v>2.47</v>
       </c>
-      <c r="L16" s="19" t="n">
+      <c r="L16" s="16" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="M16" s="19" t="n">
+      <c r="M16" s="16" t="n">
         <v>12.6</v>
       </c>
-      <c r="O16" s="19" t="n">
+      <c r="O16" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="P16" s="19" t="n">
+      <c r="P16" s="16" t="n">
         <v>-2.34</v>
       </c>
-      <c r="Q16" s="19" t="n">
+      <c r="Q16" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="R16" s="19" t="n">
+      <c r="R16" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="T16" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W16" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="19" t="n">
+      <c r="T16" s="16" t="n">
         <v>4958</v>
       </c>
-      <c r="Z16" s="19" t="n">
+      <c r="U16" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA16" s="19" t="n">
+      <c r="V16" s="16" t="n">
         <v>86.3062</v>
       </c>
-      <c r="AB16" s="19" t="n">
+      <c r="W16" s="16" t="n">
         <v>10.5448</v>
       </c>
-      <c r="AC16" s="19" t="n">
+      <c r="X16" s="16" t="n">
         <v>59.1445</v>
       </c>
-      <c r="AD16" s="19" t="n">
+      <c r="Y16" s="16" t="n">
         <v>60.9046</v>
       </c>
-      <c r="AE16" s="19" t="n">
+      <c r="Z16" s="16" t="n">
         <v>61.7752</v>
       </c>
-      <c r="AF16" s="19" t="n">
+      <c r="AA16" s="16" t="n">
         <v>63.4229</v>
       </c>
-      <c r="AG16" s="19" t="n">
+      <c r="AB16" s="16" t="n">
         <v>62.3078</v>
       </c>
-      <c r="AH16" s="19" t="n">
+      <c r="AC16" s="16" t="n">
         <v>63.4844</v>
       </c>
-      <c r="AI16" s="19" t="n">
+      <c r="AD16" s="16" t="n">
         <v>64.0973</v>
       </c>
-      <c r="AJ16" s="19" t="n">
+      <c r="AE16" s="16" t="n">
         <v>65.3065</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Q15</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>indene</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>C12=CC=CC=C1C=CC2</t>
         </is>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="16" t="n">
         <v>61.5</v>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G17" s="16" t="n">
         <v>17.9</v>
       </c>
-      <c r="H17" s="19" t="n">
+      <c r="H17" s="16" t="n">
         <v>17.9</v>
       </c>
-      <c r="J17" s="19" t="n">
+      <c r="J17" s="16" t="n">
         <v>136.3</v>
       </c>
-      <c r="K17" s="19" t="n">
+      <c r="K17" s="16" t="n">
         <v>1.49</v>
       </c>
-      <c r="L17" s="19" t="n">
+      <c r="L17" s="16" t="n">
         <v>4.3</v>
       </c>
-      <c r="M17" s="19" t="n">
+      <c r="M17" s="16" t="n">
         <v>4.4</v>
       </c>
-      <c r="O17" s="19" t="n">
+      <c r="O17" s="16" t="n">
         <v>32.7</v>
       </c>
-      <c r="P17" s="19" t="n">
+      <c r="P17" s="16" t="n">
         <v>-3</v>
       </c>
-      <c r="Q17" s="19" t="n">
+      <c r="Q17" s="16" t="n">
         <v>5.9</v>
       </c>
-      <c r="R17" s="19" t="n">
+      <c r="R17" s="16" t="n">
         <v>5.4</v>
       </c>
-      <c r="T17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="19" t="n">
+      <c r="T17" s="16" t="n">
         <v>4958</v>
       </c>
-      <c r="Z17" s="19" t="n">
+      <c r="U17" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA17" s="19" t="n">
+      <c r="V17" s="16" t="n">
         <v>80.7985</v>
       </c>
-      <c r="AB17" s="19" t="n">
+      <c r="W17" s="16" t="n">
         <v>8.421849999999999</v>
       </c>
-      <c r="AC17" s="19" t="n">
+      <c r="X17" s="16" t="n">
         <v>59.1052</v>
       </c>
-      <c r="AD17" s="19" t="n">
+      <c r="Y17" s="16" t="n">
         <v>60.5109</v>
       </c>
-      <c r="AE17" s="19" t="n">
+      <c r="Z17" s="16" t="n">
         <v>61.2063</v>
       </c>
-      <c r="AF17" s="19" t="n">
+      <c r="AA17" s="16" t="n">
         <v>62.5223</v>
       </c>
-      <c r="AG17" s="19" t="n">
+      <c r="AB17" s="16" t="n">
         <v>57.2361</v>
       </c>
-      <c r="AH17" s="19" t="n">
+      <c r="AC17" s="16" t="n">
         <v>58.6722</v>
       </c>
-      <c r="AI17" s="19" t="n">
+      <c r="AD17" s="16" t="n">
         <v>59.397</v>
       </c>
-      <c r="AJ17" s="19" t="n">
+      <c r="AE17" s="16" t="n">
         <v>60.9053</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="n">
+      <c r="A18" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>5-methylpyridin-2(1H)-one</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>O=C1NC=C(C)C=C1</t>
         </is>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="16" t="n">
         <v>57.4</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G18" s="16" t="n">
         <v>11.6</v>
       </c>
-      <c r="H18" s="19" t="n">
+      <c r="H18" s="16" t="n">
         <v>11.2</v>
       </c>
-      <c r="J18" s="19" t="n">
+      <c r="J18" s="16" t="n">
         <v>134.5</v>
       </c>
-      <c r="K18" s="19" t="n">
+      <c r="K18" s="16" t="n">
         <v>1.41</v>
       </c>
-      <c r="L18" s="19" t="n">
+      <c r="L18" s="16" t="n">
         <v>5.5</v>
       </c>
-      <c r="M18" s="19" t="n">
+      <c r="M18" s="16" t="n">
         <v>4.3</v>
       </c>
-      <c r="O18" s="19" t="n">
+      <c r="O18" s="16" t="n">
         <v>45.5</v>
       </c>
-      <c r="P18" s="19" t="n">
+      <c r="P18" s="16" t="n">
         <v>-2.45</v>
       </c>
-      <c r="Q18" s="19" t="n">
+      <c r="Q18" s="16" t="n">
         <v>6.3</v>
       </c>
-      <c r="R18" s="19" t="n">
+      <c r="R18" s="16" t="n">
         <v>5.9</v>
       </c>
-      <c r="T18" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W18" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="19" t="n">
+      <c r="T18" s="16" t="n">
         <v>4973</v>
       </c>
-      <c r="Z18" s="19" t="n">
+      <c r="U18" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA18" s="19" t="n">
+      <c r="V18" s="16" t="n">
         <v>71.9087</v>
       </c>
-      <c r="AB18" s="19" t="n">
+      <c r="W18" s="16" t="n">
         <v>6.64359</v>
       </c>
-      <c r="AC18" s="19" t="n">
+      <c r="X18" s="16" t="n">
         <v>54.796</v>
       </c>
-      <c r="AD18" s="19" t="n">
+      <c r="Y18" s="16" t="n">
         <v>55.9049</v>
       </c>
-      <c r="AE18" s="19" t="n">
+      <c r="Z18" s="16" t="n">
         <v>56.4534</v>
       </c>
-      <c r="AF18" s="19" t="n">
+      <c r="AA18" s="16" t="n">
         <v>57.4915</v>
       </c>
-      <c r="AG18" s="19" t="n">
+      <c r="AB18" s="16" t="n">
         <v>55.8253</v>
       </c>
-      <c r="AH18" s="19" t="n">
+      <c r="AC18" s="16" t="n">
         <v>56.8237</v>
       </c>
-      <c r="AI18" s="19" t="n">
+      <c r="AD18" s="16" t="n">
         <v>57.3082</v>
       </c>
-      <c r="AJ18" s="19" t="n">
+      <c r="AE18" s="16" t="n">
         <v>58.194</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="16" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>dibenzyl diselenide</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>C1(C[Se][Se]CC2=CC=CC=C2)=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="16" t="n">
         <v>47.1</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G19" s="16" t="n">
         <v>36.8</v>
       </c>
-      <c r="H19" s="19" t="n">
+      <c r="H19" s="16" t="n">
         <v>35.5</v>
       </c>
-      <c r="J19" s="19" t="n">
+      <c r="J19" s="16" t="n">
         <v>132.9</v>
       </c>
-      <c r="K19" s="19" t="n">
+      <c r="K19" s="16" t="n">
         <v>1.34</v>
       </c>
-      <c r="L19" s="19" t="n">
+      <c r="L19" s="16" t="n">
         <v>7.5</v>
       </c>
-      <c r="M19" s="19" t="n">
+      <c r="M19" s="16" t="n">
         <v>13.7</v>
       </c>
-      <c r="O19" s="19" t="n">
+      <c r="O19" s="16" t="n">
         <v>54.2</v>
       </c>
-      <c r="P19" s="19" t="n">
+      <c r="P19" s="16" t="n">
         <v>-2.07</v>
       </c>
-      <c r="Q19" s="19" t="n">
+      <c r="Q19" s="16" t="n">
         <v>119.6</v>
       </c>
-      <c r="R19" s="19" t="n">
+      <c r="R19" s="16" t="n">
         <v>29.8</v>
       </c>
-      <c r="T19" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W19" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y19" s="19" t="n">
+      <c r="T19" s="16" t="n">
         <v>4848</v>
       </c>
-      <c r="Z19" s="19" t="n">
+      <c r="U19" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA19" s="19" t="n">
+      <c r="V19" s="16" t="n">
         <v>73.5851</v>
       </c>
-      <c r="AB19" s="19" t="n">
+      <c r="W19" s="16" t="n">
         <v>7.09328</v>
       </c>
-      <c r="AC19" s="19" t="n">
+      <c r="X19" s="16" t="n">
         <v>55.314</v>
       </c>
-      <c r="AD19" s="19" t="n">
+      <c r="Y19" s="16" t="n">
         <v>56.498</v>
       </c>
-      <c r="AE19" s="19" t="n">
+      <c r="Z19" s="16" t="n">
         <v>57.0837</v>
       </c>
-      <c r="AF19" s="19" t="n">
+      <c r="AA19" s="16" t="n">
         <v>58.1921</v>
       </c>
-      <c r="AG19" s="19" t="n">
+      <c r="AB19" s="16" t="n">
         <v>56.1115</v>
       </c>
-      <c r="AH19" s="19" t="n">
+      <c r="AC19" s="16" t="n">
         <v>57.1978</v>
       </c>
-      <c r="AI19" s="19" t="n">
+      <c r="AD19" s="16" t="n">
         <v>57.7751</v>
       </c>
-      <c r="AJ19" s="19" t="n">
+      <c r="AE19" s="16" t="n">
         <v>58.875</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="n">
+      <c r="A20" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>5,5-dimethyl-3-phenyl-4,5-dihydro-1,2,4-oxadiazole</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>CC1(C)NC(C2=CC=CC=C2)=NO1</t>
         </is>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="16" t="n">
         <v>52.2</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G20" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="H20" s="19" t="n">
+      <c r="H20" s="16" t="n">
         <v>21.4</v>
       </c>
-      <c r="J20" s="19" t="n">
+      <c r="J20" s="16" t="n">
         <v>124.5</v>
       </c>
-      <c r="K20" s="19" t="n">
+      <c r="K20" s="16" t="n">
         <v>0.98</v>
       </c>
-      <c r="L20" s="19" t="n">
+      <c r="L20" s="16" t="n">
         <v>10.4</v>
       </c>
-      <c r="M20" s="19" t="n">
+      <c r="M20" s="16" t="n">
         <v>13.8</v>
       </c>
-      <c r="O20" s="19" t="n">
+      <c r="O20" s="16" t="n">
         <v>44</v>
       </c>
-      <c r="P20" s="19" t="n">
+      <c r="P20" s="16" t="n">
         <v>-2.51</v>
       </c>
-      <c r="Q20" s="19" t="n">
+      <c r="Q20" s="16" t="n">
         <v>7.2</v>
       </c>
-      <c r="R20" s="19" t="n">
+      <c r="R20" s="16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="T20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W20" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y20" s="19" t="n">
+      <c r="T20" s="16" t="n">
         <v>4955</v>
       </c>
-      <c r="Z20" s="19" t="n">
+      <c r="U20" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA20" s="19" t="n">
+      <c r="V20" s="16" t="n">
         <v>77.9113</v>
       </c>
-      <c r="AB20" s="19" t="n">
+      <c r="W20" s="16" t="n">
         <v>8.636889999999999</v>
       </c>
-      <c r="AC20" s="19" t="n">
+      <c r="X20" s="16" t="n">
         <v>55.6641</v>
       </c>
-      <c r="AD20" s="19" t="n">
+      <c r="Y20" s="16" t="n">
         <v>57.1057</v>
       </c>
-      <c r="AE20" s="19" t="n">
+      <c r="Z20" s="16" t="n">
         <v>57.8189</v>
       </c>
-      <c r="AF20" s="19" t="n">
+      <c r="AA20" s="16" t="n">
         <v>59.1685</v>
       </c>
-      <c r="AG20" s="19" t="n">
+      <c r="AB20" s="16" t="n">
         <v>56.2373</v>
       </c>
-      <c r="AH20" s="19" t="n">
+      <c r="AC20" s="16" t="n">
         <v>57.5978</v>
       </c>
-      <c r="AI20" s="19" t="n">
+      <c r="AD20" s="16" t="n">
         <v>58.2641</v>
       </c>
-      <c r="AJ20" s="19" t="n">
+      <c r="AE20" s="16" t="n">
         <v>59.4959</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="n">
+      <c r="A21" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Q19</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>benzophenone O-[(benzylsulfanyl)carbonyl] oxime</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>O=C(SCC1=CC=CC=C1)O/N=C(C2=CC=CC=C2)\C3=CC=CC=C3</t>
         </is>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="16" t="n">
         <v>52.6</v>
       </c>
-      <c r="G21" s="19" t="n">
+      <c r="G21" s="16" t="n">
         <v>54.3</v>
       </c>
-      <c r="H21" s="19" t="n">
+      <c r="H21" s="16" t="n">
         <v>34.2</v>
       </c>
-      <c r="J21" s="19" t="n">
+      <c r="J21" s="16" t="n">
         <v>153</v>
       </c>
-      <c r="K21" s="19" t="n">
+      <c r="K21" s="16" t="n">
         <v>2.21</v>
       </c>
-      <c r="L21" s="19" t="n">
+      <c r="L21" s="16" t="n">
         <v>5.5</v>
       </c>
-      <c r="M21" s="19" t="n">
+      <c r="M21" s="16" t="n">
         <v>4.6</v>
       </c>
-      <c r="O21" s="19" t="n">
+      <c r="O21" s="16" t="n">
         <v>57.1</v>
       </c>
-      <c r="P21" s="19" t="n">
+      <c r="P21" s="16" t="n">
         <v>-1.94</v>
       </c>
-      <c r="Q21" s="19" t="n">
+      <c r="Q21" s="16" t="n">
         <v>10.6</v>
       </c>
-      <c r="R21" s="19" t="n">
+      <c r="R21" s="16" t="n">
         <v>12.2</v>
       </c>
-      <c r="T21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W21" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y21" s="19" t="n">
+      <c r="T21" s="16" t="n">
         <v>4696</v>
       </c>
-      <c r="Z21" s="19" t="n">
+      <c r="U21" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA21" s="19" t="n">
+      <c r="V21" s="16" t="n">
         <v>85.2851</v>
       </c>
-      <c r="AB21" s="19" t="n">
+      <c r="W21" s="16" t="n">
         <v>10.8324</v>
       </c>
-      <c r="AC21" s="19" t="n">
+      <c r="X21" s="16" t="n">
         <v>57.3827</v>
       </c>
-      <c r="AD21" s="19" t="n">
+      <c r="Y21" s="16" t="n">
         <v>59.1908</v>
       </c>
-      <c r="AE21" s="19" t="n">
+      <c r="Z21" s="16" t="n">
         <v>60.0852</v>
       </c>
-      <c r="AF21" s="19" t="n">
+      <c r="AA21" s="16" t="n">
         <v>61.7779</v>
       </c>
-      <c r="AG21" s="19" t="n">
+      <c r="AB21" s="16" t="n">
         <v>62.1043</v>
       </c>
-      <c r="AH21" s="19" t="n">
+      <c r="AC21" s="16" t="n">
         <v>63.4646</v>
       </c>
-      <c r="AI21" s="19" t="n">
+      <c r="AD21" s="16" t="n">
         <v>64.14449999999999</v>
       </c>
-      <c r="AJ21" s="19" t="n">
+      <c r="AE21" s="16" t="n">
         <v>65.459</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="n">
+      <c r="A22" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Q20</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>naphthalene</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>C12=CC=CC=C1C=CC=C2</t>
         </is>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="16" t="n">
         <v>60.6</v>
       </c>
-      <c r="G22" s="19" t="n">
+      <c r="G22" s="16" t="n">
         <v>13.3</v>
       </c>
-      <c r="H22" s="19" t="n">
+      <c r="H22" s="16" t="n">
         <v>13.6</v>
       </c>
-      <c r="J22" s="19" t="n">
+      <c r="J22" s="16" t="n">
         <v>138.8</v>
       </c>
-      <c r="K22" s="19" t="n">
+      <c r="K22" s="16" t="n">
         <v>1.6</v>
       </c>
-      <c r="L22" s="19" t="n">
+      <c r="L22" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="M22" s="19" t="n">
+      <c r="M22" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="O22" s="19" t="n">
+      <c r="O22" s="16" t="n">
         <v>41.8</v>
       </c>
-      <c r="P22" s="19" t="n">
+      <c r="P22" s="16" t="n">
         <v>-2.61</v>
       </c>
-      <c r="Q22" s="19" t="n">
+      <c r="Q22" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="R22" s="19" t="n">
+      <c r="R22" s="16" t="n">
         <v>3.8</v>
       </c>
-      <c r="T22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" s="19" t="n">
+      <c r="T22" s="16" t="n">
         <v>4984</v>
       </c>
-      <c r="Z22" s="19" t="n">
+      <c r="U22" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA22" s="19" t="n">
+      <c r="V22" s="16" t="n">
         <v>74.869</v>
       </c>
-      <c r="AB22" s="19" t="n">
+      <c r="W22" s="16" t="n">
         <v>7.42977</v>
       </c>
-      <c r="AC22" s="19" t="n">
+      <c r="X22" s="16" t="n">
         <v>55.7312</v>
       </c>
-      <c r="AD22" s="19" t="n">
+      <c r="Y22" s="16" t="n">
         <v>56.9713</v>
       </c>
-      <c r="AE22" s="19" t="n">
+      <c r="Z22" s="16" t="n">
         <v>57.5847</v>
       </c>
-      <c r="AF22" s="19" t="n">
+      <c r="AA22" s="16" t="n">
         <v>58.7457</v>
       </c>
-      <c r="AG22" s="19" t="n">
+      <c r="AB22" s="16" t="n">
         <v>55.9742</v>
       </c>
-      <c r="AH22" s="19" t="n">
+      <c r="AC22" s="16" t="n">
         <v>57.1039</v>
       </c>
-      <c r="AI22" s="19" t="n">
+      <c r="AD22" s="16" t="n">
         <v>57.657</v>
       </c>
-      <c r="AJ22" s="19" t="n">
+      <c r="AE22" s="16" t="n">
         <v>58.7144</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="n">
+      <c r="A23" s="16" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>ethyl 3-phenylpropiolate</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>CCOC(=O)C#Cc1ccccc1</t>
         </is>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="16" t="n">
         <v>67.7</v>
       </c>
-      <c r="G23" s="19" t="n">
+      <c r="G23" s="16" t="n">
         <v>13.9</v>
       </c>
-      <c r="H23" s="19" t="n">
+      <c r="H23" s="16" t="n">
         <v>13.8</v>
       </c>
-      <c r="J23" s="19" t="n">
+      <c r="J23" s="16" t="n">
         <v>155.8</v>
       </c>
-      <c r="K23" s="19" t="n">
+      <c r="K23" s="16" t="n">
         <v>2.34</v>
       </c>
-      <c r="L23" s="19" t="n">
+      <c r="L23" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="M23" s="19" t="n">
+      <c r="M23" s="16" t="n">
         <v>5.3</v>
       </c>
-      <c r="O23" s="19" t="n">
+      <c r="O23" s="16" t="n">
         <v>56.7</v>
       </c>
-      <c r="P23" s="19" t="n">
+      <c r="P23" s="16" t="n">
         <v>-1.96</v>
       </c>
-      <c r="Q23" s="19" t="n">
+      <c r="Q23" s="16" t="n">
         <v>7.3</v>
       </c>
-      <c r="R23" s="19" t="n">
+      <c r="R23" s="16" t="n">
         <v>6.8</v>
       </c>
-      <c r="T23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="19" t="n">
+      <c r="T23" s="16" t="n">
         <v>4935</v>
       </c>
-      <c r="Z23" s="19" t="n">
+      <c r="U23" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA23" s="19" t="n">
+      <c r="V23" s="16" t="n">
         <v>82.84999999999999</v>
       </c>
-      <c r="AB23" s="19" t="n">
+      <c r="W23" s="16" t="n">
         <v>7.30885</v>
       </c>
-      <c r="AC23" s="19" t="n">
+      <c r="X23" s="16" t="n">
         <v>64.02370000000001</v>
       </c>
-      <c r="AD23" s="19" t="n">
+      <c r="Y23" s="16" t="n">
         <v>65.2436</v>
       </c>
-      <c r="AE23" s="19" t="n">
+      <c r="Z23" s="16" t="n">
         <v>65.8471</v>
       </c>
-      <c r="AF23" s="19" t="n">
+      <c r="AA23" s="16" t="n">
         <v>66.98909999999999</v>
       </c>
-      <c r="AG23" s="19" t="n">
+      <c r="AB23" s="16" t="n">
         <v>62.7078</v>
       </c>
-      <c r="AH23" s="19" t="n">
+      <c r="AC23" s="16" t="n">
         <v>64.2711</v>
       </c>
-      <c r="AI23" s="19" t="n">
+      <c r="AD23" s="16" t="n">
         <v>65.0073</v>
       </c>
-      <c r="AJ23" s="19" t="n">
+      <c r="AE23" s="16" t="n">
         <v>66.2945</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="n">
+      <c r="A24" s="16" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Q22</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>4-oxo-2-phenylquinazolin-3(4H)-yl 3-phenylpropanoate</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>O=C1N(OC(CCC2=CC=CC=C2)=O)C(C3=CC=CC=C3)=NC4=CC=CC=C41</t>
         </is>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="16" t="n">
         <v>58.3</v>
       </c>
-      <c r="G24" s="19" t="n">
+      <c r="G24" s="16" t="n">
         <v>28.6</v>
       </c>
-      <c r="H24" s="19" t="n">
+      <c r="H24" s="16" t="n">
         <v>27.2</v>
       </c>
-      <c r="J24" s="19" t="n">
+      <c r="J24" s="16" t="n">
         <v>148.9</v>
       </c>
-      <c r="K24" s="19" t="n">
+      <c r="K24" s="16" t="n">
         <v>2.04</v>
       </c>
-      <c r="L24" s="19" t="n">
+      <c r="L24" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="M24" s="19" t="n">
+      <c r="M24" s="16" t="n">
         <v>7.1</v>
       </c>
-      <c r="O24" s="19" t="n">
+      <c r="O24" s="16" t="n">
         <v>57.2</v>
       </c>
-      <c r="P24" s="19" t="n">
+      <c r="P24" s="16" t="n">
         <v>-1.94</v>
       </c>
-      <c r="Q24" s="19" t="n">
+      <c r="Q24" s="16" t="n">
         <v>12.2</v>
       </c>
-      <c r="R24" s="19" t="n">
+      <c r="R24" s="16" t="n">
         <v>11.9</v>
       </c>
-      <c r="T24" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W24" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y24" s="19" t="n">
+      <c r="T24" s="16" t="n">
         <v>4934</v>
       </c>
-      <c r="Z24" s="19" t="n">
+      <c r="U24" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA24" s="19" t="n">
+      <c r="V24" s="16" t="n">
         <v>80.73999999999999</v>
       </c>
-      <c r="AB24" s="19" t="n">
+      <c r="W24" s="16" t="n">
         <v>6.52413</v>
       </c>
-      <c r="AC24" s="19" t="n">
+      <c r="X24" s="16" t="n">
         <v>63.935</v>
       </c>
-      <c r="AD24" s="19" t="n">
+      <c r="Y24" s="16" t="n">
         <v>65.0239</v>
       </c>
-      <c r="AE24" s="19" t="n">
+      <c r="Z24" s="16" t="n">
         <v>65.5626</v>
       </c>
-      <c r="AF24" s="19" t="n">
+      <c r="AA24" s="16" t="n">
         <v>66.58199999999999</v>
       </c>
-      <c r="AG24" s="19" t="n">
+      <c r="AB24" s="16" t="n">
         <v>61.2879</v>
       </c>
-      <c r="AH24" s="19" t="n">
+      <c r="AC24" s="16" t="n">
         <v>62.7064</v>
       </c>
-      <c r="AI24" s="19" t="n">
+      <c r="AD24" s="16" t="n">
         <v>63.4067</v>
       </c>
-      <c r="AJ24" s="19" t="n">
+      <c r="AE24" s="16" t="n">
         <v>64.7747</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="n">
+      <c r="A25" s="16" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>2-(benzo[b]thiophen-2-yl)-4,4,5,5-tetramethyl-1,3,2-dioxaborolane</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>CC(O1)(C)C(C)(C)OB1C2=CC3=CC=CC=C3S2</t>
         </is>
       </c>
-      <c r="F25" s="19" t="n">
+      <c r="F25" s="16" t="n">
         <v>61.6</v>
       </c>
-      <c r="G25" s="19" t="n">
+      <c r="G25" s="16" t="n">
         <v>13.4</v>
       </c>
-      <c r="H25" s="19" t="n">
+      <c r="H25" s="16" t="n">
         <v>13.2</v>
       </c>
-      <c r="J25" s="19" t="n">
+      <c r="J25" s="16" t="n">
         <v>140.7</v>
       </c>
-      <c r="K25" s="19" t="n">
+      <c r="K25" s="16" t="n">
         <v>1.68</v>
       </c>
-      <c r="L25" s="19" t="n">
+      <c r="L25" s="16" t="n">
         <v>3.9</v>
       </c>
-      <c r="M25" s="19" t="n">
+      <c r="M25" s="16" t="n">
         <v>3.4</v>
       </c>
-      <c r="O25" s="19" t="n">
+      <c r="O25" s="16" t="n">
         <v>45.5</v>
       </c>
-      <c r="P25" s="19" t="n">
+      <c r="P25" s="16" t="n">
         <v>-2.45</v>
       </c>
-      <c r="Q25" s="19" t="n">
+      <c r="Q25" s="16" t="n">
         <v>6.5</v>
       </c>
-      <c r="R25" s="19" t="n">
+      <c r="R25" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="T25" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W25" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" s="19" t="n">
+      <c r="T25" s="16" t="n">
         <v>4945</v>
       </c>
-      <c r="Z25" s="19" t="n">
+      <c r="U25" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA25" s="19" t="n">
+      <c r="V25" s="16" t="n">
         <v>76.9389</v>
       </c>
-      <c r="AB25" s="19" t="n">
+      <c r="W25" s="16" t="n">
         <v>7.46928</v>
       </c>
-      <c r="AC25" s="19" t="n">
+      <c r="X25" s="16" t="n">
         <v>57.6993</v>
       </c>
-      <c r="AD25" s="19" t="n">
+      <c r="Y25" s="16" t="n">
         <v>58.9461</v>
       </c>
-      <c r="AE25" s="19" t="n">
+      <c r="Z25" s="16" t="n">
         <v>59.5628</v>
       </c>
-      <c r="AF25" s="19" t="n">
+      <c r="AA25" s="16" t="n">
         <v>60.7299</v>
       </c>
-      <c r="AG25" s="19" t="n">
+      <c r="AB25" s="16" t="n">
         <v>58.2519</v>
       </c>
-      <c r="AH25" s="19" t="n">
+      <c r="AC25" s="16" t="n">
         <v>59.357</v>
       </c>
-      <c r="AI25" s="19" t="n">
+      <c r="AD25" s="16" t="n">
         <v>59.8748</v>
       </c>
-      <c r="AJ25" s="19" t="n">
+      <c r="AE25" s="16" t="n">
         <v>60.8273</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="n">
+      <c r="A26" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>2-(benzofuran-2-yl)-4,4,5,5-tetramethyl-1,3,2-dioxaborolane</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>CC(O1)(C)C(C)(C)OB1C2=CC3=CC=CC=C3O2</t>
         </is>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="16" t="n">
         <v>64.2</v>
       </c>
-      <c r="G26" s="19" t="n">
+      <c r="G26" s="16" t="n">
         <v>14.4</v>
       </c>
-      <c r="H26" s="19" t="n">
+      <c r="H26" s="16" t="n">
         <v>14.4</v>
       </c>
-      <c r="J26" s="19" t="n">
+      <c r="J26" s="16" t="n">
         <v>142.3</v>
       </c>
-      <c r="K26" s="19" t="n">
+      <c r="K26" s="16" t="n">
         <v>1.75</v>
       </c>
-      <c r="L26" s="19" t="n">
+      <c r="L26" s="16" t="n">
         <v>5.3</v>
       </c>
-      <c r="M26" s="19" t="n">
+      <c r="M26" s="16" t="n">
         <v>5.4</v>
       </c>
-      <c r="O26" s="19" t="n">
+      <c r="O26" s="16" t="n">
         <v>42.7</v>
       </c>
-      <c r="P26" s="19" t="n">
+      <c r="P26" s="16" t="n">
         <v>-2.57</v>
       </c>
-      <c r="Q26" s="19" t="n">
+      <c r="Q26" s="16" t="n">
         <v>6.9</v>
       </c>
-      <c r="R26" s="19" t="n">
+      <c r="R26" s="16" t="n">
         <v>6.2</v>
       </c>
-      <c r="T26" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V26" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W26" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" s="19" t="n">
+      <c r="T26" s="16" t="n">
         <v>4935</v>
       </c>
-      <c r="Z26" s="19" t="n">
+      <c r="U26" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA26" s="19" t="n">
+      <c r="V26" s="16" t="n">
         <v>79.9815</v>
       </c>
-      <c r="AB26" s="19" t="n">
+      <c r="W26" s="16" t="n">
         <v>7.13077</v>
       </c>
-      <c r="AC26" s="19" t="n">
+      <c r="X26" s="16" t="n">
         <v>61.6138</v>
       </c>
-      <c r="AD26" s="19" t="n">
+      <c r="Y26" s="16" t="n">
         <v>62.8041</v>
       </c>
-      <c r="AE26" s="19" t="n">
+      <c r="Z26" s="16" t="n">
         <v>63.3928</v>
       </c>
-      <c r="AF26" s="19" t="n">
+      <c r="AA26" s="16" t="n">
         <v>64.50709999999999</v>
       </c>
-      <c r="AG26" s="19" t="n">
+      <c r="AB26" s="16" t="n">
         <v>62.1684</v>
       </c>
-      <c r="AH26" s="19" t="n">
+      <c r="AC26" s="16" t="n">
         <v>63.1976</v>
       </c>
-      <c r="AI26" s="19" t="n">
+      <c r="AD26" s="16" t="n">
         <v>63.7058</v>
       </c>
-      <c r="AJ26" s="19" t="n">
+      <c r="AE26" s="16" t="n">
         <v>64.6735</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="n">
+      <c r="A27" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>2-bromobenzo[b]thiophene</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>BrC1=CC2=CC=CC=C2S1</t>
         </is>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="16" t="n">
         <v>60.5</v>
       </c>
-      <c r="G27" s="19" t="n">
+      <c r="G27" s="16" t="n">
         <v>35.5</v>
       </c>
-      <c r="H27" s="19" t="n">
+      <c r="H27" s="16" t="n">
         <v>20.6</v>
       </c>
-      <c r="J27" s="19" t="n">
+      <c r="J27" s="16" t="n">
         <v>141.3</v>
       </c>
-      <c r="K27" s="19" t="n">
+      <c r="K27" s="16" t="n">
         <v>1.71</v>
       </c>
-      <c r="L27" s="19" t="n">
+      <c r="L27" s="16" t="n">
         <v>4.6</v>
       </c>
-      <c r="M27" s="19" t="n">
+      <c r="M27" s="16" t="n">
         <v>4.5</v>
       </c>
-      <c r="O27" s="19" t="n">
+      <c r="O27" s="16" t="n">
         <v>64.59999999999999</v>
       </c>
-      <c r="P27" s="19" t="n">
+      <c r="P27" s="16" t="n">
         <v>-1.62</v>
       </c>
-      <c r="Q27" s="19" t="n">
+      <c r="Q27" s="16" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="R27" s="19" t="n">
+      <c r="R27" s="16" t="n">
         <v>30.9</v>
       </c>
-      <c r="T27" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W27" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y27" s="19" t="n">
+      <c r="T27" s="16" t="n">
         <v>4972</v>
       </c>
-      <c r="Z27" s="19" t="n">
+      <c r="U27" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA27" s="19" t="n">
+      <c r="V27" s="16" t="n">
         <v>81.6883</v>
       </c>
-      <c r="AB27" s="19" t="n">
+      <c r="W27" s="16" t="n">
         <v>6.92583</v>
       </c>
-      <c r="AC27" s="19" t="n">
+      <c r="X27" s="16" t="n">
         <v>63.8485</v>
       </c>
-      <c r="AD27" s="19" t="n">
+      <c r="Y27" s="16" t="n">
         <v>65.00449999999999</v>
       </c>
-      <c r="AE27" s="19" t="n">
+      <c r="Z27" s="16" t="n">
         <v>65.57640000000001</v>
       </c>
-      <c r="AF27" s="19" t="n">
+      <c r="AA27" s="16" t="n">
         <v>66.65860000000001</v>
       </c>
-      <c r="AG27" s="19" t="n">
+      <c r="AB27" s="16" t="n">
         <v>63.7562</v>
       </c>
-      <c r="AH27" s="19" t="n">
+      <c r="AC27" s="16" t="n">
         <v>64.87690000000001</v>
       </c>
-      <c r="AI27" s="19" t="n">
+      <c r="AD27" s="16" t="n">
         <v>65.4678</v>
       </c>
-      <c r="AJ27" s="19" t="n">
+      <c r="AE27" s="16" t="n">
         <v>66.5406</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="n">
+      <c r="A28" s="16" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>2-bromobenzofuran</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>BrC1=CC2=CC=CC=C2O1</t>
         </is>
       </c>
-      <c r="F28" s="19" t="n">
+      <c r="F28" s="16" t="n">
         <v>59.9</v>
       </c>
-      <c r="G28" s="19" t="n">
+      <c r="G28" s="16" t="n">
         <v>36.4</v>
       </c>
-      <c r="H28" s="19" t="n">
+      <c r="H28" s="16" t="n">
         <v>25.7</v>
       </c>
-      <c r="J28" s="19" t="n">
+      <c r="J28" s="16" t="n">
         <v>140.8</v>
       </c>
-      <c r="K28" s="19" t="n">
+      <c r="K28" s="16" t="n">
         <v>1.69</v>
       </c>
-      <c r="L28" s="19" t="n">
+      <c r="L28" s="16" t="n">
         <v>5.1</v>
       </c>
-      <c r="M28" s="19" t="n">
+      <c r="M28" s="16" t="n">
         <v>5.2</v>
       </c>
-      <c r="O28" s="19" t="n">
+      <c r="O28" s="16" t="n">
         <v>62.2</v>
       </c>
-      <c r="P28" s="19" t="n">
+      <c r="P28" s="16" t="n">
         <v>-1.72</v>
       </c>
-      <c r="Q28" s="19" t="n">
+      <c r="Q28" s="16" t="n">
         <v>73.5</v>
       </c>
-      <c r="R28" s="19" t="n">
+      <c r="R28" s="16" t="n">
         <v>32.6</v>
       </c>
-      <c r="T28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" s="19" t="n">
+      <c r="T28" s="16" t="n">
         <v>4960</v>
       </c>
-      <c r="Z28" s="19" t="n">
+      <c r="U28" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA28" s="19" t="n">
+      <c r="V28" s="16" t="n">
         <v>85.09529999999999</v>
       </c>
-      <c r="AB28" s="19" t="n">
+      <c r="W28" s="16" t="n">
         <v>6.8098</v>
       </c>
-      <c r="AC28" s="19" t="n">
+      <c r="X28" s="16" t="n">
         <v>67.5544</v>
       </c>
-      <c r="AD28" s="19" t="n">
+      <c r="Y28" s="16" t="n">
         <v>68.69110000000001</v>
       </c>
-      <c r="AE28" s="19" t="n">
+      <c r="Z28" s="16" t="n">
         <v>69.2534</v>
       </c>
-      <c r="AF28" s="19" t="n">
+      <c r="AA28" s="16" t="n">
         <v>70.31740000000001</v>
       </c>
-      <c r="AG28" s="19" t="n">
+      <c r="AB28" s="16" t="n">
         <v>67.11709999999999</v>
       </c>
-      <c r="AH28" s="19" t="n">
+      <c r="AC28" s="16" t="n">
         <v>68.07599999999999</v>
       </c>
-      <c r="AI28" s="19" t="n">
+      <c r="AD28" s="16" t="n">
         <v>68.5727</v>
       </c>
-      <c r="AJ28" s="19" t="n">
+      <c r="AE28" s="16" t="n">
         <v>69.5817</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="n">
+      <c r="A29" s="16" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>2,5-dibromothiophene</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>BrC1=CC=C(Br)S1</t>
         </is>
       </c>
-      <c r="F29" s="19" t="n">
+      <c r="F29" s="16" t="n">
         <v>58.5</v>
       </c>
-      <c r="G29" s="19" t="n">
+      <c r="G29" s="16" t="n">
         <v>36.2</v>
       </c>
-      <c r="H29" s="19" t="n">
+      <c r="H29" s="16" t="n">
         <v>19.8</v>
       </c>
-      <c r="J29" s="19" t="n">
+      <c r="J29" s="16" t="n">
         <v>144.2</v>
       </c>
-      <c r="K29" s="19" t="n">
+      <c r="K29" s="16" t="n">
         <v>1.83</v>
       </c>
-      <c r="L29" s="19" t="n">
+      <c r="L29" s="16" t="n">
         <v>5.3</v>
       </c>
-      <c r="M29" s="19" t="n">
+      <c r="M29" s="16" t="n">
         <v>5.4</v>
       </c>
-      <c r="O29" s="19" t="n">
+      <c r="O29" s="16" t="n">
         <v>65.3</v>
       </c>
-      <c r="P29" s="19" t="n">
+      <c r="P29" s="16" t="n">
         <v>-1.59</v>
       </c>
-      <c r="Q29" s="19" t="n">
+      <c r="Q29" s="16" t="n">
         <v>68</v>
       </c>
-      <c r="R29" s="19" t="n">
+      <c r="R29" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="T29" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" s="19" t="n">
+      <c r="T29" s="16" t="n">
         <v>4982</v>
       </c>
-      <c r="Z29" s="19" t="n">
+      <c r="U29" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA29" s="19" t="n">
+      <c r="V29" s="16" t="n">
         <v>81.8836</v>
       </c>
-      <c r="AB29" s="19" t="n">
+      <c r="W29" s="16" t="n">
         <v>7.56305</v>
       </c>
-      <c r="AC29" s="19" t="n">
+      <c r="X29" s="16" t="n">
         <v>62.4024</v>
       </c>
-      <c r="AD29" s="19" t="n">
+      <c r="Y29" s="16" t="n">
         <v>63.6648</v>
       </c>
-      <c r="AE29" s="19" t="n">
+      <c r="Z29" s="16" t="n">
         <v>64.2893</v>
       </c>
-      <c r="AF29" s="19" t="n">
+      <c r="AA29" s="16" t="n">
         <v>65.47110000000001</v>
       </c>
-      <c r="AG29" s="19" t="n">
+      <c r="AB29" s="16" t="n">
         <v>64.8265</v>
       </c>
-      <c r="AH29" s="19" t="n">
+      <c r="AC29" s="16" t="n">
         <v>65.6125</v>
       </c>
-      <c r="AI29" s="19" t="n">
+      <c r="AD29" s="16" t="n">
         <v>66.0116</v>
       </c>
-      <c r="AJ29" s="19" t="n">
+      <c r="AE29" s="16" t="n">
         <v>66.79170000000001</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="n">
+      <c r="A30" s="16" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>2-benzoylthiazole</t>
         </is>
       </c>
-      <c r="D30" s="19" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>O=C(C1=CC=CC=C1)C2=NC=CS2</t>
         </is>
       </c>
-      <c r="F30" s="19" t="n">
+      <c r="F30" s="16" t="n">
         <v>58.2</v>
       </c>
-      <c r="G30" s="19" t="n">
+      <c r="G30" s="16" t="n">
         <v>12.6</v>
       </c>
-      <c r="H30" s="19" t="n">
+      <c r="H30" s="16" t="n">
         <v>13.8</v>
       </c>
-      <c r="J30" s="19" t="n">
+      <c r="J30" s="16" t="n">
         <v>159.3</v>
       </c>
-      <c r="K30" s="19" t="n">
+      <c r="K30" s="16" t="n">
         <v>2.49</v>
       </c>
-      <c r="L30" s="19" t="n">
+      <c r="L30" s="16" t="n">
         <v>6.3</v>
       </c>
-      <c r="M30" s="19" t="n">
+      <c r="M30" s="16" t="n">
         <v>5.9</v>
       </c>
-      <c r="O30" s="19" t="n">
+      <c r="O30" s="16" t="n">
         <v>71</v>
       </c>
-      <c r="P30" s="19" t="n">
+      <c r="P30" s="16" t="n">
         <v>-1.34</v>
       </c>
-      <c r="Q30" s="19" t="n">
+      <c r="Q30" s="16" t="n">
         <v>6.6</v>
       </c>
-      <c r="R30" s="19" t="n">
+      <c r="R30" s="16" t="n">
         <v>7.2</v>
       </c>
-      <c r="T30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" s="19" t="n">
+      <c r="T30" s="16" t="n">
         <v>4938</v>
       </c>
-      <c r="Z30" s="19" t="n">
+      <c r="U30" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA30" s="19" t="n">
+      <c r="V30" s="16" t="n">
         <v>74.91030000000001</v>
       </c>
-      <c r="AB30" s="19" t="n">
+      <c r="W30" s="16" t="n">
         <v>6.72327</v>
       </c>
-      <c r="AC30" s="19" t="n">
+      <c r="X30" s="16" t="n">
         <v>57.5923</v>
       </c>
-      <c r="AD30" s="19" t="n">
+      <c r="Y30" s="16" t="n">
         <v>58.7145</v>
       </c>
-      <c r="AE30" s="19" t="n">
+      <c r="Z30" s="16" t="n">
         <v>59.2696</v>
       </c>
-      <c r="AF30" s="19" t="n">
+      <c r="AA30" s="16" t="n">
         <v>60.3202</v>
       </c>
-      <c r="AG30" s="19" t="n">
+      <c r="AB30" s="16" t="n">
         <v>58.0346</v>
       </c>
-      <c r="AH30" s="19" t="n">
+      <c r="AC30" s="16" t="n">
         <v>59.0484</v>
       </c>
-      <c r="AI30" s="19" t="n">
+      <c r="AD30" s="16" t="n">
         <v>59.5599</v>
       </c>
-      <c r="AJ30" s="19" t="n">
+      <c r="AE30" s="16" t="n">
         <v>60.5272</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="n">
+      <c r="A31" s="16" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>4,4-dimethyl-3-phenylisoxazol-5(4H)-one</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>O=C1C(C)(C)C(C2=CC=CC=C2)=NO1</t>
         </is>
       </c>
-      <c r="F31" s="19" t="n">
+      <c r="F31" s="16" t="n">
         <v>59</v>
       </c>
-      <c r="G31" s="19" t="n">
+      <c r="G31" s="16" t="n">
         <v>23.3</v>
       </c>
-      <c r="H31" s="19" t="n">
+      <c r="H31" s="16" t="n">
         <v>21.5</v>
       </c>
-      <c r="J31" s="19" t="n">
+      <c r="J31" s="16" t="n">
         <v>154.9</v>
       </c>
-      <c r="K31" s="19" t="n">
+      <c r="K31" s="16" t="n">
         <v>2.3</v>
       </c>
-      <c r="L31" s="19" t="n">
+      <c r="L31" s="16" t="n">
         <v>7.9</v>
       </c>
-      <c r="M31" s="19" t="n">
+      <c r="M31" s="16" t="n">
         <v>6.2</v>
       </c>
-      <c r="O31" s="19" t="n">
+      <c r="O31" s="16" t="n">
         <v>55</v>
       </c>
-      <c r="P31" s="19" t="n">
+      <c r="P31" s="16" t="n">
         <v>-2.04</v>
       </c>
-      <c r="Q31" s="19" t="n">
+      <c r="Q31" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="R31" s="19" t="n">
+      <c r="R31" s="16" t="n">
         <v>6.7</v>
       </c>
-      <c r="T31" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U31" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V31" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W31" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y31" s="19" t="n">
+      <c r="T31" s="16" t="n">
         <v>4936</v>
       </c>
-      <c r="Z31" s="19" t="n">
+      <c r="U31" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA31" s="19" t="n">
+      <c r="V31" s="16" t="n">
         <v>82.4918</v>
       </c>
-      <c r="AB31" s="19" t="n">
+      <c r="W31" s="16" t="n">
         <v>8.193899999999999</v>
       </c>
-      <c r="AC31" s="19" t="n">
+      <c r="X31" s="16" t="n">
         <v>61.3857</v>
       </c>
-      <c r="AD31" s="19" t="n">
+      <c r="Y31" s="16" t="n">
         <v>62.7534</v>
       </c>
-      <c r="AE31" s="19" t="n">
+      <c r="Z31" s="16" t="n">
         <v>63.4299</v>
       </c>
-      <c r="AF31" s="19" t="n">
+      <c r="AA31" s="16" t="n">
         <v>64.7103</v>
       </c>
-      <c r="AG31" s="19" t="n">
+      <c r="AB31" s="16" t="n">
         <v>60.2419</v>
       </c>
-      <c r="AH31" s="19" t="n">
+      <c r="AC31" s="16" t="n">
         <v>61.7073</v>
       </c>
-      <c r="AI31" s="19" t="n">
+      <c r="AD31" s="16" t="n">
         <v>62.4026</v>
       </c>
-      <c r="AJ31" s="19" t="n">
+      <c r="AE31" s="16" t="n">
         <v>63.7671</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="n">
+      <c r="A32" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>Q30</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>(E)-stilbene</t>
         </is>
       </c>
-      <c r="D32" s="19" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>C1(/C=C/C2=CC=CC=C2)=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F32" s="19" t="n">
+      <c r="F32" s="16" t="n">
         <v>42.8</v>
       </c>
-      <c r="G32" s="19" t="n">
+      <c r="G32" s="16" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="H32" s="19" t="n">
+      <c r="H32" s="16" t="n">
         <v>22.1</v>
       </c>
-      <c r="J32" s="19" t="n">
+      <c r="J32" s="16" t="n">
         <v>132.6</v>
       </c>
-      <c r="K32" s="19" t="n">
+      <c r="K32" s="16" t="n">
         <v>1.33</v>
       </c>
-      <c r="L32" s="19" t="n">
+      <c r="L32" s="16" t="n">
         <v>4.8</v>
       </c>
-      <c r="M32" s="19" t="n">
+      <c r="M32" s="16" t="n">
         <v>4.7</v>
       </c>
-      <c r="O32" s="19" t="n">
+      <c r="O32" s="16" t="n">
         <v>49.3</v>
       </c>
-      <c r="P32" s="19" t="n">
+      <c r="P32" s="16" t="n">
         <v>-2.28</v>
       </c>
-      <c r="Q32" s="19" t="n">
+      <c r="Q32" s="16" t="n">
         <v>5.4</v>
       </c>
-      <c r="R32" s="19" t="n">
+      <c r="R32" s="16" t="n">
         <v>5.1</v>
       </c>
-      <c r="T32" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V32" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W32" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y32" s="19" t="n">
+      <c r="T32" s="16" t="n">
         <v>4948</v>
       </c>
-      <c r="Z32" s="19" t="n">
+      <c r="U32" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA32" s="19" t="n">
+      <c r="V32" s="16" t="n">
         <v>70.6266</v>
       </c>
-      <c r="AB32" s="19" t="n">
+      <c r="W32" s="16" t="n">
         <v>9.087770000000001</v>
       </c>
-      <c r="AC32" s="19" t="n">
+      <c r="X32" s="16" t="n">
         <v>47.2181</v>
       </c>
-      <c r="AD32" s="19" t="n">
+      <c r="Y32" s="16" t="n">
         <v>48.735</v>
       </c>
-      <c r="AE32" s="19" t="n">
+      <c r="Z32" s="16" t="n">
         <v>49.4853</v>
       </c>
-      <c r="AF32" s="19" t="n">
+      <c r="AA32" s="16" t="n">
         <v>50.9054</v>
       </c>
-      <c r="AG32" s="19" t="n">
+      <c r="AB32" s="16" t="n">
         <v>46.755</v>
       </c>
-      <c r="AH32" s="19" t="n">
+      <c r="AC32" s="16" t="n">
         <v>48.1417</v>
       </c>
-      <c r="AI32" s="19" t="n">
+      <c r="AD32" s="16" t="n">
         <v>48.9057</v>
       </c>
-      <c r="AJ32" s="19" t="n">
+      <c r="AE32" s="16" t="n">
         <v>50.4689</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="n">
+      <c r="A33" s="16" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="19" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Q31</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>6-phenyl-5-oxa-6-azaspiro[2.4]heptane-4,7-dione</t>
         </is>
       </c>
-      <c r="D33" s="19" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>O=C1N(C2=CC=CC=C2)OC(C13CC3)=O</t>
         </is>
       </c>
-      <c r="F33" s="19" t="n">
+      <c r="F33" s="16" t="n">
         <v>76.40000000000001</v>
       </c>
-      <c r="G33" s="19" t="n">
+      <c r="G33" s="16" t="n">
         <v>37</v>
       </c>
-      <c r="H33" s="19" t="n">
+      <c r="H33" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="J33" s="19" t="n">
+      <c r="J33" s="16" t="n">
         <v>142.4</v>
       </c>
-      <c r="K33" s="19" t="n">
+      <c r="K33" s="16" t="n">
         <v>1.75</v>
       </c>
-      <c r="L33" s="19" t="n">
+      <c r="L33" s="16" t="n">
         <v>7.4</v>
       </c>
-      <c r="M33" s="19" t="n">
+      <c r="M33" s="16" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="O33" s="19" t="n">
+      <c r="O33" s="16" t="n">
         <v>40.2</v>
       </c>
-      <c r="P33" s="19" t="n">
+      <c r="P33" s="16" t="n">
         <v>-2.68</v>
       </c>
-      <c r="Q33" s="19" t="n">
+      <c r="Q33" s="16" t="n">
         <v>27.2</v>
       </c>
-      <c r="R33" s="19" t="n">
+      <c r="R33" s="16" t="n">
         <v>11.8</v>
       </c>
-      <c r="T33" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W33" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" s="19" t="n">
+      <c r="T33" s="16" t="n">
         <v>4939</v>
       </c>
-      <c r="Z33" s="19" t="n">
+      <c r="U33" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA33" s="19" t="n">
+      <c r="V33" s="16" t="n">
         <v>89.218</v>
       </c>
-      <c r="AB33" s="19" t="n">
+      <c r="W33" s="16" t="n">
         <v>6.19149</v>
       </c>
-      <c r="AC33" s="19" t="n">
+      <c r="X33" s="16" t="n">
         <v>73.2697</v>
       </c>
-      <c r="AD33" s="19" t="n">
+      <c r="Y33" s="16" t="n">
         <v>74.3032</v>
       </c>
-      <c r="AE33" s="19" t="n">
+      <c r="Z33" s="16" t="n">
         <v>74.81440000000001</v>
       </c>
-      <c r="AF33" s="19" t="n">
+      <c r="AA33" s="16" t="n">
         <v>75.78189999999999</v>
       </c>
-      <c r="AG33" s="19" t="n">
+      <c r="AB33" s="16" t="n">
         <v>71.6968</v>
       </c>
-      <c r="AH33" s="19" t="n">
+      <c r="AC33" s="16" t="n">
         <v>73.15309999999999</v>
       </c>
-      <c r="AI33" s="19" t="n">
+      <c r="AD33" s="16" t="n">
         <v>73.82850000000001</v>
       </c>
-      <c r="AJ33" s="19" t="n">
+      <c r="AE33" s="16" t="n">
         <v>74.9969</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="n">
+      <c r="A34" s="16" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>Q32</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>1-(thiobenzoyl)pyrrolidine</t>
         </is>
       </c>
-      <c r="D34" s="19" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>S=C(N1CCCC1)C2=CC=CC=C2</t>
         </is>
       </c>
-      <c r="F34" s="19" t="n">
+      <c r="F34" s="16" t="n">
         <v>54.7</v>
       </c>
-      <c r="G34" s="19" t="n">
+      <c r="G34" s="16" t="n">
         <v>41.8</v>
       </c>
-      <c r="H34" s="19" t="n">
+      <c r="H34" s="16" t="n">
         <v>18.8</v>
       </c>
-      <c r="J34" s="19" t="n">
+      <c r="J34" s="16" t="n">
         <v>134.1</v>
       </c>
-      <c r="K34" s="19" t="n">
+      <c r="K34" s="16" t="n">
         <v>1.4</v>
       </c>
-      <c r="L34" s="19" t="n">
+      <c r="L34" s="16" t="n">
         <v>2.5</v>
       </c>
-      <c r="M34" s="19" t="n">
+      <c r="M34" s="16" t="n">
         <v>2.2</v>
       </c>
-      <c r="O34" s="19" t="n">
+      <c r="O34" s="16" t="n">
         <v>53.8</v>
       </c>
-      <c r="P34" s="19" t="n">
+      <c r="P34" s="16" t="n">
         <v>-2.09</v>
       </c>
-      <c r="Q34" s="19" t="n">
+      <c r="Q34" s="16" t="n">
         <v>21.1</v>
       </c>
-      <c r="R34" s="19" t="n">
+      <c r="R34" s="16" t="n">
         <v>17.1</v>
       </c>
-      <c r="T34" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U34" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V34" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" s="19" t="n">
+      <c r="T34" s="16" t="n">
         <v>4941</v>
       </c>
-      <c r="Z34" s="19" t="n">
+      <c r="U34" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA34" s="19" t="n">
+      <c r="V34" s="16" t="n">
         <v>73.4991</v>
       </c>
-      <c r="AB34" s="19" t="n">
+      <c r="W34" s="16" t="n">
         <v>5.38119</v>
       </c>
-      <c r="AC34" s="19" t="n">
+      <c r="X34" s="16" t="n">
         <v>59.6381</v>
       </c>
-      <c r="AD34" s="19" t="n">
+      <c r="Y34" s="16" t="n">
         <v>60.5363</v>
       </c>
-      <c r="AE34" s="19" t="n">
+      <c r="Z34" s="16" t="n">
         <v>60.9806</v>
       </c>
-      <c r="AF34" s="19" t="n">
+      <c r="AA34" s="16" t="n">
         <v>61.8215</v>
       </c>
-      <c r="AG34" s="19" t="n">
+      <c r="AB34" s="16" t="n">
         <v>59.8759</v>
       </c>
-      <c r="AH34" s="19" t="n">
+      <c r="AC34" s="16" t="n">
         <v>60.7176</v>
       </c>
-      <c r="AI34" s="19" t="n">
+      <c r="AD34" s="16" t="n">
         <v>61.1636</v>
       </c>
-      <c r="AJ34" s="19" t="n">
+      <c r="AE34" s="16" t="n">
         <v>61.9959</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="n">
+      <c r="A35" s="16" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="19" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>Q33</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>N-methyl-N-phenylpropanethioamide</t>
         </is>
       </c>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>S=C(N(C1=CC=CC=C1)C)CC</t>
         </is>
       </c>
-      <c r="F35" s="19" t="n">
+      <c r="F35" s="16" t="n">
         <v>58.7</v>
       </c>
-      <c r="G35" s="19" t="n">
+      <c r="G35" s="16" t="n">
         <v>32.9</v>
       </c>
-      <c r="H35" s="19" t="n">
+      <c r="H35" s="16" t="n">
         <v>16.8</v>
       </c>
-      <c r="J35" s="19" t="n">
+      <c r="J35" s="16" t="n">
         <v>133.5</v>
       </c>
-      <c r="K35" s="19" t="n">
+      <c r="K35" s="16" t="n">
         <v>1.37</v>
       </c>
-      <c r="L35" s="19" t="n">
+      <c r="L35" s="16" t="n">
         <v>7.2</v>
       </c>
-      <c r="M35" s="19" t="n">
+      <c r="M35" s="16" t="n">
         <v>3.1</v>
       </c>
-      <c r="O35" s="19" t="n">
+      <c r="O35" s="16" t="n">
         <v>51.3</v>
       </c>
-      <c r="P35" s="19" t="n">
+      <c r="P35" s="16" t="n">
         <v>-2.2</v>
       </c>
-      <c r="Q35" s="19" t="n">
+      <c r="Q35" s="16" t="n">
         <v>23.5</v>
       </c>
-      <c r="R35" s="19" t="n">
+      <c r="R35" s="16" t="n">
         <v>26.8</v>
       </c>
-      <c r="T35" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V35" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W35" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y35" s="19" t="n">
+      <c r="T35" s="16" t="n">
         <v>4922</v>
       </c>
-      <c r="Z35" s="19" t="n">
+      <c r="U35" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA35" s="19" t="n">
+      <c r="V35" s="16" t="n">
         <v>75.2128</v>
       </c>
-      <c r="AB35" s="19" t="n">
+      <c r="W35" s="16" t="n">
         <v>4.85368</v>
       </c>
-      <c r="AC35" s="19" t="n">
+      <c r="X35" s="16" t="n">
         <v>62.7105</v>
       </c>
-      <c r="AD35" s="19" t="n">
+      <c r="Y35" s="16" t="n">
         <v>63.5207</v>
       </c>
-      <c r="AE35" s="19" t="n">
+      <c r="Z35" s="16" t="n">
         <v>63.9214</v>
       </c>
-      <c r="AF35" s="19" t="n">
+      <c r="AA35" s="16" t="n">
         <v>64.6799</v>
       </c>
-      <c r="AG35" s="19" t="n">
+      <c r="AB35" s="16" t="n">
         <v>62.2521</v>
       </c>
-      <c r="AH35" s="19" t="n">
+      <c r="AC35" s="16" t="n">
         <v>63.2643</v>
       </c>
-      <c r="AI35" s="19" t="n">
+      <c r="AD35" s="16" t="n">
         <v>63.7302</v>
       </c>
-      <c r="AJ35" s="19" t="n">
+      <c r="AE35" s="16" t="n">
         <v>64.5461</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="n">
+      <c r="A36" s="16" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>Q34</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>(Z)-3,4-dihydronaphthalen-1(2H)-one O-methyl oxime</t>
         </is>
       </c>
-      <c r="D36" s="19" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>CO/N=C1CCCC2=CC=CC=C2/1</t>
         </is>
       </c>
-      <c r="F36" s="19" t="n">
+      <c r="F36" s="16" t="n">
         <v>42.2</v>
       </c>
-      <c r="G36" s="19" t="n">
+      <c r="G36" s="16" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="H36" s="19" t="n">
+      <c r="H36" s="16" t="n">
         <v>40.5</v>
       </c>
-      <c r="J36" s="19" t="n">
+      <c r="J36" s="16" t="n">
         <v>139.8</v>
       </c>
-      <c r="K36" s="19" t="n">
+      <c r="K36" s="16" t="n">
         <v>1.64</v>
       </c>
-      <c r="L36" s="19" t="n">
+      <c r="L36" s="16" t="n">
         <v>13.6</v>
       </c>
-      <c r="M36" s="19" t="n">
+      <c r="M36" s="16" t="n">
         <v>10.1</v>
       </c>
-      <c r="O36" s="19" t="n">
+      <c r="O36" s="16" t="n">
         <v>44</v>
       </c>
-      <c r="P36" s="19" t="n">
+      <c r="P36" s="16" t="n">
         <v>-2.51</v>
       </c>
-      <c r="Q36" s="19" t="n">
+      <c r="Q36" s="16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="R36" s="19" t="n">
+      <c r="R36" s="16" t="n">
         <v>8.9</v>
       </c>
-      <c r="T36" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V36" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W36" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y36" s="19" t="n">
+      <c r="T36" s="16" t="n">
         <v>4936</v>
       </c>
-      <c r="Z36" s="19" t="n">
+      <c r="U36" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA36" s="19" t="n">
+      <c r="V36" s="16" t="n">
         <v>81.9498</v>
       </c>
-      <c r="AB36" s="19" t="n">
+      <c r="W36" s="16" t="n">
         <v>8.21738</v>
       </c>
-      <c r="AC36" s="19" t="n">
+      <c r="X36" s="16" t="n">
         <v>60.7833</v>
       </c>
-      <c r="AD36" s="19" t="n">
+      <c r="Y36" s="16" t="n">
         <v>62.1549</v>
       </c>
-      <c r="AE36" s="19" t="n">
+      <c r="Z36" s="16" t="n">
         <v>62.8334</v>
       </c>
-      <c r="AF36" s="19" t="n">
+      <c r="AA36" s="16" t="n">
         <v>64.1174</v>
       </c>
-      <c r="AG36" s="19" t="n">
+      <c r="AB36" s="16" t="n">
         <v>60.8441</v>
       </c>
-      <c r="AH36" s="19" t="n">
+      <c r="AC36" s="16" t="n">
         <v>62.039</v>
       </c>
-      <c r="AI36" s="19" t="n">
+      <c r="AD36" s="16" t="n">
         <v>62.6255</v>
       </c>
-      <c r="AJ36" s="19" t="n">
+      <c r="AE36" s="16" t="n">
         <v>63.7688</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="n">
+      <c r="A37" s="16" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="19" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Q35</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>(Z)-stilbene</t>
         </is>
       </c>
-      <c r="D37" s="19" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>C1(/C=C\C2=CC=CC=C2)=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F37" s="19" t="n">
+      <c r="F37" s="16" t="n">
         <v>39.2</v>
       </c>
-      <c r="G37" s="19" t="n">
+      <c r="G37" s="16" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="H37" s="19" t="n">
+      <c r="H37" s="16" t="n">
         <v>40.4</v>
       </c>
-      <c r="J37" s="19" t="n">
+      <c r="J37" s="16" t="n">
         <v>135.6</v>
       </c>
-      <c r="K37" s="19" t="n">
+      <c r="K37" s="16" t="n">
         <v>1.46</v>
       </c>
-      <c r="L37" s="19" t="n">
+      <c r="L37" s="16" t="n">
         <v>8.6</v>
       </c>
-      <c r="M37" s="19" t="n">
+      <c r="M37" s="16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="O37" s="19" t="n">
+      <c r="O37" s="16" t="n">
         <v>52.8</v>
       </c>
-      <c r="P37" s="19" t="n">
+      <c r="P37" s="16" t="n">
         <v>-2.13</v>
       </c>
-      <c r="Q37" s="19" t="n">
+      <c r="Q37" s="16" t="n">
         <v>1.9</v>
       </c>
-      <c r="R37" s="19" t="n">
+      <c r="R37" s="16" t="n">
         <v>18.1</v>
       </c>
-      <c r="T37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y37" s="19" t="n">
+      <c r="T37" s="16" t="n">
         <v>4952</v>
       </c>
-      <c r="Z37" s="19" t="n">
+      <c r="U37" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA37" s="19" t="n">
+      <c r="V37" s="16" t="n">
         <v>77.6763</v>
       </c>
-      <c r="AB37" s="19" t="n">
+      <c r="W37" s="16" t="n">
         <v>8.577819999999999</v>
       </c>
-      <c r="AC37" s="19" t="n">
+      <c r="X37" s="16" t="n">
         <v>55.5813</v>
       </c>
-      <c r="AD37" s="19" t="n">
+      <c r="Y37" s="16" t="n">
         <v>57.0131</v>
       </c>
-      <c r="AE37" s="19" t="n">
+      <c r="Z37" s="16" t="n">
         <v>57.7214</v>
       </c>
-      <c r="AF37" s="19" t="n">
+      <c r="AA37" s="16" t="n">
         <v>59.0617</v>
       </c>
-      <c r="AG37" s="19" t="n">
+      <c r="AB37" s="16" t="n">
         <v>54.7377</v>
       </c>
-      <c r="AH37" s="19" t="n">
+      <c r="AC37" s="16" t="n">
         <v>56.0399</v>
       </c>
-      <c r="AI37" s="19" t="n">
+      <c r="AD37" s="16" t="n">
         <v>56.692</v>
       </c>
-      <c r="AJ37" s="19" t="n">
+      <c r="AE37" s="16" t="n">
         <v>57.9615</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="n">
+      <c r="A38" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="19" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="C38" s="19" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>2-acetyl-1-methylpyrrole</t>
         </is>
       </c>
-      <c r="D38" s="19" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>CN1C(C(C)=O)=CC=C1</t>
         </is>
       </c>
-      <c r="F38" s="19" t="n">
+      <c r="F38" s="16" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="G38" s="19" t="n">
+      <c r="G38" s="16" t="n">
         <v>9.6</v>
       </c>
-      <c r="H38" s="19" t="n">
+      <c r="H38" s="16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J38" s="19" t="n">
+      <c r="J38" s="16" t="n">
         <v>138.4</v>
       </c>
-      <c r="K38" s="19" t="n">
+      <c r="K38" s="16" t="n">
         <v>1.58</v>
       </c>
-      <c r="L38" s="19" t="n">
+      <c r="L38" s="16" t="n">
         <v>4.6</v>
       </c>
-      <c r="M38" s="19" t="n">
+      <c r="M38" s="16" t="n">
         <v>4.6</v>
       </c>
-      <c r="O38" s="19" t="n">
+      <c r="O38" s="16" t="n">
         <v>44.9</v>
       </c>
-      <c r="P38" s="19" t="n">
+      <c r="P38" s="16" t="n">
         <v>-2.47</v>
       </c>
-      <c r="Q38" s="19" t="n">
+      <c r="Q38" s="16" t="n">
         <v>6.9</v>
       </c>
-      <c r="R38" s="19" t="n">
+      <c r="R38" s="16" t="n">
         <v>6.2</v>
       </c>
-      <c r="T38" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W38" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y38" s="19" t="n">
+      <c r="T38" s="16" t="n">
         <v>4970</v>
       </c>
-      <c r="Z38" s="19" t="n">
+      <c r="U38" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA38" s="19" t="n">
+      <c r="V38" s="16" t="n">
         <v>78.447</v>
       </c>
-      <c r="AB38" s="19" t="n">
+      <c r="W38" s="16" t="n">
         <v>5.90028</v>
       </c>
-      <c r="AC38" s="19" t="n">
+      <c r="X38" s="16" t="n">
         <v>63.2489</v>
       </c>
-      <c r="AD38" s="19" t="n">
+      <c r="Y38" s="16" t="n">
         <v>64.2338</v>
       </c>
-      <c r="AE38" s="19" t="n">
+      <c r="Z38" s="16" t="n">
         <v>64.7209</v>
       </c>
-      <c r="AF38" s="19" t="n">
+      <c r="AA38" s="16" t="n">
         <v>65.6429</v>
       </c>
-      <c r="AG38" s="19" t="n">
+      <c r="AB38" s="16" t="n">
         <v>63.0796</v>
       </c>
-      <c r="AH38" s="19" t="n">
+      <c r="AC38" s="16" t="n">
         <v>64.0748</v>
       </c>
-      <c r="AI38" s="19" t="n">
+      <c r="AD38" s="16" t="n">
         <v>64.5448</v>
       </c>
-      <c r="AJ38" s="19" t="n">
+      <c r="AE38" s="16" t="n">
         <v>65.4285</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="n">
+      <c r="A39" s="16" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>Q37</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>1-bromo-4-(2,2-difluorovinyl)benzene</t>
         </is>
       </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>F/C(F)=C/C1=CC=C(Br)C=C1</t>
         </is>
       </c>
-      <c r="F39" s="19" t="n">
+      <c r="F39" s="16" t="n">
         <v>48.4</v>
       </c>
-      <c r="G39" s="19" t="n">
+      <c r="G39" s="16" t="n">
         <v>85.3</v>
       </c>
-      <c r="H39" s="19" t="n">
+      <c r="H39" s="16" t="n">
         <v>32.6</v>
       </c>
-      <c r="J39" s="19" t="n">
+      <c r="J39" s="16" t="n">
         <v>143.1</v>
       </c>
-      <c r="K39" s="19" t="n">
+      <c r="K39" s="16" t="n">
         <v>1.79</v>
       </c>
-      <c r="L39" s="19" t="n">
+      <c r="L39" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="M39" s="19" t="n">
+      <c r="M39" s="16" t="n">
         <v>6.1</v>
       </c>
-      <c r="O39" s="19" t="n">
+      <c r="O39" s="16" t="n">
         <v>44.7</v>
       </c>
-      <c r="P39" s="19" t="n">
+      <c r="P39" s="16" t="n">
         <v>-2.48</v>
       </c>
-      <c r="Q39" s="19" t="n">
+      <c r="Q39" s="16" t="n">
         <v>26.9</v>
       </c>
-      <c r="R39" s="19" t="n">
+      <c r="R39" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="T39" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W39" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y39" s="19" t="n">
+      <c r="T39" s="16" t="n">
         <v>4952</v>
       </c>
-      <c r="Z39" s="19" t="n">
+      <c r="U39" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA39" s="19" t="n">
+      <c r="V39" s="16" t="n">
         <v>82.68300000000001</v>
       </c>
-      <c r="AB39" s="19" t="n">
+      <c r="W39" s="16" t="n">
         <v>7.89385</v>
       </c>
-      <c r="AC39" s="19" t="n">
+      <c r="X39" s="16" t="n">
         <v>62.3498</v>
       </c>
-      <c r="AD39" s="19" t="n">
+      <c r="Y39" s="16" t="n">
         <v>63.6674</v>
       </c>
-      <c r="AE39" s="19" t="n">
+      <c r="Z39" s="16" t="n">
         <v>64.3192</v>
       </c>
-      <c r="AF39" s="19" t="n">
+      <c r="AA39" s="16" t="n">
         <v>65.5527</v>
       </c>
-      <c r="AG39" s="19" t="n">
+      <c r="AB39" s="16" t="n">
         <v>60.1772</v>
       </c>
-      <c r="AH39" s="19" t="n">
+      <c r="AC39" s="16" t="n">
         <v>61.6659</v>
       </c>
-      <c r="AI39" s="19" t="n">
+      <c r="AD39" s="16" t="n">
         <v>62.4197</v>
       </c>
-      <c r="AJ39" s="19" t="n">
+      <c r="AE39" s="16" t="n">
         <v>63.8438</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="19" t="n">
+      <c r="A40" s="16" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="19" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>Q38</t>
         </is>
       </c>
-      <c r="C40" s="19" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>1,3-butadiene</t>
         </is>
       </c>
-      <c r="D40" s="19" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>C=CC=C</t>
         </is>
       </c>
-      <c r="F40" s="19" t="n">
+      <c r="F40" s="16" t="n">
         <v>50.6</v>
       </c>
-      <c r="G40" s="19" t="n">
+      <c r="G40" s="16" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="H40" s="19" t="n">
+      <c r="H40" s="16" t="n">
         <v>25.8</v>
       </c>
-      <c r="J40" s="19" t="n">
+      <c r="J40" s="16" t="n">
         <v>145.6</v>
       </c>
-      <c r="K40" s="19" t="n">
+      <c r="K40" s="16" t="n">
         <v>1.89</v>
       </c>
-      <c r="L40" s="19" t="n">
+      <c r="L40" s="16" t="n">
         <v>4.5</v>
       </c>
-      <c r="M40" s="19" t="n">
+      <c r="M40" s="16" t="n">
         <v>4.5</v>
       </c>
-      <c r="O40" s="19" t="n">
+      <c r="O40" s="16" t="n">
         <v>41.6</v>
       </c>
-      <c r="P40" s="19" t="n">
+      <c r="P40" s="16" t="n">
         <v>-2.62</v>
       </c>
-      <c r="Q40" s="19" t="n">
+      <c r="Q40" s="16" t="n">
         <v>8.9</v>
       </c>
-      <c r="R40" s="19" t="n">
+      <c r="R40" s="16" t="n">
         <v>9.4</v>
       </c>
-      <c r="T40" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V40" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W40" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y40" s="19" t="n">
+      <c r="T40" s="16" t="n">
         <v>4985</v>
       </c>
-      <c r="Z40" s="19" t="n">
+      <c r="U40" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA40" s="19" t="n">
+      <c r="V40" s="16" t="n">
         <v>77.7771</v>
       </c>
-      <c r="AB40" s="19" t="n">
+      <c r="W40" s="16" t="n">
         <v>10.8169</v>
       </c>
-      <c r="AC40" s="19" t="n">
+      <c r="X40" s="16" t="n">
         <v>49.9147</v>
       </c>
-      <c r="AD40" s="19" t="n">
+      <c r="Y40" s="16" t="n">
         <v>51.7202</v>
       </c>
-      <c r="AE40" s="19" t="n">
+      <c r="Z40" s="16" t="n">
         <v>52.6133</v>
       </c>
-      <c r="AF40" s="19" t="n">
+      <c r="AA40" s="16" t="n">
         <v>54.3035</v>
       </c>
-      <c r="AG40" s="19" t="n">
+      <c r="AB40" s="16" t="n">
         <v>50.9725</v>
       </c>
-      <c r="AH40" s="19" t="n">
+      <c r="AC40" s="16" t="n">
         <v>52.5491</v>
       </c>
-      <c r="AI40" s="19" t="n">
+      <c r="AD40" s="16" t="n">
         <v>53.334</v>
       </c>
-      <c r="AJ40" s="19" t="n">
+      <c r="AE40" s="16" t="n">
         <v>54.7985</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="n">
+      <c r="A41" s="16" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="19" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>Q39</t>
         </is>
       </c>
-      <c r="C41" s="19" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>4-methyl-2-phenylthiazole</t>
         </is>
       </c>
-      <c r="D41" s="19" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>CC1=CSC(=N1)C2=CC=CC=C2</t>
         </is>
       </c>
-      <c r="F41" s="19" t="n">
+      <c r="F41" s="16" t="n">
         <v>55.2</v>
       </c>
-      <c r="G41" s="19" t="n">
+      <c r="G41" s="16" t="n">
         <v>17.5</v>
       </c>
-      <c r="H41" s="19" t="n">
+      <c r="H41" s="16" t="n">
         <v>19.3</v>
       </c>
-      <c r="J41" s="19" t="n">
+      <c r="J41" s="16" t="n">
         <v>139</v>
       </c>
-      <c r="K41" s="19" t="n">
+      <c r="K41" s="16" t="n">
         <v>1.61</v>
       </c>
-      <c r="L41" s="19" t="n">
+      <c r="L41" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="M41" s="19" t="n">
+      <c r="M41" s="16" t="n">
         <v>6.7</v>
       </c>
-      <c r="O41" s="19" t="n">
+      <c r="O41" s="16" t="n">
         <v>49.9</v>
       </c>
-      <c r="P41" s="19" t="n">
+      <c r="P41" s="16" t="n">
         <v>-2.26</v>
       </c>
-      <c r="Q41" s="19" t="n">
+      <c r="Q41" s="16" t="n">
         <v>5.5</v>
       </c>
-      <c r="R41" s="19" t="n">
+      <c r="R41" s="16" t="n">
         <v>6.7</v>
       </c>
-      <c r="T41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y41" s="19" t="n">
+      <c r="T41" s="16" t="n">
         <v>4946</v>
       </c>
-      <c r="Z41" s="19" t="n">
+      <c r="U41" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA41" s="19" t="n">
+      <c r="V41" s="16" t="n">
         <v>76.28879999999999</v>
       </c>
-      <c r="AB41" s="19" t="n">
+      <c r="W41" s="16" t="n">
         <v>8.077199999999999</v>
       </c>
-      <c r="AC41" s="19" t="n">
+      <c r="X41" s="16" t="n">
         <v>55.4833</v>
       </c>
-      <c r="AD41" s="19" t="n">
+      <c r="Y41" s="16" t="n">
         <v>56.8315</v>
       </c>
-      <c r="AE41" s="19" t="n">
+      <c r="Z41" s="16" t="n">
         <v>57.4984</v>
       </c>
-      <c r="AF41" s="19" t="n">
+      <c r="AA41" s="16" t="n">
         <v>58.7605</v>
       </c>
-      <c r="AG41" s="19" t="n">
+      <c r="AB41" s="16" t="n">
         <v>55.8865</v>
       </c>
-      <c r="AH41" s="19" t="n">
+      <c r="AC41" s="16" t="n">
         <v>56.9763</v>
       </c>
-      <c r="AI41" s="19" t="n">
+      <c r="AD41" s="16" t="n">
         <v>57.5098</v>
       </c>
-      <c r="AJ41" s="19" t="n">
+      <c r="AE41" s="16" t="n">
         <v>58.5539</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="n">
+      <c r="A42" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="19" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>Q40</t>
         </is>
       </c>
-      <c r="C42" s="19" t="inlineStr">
+      <c r="C42" s="16" t="inlineStr">
         <is>
           <t>2-phenyloxazole</t>
         </is>
       </c>
-      <c r="D42" s="19" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>C1(C2=CC=CC=C2)=NC=CO1</t>
         </is>
       </c>
-      <c r="F42" s="19" t="n">
+      <c r="F42" s="16" t="n">
         <v>62.7</v>
       </c>
-      <c r="G42" s="19" t="n">
+      <c r="G42" s="16" t="n">
         <v>18.7</v>
       </c>
-      <c r="H42" s="19" t="n">
+      <c r="H42" s="16" t="n">
         <v>19.3</v>
       </c>
-      <c r="J42" s="19" t="n">
+      <c r="J42" s="16" t="n">
         <v>144</v>
       </c>
-      <c r="K42" s="19" t="n">
+      <c r="K42" s="16" t="n">
         <v>1.82</v>
       </c>
-      <c r="L42" s="19" t="n">
+      <c r="L42" s="16" t="n">
         <v>6.5</v>
       </c>
-      <c r="M42" s="19" t="n">
+      <c r="M42" s="16" t="n">
         <v>6.5</v>
       </c>
-      <c r="O42" s="19" t="n">
+      <c r="O42" s="16" t="n">
         <v>45.7</v>
       </c>
-      <c r="P42" s="19" t="n">
+      <c r="P42" s="16" t="n">
         <v>-2.44</v>
       </c>
-      <c r="Q42" s="19" t="n">
+      <c r="Q42" s="16" t="n">
         <v>5.8</v>
       </c>
-      <c r="R42" s="19" t="n">
+      <c r="R42" s="16" t="n">
         <v>5.5</v>
       </c>
-      <c r="T42" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V42" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W42" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y42" s="19" t="n">
+      <c r="T42" s="16" t="n">
         <v>4931</v>
       </c>
-      <c r="Z42" s="19" t="n">
+      <c r="U42" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA42" s="19" t="n">
+      <c r="V42" s="16" t="n">
         <v>81.5474</v>
       </c>
-      <c r="AB42" s="19" t="n">
+      <c r="W42" s="16" t="n">
         <v>7.92414</v>
       </c>
-      <c r="AC42" s="19" t="n">
+      <c r="X42" s="16" t="n">
         <v>61.1362</v>
       </c>
-      <c r="AD42" s="19" t="n">
+      <c r="Y42" s="16" t="n">
         <v>62.4588</v>
       </c>
-      <c r="AE42" s="19" t="n">
+      <c r="Z42" s="16" t="n">
         <v>63.1131</v>
       </c>
-      <c r="AF42" s="19" t="n">
+      <c r="AA42" s="16" t="n">
         <v>64.35129999999999</v>
       </c>
-      <c r="AG42" s="19" t="n">
+      <c r="AB42" s="16" t="n">
         <v>60.9347</v>
       </c>
-      <c r="AH42" s="19" t="n">
+      <c r="AC42" s="16" t="n">
         <v>62.1676</v>
       </c>
-      <c r="AI42" s="19" t="n">
+      <c r="AD42" s="16" t="n">
         <v>62.7677</v>
       </c>
-      <c r="AJ42" s="19" t="n">
+      <c r="AE42" s="16" t="n">
         <v>63.8991</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="19" t="n">
+      <c r="A43" s="16" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>Q41</t>
         </is>
       </c>
-      <c r="C43" s="19" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>alpha-methylstyrene</t>
         </is>
       </c>
-      <c r="D43" s="19" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>C=C(C)C1=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F43" s="19" t="n">
+      <c r="F43" s="16" t="n">
         <v>51.4</v>
       </c>
-      <c r="G43" s="19" t="n">
+      <c r="G43" s="16" t="n">
         <v>85.2</v>
       </c>
-      <c r="H43" s="19" t="n">
+      <c r="H43" s="16" t="n">
         <v>33.4</v>
       </c>
-      <c r="J43" s="19" t="n">
+      <c r="J43" s="16" t="n">
         <v>141.3</v>
       </c>
-      <c r="K43" s="19" t="n">
+      <c r="K43" s="16" t="n">
         <v>1.71</v>
       </c>
-      <c r="L43" s="19" t="n">
+      <c r="L43" s="16" t="n">
         <v>5.1</v>
       </c>
-      <c r="M43" s="19" t="n">
+      <c r="M43" s="16" t="n">
         <v>6.5</v>
       </c>
-      <c r="O43" s="19" t="n">
+      <c r="O43" s="16" t="n">
         <v>39.5</v>
       </c>
-      <c r="P43" s="19" t="n">
+      <c r="P43" s="16" t="n">
         <v>-2.71</v>
       </c>
-      <c r="Q43" s="19" t="n">
+      <c r="Q43" s="16" t="n">
         <v>6.1</v>
       </c>
-      <c r="R43" s="19" t="n">
+      <c r="R43" s="16" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="T43" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W43" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y43" s="19" t="n">
+      <c r="T43" s="16" t="n">
         <v>4909</v>
       </c>
-      <c r="Z43" s="19" t="n">
+      <c r="U43" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA43" s="19" t="n">
+      <c r="V43" s="16" t="n">
         <v>83.947</v>
       </c>
-      <c r="AB43" s="19" t="n">
+      <c r="W43" s="16" t="n">
         <v>9.09854</v>
       </c>
-      <c r="AC43" s="19" t="n">
+      <c r="X43" s="16" t="n">
         <v>60.5107</v>
       </c>
-      <c r="AD43" s="19" t="n">
+      <c r="Y43" s="16" t="n">
         <v>62.0294</v>
       </c>
-      <c r="AE43" s="19" t="n">
+      <c r="Z43" s="16" t="n">
         <v>62.7806</v>
       </c>
-      <c r="AF43" s="19" t="n">
+      <c r="AA43" s="16" t="n">
         <v>64.2024</v>
       </c>
-      <c r="AG43" s="19" t="n">
+      <c r="AB43" s="16" t="n">
         <v>58.5424</v>
       </c>
-      <c r="AH43" s="19" t="n">
+      <c r="AC43" s="16" t="n">
         <v>60.0801</v>
       </c>
-      <c r="AI43" s="19" t="n">
+      <c r="AD43" s="16" t="n">
         <v>60.8688</v>
       </c>
-      <c r="AJ43" s="19" t="n">
+      <c r="AE43" s="16" t="n">
         <v>62.4435</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="19" t="n">
+      <c r="A44" s="16" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="19" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>Q42</t>
         </is>
       </c>
-      <c r="C44" s="19" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>2-benzoylfuran</t>
         </is>
       </c>
-      <c r="D44" s="19" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>O=C(C1=CC=CC=C1)C2=CC=CO2</t>
         </is>
       </c>
-      <c r="F44" s="19" t="n">
+      <c r="F44" s="16" t="n">
         <v>58.7</v>
       </c>
-      <c r="G44" s="19" t="n">
+      <c r="G44" s="16" t="n">
         <v>12.2</v>
       </c>
-      <c r="H44" s="19" t="n">
+      <c r="H44" s="16" t="n">
         <v>11.9</v>
       </c>
-      <c r="J44" s="19" t="n">
+      <c r="J44" s="16" t="n">
         <v>150.9</v>
       </c>
-      <c r="K44" s="19" t="n">
+      <c r="K44" s="16" t="n">
         <v>2.12</v>
       </c>
-      <c r="L44" s="19" t="n">
+      <c r="L44" s="16" t="n">
         <v>7.1</v>
       </c>
-      <c r="M44" s="19" t="n">
+      <c r="M44" s="16" t="n">
         <v>5.6</v>
       </c>
-      <c r="O44" s="19" t="n">
+      <c r="O44" s="16" t="n">
         <v>61.4</v>
       </c>
-      <c r="P44" s="19" t="n">
+      <c r="P44" s="16" t="n">
         <v>-1.76</v>
       </c>
-      <c r="Q44" s="19" t="n">
+      <c r="Q44" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="19" t="n">
+      <c r="R44" s="16" t="n">
         <v>6.8</v>
       </c>
-      <c r="T44" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V44" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W44" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y44" s="19" t="n">
+      <c r="T44" s="16" t="n">
         <v>4909</v>
       </c>
-      <c r="Z44" s="19" t="n">
+      <c r="U44" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA44" s="19" t="n">
+      <c r="V44" s="16" t="n">
         <v>73.0877</v>
       </c>
-      <c r="AB44" s="19" t="n">
+      <c r="W44" s="16" t="n">
         <v>6.7003</v>
       </c>
-      <c r="AC44" s="19" t="n">
+      <c r="X44" s="16" t="n">
         <v>55.8288</v>
       </c>
-      <c r="AD44" s="19" t="n">
+      <c r="Y44" s="16" t="n">
         <v>56.9472</v>
       </c>
-      <c r="AE44" s="19" t="n">
+      <c r="Z44" s="16" t="n">
         <v>57.5004</v>
       </c>
-      <c r="AF44" s="19" t="n">
+      <c r="AA44" s="16" t="n">
         <v>58.5474</v>
       </c>
-      <c r="AG44" s="19" t="n">
+      <c r="AB44" s="16" t="n">
         <v>56.2126</v>
       </c>
-      <c r="AH44" s="19" t="n">
+      <c r="AC44" s="16" t="n">
         <v>57.234</v>
       </c>
-      <c r="AI44" s="19" t="n">
+      <c r="AD44" s="16" t="n">
         <v>57.7346</v>
       </c>
-      <c r="AJ44" s="19" t="n">
+      <c r="AE44" s="16" t="n">
         <v>58.6853</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="19" t="n">
+      <c r="A45" s="16" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="19" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>Q43</t>
         </is>
       </c>
-      <c r="C45" s="19" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>2-acetyl-4-methylthiophene</t>
         </is>
       </c>
-      <c r="D45" s="19" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>O=C(C)C1=CC(C)=CS1</t>
         </is>
       </c>
-      <c r="F45" s="19" t="n">
+      <c r="F45" s="16" t="n">
         <v>58.4</v>
       </c>
-      <c r="G45" s="19" t="n">
+      <c r="G45" s="16" t="n">
         <v>11.9</v>
       </c>
-      <c r="H45" s="19" t="n">
+      <c r="H45" s="16" t="n">
         <v>12.9</v>
       </c>
-      <c r="J45" s="19" t="n">
+      <c r="J45" s="16" t="n">
         <v>147.3</v>
       </c>
-      <c r="K45" s="19" t="n">
+      <c r="K45" s="16" t="n">
         <v>1.97</v>
       </c>
-      <c r="L45" s="19" t="n">
+      <c r="L45" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="M45" s="19" t="n">
+      <c r="M45" s="16" t="n">
         <v>5.6</v>
       </c>
-      <c r="O45" s="19" t="n">
+      <c r="O45" s="16" t="n">
         <v>57.1</v>
       </c>
-      <c r="P45" s="19" t="n">
+      <c r="P45" s="16" t="n">
         <v>-1.94</v>
       </c>
-      <c r="Q45" s="19" t="n">
+      <c r="Q45" s="16" t="n">
         <v>6.9</v>
       </c>
-      <c r="R45" s="19" t="n">
+      <c r="R45" s="16" t="n">
         <v>54.6</v>
       </c>
-      <c r="T45" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W45" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y45" s="19" t="n">
+      <c r="T45" s="16" t="n">
         <v>4938</v>
       </c>
-      <c r="Z45" s="19" t="n">
+      <c r="U45" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA45" s="19" t="n">
+      <c r="V45" s="16" t="n">
         <v>74.395</v>
       </c>
-      <c r="AB45" s="19" t="n">
+      <c r="W45" s="16" t="n">
         <v>6.44363</v>
       </c>
-      <c r="AC45" s="19" t="n">
+      <c r="X45" s="16" t="n">
         <v>57.7973</v>
       </c>
-      <c r="AD45" s="19" t="n">
+      <c r="Y45" s="16" t="n">
         <v>58.8728</v>
       </c>
-      <c r="AE45" s="19" t="n">
+      <c r="Z45" s="16" t="n">
         <v>59.4049</v>
       </c>
-      <c r="AF45" s="19" t="n">
+      <c r="AA45" s="16" t="n">
         <v>60.4117</v>
       </c>
-      <c r="AG45" s="19" t="n">
+      <c r="AB45" s="16" t="n">
         <v>58.323</v>
       </c>
-      <c r="AH45" s="19" t="n">
+      <c r="AC45" s="16" t="n">
         <v>59.3275</v>
       </c>
-      <c r="AI45" s="19" t="n">
+      <c r="AD45" s="16" t="n">
         <v>59.821</v>
       </c>
-      <c r="AJ45" s="19" t="n">
+      <c r="AE45" s="16" t="n">
         <v>60.7325</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="19" t="n">
+      <c r="A46" s="16" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="19" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>Q44</t>
         </is>
       </c>
-      <c r="C46" s="19" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>2-acetylpyridine</t>
         </is>
       </c>
-      <c r="D46" s="19" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>CC(C1=NC=CC=C1)=O</t>
         </is>
       </c>
-      <c r="F46" s="19" t="n">
+      <c r="F46" s="16" t="n">
         <v>82.5</v>
       </c>
-      <c r="G46" s="19" t="n">
+      <c r="G46" s="16" t="n">
         <v>11.4</v>
       </c>
-      <c r="H46" s="19" t="n">
+      <c r="H46" s="16" t="n">
         <v>3.9</v>
       </c>
-      <c r="J46" s="19" t="n">
+      <c r="J46" s="16" t="n">
         <v>161.4</v>
       </c>
-      <c r="K46" s="19" t="n">
+      <c r="K46" s="16" t="n">
         <v>2.58</v>
       </c>
-      <c r="L46" s="19" t="n">
+      <c r="L46" s="16" t="n">
         <v>11.4</v>
       </c>
-      <c r="M46" s="19" t="n">
+      <c r="M46" s="16" t="n">
         <v>10.2</v>
       </c>
-      <c r="O46" s="19" t="n">
+      <c r="O46" s="16" t="n">
         <v>60.1</v>
       </c>
-      <c r="P46" s="19" t="n">
+      <c r="P46" s="16" t="n">
         <v>-1.81</v>
       </c>
-      <c r="Q46" s="19" t="n">
+      <c r="Q46" s="16" t="n">
         <v>7.8</v>
       </c>
-      <c r="R46" s="19" t="n">
+      <c r="R46" s="16" t="n">
         <v>7.6</v>
       </c>
-      <c r="T46" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U46" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W46" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y46" s="19" t="n">
+      <c r="T46" s="16" t="n">
         <v>4940</v>
       </c>
-      <c r="Z46" s="19" t="n">
+      <c r="U46" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA46" s="19" t="n">
+      <c r="V46" s="16" t="n">
         <v>81.16889999999999</v>
       </c>
-      <c r="AB46" s="19" t="n">
+      <c r="W46" s="16" t="n">
         <v>5.51797</v>
       </c>
-      <c r="AC46" s="19" t="n">
+      <c r="X46" s="16" t="n">
         <v>66.9555</v>
       </c>
-      <c r="AD46" s="19" t="n">
+      <c r="Y46" s="16" t="n">
         <v>67.8766</v>
       </c>
-      <c r="AE46" s="19" t="n">
+      <c r="Z46" s="16" t="n">
         <v>68.3322</v>
       </c>
-      <c r="AF46" s="19" t="n">
+      <c r="AA46" s="16" t="n">
         <v>69.1944</v>
       </c>
-      <c r="AG46" s="19" t="n">
+      <c r="AB46" s="16" t="n">
         <v>66.7513</v>
       </c>
-      <c r="AH46" s="19" t="n">
+      <c r="AC46" s="16" t="n">
         <v>67.7276</v>
       </c>
-      <c r="AI46" s="19" t="n">
+      <c r="AD46" s="16" t="n">
         <v>68.19840000000001</v>
       </c>
-      <c r="AJ46" s="19" t="n">
+      <c r="AE46" s="16" t="n">
         <v>69.0681</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="19" t="n">
+      <c r="A47" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="19" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>Q45</t>
         </is>
       </c>
-      <c r="C47" s="19" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>phenyl vinyl selenoxide</t>
         </is>
       </c>
-      <c r="D47" s="19" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>O=[Se](C=C)C1=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F47" s="19" t="n">
+      <c r="F47" s="16" t="n">
         <v>48.3</v>
       </c>
-      <c r="G47" s="19" t="n">
+      <c r="G47" s="16" t="n">
         <v>104.8</v>
       </c>
-      <c r="H47" s="19" t="n">
+      <c r="H47" s="16" t="n">
         <v>51.6</v>
       </c>
-      <c r="J47" s="19" t="n">
+      <c r="J47" s="16" t="n">
         <v>152.6</v>
       </c>
-      <c r="K47" s="19" t="n">
+      <c r="K47" s="16" t="n">
         <v>2.2</v>
       </c>
-      <c r="L47" s="19" t="n">
+      <c r="L47" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="M47" s="19" t="n">
+      <c r="M47" s="16" t="n">
         <v>4.2</v>
       </c>
-      <c r="O47" s="19" t="n">
+      <c r="O47" s="16" t="n">
         <v>46.4</v>
       </c>
-      <c r="P47" s="19" t="n">
+      <c r="P47" s="16" t="n">
         <v>-2.41</v>
       </c>
-      <c r="Q47" s="19" t="n">
+      <c r="Q47" s="16" t="n">
         <v>12.2</v>
       </c>
-      <c r="R47" s="19" t="n">
+      <c r="R47" s="16" t="n">
         <v>14.1</v>
       </c>
-      <c r="T47" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V47" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W47" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y47" s="19" t="n">
+      <c r="T47" s="16" t="n">
         <v>4890</v>
       </c>
-      <c r="Z47" s="19" t="n">
+      <c r="U47" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA47" s="19" t="n">
+      <c r="V47" s="16" t="n">
         <v>91.6985</v>
       </c>
-      <c r="AB47" s="19" t="n">
+      <c r="W47" s="16" t="n">
         <v>7.23364</v>
       </c>
-      <c r="AC47" s="19" t="n">
+      <c r="X47" s="16" t="n">
         <v>73.0658</v>
       </c>
-      <c r="AD47" s="19" t="n">
+      <c r="Y47" s="16" t="n">
         <v>74.2732</v>
       </c>
-      <c r="AE47" s="19" t="n">
+      <c r="Z47" s="16" t="n">
         <v>74.87050000000001</v>
       </c>
-      <c r="AF47" s="19" t="n">
+      <c r="AA47" s="16" t="n">
         <v>76.0008</v>
       </c>
-      <c r="AG47" s="19" t="n">
+      <c r="AB47" s="16" t="n">
         <v>71.60760000000001</v>
       </c>
-      <c r="AH47" s="19" t="n">
+      <c r="AC47" s="16" t="n">
         <v>72.9807</v>
       </c>
-      <c r="AI47" s="19" t="n">
+      <c r="AD47" s="16" t="n">
         <v>73.6249</v>
       </c>
-      <c r="AJ47" s="19" t="n">
+      <c r="AE47" s="16" t="n">
         <v>74.8154</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="19" t="n">
+      <c r="A48" s="16" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="19" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>Q46</t>
         </is>
       </c>
-      <c r="C48" s="19" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>2,2-dimethyl-3-phenyl-2H-azirine</t>
         </is>
       </c>
-      <c r="D48" s="19" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>CC1(C)C(C2=CC=CC=C2)=N1</t>
         </is>
       </c>
-      <c r="F48" s="19" t="n">
+      <c r="F48" s="16" t="n">
         <v>62.5</v>
       </c>
-      <c r="G48" s="19" t="n">
+      <c r="G48" s="16" t="n">
         <v>34.2</v>
       </c>
-      <c r="H48" s="19" t="n">
+      <c r="H48" s="16" t="n">
         <v>24.5</v>
       </c>
-      <c r="J48" s="19" t="n">
+      <c r="J48" s="16" t="n">
         <v>145.4</v>
       </c>
-      <c r="K48" s="19" t="n">
+      <c r="K48" s="16" t="n">
         <v>1.89</v>
       </c>
-      <c r="L48" s="19" t="n">
+      <c r="L48" s="16" t="n">
         <v>31.1</v>
       </c>
-      <c r="M48" s="19" t="n">
+      <c r="M48" s="16" t="n">
         <v>16.3</v>
       </c>
-      <c r="O48" s="19" t="n">
+      <c r="O48" s="16" t="n">
         <v>51.7</v>
       </c>
-      <c r="P48" s="19" t="n">
+      <c r="P48" s="16" t="n">
         <v>-2.18</v>
       </c>
-      <c r="Q48" s="19" t="n">
+      <c r="Q48" s="16" t="n">
         <v>6.1</v>
       </c>
-      <c r="R48" s="19" t="n">
+      <c r="R48" s="16" t="n">
         <v>5.8</v>
       </c>
-      <c r="T48" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U48" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V48" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W48" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y48" s="19" t="n">
+      <c r="T48" s="16" t="n">
         <v>4935</v>
       </c>
-      <c r="Z48" s="19" t="n">
+      <c r="U48" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA48" s="19" t="n">
+      <c r="V48" s="16" t="n">
         <v>82.2067</v>
       </c>
-      <c r="AB48" s="19" t="n">
+      <c r="W48" s="16" t="n">
         <v>6.96787</v>
       </c>
-      <c r="AC48" s="19" t="n">
+      <c r="X48" s="16" t="n">
         <v>64.2587</v>
       </c>
-      <c r="AD48" s="19" t="n">
+      <c r="Y48" s="16" t="n">
         <v>65.4217</v>
       </c>
-      <c r="AE48" s="19" t="n">
+      <c r="Z48" s="16" t="n">
         <v>65.9971</v>
       </c>
-      <c r="AF48" s="19" t="n">
+      <c r="AA48" s="16" t="n">
         <v>67.08580000000001</v>
       </c>
-      <c r="AG48" s="19" t="n">
+      <c r="AB48" s="16" t="n">
         <v>63.9833</v>
       </c>
-      <c r="AH48" s="19" t="n">
+      <c r="AC48" s="16" t="n">
         <v>65.07259999999999</v>
       </c>
-      <c r="AI48" s="19" t="n">
+      <c r="AD48" s="16" t="n">
         <v>65.60290000000001</v>
       </c>
-      <c r="AJ48" s="19" t="n">
+      <c r="AE48" s="16" t="n">
         <v>66.6221</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="19" t="n">
+      <c r="A49" s="16" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="19" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>Q47</t>
         </is>
       </c>
-      <c r="C49" s="19" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>methyl quinoline-8-carboxylate</t>
         </is>
       </c>
-      <c r="D49" s="19" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>O=C(C1=CC=CC2=CC=CN=C21)OC</t>
         </is>
       </c>
-      <c r="F49" s="19" t="n">
+      <c r="F49" s="16" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="G49" s="19" t="n">
+      <c r="G49" s="16" t="n">
         <v>25.7</v>
       </c>
-      <c r="H49" s="19" t="n">
+      <c r="H49" s="16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J49" s="19" t="n">
+      <c r="J49" s="16" t="n">
         <v>152.7</v>
       </c>
-      <c r="K49" s="19" t="n">
+      <c r="K49" s="16" t="n">
         <v>2.2</v>
       </c>
-      <c r="L49" s="19" t="n">
+      <c r="L49" s="16" t="n">
         <v>25.6</v>
       </c>
-      <c r="M49" s="19" t="n">
+      <c r="M49" s="16" t="n">
         <v>4.7</v>
       </c>
-      <c r="O49" s="19" t="n">
+      <c r="O49" s="16" t="n">
         <v>58.2</v>
       </c>
-      <c r="P49" s="19" t="n">
+      <c r="P49" s="16" t="n">
         <v>-1.9</v>
       </c>
-      <c r="Q49" s="19" t="n">
+      <c r="Q49" s="16" t="n">
         <v>7.8</v>
       </c>
-      <c r="R49" s="19" t="n">
+      <c r="R49" s="16" t="n">
         <v>7.9</v>
       </c>
-      <c r="T49" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U49" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V49" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W49" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y49" s="19" t="n">
+      <c r="T49" s="16" t="n">
         <v>4934</v>
       </c>
-      <c r="Z49" s="19" t="n">
+      <c r="U49" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA49" s="19" t="n">
+      <c r="V49" s="16" t="n">
         <v>75.6027</v>
       </c>
-      <c r="AB49" s="19" t="n">
+      <c r="W49" s="16" t="n">
         <v>7.06523</v>
       </c>
-      <c r="AC49" s="19" t="n">
+      <c r="X49" s="16" t="n">
         <v>57.4038</v>
       </c>
-      <c r="AD49" s="19" t="n">
+      <c r="Y49" s="16" t="n">
         <v>58.5831</v>
       </c>
-      <c r="AE49" s="19" t="n">
+      <c r="Z49" s="16" t="n">
         <v>59.1665</v>
       </c>
-      <c r="AF49" s="19" t="n">
+      <c r="AA49" s="16" t="n">
         <v>60.2705</v>
       </c>
-      <c r="AG49" s="19" t="n">
+      <c r="AB49" s="16" t="n">
         <v>57.5788</v>
       </c>
-      <c r="AH49" s="19" t="n">
+      <c r="AC49" s="16" t="n">
         <v>58.7068</v>
       </c>
-      <c r="AI49" s="19" t="n">
+      <c r="AD49" s="16" t="n">
         <v>59.2283</v>
       </c>
-      <c r="AJ49" s="19" t="n">
+      <c r="AE49" s="16" t="n">
         <v>60.1915</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="19" t="n">
+      <c r="A50" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="19" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>Q48</t>
         </is>
       </c>
-      <c r="C50" s="19" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>cyclohex-2-en-1-one</t>
         </is>
       </c>
-      <c r="D50" s="19" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>O=C1C=CCCC1</t>
         </is>
       </c>
-      <c r="F50" s="19" t="n">
+      <c r="F50" s="16" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="G50" s="19" t="n">
+      <c r="G50" s="16" t="n">
         <v>10.4</v>
       </c>
-      <c r="H50" s="19" t="n">
+      <c r="H50" s="16" t="n">
         <v>7.5</v>
       </c>
-      <c r="J50" s="19" t="n">
+      <c r="J50" s="16" t="n">
         <v>158.9</v>
       </c>
-      <c r="K50" s="19" t="n">
+      <c r="K50" s="16" t="n">
         <v>2.47</v>
       </c>
-      <c r="L50" s="19" t="n">
+      <c r="L50" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="M50" s="19" t="n">
+      <c r="M50" s="16" t="n">
         <v>2.5</v>
       </c>
-      <c r="O50" s="19" t="n">
+      <c r="O50" s="16" t="n">
         <v>51.9</v>
       </c>
-      <c r="P50" s="19" t="n">
+      <c r="P50" s="16" t="n">
         <v>-2.17</v>
       </c>
-      <c r="Q50" s="19" t="n">
+      <c r="Q50" s="16" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="R50" s="19" t="n">
+      <c r="R50" s="16" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="T50" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U50" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V50" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W50" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y50" s="19" t="n">
+      <c r="T50" s="16" t="n">
         <v>4959</v>
       </c>
-      <c r="Z50" s="19" t="n">
+      <c r="U50" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="AA50" s="19" t="n">
+      <c r="V50" s="16" t="n">
         <v>79.7657</v>
       </c>
-      <c r="AB50" s="19" t="n">
+      <c r="W50" s="16" t="n">
         <v>5.2649</v>
       </c>
-      <c r="AC50" s="19" t="n">
+      <c r="X50" s="16" t="n">
         <v>66.2042</v>
       </c>
-      <c r="AD50" s="19" t="n">
+      <c r="Y50" s="16" t="n">
         <v>67.083</v>
       </c>
-      <c r="AE50" s="19" t="n">
+      <c r="Z50" s="16" t="n">
         <v>67.5177</v>
       </c>
-      <c r="AF50" s="19" t="n">
+      <c r="AA50" s="16" t="n">
         <v>68.3404</v>
       </c>
-      <c r="AG50" s="19" t="n">
+      <c r="AB50" s="16" t="n">
         <v>64.3464</v>
       </c>
-      <c r="AH50" s="19" t="n">
+      <c r="AC50" s="16" t="n">
         <v>65.5279</v>
       </c>
-      <c r="AI50" s="19" t="n">
+      <c r="AD50" s="16" t="n">
         <v>66.1712</v>
       </c>
-      <c r="AJ50" s="19" t="n">
+      <c r="AE50" s="16" t="n">
         <v>67.4205</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="T1:AE1"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="Y1:AJ1"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="O1:R1"/>
-    <mergeCell ref="T1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5614,7 +4992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5625,890 +5003,798 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Block</t>
         </is>
       </c>
-      <c r="B1" s="20" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="20" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D1" s="20" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E1" s="20" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>Taken from</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>quencher_id</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr"/>
-      <c r="D2" s="22" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr"/>
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>Quencher number.</t>
         </is>
       </c>
-      <c r="E2" s="21" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: quencher_id</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>quencher_name</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr"/>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr"/>
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Label used throughout, Q&lt;n&gt;.</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
-        <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: quencher_name</t>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>compound_identification.xlsx: Quenchers/quencher_id</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>compound</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr"/>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr"/>
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>Name derived from the SMILES, as in the experimental workbook.</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: name</t>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>compound_identification.xlsx: Quenchers/name</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>smiles</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr"/>
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Structure.</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>experimental_data_raw/compound_records/compound_records_quenchers.csv: smiles</t>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>compound_identification.xlsx: Quenchers/smiles</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Triplet state, adiabatic DFT / kcal mol-1</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>E_T / kcal mol-1</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Adiabatic triplet energy, Gibbs-corrected, lowest conformer of each state.</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: E_T</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Triplet state, adiabatic DFT / kcal mol-1</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>lambda_S_T / kcal mol-1</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Singlet surface: E_S0 at the T1 geometry minus E_S0 at the S0 geometry.</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S_T</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Triplet state, adiabatic DFT / kcal mol-1</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>lambda_T_S / kcal mol-1</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Triplet surface: E_T1 at the S0 geometry minus E_T1 at the T1 geometry.</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_T_S</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Oxidation, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>dG_Ox / kcal mol-1</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Free energy of Q -&gt; Q+.</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: dG_Ox</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Oxidation, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>E_Ox_vs_SCE_calc / V</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>dG_Ox / F - 4.42 V.</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: E_Ox_vs_SCE_calc</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Oxidation, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>lambda_S0_D+ / kcal mol-1</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Neutral surface: E_S0 at the cation geometry minus E_S0.</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S0_D+</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Oxidation, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>lambda_D+_S0 / kcal mol-1</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>Cation surface: E_cation at the S0 geometry minus E_cation.</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_D+_S0</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Reduction, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>dG_Red / kcal mol-1</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Free energy released by Q -&gt; Q-.</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: dG_Red</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Reduction, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>E_Red_vs_SCE_calc / V</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>dG_Red / F - 4.42 V.</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: E_Red_vs_SCE_calc</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Reduction, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>lambda_S0_D- / kcal mol-1</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Neutral surface: E_S0 at the anion geometry minus E_S0.</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S0_D-</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Reduction, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>lambda_D-_S0 / kcal mol-1</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>Anion surface: E_anion at the S0 geometry minus E_anion.</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_D-_S0</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>Conformers</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>n_conformers_S0</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr"/>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>Conformers computed for S0; the lowest in energy is used.</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: n_conformers_S0</t>
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>n_samples</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr"/>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Sampled geometries with both single points.</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: n_samples</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>Conformers</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>n_conformers_T1</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr"/>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>Conformers computed for T1; the lowest in energy is used.</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: n_conformers_T1</t>
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>n_trajectories</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr"/>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>MD trajectories sampled.</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: n_trajectories</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>Conformers</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>n_conformers_ox</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr"/>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>Conformers computed for ox; the lowest in energy is used.</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: n_conformers_ox</t>
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>dvte_mu / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>kcal mol-1</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Mean vertical singlet-triplet gap.</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_mu</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>Conformers</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>n_conformers_red</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr"/>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>Conformers computed for red; the lowest in energy is used.</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: n_conformers_red</t>
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>dvte_std / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>kcal mol-1</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Standard deviation of the gaps.</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_std</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>n_samples</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr"/>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>Sampled geometries with both single points.</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: n_samples</t>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>dvte_0.005 / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>kcal mol-1</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>0.005 quantile of a normal distribution with that mean and deviation.</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.005</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>n_trajectories</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr"/>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>MD trajectories sampled.</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: n_trajectories</t>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>dvte_0.008 / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>kcal mol-1</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>0.008 quantile of a normal distribution with that mean and deviation.</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.008</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>dvte_mu / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>dvte_0.01 / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>Mean vertical singlet-triplet gap.</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_mu</t>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>0.01 quantile of a normal distribution with that mean and deviation.</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.01</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>dvte_std / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>dvte_0.015 / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>Standard deviation of the gaps.</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_std</t>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>0.015 quantile of a normal distribution with that mean and deviation.</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.015</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>dvte_0.005 / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>dvte_0.005_kde / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>0.005 quantile of a normal distribution with that mean and deviation.</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.005</t>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>0.005 quantile of a kernel density estimate of the samples (Scott's rule).</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.005_kde</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>dvte_0.008 / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>dvte_0.008_kde / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
-        <is>
-          <t>0.008 quantile of a normal distribution with that mean and deviation.</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.008</t>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>0.008 quantile of a kernel density estimate of the samples (Scott's rule).</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.008_kde</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>dvte_0.01 / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>dvte_0.01_kde / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>0.01 quantile of a normal distribution with that mean and deviation.</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.01</t>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>0.01 quantile of a kernel density estimate of the samples (Scott's rule).</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.01_kde</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>dvte_0.015 / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>dvte_0.015_kde / kcal mol-1</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>0.015 quantile of a normal distribution with that mean and deviation.</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.015</t>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>0.015 quantile of a kernel density estimate of the samples (Scott's rule).</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.015_kde</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
-        <is>
-          <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="B29" s="21" t="inlineStr">
-        <is>
-          <t>dvte_0.005_kde / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>kcal mol-1</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="inlineStr">
-        <is>
-          <t>0.005 quantile of a kernel density estimate of the samples (Scott's rule).</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.005_kde</t>
-        </is>
-      </c>
+      <c r="A29" s="18" t="n"/>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="18" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>dvte_0.008_kde / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>kcal mol-1</t>
-        </is>
-      </c>
-      <c r="D30" s="22" t="inlineStr">
-        <is>
-          <t>0.008 quantile of a kernel density estimate of the samples (Scott's rule).</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.008_kde</t>
-        </is>
-      </c>
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>One row per quencher. Roundings are the original pipeline's: 1 decimal in kcal/mol,</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="18" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
-        <is>
-          <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
-        <is>
-          <t>dvte_0.01_kde / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>kcal mol-1</t>
-        </is>
-      </c>
-      <c r="D31" s="22" t="inlineStr">
-        <is>
-          <t>0.01 quantile of a kernel density estimate of the samples (Scott's rule).</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.01_kde</t>
-        </is>
-      </c>
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>2 in V. The energies behind each value are in the deposited ORCA outputs under</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="18" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="inlineStr">
-        <is>
-          <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="B32" s="21" t="inlineStr">
-        <is>
-          <t>dvte_0.015_kde / kcal mol-1</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>kcal mol-1</t>
-        </is>
-      </c>
-      <c r="D32" s="22" t="inlineStr">
-        <is>
-          <t>0.015 quantile of a kernel density estimate of the samples (Scott's rule).</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.015_kde</t>
-        </is>
-      </c>
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DFT/Q&lt;n&gt;/&lt;state&gt;/, and every sampled gap in</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="18" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="n"/>
-      <c r="B33" s="21" t="n"/>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="22" t="n"/>
-      <c r="E33" s="21" t="n"/>
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte_samples.csv.gz.</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="18" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>One row per quencher. Roundings are the original pipeline's: 1 decimal in kcal/mol,</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="n"/>
-      <c r="C34" s="21" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="21" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="21" t="inlineStr">
-        <is>
-          <t>2 in V. Per-conformer energies are in</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="n"/>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="21" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft_conformers.csv, and every</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="n"/>
-      <c r="C36" s="21" t="n"/>
-      <c r="D36" s="22" t="n"/>
-      <c r="E36" s="21" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="21" t="inlineStr">
-        <is>
-          <t>sampled gap in computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte_samples.csv.gz.</t>
-        </is>
-      </c>
-      <c r="B37" s="21" t="n"/>
-      <c r="C37" s="21" t="n"/>
-      <c r="D37" s="22" t="n"/>
-      <c r="E37" s="21" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>Read with pandas as: pd.read_excel(path, header=1), then drop the 'Unnamed' columns.</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n"/>
-      <c r="C38" s="21" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="21" t="n"/>
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="19" t="n"/>
+      <c r="E34" s="18" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/computational_data_processed/quencher_properties_calc.xlsx
+++ b/data/computational_data_processed/quencher_properties_calc.xlsx
@@ -505,18 +505,18 @@
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="2" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="27" customWidth="1" min="12" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
     <col width="2" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="27" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="31" customWidth="1" min="17" max="17"/>
+    <col width="31" customWidth="1" min="18" max="18"/>
     <col width="2" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
@@ -609,12 +609,12 @@
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
-          <t>lambda_S_T / kcal mol-1</t>
+          <t>lambda_S0_T1 / kcal mol-1</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>lambda_T_S / kcal mol-1</t>
+          <t>lambda_T1_S0 / kcal mol-1</t>
         </is>
       </c>
       <c r="J2" s="13" t="inlineStr">
@@ -629,12 +629,12 @@
       </c>
       <c r="L2" s="13" t="inlineStr">
         <is>
-          <t>lambda_S0_D+ / kcal mol-1</t>
+          <t>lambda_S0_Dplus / kcal mol-1</t>
         </is>
       </c>
       <c r="M2" s="13" t="inlineStr">
         <is>
-          <t>lambda_D+_S0 / kcal mol-1</t>
+          <t>lambda_Dplus_S0 / kcal mol-1</t>
         </is>
       </c>
       <c r="O2" s="14" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="Q2" s="14" t="inlineStr">
         <is>
-          <t>lambda_S0_D- / kcal mol-1</t>
+          <t>lambda_S0_Dminus / kcal mol-1</t>
         </is>
       </c>
       <c r="R2" s="14" t="inlineStr">
         <is>
-          <t>lambda_D-_S0 / kcal mol-1</t>
+          <t>lambda_Dminus_S0 / kcal mol-1</t>
         </is>
       </c>
       <c r="T2" s="15" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>lambda_S_T / kcal mol-1</t>
+          <t>lambda_S0_T1 / kcal mol-1</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>Singlet surface: E_S0 at the T1 geometry minus E_S0 at the S0 geometry.</t>
+          <t>S0 surface: E_S0 at the T1 geometry minus E_S0 at its own.</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S_T</t>
+          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S0_T1</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>lambda_T_S / kcal mol-1</t>
+          <t>lambda_T1_S0 / kcal mol-1</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>Triplet surface: E_T1 at the S0 geometry minus E_T1 at the T1 geometry.</t>
+          <t>T1 surface: E_T1 at the S0 geometry minus E_T1 at its own.</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_T_S</t>
+          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_T1_S0</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>lambda_S0_D+ / kcal mol-1</t>
+          <t>lambda_S0_Dplus / kcal mol-1</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>Neutral surface: E_S0 at the cation geometry minus E_S0.</t>
+          <t>S0 surface: E_S0 at the Dplus (radical cation) geometry minus E_S0 at its own.</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S0_D+</t>
+          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S0_Dplus</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>lambda_D+_S0 / kcal mol-1</t>
+          <t>lambda_Dplus_S0 / kcal mol-1</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>Cation surface: E_cation at the S0 geometry minus E_cation.</t>
+          <t>Dplus surface: E_Dplus at the S0 geometry minus E_Dplus at its own.</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_D+_S0</t>
+          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_Dplus_S0</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>lambda_S0_D- / kcal mol-1</t>
+          <t>lambda_S0_Dminus / kcal mol-1</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>Neutral surface: E_S0 at the anion geometry minus E_S0.</t>
+          <t>S0 surface: E_S0 at the Dminus (radical anion) geometry minus E_S0 at its own.</t>
         </is>
       </c>
       <c r="E15" s="18" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S0_D-</t>
+          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S0_Dminus</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>lambda_D-_S0 / kcal mol-1</t>
+          <t>lambda_Dminus_S0 / kcal mol-1</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>Anion surface: E_anion at the S0 geometry minus E_anion.</t>
+          <t>Dminus surface: E_Dminus at the S0 geometry minus E_Dminus at its own.</t>
         </is>
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_D-_S0</t>
+          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_Dminus_S0</t>
         </is>
       </c>
     </row>

--- a/data/computational_data_processed/quencher_properties_calc.xlsx
+++ b/data/computational_data_processed/quencher_properties_calc.xlsx
@@ -5744,7 +5744,7 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>One row per quencher. Roundings are the original pipeline's: 1 decimal in kcal/mol,</t>
+          <t>One row per quencher. DFT values are rounded to 1 decimal in kcal/mol and 2 in V.</t>
         </is>
       </c>
       <c r="B30" s="18" t="n"/>
@@ -5755,7 +5755,7 @@
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>2 in V. The energies behind each value are in the deposited ORCA outputs under</t>
+          <t>The energies behind each value are in the deposited ORCA outputs under</t>
         </is>
       </c>
       <c r="B31" s="18" t="n"/>

--- a/data/computational_data_processed/quencher_properties_calc.xlsx
+++ b/data/computational_data_processed/quencher_properties_calc.xlsx
@@ -738,37 +738,37 @@
         </is>
       </c>
       <c r="F3" s="16" t="n">
-        <v>60.2</v>
+        <v>60.18</v>
       </c>
       <c r="G3" s="16" t="n">
-        <v>14.4</v>
+        <v>14.37</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>15.8</v>
+        <v>15.81</v>
       </c>
       <c r="J3" s="16" t="n">
-        <v>144.5</v>
+        <v>144.48</v>
       </c>
       <c r="K3" s="16" t="n">
         <v>1.85</v>
       </c>
       <c r="L3" s="16" t="n">
-        <v>4.5</v>
+        <v>4.51</v>
       </c>
       <c r="M3" s="16" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="O3" s="16" t="n">
-        <v>49.9</v>
+        <v>49.93</v>
       </c>
       <c r="P3" s="16" t="n">
-        <v>-2.26</v>
+        <v>-2.25</v>
       </c>
       <c r="Q3" s="16" t="n">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
       <c r="R3" s="16" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="T3" s="16" t="n">
         <v>4865</v>
@@ -777,34 +777,34 @@
         <v>25</v>
       </c>
       <c r="V3" s="16" t="n">
-        <v>76.1883</v>
+        <v>76.19</v>
       </c>
       <c r="W3" s="16" t="n">
-        <v>7.14234</v>
+        <v>7.14</v>
       </c>
       <c r="X3" s="16" t="n">
-        <v>57.7909</v>
+        <v>57.79</v>
       </c>
       <c r="Y3" s="16" t="n">
-        <v>58.983</v>
+        <v>58.98</v>
       </c>
       <c r="Z3" s="16" t="n">
-        <v>59.5727</v>
+        <v>59.57</v>
       </c>
       <c r="AA3" s="16" t="n">
-        <v>60.6888</v>
+        <v>60.69</v>
       </c>
       <c r="AB3" s="16" t="n">
-        <v>56.925</v>
+        <v>56.93</v>
       </c>
       <c r="AC3" s="16" t="n">
-        <v>58.1419</v>
+        <v>58.14</v>
       </c>
       <c r="AD3" s="16" t="n">
-        <v>58.7237</v>
+        <v>58.72</v>
       </c>
       <c r="AE3" s="16" t="n">
-        <v>59.848</v>
+        <v>59.85</v>
       </c>
     </row>
     <row r="4">
@@ -827,16 +827,16 @@
         </is>
       </c>
       <c r="F4" s="16" t="n">
-        <v>52.2</v>
+        <v>52.17</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>86</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>26.7</v>
+        <v>26.65</v>
       </c>
       <c r="J4" s="16" t="n">
-        <v>142.9</v>
+        <v>142.92</v>
       </c>
       <c r="K4" s="16" t="n">
         <v>1.78</v>
@@ -845,19 +845,19 @@
         <v>4.4</v>
       </c>
       <c r="M4" s="16" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="O4" s="16" t="n">
-        <v>41.4</v>
+        <v>41.41</v>
       </c>
       <c r="P4" s="16" t="n">
         <v>-2.62</v>
       </c>
       <c r="Q4" s="16" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="R4" s="16" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="T4" s="16" t="n">
         <v>4877</v>
@@ -866,34 +866,34 @@
         <v>25</v>
       </c>
       <c r="V4" s="16" t="n">
-        <v>81.3467</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="W4" s="16" t="n">
-        <v>9.08047</v>
+        <v>9.08</v>
       </c>
       <c r="X4" s="16" t="n">
-        <v>57.957</v>
+        <v>57.96</v>
       </c>
       <c r="Y4" s="16" t="n">
-        <v>59.4726</v>
+        <v>59.47</v>
       </c>
       <c r="Z4" s="16" t="n">
-        <v>60.2224</v>
+        <v>60.22</v>
       </c>
       <c r="AA4" s="16" t="n">
-        <v>61.6413</v>
+        <v>61.64</v>
       </c>
       <c r="AB4" s="16" t="n">
-        <v>56.8652</v>
+        <v>56.87</v>
       </c>
       <c r="AC4" s="16" t="n">
-        <v>58.3881</v>
+        <v>58.39</v>
       </c>
       <c r="AD4" s="16" t="n">
-        <v>59.0995</v>
+        <v>59.1</v>
       </c>
       <c r="AE4" s="16" t="n">
-        <v>60.3927</v>
+        <v>60.39</v>
       </c>
     </row>
     <row r="5">
@@ -919,10 +919,10 @@
         <v>60.8</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>32.3</v>
+        <v>32.35</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>17.4</v>
+        <v>17.39</v>
       </c>
       <c r="J5" s="16" t="n">
         <v>155.5</v>
@@ -931,22 +931,22 @@
         <v>2.32</v>
       </c>
       <c r="L5" s="16" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="M5" s="16" t="n">
         <v>11</v>
       </c>
       <c r="O5" s="16" t="n">
-        <v>73</v>
+        <v>73.03</v>
       </c>
       <c r="P5" s="16" t="n">
         <v>-1.25</v>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>12.9</v>
+        <v>12.85</v>
       </c>
       <c r="R5" s="16" t="n">
-        <v>11.4</v>
+        <v>11.38</v>
       </c>
       <c r="T5" s="16" t="n">
         <v>4876</v>
@@ -955,34 +955,34 @@
         <v>25</v>
       </c>
       <c r="V5" s="16" t="n">
-        <v>78.8339</v>
+        <v>78.83</v>
       </c>
       <c r="W5" s="16" t="n">
-        <v>7.00378</v>
+        <v>7</v>
       </c>
       <c r="X5" s="16" t="n">
-        <v>60.7934</v>
+        <v>60.79</v>
       </c>
       <c r="Y5" s="16" t="n">
-        <v>61.9624</v>
+        <v>61.96</v>
       </c>
       <c r="Z5" s="16" t="n">
-        <v>62.5407</v>
+        <v>62.54</v>
       </c>
       <c r="AA5" s="16" t="n">
-        <v>63.6351</v>
+        <v>63.64</v>
       </c>
       <c r="AB5" s="16" t="n">
-        <v>61.1571</v>
+        <v>61.16</v>
       </c>
       <c r="AC5" s="16" t="n">
-        <v>62.1824</v>
+        <v>62.18</v>
       </c>
       <c r="AD5" s="16" t="n">
-        <v>62.7172</v>
+        <v>62.72</v>
       </c>
       <c r="AE5" s="16" t="n">
-        <v>63.7767</v>
+        <v>63.78</v>
       </c>
     </row>
     <row r="6">
@@ -1005,34 +1005,34 @@
         </is>
       </c>
       <c r="F6" s="16" t="n">
-        <v>67.8</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>19.7</v>
+        <v>19.69</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>15.9</v>
+        <v>15.87</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>139.5</v>
+        <v>139.46</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>1.63</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>35.4</v>
+        <v>35.44</v>
       </c>
       <c r="P6" s="16" t="n">
         <v>-2.88</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="R6" s="16" t="n">
         <v>4.7</v>
@@ -1044,34 +1044,34 @@
         <v>25</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>83.5459</v>
+        <v>83.55</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>6.65662</v>
+        <v>6.66</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>66.39960000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>67.5107</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="Z6" s="16" t="n">
-        <v>68.0603</v>
+        <v>68.06</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>69.1005</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>65.50749999999999</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>66.64100000000001</v>
+        <v>66.64</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>67.2462</v>
+        <v>67.25</v>
       </c>
       <c r="AE6" s="16" t="n">
-        <v>68.4359</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="7">
@@ -1094,34 +1094,34 @@
         </is>
       </c>
       <c r="F7" s="16" t="n">
-        <v>58.6</v>
+        <v>58.57</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>14.1</v>
+        <v>14.06</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>14.3</v>
+        <v>14.33</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>158.8</v>
+        <v>155.3</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>10.1</v>
+        <v>3.49</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>-1.8</v>
+        <v>3.49</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>63.9</v>
+        <v>63.87</v>
       </c>
       <c r="P7" s="16" t="n">
         <v>-1.65</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="R7" s="16" t="n">
         <v>4.7</v>
@@ -1133,34 +1133,34 @@
         <v>25</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>72.5236</v>
+        <v>72.52</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>5.90317</v>
+        <v>5.9</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>57.3181</v>
+        <v>57.32</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>58.3034</v>
+        <v>58.3</v>
       </c>
       <c r="Z7" s="16" t="n">
-        <v>58.7908</v>
+        <v>58.79</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>59.7132</v>
+        <v>59.71</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>55.6201</v>
+        <v>55.62</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>56.6554</v>
+        <v>56.66</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>57.2407</v>
+        <v>57.24</v>
       </c>
       <c r="AE7" s="16" t="n">
-        <v>58.4453</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="8">
@@ -1183,37 +1183,37 @@
         </is>
       </c>
       <c r="F8" s="16" t="n">
-        <v>60.1</v>
+        <v>60.09</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>14.3</v>
+        <v>14.27</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>14.5</v>
+        <v>14.49</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>145.5</v>
+        <v>145.54</v>
       </c>
       <c r="K8" s="16" t="n">
         <v>1.89</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="M8" s="16" t="n">
         <v>3.5</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>49.6</v>
+        <v>49.56</v>
       </c>
       <c r="P8" s="16" t="n">
         <v>-2.27</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
       <c r="R8" s="16" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="T8" s="16" t="n">
         <v>4939</v>
@@ -1222,34 +1222,34 @@
         <v>25</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>75.4422</v>
+        <v>75.44</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>7.31194</v>
+        <v>7.31</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>56.6079</v>
+        <v>56.61</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>57.8284</v>
+        <v>57.83</v>
       </c>
       <c r="Z8" s="16" t="n">
-        <v>58.4321</v>
+        <v>58.43</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>59.5746</v>
+        <v>59.57</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>56.8972</v>
+        <v>56.9</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>57.944</v>
+        <v>57.94</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>58.4797</v>
+        <v>58.48</v>
       </c>
       <c r="AE8" s="16" t="n">
-        <v>59.516</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="9">
@@ -1272,37 +1272,37 @@
         </is>
       </c>
       <c r="F9" s="16" t="n">
-        <v>60</v>
+        <v>60.01</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>12.4</v>
+        <v>12.42</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>12.7</v>
+        <v>12.66</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>151.3</v>
+        <v>151.33</v>
       </c>
       <c r="K9" s="16" t="n">
         <v>2.14</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="M9" s="16" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>60.3</v>
+        <v>60.27</v>
       </c>
       <c r="P9" s="16" t="n">
         <v>-1.81</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>6.7</v>
+        <v>6.72</v>
       </c>
       <c r="R9" s="16" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
       <c r="T9" s="16" t="n">
         <v>4941</v>
@@ -1311,34 +1311,34 @@
         <v>25</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>75.5534</v>
+        <v>75.55</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>7.38718</v>
+        <v>7.39</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>56.5252</v>
+        <v>56.53</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>57.7583</v>
+        <v>57.76</v>
       </c>
       <c r="Z9" s="16" t="n">
-        <v>58.3682</v>
+        <v>58.37</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>59.5225</v>
+        <v>59.52</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>55.4952</v>
+        <v>55.5</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>56.8322</v>
+        <v>56.83</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>57.4607</v>
+        <v>57.46</v>
       </c>
       <c r="AE9" s="16" t="n">
-        <v>58.6718</v>
+        <v>58.67</v>
       </c>
     </row>
     <row r="10">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="F10" s="16" t="n">
-        <v>51.8</v>
+        <v>51.79</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>53.7</v>
+        <v>53.72</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>36</v>
+        <v>36.05</v>
       </c>
       <c r="J10" s="16" t="n">
         <v>158.2</v>
@@ -1376,22 +1376,22 @@
         <v>2.44</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>24.4</v>
+        <v>24.37</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>5.9</v>
+        <v>5.93</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>54.8</v>
+        <v>54.84</v>
       </c>
       <c r="P10" s="16" t="n">
         <v>-2.04</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>11.3</v>
+        <v>11.34</v>
       </c>
       <c r="R10" s="16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="T10" s="16" t="n">
         <v>4744</v>
@@ -1400,34 +1400,34 @@
         <v>25</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>82.666</v>
+        <v>82.67</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>7.10289</v>
+        <v>7.1</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>64.3702</v>
+        <v>64.37</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>65.5557</v>
+        <v>65.56</v>
       </c>
       <c r="Z10" s="16" t="n">
-        <v>66.1422</v>
+        <v>66.14</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>67.2521</v>
+        <v>67.25</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>62.7799</v>
+        <v>62.78</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>64.2259</v>
+        <v>64.23</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>64.9298</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="AE10" s="16" t="n">
-        <v>66.26519999999999</v>
+        <v>66.27</v>
       </c>
     </row>
     <row r="11">
@@ -1453,34 +1453,34 @@
         <v>58.5</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>16.9</v>
+        <v>16.91</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>21.7</v>
+        <v>21.67</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>134.8</v>
+        <v>134.82</v>
       </c>
       <c r="K11" s="16" t="n">
         <v>1.43</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>6.9</v>
+        <v>6.87</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>39.1</v>
+        <v>39.09</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>-2.72</v>
+        <v>-2.73</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>7.4</v>
+        <v>7.41</v>
       </c>
       <c r="R11" s="16" t="n">
-        <v>10.6</v>
+        <v>10.61</v>
       </c>
       <c r="T11" s="16" t="n">
         <v>4907</v>
@@ -1489,34 +1489,34 @@
         <v>25</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>82.15179999999999</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>7.57912</v>
+        <v>7.58</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>62.6292</v>
+        <v>62.63</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>63.8943</v>
+        <v>63.89</v>
       </c>
       <c r="Z11" s="16" t="n">
-        <v>64.5201</v>
+        <v>64.52</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>65.70440000000001</v>
+        <v>65.7</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>61.6092</v>
+        <v>61.61</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>62.9839</v>
+        <v>62.98</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>63.6924</v>
+        <v>63.69</v>
       </c>
       <c r="AE11" s="16" t="n">
-        <v>65.0989</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1539,25 +1539,25 @@
         </is>
       </c>
       <c r="F12" s="16" t="n">
-        <v>40.3</v>
+        <v>40.29</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>77.59999999999999</v>
+        <v>77.58</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>42.6</v>
+        <v>42.55</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>137.6</v>
+        <v>137.58</v>
       </c>
       <c r="K12" s="16" t="n">
         <v>1.55</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>10.5</v>
+        <v>10.52</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>16.6</v>
+        <v>16.62</v>
       </c>
       <c r="O12" s="16" t="n"/>
       <c r="P12" s="16" t="n"/>
@@ -1570,34 +1570,34 @@
         <v>25</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>82.056</v>
+        <v>82.06</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>7.97085</v>
+        <v>7.97</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>61.5245</v>
+        <v>61.52</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>62.8549</v>
+        <v>62.85</v>
       </c>
       <c r="Z12" s="16" t="n">
-        <v>63.513</v>
+        <v>63.51</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>64.7585</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>57.9689</v>
+        <v>57.97</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>59.6312</v>
+        <v>59.63</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>60.491</v>
+        <v>60.49</v>
       </c>
       <c r="AE12" s="16" t="n">
-        <v>62.1933</v>
+        <v>62.19</v>
       </c>
     </row>
     <row r="13">
@@ -1620,22 +1620,22 @@
         </is>
       </c>
       <c r="F13" s="16" t="n">
-        <v>56.6</v>
+        <v>56.63</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>45.5</v>
+        <v>45.54</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>45.1</v>
+        <v>45.14</v>
       </c>
       <c r="J13" s="16" t="n">
-        <v>136.7</v>
+        <v>136.72</v>
       </c>
       <c r="K13" s="16" t="n">
         <v>1.51</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>9.300000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="M13" s="16" t="n">
         <v>18</v>
@@ -1651,34 +1651,34 @@
         <v>25</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>87.7253</v>
+        <v>87.73</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>6.79933</v>
+        <v>6.8</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>70.2114</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>71.3463</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="Z13" s="16" t="n">
-        <v>71.90770000000001</v>
+        <v>71.91</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>72.97020000000001</v>
+        <v>72.97</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>70.2144</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>71.40779999999999</v>
+        <v>71.41</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>71.9838</v>
+        <v>71.98</v>
       </c>
       <c r="AE13" s="16" t="n">
-        <v>73.0975</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1701,25 +1701,25 @@
         </is>
       </c>
       <c r="F14" s="16" t="n">
-        <v>66.40000000000001</v>
+        <v>66.41</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>13.5</v>
+        <v>13.52</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>13.1</v>
+        <v>13.12</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>140.9</v>
+        <v>140.94</v>
       </c>
       <c r="K14" s="16" t="n">
         <v>1.69</v>
       </c>
       <c r="L14" s="16" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="M14" s="16" t="n">
-        <v>4.6</v>
+        <v>4.57</v>
       </c>
       <c r="O14" s="16" t="n">
         <v>44.5</v>
@@ -1728,7 +1728,7 @@
         <v>-2.49</v>
       </c>
       <c r="Q14" s="16" t="n">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="R14" s="16" t="n">
         <v>4.7</v>
@@ -1740,34 +1740,34 @@
         <v>25</v>
       </c>
       <c r="V14" s="16" t="n">
-        <v>79.16759999999999</v>
+        <v>79.17</v>
       </c>
       <c r="W14" s="16" t="n">
-        <v>6.45295</v>
+        <v>6.45</v>
       </c>
       <c r="X14" s="16" t="n">
-        <v>62.5459</v>
+        <v>62.55</v>
       </c>
       <c r="Y14" s="16" t="n">
-        <v>63.623</v>
+        <v>63.62</v>
       </c>
       <c r="Z14" s="16" t="n">
-        <v>64.1558</v>
+        <v>64.16</v>
       </c>
       <c r="AA14" s="16" t="n">
-        <v>65.1641</v>
+        <v>65.16</v>
       </c>
       <c r="AB14" s="16" t="n">
-        <v>60.1854</v>
+        <v>60.19</v>
       </c>
       <c r="AC14" s="16" t="n">
-        <v>61.4605</v>
+        <v>61.46</v>
       </c>
       <c r="AD14" s="16" t="n">
-        <v>62.1007</v>
+        <v>62.1</v>
       </c>
       <c r="AE14" s="16" t="n">
-        <v>63.3326</v>
+        <v>63.33</v>
       </c>
     </row>
     <row r="15">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="F15" s="16" t="n">
-        <v>56.7</v>
+        <v>56.74</v>
       </c>
       <c r="G15" s="16" t="n">
-        <v>18.9</v>
+        <v>18.89</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>18.2</v>
+        <v>18.15</v>
       </c>
       <c r="J15" s="16" t="n">
-        <v>172.2</v>
+        <v>172.16</v>
       </c>
       <c r="K15" s="16" t="n">
         <v>3.05</v>
@@ -1808,19 +1808,19 @@
         <v>8.9</v>
       </c>
       <c r="M15" s="16" t="n">
-        <v>6.9</v>
+        <v>6.92</v>
       </c>
       <c r="O15" s="16" t="n">
-        <v>76.09999999999999</v>
+        <v>76.12</v>
       </c>
       <c r="P15" s="16" t="n">
         <v>-1.12</v>
       </c>
       <c r="Q15" s="16" t="n">
-        <v>9.300000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="R15" s="16" t="n">
-        <v>8.9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="T15" s="16" t="n">
         <v>4977</v>
@@ -1829,34 +1829,34 @@
         <v>25</v>
       </c>
       <c r="V15" s="16" t="n">
-        <v>76.7282</v>
+        <v>76.73</v>
       </c>
       <c r="W15" s="16" t="n">
-        <v>7.99366</v>
+        <v>7.99</v>
       </c>
       <c r="X15" s="16" t="n">
-        <v>56.1379</v>
+        <v>56.14</v>
       </c>
       <c r="Y15" s="16" t="n">
-        <v>57.4722</v>
+        <v>57.47</v>
       </c>
       <c r="Z15" s="16" t="n">
-        <v>58.1322</v>
+        <v>58.13</v>
       </c>
       <c r="AA15" s="16" t="n">
-        <v>59.3812</v>
+        <v>59.38</v>
       </c>
       <c r="AB15" s="16" t="n">
-        <v>55.5665</v>
+        <v>55.57</v>
       </c>
       <c r="AC15" s="16" t="n">
-        <v>56.8887</v>
+        <v>56.89</v>
       </c>
       <c r="AD15" s="16" t="n">
-        <v>57.5281</v>
+        <v>57.53</v>
       </c>
       <c r="AE15" s="16" t="n">
-        <v>58.7158</v>
+        <v>58.72</v>
       </c>
     </row>
     <row r="16">
@@ -1882,22 +1882,22 @@
         <v>53.6</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>87.59999999999999</v>
+        <v>87.62</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>30.8</v>
+        <v>30.77</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>159</v>
+        <v>163.32</v>
       </c>
       <c r="K16" s="16" t="n">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="L16" s="16" t="n">
-        <v>90.90000000000001</v>
+        <v>11.79</v>
       </c>
       <c r="M16" s="16" t="n">
-        <v>12.6</v>
+        <v>7.49</v>
       </c>
       <c r="O16" s="16" t="n">
         <v>48</v>
@@ -1906,10 +1906,10 @@
         <v>-2.34</v>
       </c>
       <c r="Q16" s="16" t="n">
-        <v>11</v>
+        <v>11.03</v>
       </c>
       <c r="R16" s="16" t="n">
-        <v>9</v>
+        <v>9.01</v>
       </c>
       <c r="T16" s="16" t="n">
         <v>4958</v>
@@ -1918,34 +1918,34 @@
         <v>25</v>
       </c>
       <c r="V16" s="16" t="n">
-        <v>86.3062</v>
+        <v>86.31</v>
       </c>
       <c r="W16" s="16" t="n">
-        <v>10.5448</v>
+        <v>10.54</v>
       </c>
       <c r="X16" s="16" t="n">
-        <v>59.1445</v>
+        <v>59.14</v>
       </c>
       <c r="Y16" s="16" t="n">
-        <v>60.9046</v>
+        <v>60.9</v>
       </c>
       <c r="Z16" s="16" t="n">
-        <v>61.7752</v>
+        <v>61.78</v>
       </c>
       <c r="AA16" s="16" t="n">
-        <v>63.4229</v>
+        <v>63.42</v>
       </c>
       <c r="AB16" s="16" t="n">
-        <v>62.3078</v>
+        <v>62.31</v>
       </c>
       <c r="AC16" s="16" t="n">
-        <v>63.4844</v>
+        <v>63.48</v>
       </c>
       <c r="AD16" s="16" t="n">
-        <v>64.0973</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AE16" s="16" t="n">
-        <v>65.3065</v>
+        <v>65.31</v>
       </c>
     </row>
     <row r="17">
@@ -1968,37 +1968,37 @@
         </is>
       </c>
       <c r="F17" s="16" t="n">
-        <v>61.5</v>
+        <v>61.51</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>17.9</v>
+        <v>17.91</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>17.9</v>
+        <v>17.95</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>136.3</v>
+        <v>136.31</v>
       </c>
       <c r="K17" s="16" t="n">
         <v>1.49</v>
       </c>
       <c r="L17" s="16" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="M17" s="16" t="n">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="O17" s="16" t="n">
-        <v>32.7</v>
+        <v>32.73</v>
       </c>
       <c r="P17" s="16" t="n">
         <v>-3</v>
       </c>
       <c r="Q17" s="16" t="n">
-        <v>5.9</v>
+        <v>5.89</v>
       </c>
       <c r="R17" s="16" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="T17" s="16" t="n">
         <v>4958</v>
@@ -2007,34 +2007,34 @@
         <v>25</v>
       </c>
       <c r="V17" s="16" t="n">
-        <v>80.7985</v>
+        <v>80.8</v>
       </c>
       <c r="W17" s="16" t="n">
-        <v>8.421849999999999</v>
+        <v>8.42</v>
       </c>
       <c r="X17" s="16" t="n">
-        <v>59.1052</v>
+        <v>59.11</v>
       </c>
       <c r="Y17" s="16" t="n">
-        <v>60.5109</v>
+        <v>60.51</v>
       </c>
       <c r="Z17" s="16" t="n">
-        <v>61.2063</v>
+        <v>61.21</v>
       </c>
       <c r="AA17" s="16" t="n">
-        <v>62.5223</v>
+        <v>62.52</v>
       </c>
       <c r="AB17" s="16" t="n">
-        <v>57.2361</v>
+        <v>57.24</v>
       </c>
       <c r="AC17" s="16" t="n">
-        <v>58.6722</v>
+        <v>58.67</v>
       </c>
       <c r="AD17" s="16" t="n">
-        <v>59.397</v>
+        <v>59.4</v>
       </c>
       <c r="AE17" s="16" t="n">
-        <v>60.9053</v>
+        <v>60.91</v>
       </c>
     </row>
     <row r="18">
@@ -2057,37 +2057,37 @@
         </is>
       </c>
       <c r="F18" s="16" t="n">
-        <v>57.4</v>
+        <v>57.36</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>11.6</v>
+        <v>11.61</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>11.2</v>
+        <v>11.22</v>
       </c>
       <c r="J18" s="16" t="n">
-        <v>134.5</v>
+        <v>134.51</v>
       </c>
       <c r="K18" s="16" t="n">
         <v>1.41</v>
       </c>
       <c r="L18" s="16" t="n">
-        <v>5.5</v>
+        <v>5.51</v>
       </c>
       <c r="M18" s="16" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="O18" s="16" t="n">
-        <v>45.5</v>
+        <v>45.51</v>
       </c>
       <c r="P18" s="16" t="n">
         <v>-2.45</v>
       </c>
       <c r="Q18" s="16" t="n">
-        <v>6.3</v>
+        <v>6.28</v>
       </c>
       <c r="R18" s="16" t="n">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="T18" s="16" t="n">
         <v>4973</v>
@@ -2096,34 +2096,34 @@
         <v>25</v>
       </c>
       <c r="V18" s="16" t="n">
-        <v>71.9087</v>
+        <v>71.91</v>
       </c>
       <c r="W18" s="16" t="n">
-        <v>6.64359</v>
+        <v>6.64</v>
       </c>
       <c r="X18" s="16" t="n">
-        <v>54.796</v>
+        <v>54.8</v>
       </c>
       <c r="Y18" s="16" t="n">
-        <v>55.9049</v>
+        <v>55.9</v>
       </c>
       <c r="Z18" s="16" t="n">
-        <v>56.4534</v>
+        <v>56.45</v>
       </c>
       <c r="AA18" s="16" t="n">
-        <v>57.4915</v>
+        <v>57.49</v>
       </c>
       <c r="AB18" s="16" t="n">
-        <v>55.8253</v>
+        <v>55.83</v>
       </c>
       <c r="AC18" s="16" t="n">
-        <v>56.8237</v>
+        <v>56.82</v>
       </c>
       <c r="AD18" s="16" t="n">
-        <v>57.3082</v>
+        <v>57.31</v>
       </c>
       <c r="AE18" s="16" t="n">
-        <v>58.194</v>
+        <v>58.19</v>
       </c>
     </row>
     <row r="19">
@@ -2146,34 +2146,34 @@
         </is>
       </c>
       <c r="F19" s="16" t="n">
-        <v>47.1</v>
+        <v>47.11</v>
       </c>
       <c r="G19" s="16" t="n">
-        <v>36.8</v>
+        <v>36.76</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>35.5</v>
+        <v>35.47</v>
       </c>
       <c r="J19" s="16" t="n">
-        <v>132.9</v>
+        <v>132.85</v>
       </c>
       <c r="K19" s="16" t="n">
         <v>1.34</v>
       </c>
       <c r="L19" s="16" t="n">
-        <v>7.5</v>
+        <v>7.54</v>
       </c>
       <c r="M19" s="16" t="n">
-        <v>13.7</v>
+        <v>13.69</v>
       </c>
       <c r="O19" s="16" t="n">
-        <v>54.2</v>
+        <v>54.16</v>
       </c>
       <c r="P19" s="16" t="n">
         <v>-2.07</v>
       </c>
       <c r="Q19" s="16" t="n">
-        <v>119.6</v>
+        <v>119.56</v>
       </c>
       <c r="R19" s="16" t="n">
         <v>29.8</v>
@@ -2185,34 +2185,34 @@
         <v>25</v>
       </c>
       <c r="V19" s="16" t="n">
-        <v>73.5851</v>
+        <v>73.59</v>
       </c>
       <c r="W19" s="16" t="n">
-        <v>7.09328</v>
+        <v>7.09</v>
       </c>
       <c r="X19" s="16" t="n">
-        <v>55.314</v>
+        <v>55.31</v>
       </c>
       <c r="Y19" s="16" t="n">
-        <v>56.498</v>
+        <v>56.5</v>
       </c>
       <c r="Z19" s="16" t="n">
-        <v>57.0837</v>
+        <v>57.08</v>
       </c>
       <c r="AA19" s="16" t="n">
-        <v>58.1921</v>
+        <v>58.19</v>
       </c>
       <c r="AB19" s="16" t="n">
-        <v>56.1115</v>
+        <v>56.11</v>
       </c>
       <c r="AC19" s="16" t="n">
-        <v>57.1978</v>
+        <v>57.2</v>
       </c>
       <c r="AD19" s="16" t="n">
-        <v>57.7751</v>
+        <v>57.78</v>
       </c>
       <c r="AE19" s="16" t="n">
-        <v>58.875</v>
+        <v>58.87</v>
       </c>
     </row>
     <row r="20">
@@ -2235,28 +2235,28 @@
         </is>
       </c>
       <c r="F20" s="16" t="n">
-        <v>52.2</v>
+        <v>52.24</v>
       </c>
       <c r="G20" s="16" t="n">
-        <v>20</v>
+        <v>20.05</v>
       </c>
       <c r="H20" s="16" t="n">
-        <v>21.4</v>
+        <v>21.45</v>
       </c>
       <c r="J20" s="16" t="n">
-        <v>124.5</v>
+        <v>124.54</v>
       </c>
       <c r="K20" s="16" t="n">
         <v>0.98</v>
       </c>
       <c r="L20" s="16" t="n">
-        <v>10.4</v>
+        <v>10.43</v>
       </c>
       <c r="M20" s="16" t="n">
-        <v>13.8</v>
+        <v>13.82</v>
       </c>
       <c r="O20" s="16" t="n">
-        <v>44</v>
+        <v>43.96</v>
       </c>
       <c r="P20" s="16" t="n">
         <v>-2.51</v>
@@ -2265,7 +2265,7 @@
         <v>7.2</v>
       </c>
       <c r="R20" s="16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="T20" s="16" t="n">
         <v>4955</v>
@@ -2274,34 +2274,34 @@
         <v>25</v>
       </c>
       <c r="V20" s="16" t="n">
-        <v>77.9113</v>
+        <v>77.91</v>
       </c>
       <c r="W20" s="16" t="n">
-        <v>8.636889999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="X20" s="16" t="n">
-        <v>55.6641</v>
+        <v>55.66</v>
       </c>
       <c r="Y20" s="16" t="n">
-        <v>57.1057</v>
+        <v>57.11</v>
       </c>
       <c r="Z20" s="16" t="n">
-        <v>57.8189</v>
+        <v>57.82</v>
       </c>
       <c r="AA20" s="16" t="n">
-        <v>59.1685</v>
+        <v>59.17</v>
       </c>
       <c r="AB20" s="16" t="n">
-        <v>56.2373</v>
+        <v>56.24</v>
       </c>
       <c r="AC20" s="16" t="n">
-        <v>57.5978</v>
+        <v>57.6</v>
       </c>
       <c r="AD20" s="16" t="n">
-        <v>58.2641</v>
+        <v>58.26</v>
       </c>
       <c r="AE20" s="16" t="n">
-        <v>59.4959</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="21">
@@ -2324,28 +2324,28 @@
         </is>
       </c>
       <c r="F21" s="16" t="n">
-        <v>52.6</v>
+        <v>52.55</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>54.3</v>
+        <v>54.29</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>34.2</v>
+        <v>34.21</v>
       </c>
       <c r="J21" s="16" t="n">
-        <v>153</v>
+        <v>152.97</v>
       </c>
       <c r="K21" s="16" t="n">
         <v>2.21</v>
       </c>
       <c r="L21" s="16" t="n">
-        <v>5.5</v>
+        <v>5.49</v>
       </c>
       <c r="M21" s="16" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="O21" s="16" t="n">
-        <v>57.1</v>
+        <v>57.15</v>
       </c>
       <c r="P21" s="16" t="n">
         <v>-1.94</v>
@@ -2354,7 +2354,7 @@
         <v>10.6</v>
       </c>
       <c r="R21" s="16" t="n">
-        <v>12.2</v>
+        <v>12.19</v>
       </c>
       <c r="T21" s="16" t="n">
         <v>4696</v>
@@ -2363,34 +2363,34 @@
         <v>25</v>
       </c>
       <c r="V21" s="16" t="n">
-        <v>85.2851</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="W21" s="16" t="n">
-        <v>10.8324</v>
+        <v>10.83</v>
       </c>
       <c r="X21" s="16" t="n">
-        <v>57.3827</v>
+        <v>57.38</v>
       </c>
       <c r="Y21" s="16" t="n">
-        <v>59.1908</v>
+        <v>59.19</v>
       </c>
       <c r="Z21" s="16" t="n">
-        <v>60.0852</v>
+        <v>60.09</v>
       </c>
       <c r="AA21" s="16" t="n">
-        <v>61.7779</v>
+        <v>61.78</v>
       </c>
       <c r="AB21" s="16" t="n">
-        <v>62.1043</v>
+        <v>62.1</v>
       </c>
       <c r="AC21" s="16" t="n">
-        <v>63.4646</v>
+        <v>63.46</v>
       </c>
       <c r="AD21" s="16" t="n">
-        <v>64.14449999999999</v>
+        <v>64.14</v>
       </c>
       <c r="AE21" s="16" t="n">
-        <v>65.459</v>
+        <v>65.45999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2413,25 +2413,25 @@
         </is>
       </c>
       <c r="F22" s="16" t="n">
-        <v>60.6</v>
+        <v>60.58</v>
       </c>
       <c r="G22" s="16" t="n">
-        <v>13.3</v>
+        <v>13.31</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>13.6</v>
+        <v>13.61</v>
       </c>
       <c r="J22" s="16" t="n">
-        <v>138.8</v>
+        <v>138.77</v>
       </c>
       <c r="K22" s="16" t="n">
         <v>1.6</v>
       </c>
       <c r="L22" s="16" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="M22" s="16" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="O22" s="16" t="n">
         <v>41.8</v>
@@ -2440,7 +2440,7 @@
         <v>-2.61</v>
       </c>
       <c r="Q22" s="16" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="R22" s="16" t="n">
         <v>3.8</v>
@@ -2452,34 +2452,34 @@
         <v>25</v>
       </c>
       <c r="V22" s="16" t="n">
-        <v>74.869</v>
+        <v>74.87</v>
       </c>
       <c r="W22" s="16" t="n">
-        <v>7.42977</v>
+        <v>7.43</v>
       </c>
       <c r="X22" s="16" t="n">
-        <v>55.7312</v>
+        <v>55.73</v>
       </c>
       <c r="Y22" s="16" t="n">
-        <v>56.9713</v>
+        <v>56.97</v>
       </c>
       <c r="Z22" s="16" t="n">
-        <v>57.5847</v>
+        <v>57.58</v>
       </c>
       <c r="AA22" s="16" t="n">
-        <v>58.7457</v>
+        <v>58.75</v>
       </c>
       <c r="AB22" s="16" t="n">
-        <v>55.9742</v>
+        <v>55.97</v>
       </c>
       <c r="AC22" s="16" t="n">
-        <v>57.1039</v>
+        <v>57.1</v>
       </c>
       <c r="AD22" s="16" t="n">
-        <v>57.657</v>
+        <v>57.66</v>
       </c>
       <c r="AE22" s="16" t="n">
-        <v>58.7144</v>
+        <v>58.71</v>
       </c>
     </row>
     <row r="23">
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="F23" s="16" t="n">
-        <v>67.7</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>13.9</v>
+        <v>13.88</v>
       </c>
       <c r="H23" s="16" t="n">
         <v>13.8</v>
@@ -2517,22 +2517,22 @@
         <v>2.34</v>
       </c>
       <c r="L23" s="16" t="n">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="M23" s="16" t="n">
-        <v>5.3</v>
+        <v>5.32</v>
       </c>
       <c r="O23" s="16" t="n">
-        <v>56.7</v>
+        <v>56.74</v>
       </c>
       <c r="P23" s="16" t="n">
         <v>-1.96</v>
       </c>
       <c r="Q23" s="16" t="n">
-        <v>7.3</v>
+        <v>7.27</v>
       </c>
       <c r="R23" s="16" t="n">
-        <v>6.8</v>
+        <v>6.82</v>
       </c>
       <c r="T23" s="16" t="n">
         <v>4935</v>
@@ -2544,31 +2544,31 @@
         <v>82.84999999999999</v>
       </c>
       <c r="W23" s="16" t="n">
-        <v>7.30885</v>
+        <v>7.31</v>
       </c>
       <c r="X23" s="16" t="n">
-        <v>64.02370000000001</v>
+        <v>64.02</v>
       </c>
       <c r="Y23" s="16" t="n">
-        <v>65.2436</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="Z23" s="16" t="n">
-        <v>65.8471</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="AA23" s="16" t="n">
-        <v>66.98909999999999</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="AB23" s="16" t="n">
-        <v>62.7078</v>
+        <v>62.71</v>
       </c>
       <c r="AC23" s="16" t="n">
-        <v>64.2711</v>
+        <v>64.27</v>
       </c>
       <c r="AD23" s="16" t="n">
-        <v>65.0073</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AE23" s="16" t="n">
-        <v>66.2945</v>
+        <v>66.29000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -2591,34 +2591,34 @@
         </is>
       </c>
       <c r="F24" s="16" t="n">
-        <v>58.3</v>
+        <v>58.27</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>28.6</v>
+        <v>28.63</v>
       </c>
       <c r="H24" s="16" t="n">
         <v>27.2</v>
       </c>
       <c r="J24" s="16" t="n">
-        <v>148.9</v>
+        <v>148.93</v>
       </c>
       <c r="K24" s="16" t="n">
         <v>2.04</v>
       </c>
       <c r="L24" s="16" t="n">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="M24" s="16" t="n">
-        <v>7.1</v>
+        <v>7.13</v>
       </c>
       <c r="O24" s="16" t="n">
-        <v>57.2</v>
+        <v>57.17</v>
       </c>
       <c r="P24" s="16" t="n">
         <v>-1.94</v>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>12.2</v>
+        <v>12.22</v>
       </c>
       <c r="R24" s="16" t="n">
         <v>11.9</v>
@@ -2633,31 +2633,31 @@
         <v>80.73999999999999</v>
       </c>
       <c r="W24" s="16" t="n">
-        <v>6.52413</v>
+        <v>6.52</v>
       </c>
       <c r="X24" s="16" t="n">
-        <v>63.935</v>
+        <v>63.93</v>
       </c>
       <c r="Y24" s="16" t="n">
-        <v>65.0239</v>
+        <v>65.02</v>
       </c>
       <c r="Z24" s="16" t="n">
-        <v>65.5626</v>
+        <v>65.56</v>
       </c>
       <c r="AA24" s="16" t="n">
-        <v>66.58199999999999</v>
+        <v>66.58</v>
       </c>
       <c r="AB24" s="16" t="n">
-        <v>61.2879</v>
+        <v>61.29</v>
       </c>
       <c r="AC24" s="16" t="n">
-        <v>62.7064</v>
+        <v>62.71</v>
       </c>
       <c r="AD24" s="16" t="n">
-        <v>63.4067</v>
+        <v>63.41</v>
       </c>
       <c r="AE24" s="16" t="n">
-        <v>64.7747</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="25">
@@ -2680,13 +2680,13 @@
         </is>
       </c>
       <c r="F25" s="16" t="n">
-        <v>61.6</v>
+        <v>61.62</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>13.4</v>
+        <v>13.37</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>13.2</v>
+        <v>13.21</v>
       </c>
       <c r="J25" s="16" t="n">
         <v>140.7</v>
@@ -2695,13 +2695,13 @@
         <v>1.68</v>
       </c>
       <c r="L25" s="16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="M25" s="16" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="O25" s="16" t="n">
-        <v>45.5</v>
+        <v>45.49</v>
       </c>
       <c r="P25" s="16" t="n">
         <v>-2.45</v>
@@ -2710,7 +2710,7 @@
         <v>6.5</v>
       </c>
       <c r="R25" s="16" t="n">
-        <v>6</v>
+        <v>5.99</v>
       </c>
       <c r="T25" s="16" t="n">
         <v>4945</v>
@@ -2719,34 +2719,34 @@
         <v>25</v>
       </c>
       <c r="V25" s="16" t="n">
-        <v>76.9389</v>
+        <v>76.94</v>
       </c>
       <c r="W25" s="16" t="n">
-        <v>7.46928</v>
+        <v>7.47</v>
       </c>
       <c r="X25" s="16" t="n">
-        <v>57.6993</v>
+        <v>57.7</v>
       </c>
       <c r="Y25" s="16" t="n">
-        <v>58.9461</v>
+        <v>58.95</v>
       </c>
       <c r="Z25" s="16" t="n">
-        <v>59.5628</v>
+        <v>59.56</v>
       </c>
       <c r="AA25" s="16" t="n">
-        <v>60.7299</v>
+        <v>60.73</v>
       </c>
       <c r="AB25" s="16" t="n">
-        <v>58.2519</v>
+        <v>58.25</v>
       </c>
       <c r="AC25" s="16" t="n">
-        <v>59.357</v>
+        <v>59.36</v>
       </c>
       <c r="AD25" s="16" t="n">
-        <v>59.8748</v>
+        <v>59.87</v>
       </c>
       <c r="AE25" s="16" t="n">
-        <v>60.8273</v>
+        <v>60.83</v>
       </c>
     </row>
     <row r="26">
@@ -2769,37 +2769,37 @@
         </is>
       </c>
       <c r="F26" s="16" t="n">
-        <v>64.2</v>
+        <v>64.25</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>14.4</v>
+        <v>14.43</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>14.4</v>
+        <v>14.39</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>142.3</v>
+        <v>142.25</v>
       </c>
       <c r="K26" s="16" t="n">
         <v>1.75</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="M26" s="16" t="n">
         <v>5.4</v>
       </c>
       <c r="O26" s="16" t="n">
-        <v>42.7</v>
+        <v>42.69</v>
       </c>
       <c r="P26" s="16" t="n">
         <v>-2.57</v>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>6.9</v>
+        <v>6.93</v>
       </c>
       <c r="R26" s="16" t="n">
-        <v>6.2</v>
+        <v>6.21</v>
       </c>
       <c r="T26" s="16" t="n">
         <v>4935</v>
@@ -2808,34 +2808,34 @@
         <v>25</v>
       </c>
       <c r="V26" s="16" t="n">
-        <v>79.9815</v>
+        <v>79.98</v>
       </c>
       <c r="W26" s="16" t="n">
-        <v>7.13077</v>
+        <v>7.13</v>
       </c>
       <c r="X26" s="16" t="n">
-        <v>61.6138</v>
+        <v>61.61</v>
       </c>
       <c r="Y26" s="16" t="n">
-        <v>62.8041</v>
+        <v>62.8</v>
       </c>
       <c r="Z26" s="16" t="n">
-        <v>63.3928</v>
+        <v>63.39</v>
       </c>
       <c r="AA26" s="16" t="n">
-        <v>64.50709999999999</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="AB26" s="16" t="n">
-        <v>62.1684</v>
+        <v>62.17</v>
       </c>
       <c r="AC26" s="16" t="n">
-        <v>63.1976</v>
+        <v>63.2</v>
       </c>
       <c r="AD26" s="16" t="n">
-        <v>63.7058</v>
+        <v>63.71</v>
       </c>
       <c r="AE26" s="16" t="n">
-        <v>64.6735</v>
+        <v>64.67</v>
       </c>
     </row>
     <row r="27">
@@ -2861,13 +2861,13 @@
         <v>60.5</v>
       </c>
       <c r="G27" s="16" t="n">
-        <v>35.5</v>
+        <v>35.47</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>20.6</v>
+        <v>20.64</v>
       </c>
       <c r="J27" s="16" t="n">
-        <v>141.3</v>
+        <v>141.31</v>
       </c>
       <c r="K27" s="16" t="n">
         <v>1.71</v>
@@ -2876,10 +2876,10 @@
         <v>4.6</v>
       </c>
       <c r="M27" s="16" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="O27" s="16" t="n">
-        <v>64.59999999999999</v>
+        <v>64.56</v>
       </c>
       <c r="P27" s="16" t="n">
         <v>-1.62</v>
@@ -2888,7 +2888,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="R27" s="16" t="n">
-        <v>30.9</v>
+        <v>30.94</v>
       </c>
       <c r="T27" s="16" t="n">
         <v>4972</v>
@@ -2897,34 +2897,34 @@
         <v>25</v>
       </c>
       <c r="V27" s="16" t="n">
-        <v>81.6883</v>
+        <v>81.69</v>
       </c>
       <c r="W27" s="16" t="n">
-        <v>6.92583</v>
+        <v>6.93</v>
       </c>
       <c r="X27" s="16" t="n">
-        <v>63.8485</v>
+        <v>63.85</v>
       </c>
       <c r="Y27" s="16" t="n">
-        <v>65.00449999999999</v>
+        <v>65</v>
       </c>
       <c r="Z27" s="16" t="n">
-        <v>65.57640000000001</v>
+        <v>65.58</v>
       </c>
       <c r="AA27" s="16" t="n">
-        <v>66.65860000000001</v>
+        <v>66.66</v>
       </c>
       <c r="AB27" s="16" t="n">
-        <v>63.7562</v>
+        <v>63.76</v>
       </c>
       <c r="AC27" s="16" t="n">
-        <v>64.87690000000001</v>
+        <v>64.88</v>
       </c>
       <c r="AD27" s="16" t="n">
-        <v>65.4678</v>
+        <v>65.47</v>
       </c>
       <c r="AE27" s="16" t="n">
-        <v>66.5406</v>
+        <v>66.54000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2947,37 +2947,37 @@
         </is>
       </c>
       <c r="F28" s="16" t="n">
-        <v>59.9</v>
+        <v>59.92</v>
       </c>
       <c r="G28" s="16" t="n">
-        <v>36.4</v>
+        <v>36.37</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>25.7</v>
+        <v>25.68</v>
       </c>
       <c r="J28" s="16" t="n">
-        <v>140.8</v>
+        <v>140.85</v>
       </c>
       <c r="K28" s="16" t="n">
         <v>1.69</v>
       </c>
       <c r="L28" s="16" t="n">
-        <v>5.1</v>
+        <v>5.07</v>
       </c>
       <c r="M28" s="16" t="n">
-        <v>5.2</v>
+        <v>5.17</v>
       </c>
       <c r="O28" s="16" t="n">
-        <v>62.2</v>
+        <v>62.18</v>
       </c>
       <c r="P28" s="16" t="n">
         <v>-1.72</v>
       </c>
       <c r="Q28" s="16" t="n">
-        <v>73.5</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="R28" s="16" t="n">
-        <v>32.6</v>
+        <v>32.62</v>
       </c>
       <c r="T28" s="16" t="n">
         <v>4960</v>
@@ -2986,34 +2986,34 @@
         <v>25</v>
       </c>
       <c r="V28" s="16" t="n">
-        <v>85.09529999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="W28" s="16" t="n">
-        <v>6.8098</v>
+        <v>6.81</v>
       </c>
       <c r="X28" s="16" t="n">
-        <v>67.5544</v>
+        <v>67.55</v>
       </c>
       <c r="Y28" s="16" t="n">
-        <v>68.69110000000001</v>
+        <v>68.69</v>
       </c>
       <c r="Z28" s="16" t="n">
-        <v>69.2534</v>
+        <v>69.25</v>
       </c>
       <c r="AA28" s="16" t="n">
-        <v>70.31740000000001</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="AB28" s="16" t="n">
-        <v>67.11709999999999</v>
+        <v>67.12</v>
       </c>
       <c r="AC28" s="16" t="n">
-        <v>68.07599999999999</v>
+        <v>68.08</v>
       </c>
       <c r="AD28" s="16" t="n">
-        <v>68.5727</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="AE28" s="16" t="n">
-        <v>69.5817</v>
+        <v>69.58</v>
       </c>
     </row>
     <row r="29">
@@ -3036,37 +3036,37 @@
         </is>
       </c>
       <c r="F29" s="16" t="n">
-        <v>58.5</v>
+        <v>58.55</v>
       </c>
       <c r="G29" s="16" t="n">
-        <v>36.2</v>
+        <v>36.22</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>19.8</v>
+        <v>19.78</v>
       </c>
       <c r="J29" s="16" t="n">
-        <v>144.2</v>
+        <v>144.19</v>
       </c>
       <c r="K29" s="16" t="n">
         <v>1.83</v>
       </c>
       <c r="L29" s="16" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="M29" s="16" t="n">
         <v>5.4</v>
       </c>
       <c r="O29" s="16" t="n">
-        <v>65.3</v>
+        <v>65.28</v>
       </c>
       <c r="P29" s="16" t="n">
         <v>-1.59</v>
       </c>
       <c r="Q29" s="16" t="n">
-        <v>68</v>
+        <v>67.98</v>
       </c>
       <c r="R29" s="16" t="n">
-        <v>30</v>
+        <v>29.98</v>
       </c>
       <c r="T29" s="16" t="n">
         <v>4982</v>
@@ -3075,34 +3075,34 @@
         <v>25</v>
       </c>
       <c r="V29" s="16" t="n">
-        <v>81.8836</v>
+        <v>81.88</v>
       </c>
       <c r="W29" s="16" t="n">
-        <v>7.56305</v>
+        <v>7.56</v>
       </c>
       <c r="X29" s="16" t="n">
-        <v>62.4024</v>
+        <v>62.4</v>
       </c>
       <c r="Y29" s="16" t="n">
-        <v>63.6648</v>
+        <v>63.66</v>
       </c>
       <c r="Z29" s="16" t="n">
-        <v>64.2893</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="AA29" s="16" t="n">
-        <v>65.47110000000001</v>
+        <v>65.47</v>
       </c>
       <c r="AB29" s="16" t="n">
-        <v>64.8265</v>
+        <v>64.83</v>
       </c>
       <c r="AC29" s="16" t="n">
-        <v>65.6125</v>
+        <v>65.61</v>
       </c>
       <c r="AD29" s="16" t="n">
-        <v>66.0116</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="AE29" s="16" t="n">
-        <v>66.79170000000001</v>
+        <v>66.79000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3125,16 +3125,16 @@
         </is>
       </c>
       <c r="F30" s="16" t="n">
-        <v>58.2</v>
+        <v>58.22</v>
       </c>
       <c r="G30" s="16" t="n">
-        <v>12.6</v>
+        <v>12.57</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>13.8</v>
+        <v>13.84</v>
       </c>
       <c r="J30" s="16" t="n">
-        <v>159.3</v>
+        <v>159.27</v>
       </c>
       <c r="K30" s="16" t="n">
         <v>2.49</v>
@@ -3143,10 +3143,10 @@
         <v>6.3</v>
       </c>
       <c r="M30" s="16" t="n">
-        <v>5.9</v>
+        <v>5.94</v>
       </c>
       <c r="O30" s="16" t="n">
-        <v>71</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="P30" s="16" t="n">
         <v>-1.34</v>
@@ -3164,34 +3164,34 @@
         <v>25</v>
       </c>
       <c r="V30" s="16" t="n">
-        <v>74.91030000000001</v>
+        <v>74.91</v>
       </c>
       <c r="W30" s="16" t="n">
-        <v>6.72327</v>
+        <v>6.72</v>
       </c>
       <c r="X30" s="16" t="n">
-        <v>57.5923</v>
+        <v>57.59</v>
       </c>
       <c r="Y30" s="16" t="n">
-        <v>58.7145</v>
+        <v>58.71</v>
       </c>
       <c r="Z30" s="16" t="n">
-        <v>59.2696</v>
+        <v>59.27</v>
       </c>
       <c r="AA30" s="16" t="n">
-        <v>60.3202</v>
+        <v>60.32</v>
       </c>
       <c r="AB30" s="16" t="n">
-        <v>58.0346</v>
+        <v>58.03</v>
       </c>
       <c r="AC30" s="16" t="n">
-        <v>59.0484</v>
+        <v>59.05</v>
       </c>
       <c r="AD30" s="16" t="n">
-        <v>59.5599</v>
+        <v>59.56</v>
       </c>
       <c r="AE30" s="16" t="n">
-        <v>60.5272</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="31">
@@ -3214,37 +3214,37 @@
         </is>
       </c>
       <c r="F31" s="16" t="n">
-        <v>59</v>
+        <v>58.98</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>23.3</v>
+        <v>23.26</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>21.5</v>
+        <v>21.47</v>
       </c>
       <c r="J31" s="16" t="n">
-        <v>154.9</v>
+        <v>154.89</v>
       </c>
       <c r="K31" s="16" t="n">
         <v>2.3</v>
       </c>
       <c r="L31" s="16" t="n">
-        <v>7.9</v>
+        <v>7.87</v>
       </c>
       <c r="M31" s="16" t="n">
-        <v>6.2</v>
+        <v>6.24</v>
       </c>
       <c r="O31" s="16" t="n">
-        <v>55</v>
+        <v>55.05</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>-2.04</v>
+        <v>-2.03</v>
       </c>
       <c r="Q31" s="16" t="n">
-        <v>7</v>
+        <v>7.05</v>
       </c>
       <c r="R31" s="16" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
       <c r="T31" s="16" t="n">
         <v>4936</v>
@@ -3253,34 +3253,34 @@
         <v>25</v>
       </c>
       <c r="V31" s="16" t="n">
-        <v>82.4918</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="W31" s="16" t="n">
-        <v>8.193899999999999</v>
+        <v>8.19</v>
       </c>
       <c r="X31" s="16" t="n">
-        <v>61.3857</v>
+        <v>61.39</v>
       </c>
       <c r="Y31" s="16" t="n">
-        <v>62.7534</v>
+        <v>62.75</v>
       </c>
       <c r="Z31" s="16" t="n">
-        <v>63.4299</v>
+        <v>63.43</v>
       </c>
       <c r="AA31" s="16" t="n">
-        <v>64.7103</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="AB31" s="16" t="n">
-        <v>60.2419</v>
+        <v>60.24</v>
       </c>
       <c r="AC31" s="16" t="n">
-        <v>61.7073</v>
+        <v>61.71</v>
       </c>
       <c r="AD31" s="16" t="n">
-        <v>62.4026</v>
+        <v>62.4</v>
       </c>
       <c r="AE31" s="16" t="n">
-        <v>63.7671</v>
+        <v>63.77</v>
       </c>
     </row>
     <row r="32">
@@ -3303,16 +3303,16 @@
         </is>
       </c>
       <c r="F32" s="16" t="n">
-        <v>42.8</v>
+        <v>42.79</v>
       </c>
       <c r="G32" s="16" t="n">
-        <v>70.40000000000001</v>
+        <v>70.41</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>22.1</v>
+        <v>22.09</v>
       </c>
       <c r="J32" s="16" t="n">
-        <v>132.6</v>
+        <v>132.59</v>
       </c>
       <c r="K32" s="16" t="n">
         <v>1.33</v>
@@ -3321,19 +3321,19 @@
         <v>4.8</v>
       </c>
       <c r="M32" s="16" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="O32" s="16" t="n">
-        <v>49.3</v>
+        <v>49.29</v>
       </c>
       <c r="P32" s="16" t="n">
         <v>-2.28</v>
       </c>
       <c r="Q32" s="16" t="n">
-        <v>5.4</v>
+        <v>5.41</v>
       </c>
       <c r="R32" s="16" t="n">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="T32" s="16" t="n">
         <v>4948</v>
@@ -3342,34 +3342,34 @@
         <v>25</v>
       </c>
       <c r="V32" s="16" t="n">
-        <v>70.6266</v>
+        <v>70.63</v>
       </c>
       <c r="W32" s="16" t="n">
-        <v>9.087770000000001</v>
+        <v>9.09</v>
       </c>
       <c r="X32" s="16" t="n">
-        <v>47.2181</v>
+        <v>47.22</v>
       </c>
       <c r="Y32" s="16" t="n">
-        <v>48.735</v>
+        <v>48.73</v>
       </c>
       <c r="Z32" s="16" t="n">
-        <v>49.4853</v>
+        <v>49.49</v>
       </c>
       <c r="AA32" s="16" t="n">
-        <v>50.9054</v>
+        <v>50.91</v>
       </c>
       <c r="AB32" s="16" t="n">
-        <v>46.755</v>
+        <v>46.76</v>
       </c>
       <c r="AC32" s="16" t="n">
-        <v>48.1417</v>
+        <v>48.14</v>
       </c>
       <c r="AD32" s="16" t="n">
-        <v>48.9057</v>
+        <v>48.91</v>
       </c>
       <c r="AE32" s="16" t="n">
-        <v>50.4689</v>
+        <v>50.47</v>
       </c>
     </row>
     <row r="33">
@@ -3392,25 +3392,25 @@
         </is>
       </c>
       <c r="F33" s="16" t="n">
-        <v>76.40000000000001</v>
+        <v>76.37</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>37</v>
+        <v>36.98</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>15</v>
+        <v>15.04</v>
       </c>
       <c r="J33" s="16" t="n">
-        <v>142.4</v>
+        <v>142.42</v>
       </c>
       <c r="K33" s="16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="L33" s="16" t="n">
-        <v>7.4</v>
+        <v>7.44</v>
       </c>
       <c r="M33" s="16" t="n">
-        <v>9.300000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>40.2</v>
@@ -3419,7 +3419,7 @@
         <v>-2.68</v>
       </c>
       <c r="Q33" s="16" t="n">
-        <v>27.2</v>
+        <v>27.22</v>
       </c>
       <c r="R33" s="16" t="n">
         <v>11.8</v>
@@ -3431,34 +3431,34 @@
         <v>25</v>
       </c>
       <c r="V33" s="16" t="n">
-        <v>89.218</v>
+        <v>89.22</v>
       </c>
       <c r="W33" s="16" t="n">
-        <v>6.19149</v>
+        <v>6.19</v>
       </c>
       <c r="X33" s="16" t="n">
-        <v>73.2697</v>
+        <v>73.27</v>
       </c>
       <c r="Y33" s="16" t="n">
-        <v>74.3032</v>
+        <v>74.3</v>
       </c>
       <c r="Z33" s="16" t="n">
-        <v>74.81440000000001</v>
+        <v>74.81</v>
       </c>
       <c r="AA33" s="16" t="n">
-        <v>75.78189999999999</v>
+        <v>75.78</v>
       </c>
       <c r="AB33" s="16" t="n">
-        <v>71.6968</v>
+        <v>71.7</v>
       </c>
       <c r="AC33" s="16" t="n">
-        <v>73.15309999999999</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="AD33" s="16" t="n">
-        <v>73.82850000000001</v>
+        <v>73.83</v>
       </c>
       <c r="AE33" s="16" t="n">
-        <v>74.9969</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34">
@@ -3481,37 +3481,37 @@
         </is>
       </c>
       <c r="F34" s="16" t="n">
-        <v>54.7</v>
+        <v>54.73</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>41.8</v>
+        <v>41.85</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>18.8</v>
+        <v>18.79</v>
       </c>
       <c r="J34" s="16" t="n">
-        <v>134.1</v>
+        <v>134.05</v>
       </c>
       <c r="K34" s="16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="L34" s="16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M34" s="16" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="O34" s="16" t="n">
-        <v>53.8</v>
+        <v>53.76</v>
       </c>
       <c r="P34" s="16" t="n">
         <v>-2.09</v>
       </c>
       <c r="Q34" s="16" t="n">
-        <v>21.1</v>
+        <v>21.08</v>
       </c>
       <c r="R34" s="16" t="n">
-        <v>17.1</v>
+        <v>17.08</v>
       </c>
       <c r="T34" s="16" t="n">
         <v>4941</v>
@@ -3520,34 +3520,34 @@
         <v>25</v>
       </c>
       <c r="V34" s="16" t="n">
-        <v>73.4991</v>
+        <v>73.5</v>
       </c>
       <c r="W34" s="16" t="n">
-        <v>5.38119</v>
+        <v>5.38</v>
       </c>
       <c r="X34" s="16" t="n">
-        <v>59.6381</v>
+        <v>59.64</v>
       </c>
       <c r="Y34" s="16" t="n">
-        <v>60.5363</v>
+        <v>60.54</v>
       </c>
       <c r="Z34" s="16" t="n">
-        <v>60.9806</v>
+        <v>60.98</v>
       </c>
       <c r="AA34" s="16" t="n">
-        <v>61.8215</v>
+        <v>61.82</v>
       </c>
       <c r="AB34" s="16" t="n">
-        <v>59.8759</v>
+        <v>59.88</v>
       </c>
       <c r="AC34" s="16" t="n">
-        <v>60.7176</v>
+        <v>60.72</v>
       </c>
       <c r="AD34" s="16" t="n">
-        <v>61.1636</v>
+        <v>61.16</v>
       </c>
       <c r="AE34" s="16" t="n">
-        <v>61.9959</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35">
@@ -3570,37 +3570,37 @@
         </is>
       </c>
       <c r="F35" s="16" t="n">
-        <v>58.7</v>
+        <v>58.66</v>
       </c>
       <c r="G35" s="16" t="n">
-        <v>32.9</v>
+        <v>32.93</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>16.8</v>
+        <v>16.79</v>
       </c>
       <c r="J35" s="16" t="n">
-        <v>133.5</v>
+        <v>133.46</v>
       </c>
       <c r="K35" s="16" t="n">
         <v>1.37</v>
       </c>
       <c r="L35" s="16" t="n">
-        <v>7.2</v>
+        <v>7.24</v>
       </c>
       <c r="M35" s="16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O35" s="16" t="n">
-        <v>51.3</v>
+        <v>51.25</v>
       </c>
       <c r="P35" s="16" t="n">
         <v>-2.2</v>
       </c>
       <c r="Q35" s="16" t="n">
-        <v>23.5</v>
+        <v>23.49</v>
       </c>
       <c r="R35" s="16" t="n">
-        <v>26.8</v>
+        <v>26.85</v>
       </c>
       <c r="T35" s="16" t="n">
         <v>4922</v>
@@ -3609,34 +3609,34 @@
         <v>25</v>
       </c>
       <c r="V35" s="16" t="n">
-        <v>75.2128</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="W35" s="16" t="n">
-        <v>4.85368</v>
+        <v>4.85</v>
       </c>
       <c r="X35" s="16" t="n">
-        <v>62.7105</v>
+        <v>62.71</v>
       </c>
       <c r="Y35" s="16" t="n">
-        <v>63.5207</v>
+        <v>63.52</v>
       </c>
       <c r="Z35" s="16" t="n">
-        <v>63.9214</v>
+        <v>63.92</v>
       </c>
       <c r="AA35" s="16" t="n">
-        <v>64.6799</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AB35" s="16" t="n">
-        <v>62.2521</v>
+        <v>62.25</v>
       </c>
       <c r="AC35" s="16" t="n">
-        <v>63.2643</v>
+        <v>63.26</v>
       </c>
       <c r="AD35" s="16" t="n">
-        <v>63.7302</v>
+        <v>63.73</v>
       </c>
       <c r="AE35" s="16" t="n">
-        <v>64.5461</v>
+        <v>64.55</v>
       </c>
     </row>
     <row r="36">
@@ -3659,25 +3659,25 @@
         </is>
       </c>
       <c r="F36" s="16" t="n">
-        <v>42.2</v>
+        <v>42.19</v>
       </c>
       <c r="G36" s="16" t="n">
-        <v>71.40000000000001</v>
+        <v>71.38</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>40.5</v>
+        <v>40.48</v>
       </c>
       <c r="J36" s="16" t="n">
-        <v>139.8</v>
+        <v>139.76</v>
       </c>
       <c r="K36" s="16" t="n">
         <v>1.64</v>
       </c>
       <c r="L36" s="16" t="n">
-        <v>13.6</v>
+        <v>13.59</v>
       </c>
       <c r="M36" s="16" t="n">
-        <v>10.1</v>
+        <v>10.13</v>
       </c>
       <c r="O36" s="16" t="n">
         <v>44</v>
@@ -3686,7 +3686,7 @@
         <v>-2.51</v>
       </c>
       <c r="Q36" s="16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="R36" s="16" t="n">
         <v>8.9</v>
@@ -3698,34 +3698,34 @@
         <v>25</v>
       </c>
       <c r="V36" s="16" t="n">
-        <v>81.9498</v>
+        <v>81.95</v>
       </c>
       <c r="W36" s="16" t="n">
-        <v>8.21738</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="X36" s="16" t="n">
-        <v>60.7833</v>
+        <v>60.78</v>
       </c>
       <c r="Y36" s="16" t="n">
-        <v>62.1549</v>
+        <v>62.15</v>
       </c>
       <c r="Z36" s="16" t="n">
-        <v>62.8334</v>
+        <v>62.83</v>
       </c>
       <c r="AA36" s="16" t="n">
-        <v>64.1174</v>
+        <v>64.12</v>
       </c>
       <c r="AB36" s="16" t="n">
-        <v>60.8441</v>
+        <v>60.84</v>
       </c>
       <c r="AC36" s="16" t="n">
-        <v>62.039</v>
+        <v>62.04</v>
       </c>
       <c r="AD36" s="16" t="n">
-        <v>62.6255</v>
+        <v>62.63</v>
       </c>
       <c r="AE36" s="16" t="n">
-        <v>63.7688</v>
+        <v>63.77</v>
       </c>
     </row>
     <row r="37">
@@ -3748,16 +3748,16 @@
         </is>
       </c>
       <c r="F37" s="16" t="n">
-        <v>39.2</v>
+        <v>39.19</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>66.40000000000001</v>
+        <v>66.36</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>40.4</v>
+        <v>40.38</v>
       </c>
       <c r="J37" s="16" t="n">
-        <v>135.6</v>
+        <v>135.62</v>
       </c>
       <c r="K37" s="16" t="n">
         <v>1.46</v>
@@ -3766,19 +3766,19 @@
         <v>8.6</v>
       </c>
       <c r="M37" s="16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="O37" s="16" t="n">
-        <v>52.8</v>
+        <v>46.63</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-2.13</v>
+        <v>-2.4</v>
       </c>
       <c r="Q37" s="16" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="R37" s="16" t="n">
-        <v>18.1</v>
+        <v>12.28</v>
       </c>
       <c r="T37" s="16" t="n">
         <v>4952</v>
@@ -3787,34 +3787,34 @@
         <v>25</v>
       </c>
       <c r="V37" s="16" t="n">
-        <v>77.6763</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="W37" s="16" t="n">
-        <v>8.577819999999999</v>
+        <v>8.58</v>
       </c>
       <c r="X37" s="16" t="n">
-        <v>55.5813</v>
+        <v>55.58</v>
       </c>
       <c r="Y37" s="16" t="n">
-        <v>57.0131</v>
+        <v>57.01</v>
       </c>
       <c r="Z37" s="16" t="n">
-        <v>57.7214</v>
+        <v>57.72</v>
       </c>
       <c r="AA37" s="16" t="n">
-        <v>59.0617</v>
+        <v>59.06</v>
       </c>
       <c r="AB37" s="16" t="n">
-        <v>54.7377</v>
+        <v>54.74</v>
       </c>
       <c r="AC37" s="16" t="n">
-        <v>56.0399</v>
+        <v>56.04</v>
       </c>
       <c r="AD37" s="16" t="n">
-        <v>56.692</v>
+        <v>56.69</v>
       </c>
       <c r="AE37" s="16" t="n">
-        <v>57.9615</v>
+        <v>57.96</v>
       </c>
     </row>
     <row r="38">
@@ -3837,37 +3837,37 @@
         </is>
       </c>
       <c r="F38" s="16" t="n">
-        <v>64.90000000000001</v>
+        <v>64.89</v>
       </c>
       <c r="G38" s="16" t="n">
-        <v>9.6</v>
+        <v>9.59</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="J38" s="16" t="n">
-        <v>138.4</v>
+        <v>138.43</v>
       </c>
       <c r="K38" s="16" t="n">
         <v>1.58</v>
       </c>
       <c r="L38" s="16" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="M38" s="16" t="n">
-        <v>4.6</v>
+        <v>4.57</v>
       </c>
       <c r="O38" s="16" t="n">
-        <v>44.9</v>
+        <v>44.85</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>-2.47</v>
+        <v>-2.48</v>
       </c>
       <c r="Q38" s="16" t="n">
-        <v>6.9</v>
+        <v>6.89</v>
       </c>
       <c r="R38" s="16" t="n">
-        <v>6.2</v>
+        <v>6.19</v>
       </c>
       <c r="T38" s="16" t="n">
         <v>4970</v>
@@ -3876,34 +3876,34 @@
         <v>25</v>
       </c>
       <c r="V38" s="16" t="n">
-        <v>78.447</v>
+        <v>78.45</v>
       </c>
       <c r="W38" s="16" t="n">
-        <v>5.90028</v>
+        <v>5.9</v>
       </c>
       <c r="X38" s="16" t="n">
-        <v>63.2489</v>
+        <v>63.25</v>
       </c>
       <c r="Y38" s="16" t="n">
-        <v>64.2338</v>
+        <v>64.23</v>
       </c>
       <c r="Z38" s="16" t="n">
-        <v>64.7209</v>
+        <v>64.72</v>
       </c>
       <c r="AA38" s="16" t="n">
-        <v>65.6429</v>
+        <v>65.64</v>
       </c>
       <c r="AB38" s="16" t="n">
-        <v>63.0796</v>
+        <v>63.08</v>
       </c>
       <c r="AC38" s="16" t="n">
-        <v>64.0748</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="AD38" s="16" t="n">
-        <v>64.5448</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="AE38" s="16" t="n">
-        <v>65.4285</v>
+        <v>65.43000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -3926,28 +3926,28 @@
         </is>
       </c>
       <c r="F39" s="16" t="n">
-        <v>48.4</v>
+        <v>48.43</v>
       </c>
       <c r="G39" s="16" t="n">
-        <v>85.3</v>
+        <v>85.31999999999999</v>
       </c>
       <c r="H39" s="16" t="n">
-        <v>32.6</v>
+        <v>32.55</v>
       </c>
       <c r="J39" s="16" t="n">
-        <v>143.1</v>
+        <v>143.11</v>
       </c>
       <c r="K39" s="16" t="n">
         <v>1.79</v>
       </c>
       <c r="L39" s="16" t="n">
-        <v>6</v>
+        <v>5.98</v>
       </c>
       <c r="M39" s="16" t="n">
         <v>6.1</v>
       </c>
       <c r="O39" s="16" t="n">
-        <v>44.7</v>
+        <v>44.68</v>
       </c>
       <c r="P39" s="16" t="n">
         <v>-2.48</v>
@@ -3965,34 +3965,34 @@
         <v>25</v>
       </c>
       <c r="V39" s="16" t="n">
-        <v>82.68300000000001</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="W39" s="16" t="n">
-        <v>7.89385</v>
+        <v>7.89</v>
       </c>
       <c r="X39" s="16" t="n">
-        <v>62.3498</v>
+        <v>62.35</v>
       </c>
       <c r="Y39" s="16" t="n">
-        <v>63.6674</v>
+        <v>63.67</v>
       </c>
       <c r="Z39" s="16" t="n">
-        <v>64.3192</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="AA39" s="16" t="n">
-        <v>65.5527</v>
+        <v>65.55</v>
       </c>
       <c r="AB39" s="16" t="n">
-        <v>60.1772</v>
+        <v>60.18</v>
       </c>
       <c r="AC39" s="16" t="n">
-        <v>61.6659</v>
+        <v>61.67</v>
       </c>
       <c r="AD39" s="16" t="n">
-        <v>62.4197</v>
+        <v>62.42</v>
       </c>
       <c r="AE39" s="16" t="n">
-        <v>63.8438</v>
+        <v>63.84</v>
       </c>
     </row>
     <row r="40">
@@ -4015,37 +4015,37 @@
         </is>
       </c>
       <c r="F40" s="16" t="n">
-        <v>50.6</v>
+        <v>50.55</v>
       </c>
       <c r="G40" s="16" t="n">
-        <v>87.09999999999999</v>
+        <v>87.06</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>25.8</v>
+        <v>25.79</v>
       </c>
       <c r="J40" s="16" t="n">
-        <v>145.6</v>
+        <v>145.58</v>
       </c>
       <c r="K40" s="16" t="n">
         <v>1.89</v>
       </c>
       <c r="L40" s="16" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="M40" s="16" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="O40" s="16" t="n">
-        <v>41.6</v>
+        <v>41.61</v>
       </c>
       <c r="P40" s="16" t="n">
         <v>-2.62</v>
       </c>
       <c r="Q40" s="16" t="n">
-        <v>8.9</v>
+        <v>8.93</v>
       </c>
       <c r="R40" s="16" t="n">
-        <v>9.4</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="T40" s="16" t="n">
         <v>4985</v>
@@ -4054,34 +4054,34 @@
         <v>25</v>
       </c>
       <c r="V40" s="16" t="n">
-        <v>77.7771</v>
+        <v>77.78</v>
       </c>
       <c r="W40" s="16" t="n">
-        <v>10.8169</v>
+        <v>10.82</v>
       </c>
       <c r="X40" s="16" t="n">
-        <v>49.9147</v>
+        <v>49.91</v>
       </c>
       <c r="Y40" s="16" t="n">
-        <v>51.7202</v>
+        <v>51.72</v>
       </c>
       <c r="Z40" s="16" t="n">
-        <v>52.6133</v>
+        <v>52.61</v>
       </c>
       <c r="AA40" s="16" t="n">
-        <v>54.3035</v>
+        <v>54.3</v>
       </c>
       <c r="AB40" s="16" t="n">
-        <v>50.9725</v>
+        <v>50.97</v>
       </c>
       <c r="AC40" s="16" t="n">
-        <v>52.5491</v>
+        <v>52.55</v>
       </c>
       <c r="AD40" s="16" t="n">
-        <v>53.334</v>
+        <v>53.33</v>
       </c>
       <c r="AE40" s="16" t="n">
-        <v>54.7985</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="41">
@@ -4104,16 +4104,16 @@
         </is>
       </c>
       <c r="F41" s="16" t="n">
-        <v>55.2</v>
+        <v>55.25</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>17.5</v>
+        <v>17.54</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>19.3</v>
+        <v>19.28</v>
       </c>
       <c r="J41" s="16" t="n">
-        <v>139</v>
+        <v>139.03</v>
       </c>
       <c r="K41" s="16" t="n">
         <v>1.61</v>
@@ -4122,7 +4122,7 @@
         <v>7</v>
       </c>
       <c r="M41" s="16" t="n">
-        <v>6.7</v>
+        <v>6.66</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>49.9</v>
@@ -4131,10 +4131,10 @@
         <v>-2.26</v>
       </c>
       <c r="Q41" s="16" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="R41" s="16" t="n">
-        <v>6.7</v>
+        <v>6.66</v>
       </c>
       <c r="T41" s="16" t="n">
         <v>4946</v>
@@ -4143,34 +4143,34 @@
         <v>25</v>
       </c>
       <c r="V41" s="16" t="n">
-        <v>76.28879999999999</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="W41" s="16" t="n">
-        <v>8.077199999999999</v>
+        <v>8.08</v>
       </c>
       <c r="X41" s="16" t="n">
-        <v>55.4833</v>
+        <v>55.48</v>
       </c>
       <c r="Y41" s="16" t="n">
-        <v>56.8315</v>
+        <v>56.83</v>
       </c>
       <c r="Z41" s="16" t="n">
-        <v>57.4984</v>
+        <v>57.5</v>
       </c>
       <c r="AA41" s="16" t="n">
-        <v>58.7605</v>
+        <v>58.76</v>
       </c>
       <c r="AB41" s="16" t="n">
-        <v>55.8865</v>
+        <v>55.89</v>
       </c>
       <c r="AC41" s="16" t="n">
-        <v>56.9763</v>
+        <v>56.98</v>
       </c>
       <c r="AD41" s="16" t="n">
-        <v>57.5098</v>
+        <v>57.51</v>
       </c>
       <c r="AE41" s="16" t="n">
-        <v>58.5539</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="42">
@@ -4193,37 +4193,37 @@
         </is>
       </c>
       <c r="F42" s="16" t="n">
-        <v>62.7</v>
+        <v>62.71</v>
       </c>
       <c r="G42" s="16" t="n">
-        <v>18.7</v>
+        <v>18.65</v>
       </c>
       <c r="H42" s="16" t="n">
         <v>19.3</v>
       </c>
       <c r="J42" s="16" t="n">
-        <v>144</v>
+        <v>143.96</v>
       </c>
       <c r="K42" s="16" t="n">
         <v>1.82</v>
       </c>
       <c r="L42" s="16" t="n">
-        <v>6.5</v>
+        <v>6.46</v>
       </c>
       <c r="M42" s="16" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="O42" s="16" t="n">
-        <v>45.7</v>
+        <v>45.72</v>
       </c>
       <c r="P42" s="16" t="n">
         <v>-2.44</v>
       </c>
       <c r="Q42" s="16" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="R42" s="16" t="n">
-        <v>5.5</v>
+        <v>5.49</v>
       </c>
       <c r="T42" s="16" t="n">
         <v>4931</v>
@@ -4232,34 +4232,34 @@
         <v>25</v>
       </c>
       <c r="V42" s="16" t="n">
-        <v>81.5474</v>
+        <v>81.55</v>
       </c>
       <c r="W42" s="16" t="n">
-        <v>7.92414</v>
+        <v>7.92</v>
       </c>
       <c r="X42" s="16" t="n">
-        <v>61.1362</v>
+        <v>61.14</v>
       </c>
       <c r="Y42" s="16" t="n">
-        <v>62.4588</v>
+        <v>62.46</v>
       </c>
       <c r="Z42" s="16" t="n">
-        <v>63.1131</v>
+        <v>63.11</v>
       </c>
       <c r="AA42" s="16" t="n">
-        <v>64.35129999999999</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="AB42" s="16" t="n">
-        <v>60.9347</v>
+        <v>60.93</v>
       </c>
       <c r="AC42" s="16" t="n">
-        <v>62.1676</v>
+        <v>62.17</v>
       </c>
       <c r="AD42" s="16" t="n">
-        <v>62.7677</v>
+        <v>62.77</v>
       </c>
       <c r="AE42" s="16" t="n">
-        <v>63.8991</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="43">
@@ -4282,37 +4282,37 @@
         </is>
       </c>
       <c r="F43" s="16" t="n">
-        <v>51.4</v>
+        <v>51.45</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>85.2</v>
+        <v>85.22</v>
       </c>
       <c r="H43" s="16" t="n">
         <v>33.4</v>
       </c>
       <c r="J43" s="16" t="n">
-        <v>141.3</v>
+        <v>141.34</v>
       </c>
       <c r="K43" s="16" t="n">
         <v>1.71</v>
       </c>
       <c r="L43" s="16" t="n">
-        <v>5.1</v>
+        <v>5.07</v>
       </c>
       <c r="M43" s="16" t="n">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
       <c r="O43" s="16" t="n">
-        <v>39.5</v>
+        <v>39.49</v>
       </c>
       <c r="P43" s="16" t="n">
         <v>-2.71</v>
       </c>
       <c r="Q43" s="16" t="n">
-        <v>6.1</v>
+        <v>6.11</v>
       </c>
       <c r="R43" s="16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="T43" s="16" t="n">
         <v>4909</v>
@@ -4321,34 +4321,34 @@
         <v>25</v>
       </c>
       <c r="V43" s="16" t="n">
-        <v>83.947</v>
+        <v>83.95</v>
       </c>
       <c r="W43" s="16" t="n">
-        <v>9.09854</v>
+        <v>9.1</v>
       </c>
       <c r="X43" s="16" t="n">
-        <v>60.5107</v>
+        <v>60.51</v>
       </c>
       <c r="Y43" s="16" t="n">
-        <v>62.0294</v>
+        <v>62.03</v>
       </c>
       <c r="Z43" s="16" t="n">
-        <v>62.7806</v>
+        <v>62.78</v>
       </c>
       <c r="AA43" s="16" t="n">
-        <v>64.2024</v>
+        <v>64.2</v>
       </c>
       <c r="AB43" s="16" t="n">
-        <v>58.5424</v>
+        <v>58.54</v>
       </c>
       <c r="AC43" s="16" t="n">
-        <v>60.0801</v>
+        <v>60.08</v>
       </c>
       <c r="AD43" s="16" t="n">
-        <v>60.8688</v>
+        <v>60.87</v>
       </c>
       <c r="AE43" s="16" t="n">
-        <v>62.4435</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="44">
@@ -4371,37 +4371,37 @@
         </is>
       </c>
       <c r="F44" s="16" t="n">
-        <v>58.7</v>
+        <v>58.67</v>
       </c>
       <c r="G44" s="16" t="n">
-        <v>12.2</v>
+        <v>12.21</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>11.9</v>
+        <v>11.87</v>
       </c>
       <c r="J44" s="16" t="n">
-        <v>150.9</v>
+        <v>150.87</v>
       </c>
       <c r="K44" s="16" t="n">
         <v>2.12</v>
       </c>
       <c r="L44" s="16" t="n">
-        <v>7.1</v>
+        <v>7.07</v>
       </c>
       <c r="M44" s="16" t="n">
-        <v>5.6</v>
+        <v>5.56</v>
       </c>
       <c r="O44" s="16" t="n">
-        <v>61.4</v>
+        <v>61.43</v>
       </c>
       <c r="P44" s="16" t="n">
         <v>-1.76</v>
       </c>
       <c r="Q44" s="16" t="n">
-        <v>7</v>
+        <v>6.99</v>
       </c>
       <c r="R44" s="16" t="n">
-        <v>6.8</v>
+        <v>6.77</v>
       </c>
       <c r="T44" s="16" t="n">
         <v>4909</v>
@@ -4410,34 +4410,34 @@
         <v>25</v>
       </c>
       <c r="V44" s="16" t="n">
-        <v>73.0877</v>
+        <v>73.09</v>
       </c>
       <c r="W44" s="16" t="n">
-        <v>6.7003</v>
+        <v>6.7</v>
       </c>
       <c r="X44" s="16" t="n">
-        <v>55.8288</v>
+        <v>55.83</v>
       </c>
       <c r="Y44" s="16" t="n">
-        <v>56.9472</v>
+        <v>56.95</v>
       </c>
       <c r="Z44" s="16" t="n">
-        <v>57.5004</v>
+        <v>57.5</v>
       </c>
       <c r="AA44" s="16" t="n">
-        <v>58.5474</v>
+        <v>58.55</v>
       </c>
       <c r="AB44" s="16" t="n">
-        <v>56.2126</v>
+        <v>56.21</v>
       </c>
       <c r="AC44" s="16" t="n">
-        <v>57.234</v>
+        <v>57.23</v>
       </c>
       <c r="AD44" s="16" t="n">
-        <v>57.7346</v>
+        <v>57.73</v>
       </c>
       <c r="AE44" s="16" t="n">
-        <v>58.6853</v>
+        <v>58.69</v>
       </c>
     </row>
     <row r="45">
@@ -4460,37 +4460,37 @@
         </is>
       </c>
       <c r="F45" s="16" t="n">
-        <v>58.4</v>
+        <v>58.44</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>11.9</v>
+        <v>11.89</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>12.9</v>
+        <v>12.88</v>
       </c>
       <c r="J45" s="16" t="n">
-        <v>147.3</v>
+        <v>147.29</v>
       </c>
       <c r="K45" s="16" t="n">
         <v>1.97</v>
       </c>
       <c r="L45" s="16" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
       <c r="M45" s="16" t="n">
-        <v>5.6</v>
+        <v>5.56</v>
       </c>
       <c r="O45" s="16" t="n">
-        <v>57.1</v>
+        <v>57.07</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>-1.94</v>
+        <v>-1.95</v>
       </c>
       <c r="Q45" s="16" t="n">
-        <v>6.9</v>
+        <v>6.87</v>
       </c>
       <c r="R45" s="16" t="n">
-        <v>54.6</v>
+        <v>6.45</v>
       </c>
       <c r="T45" s="16" t="n">
         <v>4938</v>
@@ -4499,34 +4499,34 @@
         <v>25</v>
       </c>
       <c r="V45" s="16" t="n">
-        <v>74.395</v>
+        <v>74.39</v>
       </c>
       <c r="W45" s="16" t="n">
-        <v>6.44363</v>
+        <v>6.44</v>
       </c>
       <c r="X45" s="16" t="n">
-        <v>57.7973</v>
+        <v>57.8</v>
       </c>
       <c r="Y45" s="16" t="n">
-        <v>58.8728</v>
+        <v>58.87</v>
       </c>
       <c r="Z45" s="16" t="n">
-        <v>59.4049</v>
+        <v>59.4</v>
       </c>
       <c r="AA45" s="16" t="n">
-        <v>60.4117</v>
+        <v>60.41</v>
       </c>
       <c r="AB45" s="16" t="n">
-        <v>58.323</v>
+        <v>58.32</v>
       </c>
       <c r="AC45" s="16" t="n">
-        <v>59.3275</v>
+        <v>59.33</v>
       </c>
       <c r="AD45" s="16" t="n">
-        <v>59.821</v>
+        <v>59.82</v>
       </c>
       <c r="AE45" s="16" t="n">
-        <v>60.7325</v>
+        <v>60.73</v>
       </c>
     </row>
     <row r="46">
@@ -4549,37 +4549,37 @@
         </is>
       </c>
       <c r="F46" s="16" t="n">
-        <v>82.5</v>
+        <v>67.73</v>
       </c>
       <c r="G46" s="16" t="n">
-        <v>11.4</v>
+        <v>11.44</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>3.9</v>
+        <v>7.7</v>
       </c>
       <c r="J46" s="16" t="n">
-        <v>161.4</v>
+        <v>161.41</v>
       </c>
       <c r="K46" s="16" t="n">
         <v>2.58</v>
       </c>
       <c r="L46" s="16" t="n">
-        <v>11.4</v>
+        <v>11.35</v>
       </c>
       <c r="M46" s="16" t="n">
-        <v>10.2</v>
+        <v>10.25</v>
       </c>
       <c r="O46" s="16" t="n">
-        <v>60.1</v>
+        <v>60.11</v>
       </c>
       <c r="P46" s="16" t="n">
         <v>-1.81</v>
       </c>
       <c r="Q46" s="16" t="n">
-        <v>7.8</v>
+        <v>7.77</v>
       </c>
       <c r="R46" s="16" t="n">
-        <v>7.6</v>
+        <v>7.65</v>
       </c>
       <c r="T46" s="16" t="n">
         <v>4940</v>
@@ -4588,34 +4588,34 @@
         <v>25</v>
       </c>
       <c r="V46" s="16" t="n">
-        <v>81.16889999999999</v>
+        <v>81.17</v>
       </c>
       <c r="W46" s="16" t="n">
-        <v>5.51797</v>
+        <v>5.52</v>
       </c>
       <c r="X46" s="16" t="n">
-        <v>66.9555</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="Y46" s="16" t="n">
-        <v>67.8766</v>
+        <v>67.88</v>
       </c>
       <c r="Z46" s="16" t="n">
-        <v>68.3322</v>
+        <v>68.33</v>
       </c>
       <c r="AA46" s="16" t="n">
-        <v>69.1944</v>
+        <v>69.19</v>
       </c>
       <c r="AB46" s="16" t="n">
-        <v>66.7513</v>
+        <v>66.75</v>
       </c>
       <c r="AC46" s="16" t="n">
-        <v>67.7276</v>
+        <v>67.73</v>
       </c>
       <c r="AD46" s="16" t="n">
-        <v>68.19840000000001</v>
+        <v>68.2</v>
       </c>
       <c r="AE46" s="16" t="n">
-        <v>69.0681</v>
+        <v>69.06999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -4638,37 +4638,37 @@
         </is>
       </c>
       <c r="F47" s="16" t="n">
-        <v>48.3</v>
+        <v>48.31</v>
       </c>
       <c r="G47" s="16" t="n">
-        <v>104.8</v>
+        <v>104.82</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>51.6</v>
+        <v>51.64</v>
       </c>
       <c r="J47" s="16" t="n">
-        <v>152.6</v>
+        <v>152.61</v>
       </c>
       <c r="K47" s="16" t="n">
         <v>2.2</v>
       </c>
       <c r="L47" s="16" t="n">
-        <v>6</v>
+        <v>5.98</v>
       </c>
       <c r="M47" s="16" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="O47" s="16" t="n">
-        <v>46.4</v>
+        <v>46.38</v>
       </c>
       <c r="P47" s="16" t="n">
         <v>-2.41</v>
       </c>
       <c r="Q47" s="16" t="n">
-        <v>12.2</v>
+        <v>12.18</v>
       </c>
       <c r="R47" s="16" t="n">
-        <v>14.1</v>
+        <v>14.06</v>
       </c>
       <c r="T47" s="16" t="n">
         <v>4890</v>
@@ -4677,34 +4677,34 @@
         <v>25</v>
       </c>
       <c r="V47" s="16" t="n">
-        <v>91.6985</v>
+        <v>91.7</v>
       </c>
       <c r="W47" s="16" t="n">
-        <v>7.23364</v>
+        <v>7.23</v>
       </c>
       <c r="X47" s="16" t="n">
-        <v>73.0658</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="Y47" s="16" t="n">
-        <v>74.2732</v>
+        <v>74.27</v>
       </c>
       <c r="Z47" s="16" t="n">
-        <v>74.87050000000001</v>
+        <v>74.87</v>
       </c>
       <c r="AA47" s="16" t="n">
-        <v>76.0008</v>
+        <v>76</v>
       </c>
       <c r="AB47" s="16" t="n">
-        <v>71.60760000000001</v>
+        <v>71.61</v>
       </c>
       <c r="AC47" s="16" t="n">
-        <v>72.9807</v>
+        <v>72.98</v>
       </c>
       <c r="AD47" s="16" t="n">
-        <v>73.6249</v>
+        <v>73.62</v>
       </c>
       <c r="AE47" s="16" t="n">
-        <v>74.8154</v>
+        <v>74.81999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -4727,37 +4727,37 @@
         </is>
       </c>
       <c r="F48" s="16" t="n">
-        <v>62.5</v>
+        <v>62.47</v>
       </c>
       <c r="G48" s="16" t="n">
-        <v>34.2</v>
+        <v>34.18</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>24.5</v>
+        <v>24.49</v>
       </c>
       <c r="J48" s="16" t="n">
-        <v>145.4</v>
+        <v>145.35</v>
       </c>
       <c r="K48" s="16" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="L48" s="16" t="n">
-        <v>31.1</v>
+        <v>31.14</v>
       </c>
       <c r="M48" s="16" t="n">
         <v>16.3</v>
       </c>
       <c r="O48" s="16" t="n">
-        <v>51.7</v>
+        <v>51.66</v>
       </c>
       <c r="P48" s="16" t="n">
         <v>-2.18</v>
       </c>
       <c r="Q48" s="16" t="n">
-        <v>6.1</v>
+        <v>6.13</v>
       </c>
       <c r="R48" s="16" t="n">
-        <v>5.8</v>
+        <v>5.78</v>
       </c>
       <c r="T48" s="16" t="n">
         <v>4935</v>
@@ -4766,34 +4766,34 @@
         <v>25</v>
       </c>
       <c r="V48" s="16" t="n">
-        <v>82.2067</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="W48" s="16" t="n">
-        <v>6.96787</v>
+        <v>6.97</v>
       </c>
       <c r="X48" s="16" t="n">
-        <v>64.2587</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="Y48" s="16" t="n">
-        <v>65.4217</v>
+        <v>65.42</v>
       </c>
       <c r="Z48" s="16" t="n">
-        <v>65.9971</v>
+        <v>66</v>
       </c>
       <c r="AA48" s="16" t="n">
-        <v>67.08580000000001</v>
+        <v>67.09</v>
       </c>
       <c r="AB48" s="16" t="n">
-        <v>63.9833</v>
+        <v>63.98</v>
       </c>
       <c r="AC48" s="16" t="n">
-        <v>65.07259999999999</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="AD48" s="16" t="n">
-        <v>65.60290000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AE48" s="16" t="n">
-        <v>66.6221</v>
+        <v>66.62</v>
       </c>
     </row>
     <row r="49">
@@ -4822,31 +4822,31 @@
         <v>25.7</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="J49" s="16" t="n">
-        <v>152.7</v>
+        <v>152.71</v>
       </c>
       <c r="K49" s="16" t="n">
         <v>2.2</v>
       </c>
       <c r="L49" s="16" t="n">
-        <v>25.6</v>
+        <v>25.61</v>
       </c>
       <c r="M49" s="16" t="n">
-        <v>4.7</v>
+        <v>4.69</v>
       </c>
       <c r="O49" s="16" t="n">
-        <v>58.2</v>
+        <v>58.25</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>-1.9</v>
+        <v>-1.89</v>
       </c>
       <c r="Q49" s="16" t="n">
         <v>7.8</v>
       </c>
       <c r="R49" s="16" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
       <c r="T49" s="16" t="n">
         <v>4934</v>
@@ -4855,34 +4855,34 @@
         <v>25</v>
       </c>
       <c r="V49" s="16" t="n">
-        <v>75.6027</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="W49" s="16" t="n">
-        <v>7.06523</v>
+        <v>7.07</v>
       </c>
       <c r="X49" s="16" t="n">
-        <v>57.4038</v>
+        <v>57.4</v>
       </c>
       <c r="Y49" s="16" t="n">
-        <v>58.5831</v>
+        <v>58.58</v>
       </c>
       <c r="Z49" s="16" t="n">
-        <v>59.1665</v>
+        <v>59.17</v>
       </c>
       <c r="AA49" s="16" t="n">
-        <v>60.2705</v>
+        <v>60.27</v>
       </c>
       <c r="AB49" s="16" t="n">
-        <v>57.5788</v>
+        <v>57.58</v>
       </c>
       <c r="AC49" s="16" t="n">
-        <v>58.7068</v>
+        <v>58.71</v>
       </c>
       <c r="AD49" s="16" t="n">
-        <v>59.2283</v>
+        <v>59.23</v>
       </c>
       <c r="AE49" s="16" t="n">
-        <v>60.1915</v>
+        <v>60.19</v>
       </c>
     </row>
     <row r="50">
@@ -4905,34 +4905,34 @@
         </is>
       </c>
       <c r="F50" s="16" t="n">
-        <v>68.40000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="G50" s="16" t="n">
-        <v>10.4</v>
+        <v>10.44</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>7.5</v>
+        <v>7.55</v>
       </c>
       <c r="J50" s="16" t="n">
-        <v>158.9</v>
+        <v>158.86</v>
       </c>
       <c r="K50" s="16" t="n">
         <v>2.47</v>
       </c>
       <c r="L50" s="16" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="M50" s="16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O50" s="16" t="n">
-        <v>51.9</v>
+        <v>51.91</v>
       </c>
       <c r="P50" s="16" t="n">
         <v>-2.17</v>
       </c>
       <c r="Q50" s="16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="R50" s="16" t="n">
         <v>8.300000000000001</v>
@@ -4944,34 +4944,34 @@
         <v>25</v>
       </c>
       <c r="V50" s="16" t="n">
-        <v>79.7657</v>
+        <v>79.77</v>
       </c>
       <c r="W50" s="16" t="n">
-        <v>5.2649</v>
+        <v>5.26</v>
       </c>
       <c r="X50" s="16" t="n">
-        <v>66.2042</v>
+        <v>66.2</v>
       </c>
       <c r="Y50" s="16" t="n">
-        <v>67.083</v>
+        <v>67.08</v>
       </c>
       <c r="Z50" s="16" t="n">
-        <v>67.5177</v>
+        <v>67.52</v>
       </c>
       <c r="AA50" s="16" t="n">
-        <v>68.3404</v>
+        <v>68.34</v>
       </c>
       <c r="AB50" s="16" t="n">
-        <v>64.3464</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="AC50" s="16" t="n">
-        <v>65.5279</v>
+        <v>65.53</v>
       </c>
       <c r="AD50" s="16" t="n">
-        <v>66.1712</v>
+        <v>66.17</v>
       </c>
       <c r="AE50" s="16" t="n">
-        <v>67.4205</v>
+        <v>67.42</v>
       </c>
     </row>
   </sheetData>
@@ -5744,7 +5744,7 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>One row per quencher. DFT values are rounded to 1 decimal in kcal/mol and 2 in V.</t>
+          <t>One row per quencher. DFT values are rounded to 2 decimals in kcal/mol and V.</t>
         </is>
       </c>
       <c r="B30" s="18" t="n"/>

--- a/data/computational_data_processed/quencher_properties_calc.xlsx
+++ b/data/computational_data_processed/quencher_properties_calc.xlsx
@@ -36,7 +36,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +68,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE2F6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -86,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -108,6 +113,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -121,6 +129,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -496,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE50"/>
+  <dimension ref="A1:AG50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -530,6 +541,8 @@
     <col width="29" customWidth="1" min="29" max="29"/>
     <col width="28" customWidth="1" min="30" max="30"/>
     <col width="29" customWidth="1" min="31" max="31"/>
+    <col width="2" customWidth="1" min="32" max="32"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -580,4398 +593,4552 @@
       <c r="AC1" s="10" t="n"/>
       <c r="AD1" s="10" t="n"/>
       <c r="AE1" s="10" t="n"/>
+      <c r="AG1" s="11" t="inlineStr">
+        <is>
+          <t>Molecular size, DFT / A</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>quencher_id</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>quencher_name</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>compound</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>smiles</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>E_T / kcal mol-1</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>lambda_S0_T1 / kcal mol-1</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>lambda_T1_S0 / kcal mol-1</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>dG_Ox / kcal mol-1</t>
         </is>
       </c>
-      <c r="K2" s="13" t="inlineStr">
+      <c r="K2" s="14" t="inlineStr">
         <is>
           <t>E_Ox_vs_SCE_calc / V</t>
         </is>
       </c>
-      <c r="L2" s="13" t="inlineStr">
+      <c r="L2" s="14" t="inlineStr">
         <is>
           <t>lambda_S0_Dplus / kcal mol-1</t>
         </is>
       </c>
-      <c r="M2" s="13" t="inlineStr">
+      <c r="M2" s="14" t="inlineStr">
         <is>
           <t>lambda_Dplus_S0 / kcal mol-1</t>
         </is>
       </c>
-      <c r="O2" s="14" t="inlineStr">
+      <c r="O2" s="15" t="inlineStr">
         <is>
           <t>dG_Red / kcal mol-1</t>
         </is>
       </c>
-      <c r="P2" s="14" t="inlineStr">
+      <c r="P2" s="15" t="inlineStr">
         <is>
           <t>E_Red_vs_SCE_calc / V</t>
         </is>
       </c>
-      <c r="Q2" s="14" t="inlineStr">
+      <c r="Q2" s="15" t="inlineStr">
         <is>
           <t>lambda_S0_Dminus / kcal mol-1</t>
         </is>
       </c>
-      <c r="R2" s="14" t="inlineStr">
+      <c r="R2" s="15" t="inlineStr">
         <is>
           <t>lambda_Dminus_S0 / kcal mol-1</t>
         </is>
       </c>
-      <c r="T2" s="15" t="inlineStr">
+      <c r="T2" s="16" t="inlineStr">
         <is>
           <t>n_samples</t>
         </is>
       </c>
-      <c r="U2" s="15" t="inlineStr">
+      <c r="U2" s="16" t="inlineStr">
         <is>
           <t>n_trajectories</t>
         </is>
       </c>
-      <c r="V2" s="15" t="inlineStr">
+      <c r="V2" s="16" t="inlineStr">
         <is>
           <t>dvte_mu / kcal mol-1</t>
         </is>
       </c>
-      <c r="W2" s="15" t="inlineStr">
+      <c r="W2" s="16" t="inlineStr">
         <is>
           <t>dvte_std / kcal mol-1</t>
         </is>
       </c>
-      <c r="X2" s="15" t="inlineStr">
+      <c r="X2" s="16" t="inlineStr">
         <is>
           <t>dvte_0.005 / kcal mol-1</t>
         </is>
       </c>
-      <c r="Y2" s="15" t="inlineStr">
+      <c r="Y2" s="16" t="inlineStr">
         <is>
           <t>dvte_0.008 / kcal mol-1</t>
         </is>
       </c>
-      <c r="Z2" s="15" t="inlineStr">
+      <c r="Z2" s="16" t="inlineStr">
         <is>
           <t>dvte_0.01 / kcal mol-1</t>
         </is>
       </c>
-      <c r="AA2" s="15" t="inlineStr">
+      <c r="AA2" s="16" t="inlineStr">
         <is>
           <t>dvte_0.015 / kcal mol-1</t>
         </is>
       </c>
-      <c r="AB2" s="15" t="inlineStr">
+      <c r="AB2" s="16" t="inlineStr">
         <is>
           <t>dvte_0.005_kde / kcal mol-1</t>
         </is>
       </c>
-      <c r="AC2" s="15" t="inlineStr">
+      <c r="AC2" s="16" t="inlineStr">
         <is>
           <t>dvte_0.008_kde / kcal mol-1</t>
         </is>
       </c>
-      <c r="AD2" s="15" t="inlineStr">
+      <c r="AD2" s="16" t="inlineStr">
         <is>
           <t>dvte_0.01_kde / kcal mol-1</t>
         </is>
       </c>
-      <c r="AE2" s="15" t="inlineStr">
+      <c r="AE2" s="16" t="inlineStr">
         <is>
           <t>dvte_0.015_kde / kcal mol-1</t>
         </is>
       </c>
+      <c r="AG2" s="17" t="inlineStr">
+        <is>
+          <t>radius_S0 / A</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>6-methylquinoline</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>CC1=CC=C2C(C=CC=N2)=C1</t>
         </is>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="18" t="n">
         <v>60.18</v>
       </c>
-      <c r="G3" s="16" t="n">
+      <c r="G3" s="18" t="n">
         <v>14.37</v>
       </c>
-      <c r="H3" s="16" t="n">
+      <c r="H3" s="18" t="n">
         <v>15.81</v>
       </c>
-      <c r="J3" s="16" t="n">
+      <c r="J3" s="18" t="n">
         <v>144.48</v>
       </c>
-      <c r="K3" s="16" t="n">
+      <c r="K3" s="18" t="n">
         <v>1.85</v>
       </c>
-      <c r="L3" s="16" t="n">
+      <c r="L3" s="18" t="n">
         <v>4.51</v>
       </c>
-      <c r="M3" s="16" t="n">
+      <c r="M3" s="18" t="n">
         <v>4.14</v>
       </c>
-      <c r="O3" s="16" t="n">
+      <c r="O3" s="18" t="n">
         <v>49.93</v>
       </c>
-      <c r="P3" s="16" t="n">
+      <c r="P3" s="18" t="n">
         <v>-2.25</v>
       </c>
-      <c r="Q3" s="16" t="n">
+      <c r="Q3" s="18" t="n">
         <v>4.93</v>
       </c>
-      <c r="R3" s="16" t="n">
+      <c r="R3" s="18" t="n">
         <v>4.49</v>
       </c>
-      <c r="T3" s="16" t="n">
+      <c r="T3" s="18" t="n">
         <v>4865</v>
       </c>
-      <c r="U3" s="16" t="n">
+      <c r="U3" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V3" s="16" t="n">
+      <c r="V3" s="18" t="n">
         <v>76.19</v>
       </c>
-      <c r="W3" s="16" t="n">
+      <c r="W3" s="18" t="n">
         <v>7.14</v>
       </c>
-      <c r="X3" s="16" t="n">
+      <c r="X3" s="18" t="n">
         <v>57.79</v>
       </c>
-      <c r="Y3" s="16" t="n">
+      <c r="Y3" s="18" t="n">
         <v>58.98</v>
       </c>
-      <c r="Z3" s="16" t="n">
+      <c r="Z3" s="18" t="n">
         <v>59.57</v>
       </c>
-      <c r="AA3" s="16" t="n">
+      <c r="AA3" s="18" t="n">
         <v>60.69</v>
       </c>
-      <c r="AB3" s="16" t="n">
+      <c r="AB3" s="18" t="n">
         <v>56.93</v>
       </c>
-      <c r="AC3" s="16" t="n">
+      <c r="AC3" s="18" t="n">
         <v>58.14</v>
       </c>
-      <c r="AD3" s="16" t="n">
+      <c r="AD3" s="18" t="n">
         <v>58.72</v>
       </c>
-      <c r="AE3" s="16" t="n">
+      <c r="AE3" s="18" t="n">
         <v>59.85</v>
       </c>
+      <c r="AG3" s="18" t="n">
+        <v>3.21</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>styrene</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>C=CC1=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="18" t="n">
         <v>52.17</v>
       </c>
-      <c r="G4" s="16" t="n">
+      <c r="G4" s="18" t="n">
         <v>85.95999999999999</v>
       </c>
-      <c r="H4" s="16" t="n">
+      <c r="H4" s="18" t="n">
         <v>26.65</v>
       </c>
-      <c r="J4" s="16" t="n">
+      <c r="J4" s="18" t="n">
         <v>142.92</v>
       </c>
-      <c r="K4" s="16" t="n">
+      <c r="K4" s="18" t="n">
         <v>1.78</v>
       </c>
-      <c r="L4" s="16" t="n">
+      <c r="L4" s="18" t="n">
         <v>4.4</v>
       </c>
-      <c r="M4" s="16" t="n">
+      <c r="M4" s="18" t="n">
         <v>4.39</v>
       </c>
-      <c r="O4" s="16" t="n">
+      <c r="O4" s="18" t="n">
         <v>41.41</v>
       </c>
-      <c r="P4" s="16" t="n">
+      <c r="P4" s="18" t="n">
         <v>-2.62</v>
       </c>
-      <c r="Q4" s="16" t="n">
+      <c r="Q4" s="18" t="n">
         <v>5.47</v>
       </c>
-      <c r="R4" s="16" t="n">
+      <c r="R4" s="18" t="n">
         <v>5.09</v>
       </c>
-      <c r="T4" s="16" t="n">
+      <c r="T4" s="18" t="n">
         <v>4877</v>
       </c>
-      <c r="U4" s="16" t="n">
+      <c r="U4" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V4" s="16" t="n">
+      <c r="V4" s="18" t="n">
         <v>81.34999999999999</v>
       </c>
-      <c r="W4" s="16" t="n">
+      <c r="W4" s="18" t="n">
         <v>9.08</v>
       </c>
-      <c r="X4" s="16" t="n">
+      <c r="X4" s="18" t="n">
         <v>57.96</v>
       </c>
-      <c r="Y4" s="16" t="n">
+      <c r="Y4" s="18" t="n">
         <v>59.47</v>
       </c>
-      <c r="Z4" s="16" t="n">
+      <c r="Z4" s="18" t="n">
         <v>60.22</v>
       </c>
-      <c r="AA4" s="16" t="n">
+      <c r="AA4" s="18" t="n">
         <v>61.64</v>
       </c>
-      <c r="AB4" s="16" t="n">
+      <c r="AB4" s="18" t="n">
         <v>56.87</v>
       </c>
-      <c r="AC4" s="16" t="n">
+      <c r="AC4" s="18" t="n">
         <v>58.39</v>
       </c>
-      <c r="AD4" s="16" t="n">
+      <c r="AD4" s="18" t="n">
         <v>59.1</v>
       </c>
-      <c r="AE4" s="16" t="n">
+      <c r="AE4" s="18" t="n">
         <v>60.39</v>
       </c>
+      <c r="AG4" s="18" t="n">
+        <v>2.98</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>1,3-dimethyl-2-nitrobenzene</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>CC1=C(C(=CC=C1)C)[N+](=O)[O-]</t>
         </is>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="18" t="n">
         <v>60.8</v>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="18" t="n">
         <v>32.35</v>
       </c>
-      <c r="H5" s="16" t="n">
+      <c r="H5" s="18" t="n">
         <v>17.39</v>
       </c>
-      <c r="J5" s="16" t="n">
+      <c r="J5" s="18" t="n">
         <v>155.5</v>
       </c>
-      <c r="K5" s="16" t="n">
+      <c r="K5" s="18" t="n">
         <v>2.32</v>
       </c>
-      <c r="L5" s="16" t="n">
+      <c r="L5" s="18" t="n">
         <v>5.25</v>
       </c>
-      <c r="M5" s="16" t="n">
+      <c r="M5" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="O5" s="16" t="n">
+      <c r="O5" s="18" t="n">
         <v>73.03</v>
       </c>
-      <c r="P5" s="16" t="n">
+      <c r="P5" s="18" t="n">
         <v>-1.25</v>
       </c>
-      <c r="Q5" s="16" t="n">
+      <c r="Q5" s="18" t="n">
         <v>12.85</v>
       </c>
-      <c r="R5" s="16" t="n">
+      <c r="R5" s="18" t="n">
         <v>11.38</v>
       </c>
-      <c r="T5" s="16" t="n">
+      <c r="T5" s="18" t="n">
         <v>4876</v>
       </c>
-      <c r="U5" s="16" t="n">
+      <c r="U5" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V5" s="16" t="n">
+      <c r="V5" s="18" t="n">
         <v>78.83</v>
       </c>
-      <c r="W5" s="16" t="n">
+      <c r="W5" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="X5" s="16" t="n">
+      <c r="X5" s="18" t="n">
         <v>60.79</v>
       </c>
-      <c r="Y5" s="16" t="n">
+      <c r="Y5" s="18" t="n">
         <v>61.96</v>
       </c>
-      <c r="Z5" s="16" t="n">
+      <c r="Z5" s="18" t="n">
         <v>62.54</v>
       </c>
-      <c r="AA5" s="16" t="n">
+      <c r="AA5" s="18" t="n">
         <v>63.64</v>
       </c>
-      <c r="AB5" s="16" t="n">
+      <c r="AB5" s="18" t="n">
         <v>61.16</v>
       </c>
-      <c r="AC5" s="16" t="n">
+      <c r="AC5" s="18" t="n">
         <v>62.18</v>
       </c>
-      <c r="AD5" s="16" t="n">
+      <c r="AD5" s="18" t="n">
         <v>62.72</v>
       </c>
-      <c r="AE5" s="16" t="n">
+      <c r="AE5" s="18" t="n">
         <v>63.78</v>
       </c>
+      <c r="AG5" s="18" t="n">
+        <v>3.21</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>benzo[b]thiophene</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>C12=CC=CC=C1C=CS2</t>
         </is>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="18" t="n">
         <v>67.79000000000001</v>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="18" t="n">
         <v>19.69</v>
       </c>
-      <c r="H6" s="16" t="n">
+      <c r="H6" s="18" t="n">
         <v>15.87</v>
       </c>
-      <c r="J6" s="16" t="n">
+      <c r="J6" s="18" t="n">
         <v>139.46</v>
       </c>
-      <c r="K6" s="16" t="n">
+      <c r="K6" s="18" t="n">
         <v>1.63</v>
       </c>
-      <c r="L6" s="16" t="n">
+      <c r="L6" s="18" t="n">
         <v>3.93</v>
       </c>
-      <c r="M6" s="16" t="n">
+      <c r="M6" s="18" t="n">
         <v>3.58</v>
       </c>
-      <c r="O6" s="16" t="n">
+      <c r="O6" s="18" t="n">
         <v>35.44</v>
       </c>
-      <c r="P6" s="16" t="n">
+      <c r="P6" s="18" t="n">
         <v>-2.88</v>
       </c>
-      <c r="Q6" s="16" t="n">
+      <c r="Q6" s="18" t="n">
         <v>5.06</v>
       </c>
-      <c r="R6" s="16" t="n">
+      <c r="R6" s="18" t="n">
         <v>4.7</v>
       </c>
-      <c r="T6" s="16" t="n">
+      <c r="T6" s="18" t="n">
         <v>4861</v>
       </c>
-      <c r="U6" s="16" t="n">
+      <c r="U6" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V6" s="16" t="n">
+      <c r="V6" s="18" t="n">
         <v>83.55</v>
       </c>
-      <c r="W6" s="16" t="n">
+      <c r="W6" s="18" t="n">
         <v>6.66</v>
       </c>
-      <c r="X6" s="16" t="n">
+      <c r="X6" s="18" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="Y6" s="16" t="n">
+      <c r="Y6" s="18" t="n">
         <v>67.51000000000001</v>
       </c>
-      <c r="Z6" s="16" t="n">
+      <c r="Z6" s="18" t="n">
         <v>68.06</v>
       </c>
-      <c r="AA6" s="16" t="n">
+      <c r="AA6" s="18" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="AB6" s="16" t="n">
+      <c r="AB6" s="18" t="n">
         <v>65.51000000000001</v>
       </c>
-      <c r="AC6" s="16" t="n">
+      <c r="AC6" s="18" t="n">
         <v>66.64</v>
       </c>
-      <c r="AD6" s="16" t="n">
+      <c r="AD6" s="18" t="n">
         <v>67.25</v>
       </c>
-      <c r="AE6" s="16" t="n">
+      <c r="AE6" s="18" t="n">
         <v>68.44</v>
       </c>
+      <c r="AG6" s="18" t="n">
+        <v>3.04</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>quinoxaline</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>C12=NC=CN=C1C=CC=C2</t>
         </is>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="18" t="n">
         <v>58.57</v>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="18" t="n">
         <v>14.06</v>
       </c>
-      <c r="H7" s="16" t="n">
+      <c r="H7" s="18" t="n">
         <v>14.33</v>
       </c>
-      <c r="J7" s="16" t="n">
+      <c r="J7" s="18" t="n">
         <v>155.3</v>
       </c>
-      <c r="K7" s="16" t="n">
+      <c r="K7" s="18" t="n">
         <v>2.31</v>
       </c>
-      <c r="L7" s="16" t="n">
+      <c r="L7" s="18" t="n">
         <v>3.49</v>
       </c>
-      <c r="M7" s="16" t="n">
+      <c r="M7" s="18" t="n">
         <v>3.49</v>
       </c>
-      <c r="O7" s="16" t="n">
+      <c r="O7" s="18" t="n">
         <v>63.87</v>
       </c>
-      <c r="P7" s="16" t="n">
+      <c r="P7" s="18" t="n">
         <v>-1.65</v>
       </c>
-      <c r="Q7" s="16" t="n">
+      <c r="Q7" s="18" t="n">
         <v>4.76</v>
       </c>
-      <c r="R7" s="16" t="n">
+      <c r="R7" s="18" t="n">
         <v>4.7</v>
       </c>
-      <c r="T7" s="16" t="n">
+      <c r="T7" s="18" t="n">
         <v>4953</v>
       </c>
-      <c r="U7" s="16" t="n">
+      <c r="U7" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V7" s="16" t="n">
+      <c r="V7" s="18" t="n">
         <v>72.52</v>
       </c>
-      <c r="W7" s="16" t="n">
+      <c r="W7" s="18" t="n">
         <v>5.9</v>
       </c>
-      <c r="X7" s="16" t="n">
+      <c r="X7" s="18" t="n">
         <v>57.32</v>
       </c>
-      <c r="Y7" s="16" t="n">
+      <c r="Y7" s="18" t="n">
         <v>58.3</v>
       </c>
-      <c r="Z7" s="16" t="n">
+      <c r="Z7" s="18" t="n">
         <v>58.79</v>
       </c>
-      <c r="AA7" s="16" t="n">
+      <c r="AA7" s="18" t="n">
         <v>59.71</v>
       </c>
-      <c r="AB7" s="16" t="n">
+      <c r="AB7" s="18" t="n">
         <v>55.62</v>
       </c>
-      <c r="AC7" s="16" t="n">
+      <c r="AC7" s="18" t="n">
         <v>56.66</v>
       </c>
-      <c r="AD7" s="16" t="n">
+      <c r="AD7" s="18" t="n">
         <v>57.24</v>
       </c>
-      <c r="AE7" s="16" t="n">
+      <c r="AE7" s="18" t="n">
         <v>58.45</v>
       </c>
+      <c r="AG7" s="18" t="n">
+        <v>3.04</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>isoquinoline</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>C12=CN=CC=C1C=CC=C2</t>
         </is>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="18" t="n">
         <v>60.09</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="18" t="n">
         <v>14.27</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="18" t="n">
         <v>14.49</v>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="18" t="n">
         <v>145.54</v>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K8" s="18" t="n">
         <v>1.89</v>
       </c>
-      <c r="L8" s="16" t="n">
+      <c r="L8" s="18" t="n">
         <v>3.43</v>
       </c>
-      <c r="M8" s="16" t="n">
+      <c r="M8" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="O8" s="16" t="n">
+      <c r="O8" s="18" t="n">
         <v>49.56</v>
       </c>
-      <c r="P8" s="16" t="n">
+      <c r="P8" s="18" t="n">
         <v>-2.27</v>
       </c>
-      <c r="Q8" s="16" t="n">
+      <c r="Q8" s="18" t="n">
         <v>4.66</v>
       </c>
-      <c r="R8" s="16" t="n">
+      <c r="R8" s="18" t="n">
         <v>4.48</v>
       </c>
-      <c r="T8" s="16" t="n">
+      <c r="T8" s="18" t="n">
         <v>4939</v>
       </c>
-      <c r="U8" s="16" t="n">
+      <c r="U8" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V8" s="16" t="n">
+      <c r="V8" s="18" t="n">
         <v>75.44</v>
       </c>
-      <c r="W8" s="16" t="n">
+      <c r="W8" s="18" t="n">
         <v>7.31</v>
       </c>
-      <c r="X8" s="16" t="n">
+      <c r="X8" s="18" t="n">
         <v>56.61</v>
       </c>
-      <c r="Y8" s="16" t="n">
+      <c r="Y8" s="18" t="n">
         <v>57.83</v>
       </c>
-      <c r="Z8" s="16" t="n">
+      <c r="Z8" s="18" t="n">
         <v>58.43</v>
       </c>
-      <c r="AA8" s="16" t="n">
+      <c r="AA8" s="18" t="n">
         <v>59.57</v>
       </c>
-      <c r="AB8" s="16" t="n">
+      <c r="AB8" s="18" t="n">
         <v>56.9</v>
       </c>
-      <c r="AC8" s="16" t="n">
+      <c r="AC8" s="18" t="n">
         <v>57.94</v>
       </c>
-      <c r="AD8" s="16" t="n">
+      <c r="AD8" s="18" t="n">
         <v>58.48</v>
       </c>
-      <c r="AE8" s="16" t="n">
+      <c r="AE8" s="18" t="n">
         <v>59.52</v>
       </c>
+      <c r="AG8" s="18" t="n">
+        <v>3.08</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Q7</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>coumarin</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>O=C1Oc2ccccc2C=C1</t>
         </is>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="18" t="n">
         <v>60.01</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="18" t="n">
         <v>12.42</v>
       </c>
-      <c r="H9" s="16" t="n">
+      <c r="H9" s="18" t="n">
         <v>12.66</v>
       </c>
-      <c r="J9" s="16" t="n">
+      <c r="J9" s="18" t="n">
         <v>151.33</v>
       </c>
-      <c r="K9" s="16" t="n">
+      <c r="K9" s="18" t="n">
         <v>2.14</v>
       </c>
-      <c r="L9" s="16" t="n">
+      <c r="L9" s="18" t="n">
         <v>3.81</v>
       </c>
-      <c r="M9" s="16" t="n">
+      <c r="M9" s="18" t="n">
         <v>3.83</v>
       </c>
-      <c r="O9" s="16" t="n">
+      <c r="O9" s="18" t="n">
         <v>60.27</v>
       </c>
-      <c r="P9" s="16" t="n">
+      <c r="P9" s="18" t="n">
         <v>-1.81</v>
       </c>
-      <c r="Q9" s="16" t="n">
+      <c r="Q9" s="18" t="n">
         <v>6.72</v>
       </c>
-      <c r="R9" s="16" t="n">
+      <c r="R9" s="18" t="n">
         <v>6.59</v>
       </c>
-      <c r="T9" s="16" t="n">
+      <c r="T9" s="18" t="n">
         <v>4941</v>
       </c>
-      <c r="U9" s="16" t="n">
+      <c r="U9" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V9" s="16" t="n">
+      <c r="V9" s="18" t="n">
         <v>75.55</v>
       </c>
-      <c r="W9" s="16" t="n">
+      <c r="W9" s="18" t="n">
         <v>7.39</v>
       </c>
-      <c r="X9" s="16" t="n">
+      <c r="X9" s="18" t="n">
         <v>56.53</v>
       </c>
-      <c r="Y9" s="16" t="n">
+      <c r="Y9" s="18" t="n">
         <v>57.76</v>
       </c>
-      <c r="Z9" s="16" t="n">
+      <c r="Z9" s="18" t="n">
         <v>58.37</v>
       </c>
-      <c r="AA9" s="16" t="n">
+      <c r="AA9" s="18" t="n">
         <v>59.52</v>
       </c>
-      <c r="AB9" s="16" t="n">
+      <c r="AB9" s="18" t="n">
         <v>55.5</v>
       </c>
-      <c r="AC9" s="16" t="n">
+      <c r="AC9" s="18" t="n">
         <v>56.83</v>
       </c>
-      <c r="AD9" s="16" t="n">
+      <c r="AD9" s="18" t="n">
         <v>57.46</v>
       </c>
-      <c r="AE9" s="16" t="n">
+      <c r="AE9" s="18" t="n">
         <v>58.67</v>
       </c>
+      <c r="AG9" s="18" t="n">
+        <v>3.12</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>benzophenone O-(isopropoxycarbonyl) oxime</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>CC(OC(O/N=C(C1=CC=CC=C1)\C2=CC=CC=C2)=O)C</t>
         </is>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="18" t="n">
         <v>51.79</v>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="18" t="n">
         <v>53.72</v>
       </c>
-      <c r="H10" s="16" t="n">
+      <c r="H10" s="18" t="n">
         <v>36.05</v>
       </c>
-      <c r="J10" s="16" t="n">
+      <c r="J10" s="18" t="n">
         <v>158.2</v>
       </c>
-      <c r="K10" s="16" t="n">
+      <c r="K10" s="18" t="n">
         <v>2.44</v>
       </c>
-      <c r="L10" s="16" t="n">
+      <c r="L10" s="18" t="n">
         <v>24.37</v>
       </c>
-      <c r="M10" s="16" t="n">
+      <c r="M10" s="18" t="n">
         <v>5.93</v>
       </c>
-      <c r="O10" s="16" t="n">
+      <c r="O10" s="18" t="n">
         <v>54.84</v>
       </c>
-      <c r="P10" s="16" t="n">
+      <c r="P10" s="18" t="n">
         <v>-2.04</v>
       </c>
-      <c r="Q10" s="16" t="n">
+      <c r="Q10" s="18" t="n">
         <v>11.34</v>
       </c>
-      <c r="R10" s="16" t="n">
+      <c r="R10" s="18" t="n">
         <v>8.66</v>
       </c>
-      <c r="T10" s="16" t="n">
+      <c r="T10" s="18" t="n">
         <v>4744</v>
       </c>
-      <c r="U10" s="16" t="n">
+      <c r="U10" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V10" s="16" t="n">
+      <c r="V10" s="18" t="n">
         <v>82.67</v>
       </c>
-      <c r="W10" s="16" t="n">
+      <c r="W10" s="18" t="n">
         <v>7.1</v>
       </c>
-      <c r="X10" s="16" t="n">
+      <c r="X10" s="18" t="n">
         <v>64.37</v>
       </c>
-      <c r="Y10" s="16" t="n">
+      <c r="Y10" s="18" t="n">
         <v>65.56</v>
       </c>
-      <c r="Z10" s="16" t="n">
+      <c r="Z10" s="18" t="n">
         <v>66.14</v>
       </c>
-      <c r="AA10" s="16" t="n">
+      <c r="AA10" s="18" t="n">
         <v>67.25</v>
       </c>
-      <c r="AB10" s="16" t="n">
+      <c r="AB10" s="18" t="n">
         <v>62.78</v>
       </c>
-      <c r="AC10" s="16" t="n">
+      <c r="AC10" s="18" t="n">
         <v>64.23</v>
       </c>
-      <c r="AD10" s="16" t="n">
+      <c r="AD10" s="18" t="n">
         <v>64.93000000000001</v>
       </c>
-      <c r="AE10" s="16" t="n">
+      <c r="AE10" s="18" t="n">
         <v>66.27</v>
       </c>
+      <c r="AG10" s="18" t="n">
+        <v>3.98</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n">
+      <c r="A11" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Q9</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>3-methyl-2-phenylthiophene</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>CC1=C(C2=CC=CC=C2)SC=C1</t>
         </is>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="18" t="n">
         <v>58.5</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="18" t="n">
         <v>16.91</v>
       </c>
-      <c r="H11" s="16" t="n">
+      <c r="H11" s="18" t="n">
         <v>21.67</v>
       </c>
-      <c r="J11" s="16" t="n">
+      <c r="J11" s="18" t="n">
         <v>134.82</v>
       </c>
-      <c r="K11" s="16" t="n">
+      <c r="K11" s="18" t="n">
         <v>1.43</v>
       </c>
-      <c r="L11" s="16" t="n">
+      <c r="L11" s="18" t="n">
         <v>6.04</v>
       </c>
-      <c r="M11" s="16" t="n">
+      <c r="M11" s="18" t="n">
         <v>6.87</v>
       </c>
-      <c r="O11" s="16" t="n">
+      <c r="O11" s="18" t="n">
         <v>39.09</v>
       </c>
-      <c r="P11" s="16" t="n">
+      <c r="P11" s="18" t="n">
         <v>-2.73</v>
       </c>
-      <c r="Q11" s="16" t="n">
+      <c r="Q11" s="18" t="n">
         <v>7.41</v>
       </c>
-      <c r="R11" s="16" t="n">
+      <c r="R11" s="18" t="n">
         <v>10.61</v>
       </c>
-      <c r="T11" s="16" t="n">
+      <c r="T11" s="18" t="n">
         <v>4907</v>
       </c>
-      <c r="U11" s="16" t="n">
+      <c r="U11" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V11" s="16" t="n">
+      <c r="V11" s="18" t="n">
         <v>82.15000000000001</v>
       </c>
-      <c r="W11" s="16" t="n">
+      <c r="W11" s="18" t="n">
         <v>7.58</v>
       </c>
-      <c r="X11" s="16" t="n">
+      <c r="X11" s="18" t="n">
         <v>62.63</v>
       </c>
-      <c r="Y11" s="16" t="n">
+      <c r="Y11" s="18" t="n">
         <v>63.89</v>
       </c>
-      <c r="Z11" s="16" t="n">
+      <c r="Z11" s="18" t="n">
         <v>64.52</v>
       </c>
-      <c r="AA11" s="16" t="n">
+      <c r="AA11" s="18" t="n">
         <v>65.7</v>
       </c>
-      <c r="AB11" s="16" t="n">
+      <c r="AB11" s="18" t="n">
         <v>61.61</v>
       </c>
-      <c r="AC11" s="16" t="n">
+      <c r="AC11" s="18" t="n">
         <v>62.98</v>
       </c>
-      <c r="AD11" s="16" t="n">
+      <c r="AD11" s="18" t="n">
         <v>63.69</v>
       </c>
-      <c r="AE11" s="16" t="n">
+      <c r="AE11" s="18" t="n">
         <v>65.09999999999999</v>
       </c>
+      <c r="AG11" s="18" t="n">
+        <v>3.38</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>diphenyl disulfide</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>C1(SSC2=CC=CC=C2)=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="18" t="n">
         <v>40.29</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="18" t="n">
         <v>77.58</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="18" t="n">
         <v>42.55</v>
       </c>
-      <c r="J12" s="16" t="n">
+      <c r="J12" s="18" t="n">
         <v>137.58</v>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K12" s="18" t="n">
         <v>1.55</v>
       </c>
-      <c r="L12" s="16" t="n">
+      <c r="L12" s="18" t="n">
         <v>10.52</v>
       </c>
-      <c r="M12" s="16" t="n">
+      <c r="M12" s="18" t="n">
         <v>16.62</v>
       </c>
-      <c r="O12" s="16" t="n"/>
-      <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="16" t="n"/>
-      <c r="R12" s="16" t="n"/>
-      <c r="T12" s="16" t="n">
+      <c r="O12" s="18" t="n"/>
+      <c r="P12" s="18" t="n"/>
+      <c r="Q12" s="18" t="n"/>
+      <c r="R12" s="18" t="n"/>
+      <c r="T12" s="18" t="n">
         <v>4924</v>
       </c>
-      <c r="U12" s="16" t="n">
+      <c r="U12" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V12" s="16" t="n">
+      <c r="V12" s="18" t="n">
         <v>82.06</v>
       </c>
-      <c r="W12" s="16" t="n">
+      <c r="W12" s="18" t="n">
         <v>7.97</v>
       </c>
-      <c r="X12" s="16" t="n">
+      <c r="X12" s="18" t="n">
         <v>61.52</v>
       </c>
-      <c r="Y12" s="16" t="n">
+      <c r="Y12" s="18" t="n">
         <v>62.85</v>
       </c>
-      <c r="Z12" s="16" t="n">
+      <c r="Z12" s="18" t="n">
         <v>63.51</v>
       </c>
-      <c r="AA12" s="16" t="n">
+      <c r="AA12" s="18" t="n">
         <v>64.76000000000001</v>
       </c>
-      <c r="AB12" s="16" t="n">
+      <c r="AB12" s="18" t="n">
         <v>57.97</v>
       </c>
-      <c r="AC12" s="16" t="n">
+      <c r="AC12" s="18" t="n">
         <v>59.63</v>
       </c>
-      <c r="AD12" s="16" t="n">
+      <c r="AD12" s="18" t="n">
         <v>60.49</v>
       </c>
-      <c r="AE12" s="16" t="n">
+      <c r="AE12" s="18" t="n">
         <v>62.19</v>
       </c>
+      <c r="AG12" s="18" t="n">
+        <v>3.58</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>dibenzyl disulfide</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>C1(CSSCC2=CC=CC=C2)=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="18" t="n">
         <v>56.63</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="18" t="n">
         <v>45.54</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="18" t="n">
         <v>45.14</v>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="18" t="n">
         <v>136.72</v>
       </c>
-      <c r="K13" s="16" t="n">
+      <c r="K13" s="18" t="n">
         <v>1.51</v>
       </c>
-      <c r="L13" s="16" t="n">
+      <c r="L13" s="18" t="n">
         <v>9.32</v>
       </c>
-      <c r="M13" s="16" t="n">
+      <c r="M13" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="O13" s="16" t="n"/>
-      <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="16" t="n"/>
-      <c r="R13" s="16" t="n"/>
-      <c r="T13" s="16" t="n">
+      <c r="O13" s="18" t="n"/>
+      <c r="P13" s="18" t="n"/>
+      <c r="Q13" s="18" t="n"/>
+      <c r="R13" s="18" t="n"/>
+      <c r="T13" s="18" t="n">
         <v>4953</v>
       </c>
-      <c r="U13" s="16" t="n">
+      <c r="U13" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V13" s="16" t="n">
+      <c r="V13" s="18" t="n">
         <v>87.73</v>
       </c>
-      <c r="W13" s="16" t="n">
+      <c r="W13" s="18" t="n">
         <v>6.8</v>
       </c>
-      <c r="X13" s="16" t="n">
+      <c r="X13" s="18" t="n">
         <v>70.20999999999999</v>
       </c>
-      <c r="Y13" s="16" t="n">
+      <c r="Y13" s="18" t="n">
         <v>71.34999999999999</v>
       </c>
-      <c r="Z13" s="16" t="n">
+      <c r="Z13" s="18" t="n">
         <v>71.91</v>
       </c>
-      <c r="AA13" s="16" t="n">
+      <c r="AA13" s="18" t="n">
         <v>72.97</v>
       </c>
-      <c r="AB13" s="16" t="n">
+      <c r="AB13" s="18" t="n">
         <v>70.20999999999999</v>
       </c>
-      <c r="AC13" s="16" t="n">
+      <c r="AC13" s="18" t="n">
         <v>71.41</v>
       </c>
-      <c r="AD13" s="16" t="n">
+      <c r="AD13" s="18" t="n">
         <v>71.98</v>
       </c>
-      <c r="AE13" s="16" t="n">
+      <c r="AE13" s="18" t="n">
         <v>73.09999999999999</v>
       </c>
+      <c r="AG13" s="18" t="n">
+        <v>3.78</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n">
+      <c r="A14" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>Q12</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>1,2-dihydro-1,2-benzazaborinine</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>C12=CC=CC=C1C=CBN2</t>
         </is>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="18" t="n">
         <v>66.41</v>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="18" t="n">
         <v>13.52</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="18" t="n">
         <v>13.12</v>
       </c>
-      <c r="J14" s="16" t="n">
+      <c r="J14" s="18" t="n">
         <v>140.94</v>
       </c>
-      <c r="K14" s="16" t="n">
+      <c r="K14" s="18" t="n">
         <v>1.69</v>
       </c>
-      <c r="L14" s="16" t="n">
+      <c r="L14" s="18" t="n">
         <v>4.61</v>
       </c>
-      <c r="M14" s="16" t="n">
+      <c r="M14" s="18" t="n">
         <v>4.57</v>
       </c>
-      <c r="O14" s="16" t="n">
+      <c r="O14" s="18" t="n">
         <v>44.5</v>
       </c>
-      <c r="P14" s="16" t="n">
+      <c r="P14" s="18" t="n">
         <v>-2.49</v>
       </c>
-      <c r="Q14" s="16" t="n">
+      <c r="Q14" s="18" t="n">
         <v>5.06</v>
       </c>
-      <c r="R14" s="16" t="n">
+      <c r="R14" s="18" t="n">
         <v>4.7</v>
       </c>
-      <c r="T14" s="16" t="n">
+      <c r="T14" s="18" t="n">
         <v>4920</v>
       </c>
-      <c r="U14" s="16" t="n">
+      <c r="U14" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V14" s="16" t="n">
+      <c r="V14" s="18" t="n">
         <v>79.17</v>
       </c>
-      <c r="W14" s="16" t="n">
+      <c r="W14" s="18" t="n">
         <v>6.45</v>
       </c>
-      <c r="X14" s="16" t="n">
+      <c r="X14" s="18" t="n">
         <v>62.55</v>
       </c>
-      <c r="Y14" s="16" t="n">
+      <c r="Y14" s="18" t="n">
         <v>63.62</v>
       </c>
-      <c r="Z14" s="16" t="n">
+      <c r="Z14" s="18" t="n">
         <v>64.16</v>
       </c>
-      <c r="AA14" s="16" t="n">
+      <c r="AA14" s="18" t="n">
         <v>65.16</v>
       </c>
-      <c r="AB14" s="16" t="n">
+      <c r="AB14" s="18" t="n">
         <v>60.19</v>
       </c>
-      <c r="AC14" s="16" t="n">
+      <c r="AC14" s="18" t="n">
         <v>61.46</v>
       </c>
-      <c r="AD14" s="16" t="n">
+      <c r="AD14" s="18" t="n">
         <v>62.1</v>
       </c>
-      <c r="AE14" s="16" t="n">
+      <c r="AE14" s="18" t="n">
         <v>63.33</v>
       </c>
+      <c r="AG14" s="18" t="n">
+        <v>3.14</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="18" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>N-methylmaleimide</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>O=C1C=CC(N1C)=O</t>
         </is>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="18" t="n">
         <v>56.74</v>
       </c>
-      <c r="G15" s="16" t="n">
+      <c r="G15" s="18" t="n">
         <v>18.89</v>
       </c>
-      <c r="H15" s="16" t="n">
+      <c r="H15" s="18" t="n">
         <v>18.15</v>
       </c>
-      <c r="J15" s="16" t="n">
+      <c r="J15" s="18" t="n">
         <v>172.16</v>
       </c>
-      <c r="K15" s="16" t="n">
+      <c r="K15" s="18" t="n">
         <v>3.05</v>
       </c>
-      <c r="L15" s="16" t="n">
+      <c r="L15" s="18" t="n">
         <v>8.9</v>
       </c>
-      <c r="M15" s="16" t="n">
+      <c r="M15" s="18" t="n">
         <v>6.92</v>
       </c>
-      <c r="O15" s="16" t="n">
+      <c r="O15" s="18" t="n">
         <v>76.12</v>
       </c>
-      <c r="P15" s="16" t="n">
+      <c r="P15" s="18" t="n">
         <v>-1.12</v>
       </c>
-      <c r="Q15" s="16" t="n">
+      <c r="Q15" s="18" t="n">
         <v>9.34</v>
       </c>
-      <c r="R15" s="16" t="n">
+      <c r="R15" s="18" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="T15" s="16" t="n">
+      <c r="T15" s="18" t="n">
         <v>4977</v>
       </c>
-      <c r="U15" s="16" t="n">
+      <c r="U15" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V15" s="16" t="n">
+      <c r="V15" s="18" t="n">
         <v>76.73</v>
       </c>
-      <c r="W15" s="16" t="n">
+      <c r="W15" s="18" t="n">
         <v>7.99</v>
       </c>
-      <c r="X15" s="16" t="n">
+      <c r="X15" s="18" t="n">
         <v>56.14</v>
       </c>
-      <c r="Y15" s="16" t="n">
+      <c r="Y15" s="18" t="n">
         <v>57.47</v>
       </c>
-      <c r="Z15" s="16" t="n">
+      <c r="Z15" s="18" t="n">
         <v>58.13</v>
       </c>
-      <c r="AA15" s="16" t="n">
+      <c r="AA15" s="18" t="n">
         <v>59.38</v>
       </c>
-      <c r="AB15" s="16" t="n">
+      <c r="AB15" s="18" t="n">
         <v>55.57</v>
       </c>
-      <c r="AC15" s="16" t="n">
+      <c r="AC15" s="18" t="n">
         <v>56.89</v>
       </c>
-      <c r="AD15" s="16" t="n">
+      <c r="AD15" s="18" t="n">
         <v>57.53</v>
       </c>
-      <c r="AE15" s="16" t="n">
+      <c r="AE15" s="18" t="n">
         <v>58.72</v>
       </c>
+      <c r="AG15" s="18" t="n">
+        <v>2.84</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>butyl methacrylate</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>CC(C(OCCCC)=O)=C</t>
         </is>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="18" t="n">
         <v>53.6</v>
       </c>
-      <c r="G16" s="16" t="n">
+      <c r="G16" s="18" t="n">
         <v>87.62</v>
       </c>
-      <c r="H16" s="16" t="n">
+      <c r="H16" s="18" t="n">
         <v>30.77</v>
       </c>
-      <c r="J16" s="16" t="n">
+      <c r="J16" s="18" t="n">
         <v>163.32</v>
       </c>
-      <c r="K16" s="16" t="n">
+      <c r="K16" s="18" t="n">
         <v>2.66</v>
       </c>
-      <c r="L16" s="16" t="n">
+      <c r="L16" s="18" t="n">
         <v>11.79</v>
       </c>
-      <c r="M16" s="16" t="n">
+      <c r="M16" s="18" t="n">
         <v>7.49</v>
       </c>
-      <c r="O16" s="16" t="n">
+      <c r="O16" s="18" t="n">
         <v>48</v>
       </c>
-      <c r="P16" s="16" t="n">
+      <c r="P16" s="18" t="n">
         <v>-2.34</v>
       </c>
-      <c r="Q16" s="16" t="n">
+      <c r="Q16" s="18" t="n">
         <v>11.03</v>
       </c>
-      <c r="R16" s="16" t="n">
+      <c r="R16" s="18" t="n">
         <v>9.01</v>
       </c>
-      <c r="T16" s="16" t="n">
+      <c r="T16" s="18" t="n">
         <v>4958</v>
       </c>
-      <c r="U16" s="16" t="n">
+      <c r="U16" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V16" s="16" t="n">
+      <c r="V16" s="18" t="n">
         <v>86.31</v>
       </c>
-      <c r="W16" s="16" t="n">
+      <c r="W16" s="18" t="n">
         <v>10.54</v>
       </c>
-      <c r="X16" s="16" t="n">
+      <c r="X16" s="18" t="n">
         <v>59.14</v>
       </c>
-      <c r="Y16" s="16" t="n">
+      <c r="Y16" s="18" t="n">
         <v>60.9</v>
       </c>
-      <c r="Z16" s="16" t="n">
+      <c r="Z16" s="18" t="n">
         <v>61.78</v>
       </c>
-      <c r="AA16" s="16" t="n">
+      <c r="AA16" s="18" t="n">
         <v>63.42</v>
       </c>
-      <c r="AB16" s="16" t="n">
+      <c r="AB16" s="18" t="n">
         <v>62.31</v>
       </c>
-      <c r="AC16" s="16" t="n">
+      <c r="AC16" s="18" t="n">
         <v>63.48</v>
       </c>
-      <c r="AD16" s="16" t="n">
+      <c r="AD16" s="18" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="AE16" s="16" t="n">
+      <c r="AE16" s="18" t="n">
         <v>65.31</v>
       </c>
+      <c r="AG16" s="18" t="n">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Q15</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>indene</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>C12=CC=CC=C1C=CC2</t>
         </is>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="18" t="n">
         <v>61.51</v>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="18" t="n">
         <v>17.91</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="18" t="n">
         <v>17.95</v>
       </c>
-      <c r="J17" s="16" t="n">
+      <c r="J17" s="18" t="n">
         <v>136.31</v>
       </c>
-      <c r="K17" s="16" t="n">
+      <c r="K17" s="18" t="n">
         <v>1.49</v>
       </c>
-      <c r="L17" s="16" t="n">
+      <c r="L17" s="18" t="n">
         <v>4.33</v>
       </c>
-      <c r="M17" s="16" t="n">
+      <c r="M17" s="18" t="n">
         <v>4.37</v>
       </c>
-      <c r="O17" s="16" t="n">
+      <c r="O17" s="18" t="n">
         <v>32.73</v>
       </c>
-      <c r="P17" s="16" t="n">
+      <c r="P17" s="18" t="n">
         <v>-3</v>
       </c>
-      <c r="Q17" s="16" t="n">
+      <c r="Q17" s="18" t="n">
         <v>5.89</v>
       </c>
-      <c r="R17" s="16" t="n">
+      <c r="R17" s="18" t="n">
         <v>5.45</v>
       </c>
-      <c r="T17" s="16" t="n">
+      <c r="T17" s="18" t="n">
         <v>4958</v>
       </c>
-      <c r="U17" s="16" t="n">
+      <c r="U17" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V17" s="16" t="n">
+      <c r="V17" s="18" t="n">
         <v>80.8</v>
       </c>
-      <c r="W17" s="16" t="n">
+      <c r="W17" s="18" t="n">
         <v>8.42</v>
       </c>
-      <c r="X17" s="16" t="n">
+      <c r="X17" s="18" t="n">
         <v>59.11</v>
       </c>
-      <c r="Y17" s="16" t="n">
+      <c r="Y17" s="18" t="n">
         <v>60.51</v>
       </c>
-      <c r="Z17" s="16" t="n">
+      <c r="Z17" s="18" t="n">
         <v>61.21</v>
       </c>
-      <c r="AA17" s="16" t="n">
+      <c r="AA17" s="18" t="n">
         <v>62.52</v>
       </c>
-      <c r="AB17" s="16" t="n">
+      <c r="AB17" s="18" t="n">
         <v>57.24</v>
       </c>
-      <c r="AC17" s="16" t="n">
+      <c r="AC17" s="18" t="n">
         <v>58.67</v>
       </c>
-      <c r="AD17" s="16" t="n">
+      <c r="AD17" s="18" t="n">
         <v>59.4</v>
       </c>
-      <c r="AE17" s="16" t="n">
+      <c r="AE17" s="18" t="n">
         <v>60.91</v>
       </c>
+      <c r="AG17" s="18" t="n">
+        <v>3.03</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>5-methylpyridin-2(1H)-one</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>O=C1NC=C(C)C=C1</t>
         </is>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="18" t="n">
         <v>57.36</v>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="18" t="n">
         <v>11.61</v>
       </c>
-      <c r="H18" s="16" t="n">
+      <c r="H18" s="18" t="n">
         <v>11.22</v>
       </c>
-      <c r="J18" s="16" t="n">
+      <c r="J18" s="18" t="n">
         <v>134.51</v>
       </c>
-      <c r="K18" s="16" t="n">
+      <c r="K18" s="18" t="n">
         <v>1.41</v>
       </c>
-      <c r="L18" s="16" t="n">
+      <c r="L18" s="18" t="n">
         <v>5.51</v>
       </c>
-      <c r="M18" s="16" t="n">
+      <c r="M18" s="18" t="n">
         <v>4.35</v>
       </c>
-      <c r="O18" s="16" t="n">
+      <c r="O18" s="18" t="n">
         <v>45.51</v>
       </c>
-      <c r="P18" s="16" t="n">
+      <c r="P18" s="18" t="n">
         <v>-2.45</v>
       </c>
-      <c r="Q18" s="16" t="n">
+      <c r="Q18" s="18" t="n">
         <v>6.28</v>
       </c>
-      <c r="R18" s="16" t="n">
+      <c r="R18" s="18" t="n">
         <v>5.95</v>
       </c>
-      <c r="T18" s="16" t="n">
+      <c r="T18" s="18" t="n">
         <v>4973</v>
       </c>
-      <c r="U18" s="16" t="n">
+      <c r="U18" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V18" s="16" t="n">
+      <c r="V18" s="18" t="n">
         <v>71.91</v>
       </c>
-      <c r="W18" s="16" t="n">
+      <c r="W18" s="18" t="n">
         <v>6.64</v>
       </c>
-      <c r="X18" s="16" t="n">
+      <c r="X18" s="18" t="n">
         <v>54.8</v>
       </c>
-      <c r="Y18" s="16" t="n">
+      <c r="Y18" s="18" t="n">
         <v>55.9</v>
       </c>
-      <c r="Z18" s="16" t="n">
+      <c r="Z18" s="18" t="n">
         <v>56.45</v>
       </c>
-      <c r="AA18" s="16" t="n">
+      <c r="AA18" s="18" t="n">
         <v>57.49</v>
       </c>
-      <c r="AB18" s="16" t="n">
+      <c r="AB18" s="18" t="n">
         <v>55.83</v>
       </c>
-      <c r="AC18" s="16" t="n">
+      <c r="AC18" s="18" t="n">
         <v>56.82</v>
       </c>
-      <c r="AD18" s="16" t="n">
+      <c r="AD18" s="18" t="n">
         <v>57.31</v>
       </c>
-      <c r="AE18" s="16" t="n">
+      <c r="AE18" s="18" t="n">
         <v>58.19</v>
       </c>
+      <c r="AG18" s="18" t="n">
+        <v>2.91</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>dibenzyl diselenide</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>C1(C[Se][Se]CC2=CC=CC=C2)=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="18" t="n">
         <v>47.11</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="18" t="n">
         <v>36.76</v>
       </c>
-      <c r="H19" s="16" t="n">
+      <c r="H19" s="18" t="n">
         <v>35.47</v>
       </c>
-      <c r="J19" s="16" t="n">
+      <c r="J19" s="18" t="n">
         <v>132.85</v>
       </c>
-      <c r="K19" s="16" t="n">
+      <c r="K19" s="18" t="n">
         <v>1.34</v>
       </c>
-      <c r="L19" s="16" t="n">
+      <c r="L19" s="18" t="n">
         <v>7.54</v>
       </c>
-      <c r="M19" s="16" t="n">
+      <c r="M19" s="18" t="n">
         <v>13.69</v>
       </c>
-      <c r="O19" s="16" t="n">
+      <c r="O19" s="18" t="n">
         <v>54.16</v>
       </c>
-      <c r="P19" s="16" t="n">
+      <c r="P19" s="18" t="n">
         <v>-2.07</v>
       </c>
-      <c r="Q19" s="16" t="n">
+      <c r="Q19" s="18" t="n">
         <v>119.56</v>
       </c>
-      <c r="R19" s="16" t="n">
+      <c r="R19" s="18" t="n">
         <v>29.8</v>
       </c>
-      <c r="T19" s="16" t="n">
+      <c r="T19" s="18" t="n">
         <v>4848</v>
       </c>
-      <c r="U19" s="16" t="n">
+      <c r="U19" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V19" s="16" t="n">
+      <c r="V19" s="18" t="n">
         <v>73.59</v>
       </c>
-      <c r="W19" s="16" t="n">
+      <c r="W19" s="18" t="n">
         <v>7.09</v>
       </c>
-      <c r="X19" s="16" t="n">
+      <c r="X19" s="18" t="n">
         <v>55.31</v>
       </c>
-      <c r="Y19" s="16" t="n">
+      <c r="Y19" s="18" t="n">
         <v>56.5</v>
       </c>
-      <c r="Z19" s="16" t="n">
+      <c r="Z19" s="18" t="n">
         <v>57.08</v>
       </c>
-      <c r="AA19" s="16" t="n">
+      <c r="AA19" s="18" t="n">
         <v>58.19</v>
       </c>
-      <c r="AB19" s="16" t="n">
+      <c r="AB19" s="18" t="n">
         <v>56.11</v>
       </c>
-      <c r="AC19" s="16" t="n">
+      <c r="AC19" s="18" t="n">
         <v>57.2</v>
       </c>
-      <c r="AD19" s="16" t="n">
+      <c r="AD19" s="18" t="n">
         <v>57.78</v>
       </c>
-      <c r="AE19" s="16" t="n">
+      <c r="AE19" s="18" t="n">
         <v>58.87</v>
       </c>
+      <c r="AG19" s="18" t="n">
+        <v>3.82</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>5,5-dimethyl-3-phenyl-4,5-dihydro-1,2,4-oxadiazole</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>CC1(C)NC(C2=CC=CC=C2)=NO1</t>
         </is>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="18" t="n">
         <v>52.24</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="18" t="n">
         <v>20.05</v>
       </c>
-      <c r="H20" s="16" t="n">
+      <c r="H20" s="18" t="n">
         <v>21.45</v>
       </c>
-      <c r="J20" s="16" t="n">
+      <c r="J20" s="18" t="n">
         <v>124.54</v>
       </c>
-      <c r="K20" s="16" t="n">
+      <c r="K20" s="18" t="n">
         <v>0.98</v>
       </c>
-      <c r="L20" s="16" t="n">
+      <c r="L20" s="18" t="n">
         <v>10.43</v>
       </c>
-      <c r="M20" s="16" t="n">
+      <c r="M20" s="18" t="n">
         <v>13.82</v>
       </c>
-      <c r="O20" s="16" t="n">
+      <c r="O20" s="18" t="n">
         <v>43.96</v>
       </c>
-      <c r="P20" s="16" t="n">
+      <c r="P20" s="18" t="n">
         <v>-2.51</v>
       </c>
-      <c r="Q20" s="16" t="n">
+      <c r="Q20" s="18" t="n">
         <v>7.2</v>
       </c>
-      <c r="R20" s="16" t="n">
+      <c r="R20" s="18" t="n">
         <v>8.17</v>
       </c>
-      <c r="T20" s="16" t="n">
+      <c r="T20" s="18" t="n">
         <v>4955</v>
       </c>
-      <c r="U20" s="16" t="n">
+      <c r="U20" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V20" s="16" t="n">
+      <c r="V20" s="18" t="n">
         <v>77.91</v>
       </c>
-      <c r="W20" s="16" t="n">
+      <c r="W20" s="18" t="n">
         <v>8.640000000000001</v>
       </c>
-      <c r="X20" s="16" t="n">
+      <c r="X20" s="18" t="n">
         <v>55.66</v>
       </c>
-      <c r="Y20" s="16" t="n">
+      <c r="Y20" s="18" t="n">
         <v>57.11</v>
       </c>
-      <c r="Z20" s="16" t="n">
+      <c r="Z20" s="18" t="n">
         <v>57.82</v>
       </c>
-      <c r="AA20" s="16" t="n">
+      <c r="AA20" s="18" t="n">
         <v>59.17</v>
       </c>
-      <c r="AB20" s="16" t="n">
+      <c r="AB20" s="18" t="n">
         <v>56.24</v>
       </c>
-      <c r="AC20" s="16" t="n">
+      <c r="AC20" s="18" t="n">
         <v>57.6</v>
       </c>
-      <c r="AD20" s="16" t="n">
+      <c r="AD20" s="18" t="n">
         <v>58.26</v>
       </c>
-      <c r="AE20" s="16" t="n">
+      <c r="AE20" s="18" t="n">
         <v>59.5</v>
       </c>
+      <c r="AG20" s="18" t="n">
+        <v>3.41</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Q19</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>benzophenone O-[(benzylsulfanyl)carbonyl] oxime</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>O=C(SCC1=CC=CC=C1)O/N=C(C2=CC=CC=C2)\C3=CC=CC=C3</t>
         </is>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="18" t="n">
         <v>52.55</v>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="18" t="n">
         <v>54.29</v>
       </c>
-      <c r="H21" s="16" t="n">
+      <c r="H21" s="18" t="n">
         <v>34.21</v>
       </c>
-      <c r="J21" s="16" t="n">
+      <c r="J21" s="18" t="n">
         <v>152.97</v>
       </c>
-      <c r="K21" s="16" t="n">
+      <c r="K21" s="18" t="n">
         <v>2.21</v>
       </c>
-      <c r="L21" s="16" t="n">
+      <c r="L21" s="18" t="n">
         <v>5.49</v>
       </c>
-      <c r="M21" s="16" t="n">
+      <c r="M21" s="18" t="n">
         <v>4.64</v>
       </c>
-      <c r="O21" s="16" t="n">
+      <c r="O21" s="18" t="n">
         <v>57.15</v>
       </c>
-      <c r="P21" s="16" t="n">
+      <c r="P21" s="18" t="n">
         <v>-1.94</v>
       </c>
-      <c r="Q21" s="16" t="n">
+      <c r="Q21" s="18" t="n">
         <v>10.6</v>
       </c>
-      <c r="R21" s="16" t="n">
+      <c r="R21" s="18" t="n">
         <v>12.19</v>
       </c>
-      <c r="T21" s="16" t="n">
+      <c r="T21" s="18" t="n">
         <v>4696</v>
       </c>
-      <c r="U21" s="16" t="n">
+      <c r="U21" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V21" s="16" t="n">
+      <c r="V21" s="18" t="n">
         <v>85.29000000000001</v>
       </c>
-      <c r="W21" s="16" t="n">
+      <c r="W21" s="18" t="n">
         <v>10.83</v>
       </c>
-      <c r="X21" s="16" t="n">
+      <c r="X21" s="18" t="n">
         <v>57.38</v>
       </c>
-      <c r="Y21" s="16" t="n">
+      <c r="Y21" s="18" t="n">
         <v>59.19</v>
       </c>
-      <c r="Z21" s="16" t="n">
+      <c r="Z21" s="18" t="n">
         <v>60.09</v>
       </c>
-      <c r="AA21" s="16" t="n">
+      <c r="AA21" s="18" t="n">
         <v>61.78</v>
       </c>
-      <c r="AB21" s="16" t="n">
+      <c r="AB21" s="18" t="n">
         <v>62.1</v>
       </c>
-      <c r="AC21" s="16" t="n">
+      <c r="AC21" s="18" t="n">
         <v>63.46</v>
       </c>
-      <c r="AD21" s="16" t="n">
+      <c r="AD21" s="18" t="n">
         <v>64.14</v>
       </c>
-      <c r="AE21" s="16" t="n">
+      <c r="AE21" s="18" t="n">
         <v>65.45999999999999</v>
       </c>
+      <c r="AG21" s="18" t="n">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Q20</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>naphthalene</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>C12=CC=CC=C1C=CC=C2</t>
         </is>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="18" t="n">
         <v>60.58</v>
       </c>
-      <c r="G22" s="16" t="n">
+      <c r="G22" s="18" t="n">
         <v>13.31</v>
       </c>
-      <c r="H22" s="16" t="n">
+      <c r="H22" s="18" t="n">
         <v>13.61</v>
       </c>
-      <c r="J22" s="16" t="n">
+      <c r="J22" s="18" t="n">
         <v>138.77</v>
       </c>
-      <c r="K22" s="16" t="n">
+      <c r="K22" s="18" t="n">
         <v>1.6</v>
       </c>
-      <c r="L22" s="16" t="n">
+      <c r="L22" s="18" t="n">
         <v>3.01</v>
       </c>
-      <c r="M22" s="16" t="n">
+      <c r="M22" s="18" t="n">
         <v>3.03</v>
       </c>
-      <c r="O22" s="16" t="n">
+      <c r="O22" s="18" t="n">
         <v>41.8</v>
       </c>
-      <c r="P22" s="16" t="n">
+      <c r="P22" s="18" t="n">
         <v>-2.61</v>
       </c>
-      <c r="Q22" s="16" t="n">
+      <c r="Q22" s="18" t="n">
         <v>3.97</v>
       </c>
-      <c r="R22" s="16" t="n">
+      <c r="R22" s="18" t="n">
         <v>3.8</v>
       </c>
-      <c r="T22" s="16" t="n">
+      <c r="T22" s="18" t="n">
         <v>4984</v>
       </c>
-      <c r="U22" s="16" t="n">
+      <c r="U22" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V22" s="16" t="n">
+      <c r="V22" s="18" t="n">
         <v>74.87</v>
       </c>
-      <c r="W22" s="16" t="n">
+      <c r="W22" s="18" t="n">
         <v>7.43</v>
       </c>
-      <c r="X22" s="16" t="n">
+      <c r="X22" s="18" t="n">
         <v>55.73</v>
       </c>
-      <c r="Y22" s="16" t="n">
+      <c r="Y22" s="18" t="n">
         <v>56.97</v>
       </c>
-      <c r="Z22" s="16" t="n">
+      <c r="Z22" s="18" t="n">
         <v>57.58</v>
       </c>
-      <c r="AA22" s="16" t="n">
+      <c r="AA22" s="18" t="n">
         <v>58.75</v>
       </c>
-      <c r="AB22" s="16" t="n">
+      <c r="AB22" s="18" t="n">
         <v>55.97</v>
       </c>
-      <c r="AC22" s="16" t="n">
+      <c r="AC22" s="18" t="n">
         <v>57.1</v>
       </c>
-      <c r="AD22" s="16" t="n">
+      <c r="AD22" s="18" t="n">
         <v>57.66</v>
       </c>
-      <c r="AE22" s="16" t="n">
+      <c r="AE22" s="18" t="n">
         <v>58.71</v>
       </c>
+      <c r="AG22" s="18" t="n">
+        <v>3.12</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>ethyl 3-phenylpropiolate</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>CCOC(=O)C#Cc1ccccc1</t>
         </is>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="18" t="n">
         <v>67.73999999999999</v>
       </c>
-      <c r="G23" s="16" t="n">
+      <c r="G23" s="18" t="n">
         <v>13.88</v>
       </c>
-      <c r="H23" s="16" t="n">
+      <c r="H23" s="18" t="n">
         <v>13.8</v>
       </c>
-      <c r="J23" s="16" t="n">
+      <c r="J23" s="18" t="n">
         <v>155.8</v>
       </c>
-      <c r="K23" s="16" t="n">
+      <c r="K23" s="18" t="n">
         <v>2.34</v>
       </c>
-      <c r="L23" s="16" t="n">
+      <c r="L23" s="18" t="n">
         <v>4.97</v>
       </c>
-      <c r="M23" s="16" t="n">
+      <c r="M23" s="18" t="n">
         <v>5.32</v>
       </c>
-      <c r="O23" s="16" t="n">
+      <c r="O23" s="18" t="n">
         <v>56.74</v>
       </c>
-      <c r="P23" s="16" t="n">
+      <c r="P23" s="18" t="n">
         <v>-1.96</v>
       </c>
-      <c r="Q23" s="16" t="n">
+      <c r="Q23" s="18" t="n">
         <v>7.27</v>
       </c>
-      <c r="R23" s="16" t="n">
+      <c r="R23" s="18" t="n">
         <v>6.82</v>
       </c>
-      <c r="T23" s="16" t="n">
+      <c r="T23" s="18" t="n">
         <v>4935</v>
       </c>
-      <c r="U23" s="16" t="n">
+      <c r="U23" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V23" s="16" t="n">
+      <c r="V23" s="18" t="n">
         <v>82.84999999999999</v>
       </c>
-      <c r="W23" s="16" t="n">
+      <c r="W23" s="18" t="n">
         <v>7.31</v>
       </c>
-      <c r="X23" s="16" t="n">
+      <c r="X23" s="18" t="n">
         <v>64.02</v>
       </c>
-      <c r="Y23" s="16" t="n">
+      <c r="Y23" s="18" t="n">
         <v>65.23999999999999</v>
       </c>
-      <c r="Z23" s="16" t="n">
+      <c r="Z23" s="18" t="n">
         <v>65.84999999999999</v>
       </c>
-      <c r="AA23" s="16" t="n">
+      <c r="AA23" s="18" t="n">
         <v>66.98999999999999</v>
       </c>
-      <c r="AB23" s="16" t="n">
+      <c r="AB23" s="18" t="n">
         <v>62.71</v>
       </c>
-      <c r="AC23" s="16" t="n">
+      <c r="AC23" s="18" t="n">
         <v>64.27</v>
       </c>
-      <c r="AD23" s="16" t="n">
+      <c r="AD23" s="18" t="n">
         <v>65.01000000000001</v>
       </c>
-      <c r="AE23" s="16" t="n">
+      <c r="AE23" s="18" t="n">
         <v>66.29000000000001</v>
       </c>
+      <c r="AG23" s="18" t="n">
+        <v>3.41</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>Q22</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>4-oxo-2-phenylquinazolin-3(4H)-yl 3-phenylpropanoate</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>O=C1N(OC(CCC2=CC=CC=C2)=O)C(C3=CC=CC=C3)=NC4=CC=CC=C41</t>
         </is>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="18" t="n">
         <v>58.27</v>
       </c>
-      <c r="G24" s="16" t="n">
+      <c r="G24" s="18" t="n">
         <v>28.63</v>
       </c>
-      <c r="H24" s="16" t="n">
+      <c r="H24" s="18" t="n">
         <v>27.2</v>
       </c>
-      <c r="J24" s="16" t="n">
+      <c r="J24" s="18" t="n">
         <v>148.93</v>
       </c>
-      <c r="K24" s="16" t="n">
+      <c r="K24" s="18" t="n">
         <v>2.04</v>
       </c>
-      <c r="L24" s="16" t="n">
+      <c r="L24" s="18" t="n">
         <v>6.04</v>
       </c>
-      <c r="M24" s="16" t="n">
+      <c r="M24" s="18" t="n">
         <v>7.13</v>
       </c>
-      <c r="O24" s="16" t="n">
+      <c r="O24" s="18" t="n">
         <v>57.17</v>
       </c>
-      <c r="P24" s="16" t="n">
+      <c r="P24" s="18" t="n">
         <v>-1.94</v>
       </c>
-      <c r="Q24" s="16" t="n">
+      <c r="Q24" s="18" t="n">
         <v>12.22</v>
       </c>
-      <c r="R24" s="16" t="n">
+      <c r="R24" s="18" t="n">
         <v>11.9</v>
       </c>
-      <c r="T24" s="16" t="n">
+      <c r="T24" s="18" t="n">
         <v>4934</v>
       </c>
-      <c r="U24" s="16" t="n">
+      <c r="U24" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V24" s="16" t="n">
+      <c r="V24" s="18" t="n">
         <v>80.73999999999999</v>
       </c>
-      <c r="W24" s="16" t="n">
+      <c r="W24" s="18" t="n">
         <v>6.52</v>
       </c>
-      <c r="X24" s="16" t="n">
+      <c r="X24" s="18" t="n">
         <v>63.93</v>
       </c>
-      <c r="Y24" s="16" t="n">
+      <c r="Y24" s="18" t="n">
         <v>65.02</v>
       </c>
-      <c r="Z24" s="16" t="n">
+      <c r="Z24" s="18" t="n">
         <v>65.56</v>
       </c>
-      <c r="AA24" s="16" t="n">
+      <c r="AA24" s="18" t="n">
         <v>66.58</v>
       </c>
-      <c r="AB24" s="16" t="n">
+      <c r="AB24" s="18" t="n">
         <v>61.29</v>
       </c>
-      <c r="AC24" s="16" t="n">
+      <c r="AC24" s="18" t="n">
         <v>62.71</v>
       </c>
-      <c r="AD24" s="16" t="n">
+      <c r="AD24" s="18" t="n">
         <v>63.41</v>
       </c>
-      <c r="AE24" s="16" t="n">
+      <c r="AE24" s="18" t="n">
         <v>64.77</v>
       </c>
+      <c r="AG24" s="18" t="n">
+        <v>4.28</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>2-(benzo[b]thiophen-2-yl)-4,4,5,5-tetramethyl-1,3,2-dioxaborolane</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>CC(O1)(C)C(C)(C)OB1C2=CC3=CC=CC=C3S2</t>
         </is>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="F25" s="18" t="n">
         <v>61.62</v>
       </c>
-      <c r="G25" s="16" t="n">
+      <c r="G25" s="18" t="n">
         <v>13.37</v>
       </c>
-      <c r="H25" s="16" t="n">
+      <c r="H25" s="18" t="n">
         <v>13.21</v>
       </c>
-      <c r="J25" s="16" t="n">
+      <c r="J25" s="18" t="n">
         <v>140.7</v>
       </c>
-      <c r="K25" s="16" t="n">
+      <c r="K25" s="18" t="n">
         <v>1.68</v>
       </c>
-      <c r="L25" s="16" t="n">
+      <c r="L25" s="18" t="n">
         <v>3.85</v>
       </c>
-      <c r="M25" s="16" t="n">
+      <c r="M25" s="18" t="n">
         <v>3.43</v>
       </c>
-      <c r="O25" s="16" t="n">
+      <c r="O25" s="18" t="n">
         <v>45.49</v>
       </c>
-      <c r="P25" s="16" t="n">
+      <c r="P25" s="18" t="n">
         <v>-2.45</v>
       </c>
-      <c r="Q25" s="16" t="n">
+      <c r="Q25" s="18" t="n">
         <v>6.5</v>
       </c>
-      <c r="R25" s="16" t="n">
+      <c r="R25" s="18" t="n">
         <v>5.99</v>
       </c>
-      <c r="T25" s="16" t="n">
+      <c r="T25" s="18" t="n">
         <v>4945</v>
       </c>
-      <c r="U25" s="16" t="n">
+      <c r="U25" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V25" s="16" t="n">
+      <c r="V25" s="18" t="n">
         <v>76.94</v>
       </c>
-      <c r="W25" s="16" t="n">
+      <c r="W25" s="18" t="n">
         <v>7.47</v>
       </c>
-      <c r="X25" s="16" t="n">
+      <c r="X25" s="18" t="n">
         <v>57.7</v>
       </c>
-      <c r="Y25" s="16" t="n">
+      <c r="Y25" s="18" t="n">
         <v>58.95</v>
       </c>
-      <c r="Z25" s="16" t="n">
+      <c r="Z25" s="18" t="n">
         <v>59.56</v>
       </c>
-      <c r="AA25" s="16" t="n">
+      <c r="AA25" s="18" t="n">
         <v>60.73</v>
       </c>
-      <c r="AB25" s="16" t="n">
+      <c r="AB25" s="18" t="n">
         <v>58.25</v>
       </c>
-      <c r="AC25" s="16" t="n">
+      <c r="AC25" s="18" t="n">
         <v>59.36</v>
       </c>
-      <c r="AD25" s="16" t="n">
+      <c r="AD25" s="18" t="n">
         <v>59.87</v>
       </c>
-      <c r="AE25" s="16" t="n">
+      <c r="AE25" s="18" t="n">
         <v>60.83</v>
       </c>
+      <c r="AG25" s="18" t="n">
+        <v>3.87</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>2-(benzofuran-2-yl)-4,4,5,5-tetramethyl-1,3,2-dioxaborolane</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="18" t="inlineStr">
         <is>
           <t>CC(O1)(C)C(C)(C)OB1C2=CC3=CC=CC=C3O2</t>
         </is>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="18" t="n">
         <v>64.25</v>
       </c>
-      <c r="G26" s="16" t="n">
+      <c r="G26" s="18" t="n">
         <v>14.43</v>
       </c>
-      <c r="H26" s="16" t="n">
+      <c r="H26" s="18" t="n">
         <v>14.39</v>
       </c>
-      <c r="J26" s="16" t="n">
+      <c r="J26" s="18" t="n">
         <v>142.25</v>
       </c>
-      <c r="K26" s="16" t="n">
+      <c r="K26" s="18" t="n">
         <v>1.75</v>
       </c>
-      <c r="L26" s="16" t="n">
+      <c r="L26" s="18" t="n">
         <v>5.29</v>
       </c>
-      <c r="M26" s="16" t="n">
+      <c r="M26" s="18" t="n">
         <v>5.4</v>
       </c>
-      <c r="O26" s="16" t="n">
+      <c r="O26" s="18" t="n">
         <v>42.69</v>
       </c>
-      <c r="P26" s="16" t="n">
+      <c r="P26" s="18" t="n">
         <v>-2.57</v>
       </c>
-      <c r="Q26" s="16" t="n">
+      <c r="Q26" s="18" t="n">
         <v>6.93</v>
       </c>
-      <c r="R26" s="16" t="n">
+      <c r="R26" s="18" t="n">
         <v>6.21</v>
       </c>
-      <c r="T26" s="16" t="n">
+      <c r="T26" s="18" t="n">
         <v>4935</v>
       </c>
-      <c r="U26" s="16" t="n">
+      <c r="U26" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V26" s="16" t="n">
+      <c r="V26" s="18" t="n">
         <v>79.98</v>
       </c>
-      <c r="W26" s="16" t="n">
+      <c r="W26" s="18" t="n">
         <v>7.13</v>
       </c>
-      <c r="X26" s="16" t="n">
+      <c r="X26" s="18" t="n">
         <v>61.61</v>
       </c>
-      <c r="Y26" s="16" t="n">
+      <c r="Y26" s="18" t="n">
         <v>62.8</v>
       </c>
-      <c r="Z26" s="16" t="n">
+      <c r="Z26" s="18" t="n">
         <v>63.39</v>
       </c>
-      <c r="AA26" s="16" t="n">
+      <c r="AA26" s="18" t="n">
         <v>64.51000000000001</v>
       </c>
-      <c r="AB26" s="16" t="n">
+      <c r="AB26" s="18" t="n">
         <v>62.17</v>
       </c>
-      <c r="AC26" s="16" t="n">
+      <c r="AC26" s="18" t="n">
         <v>63.2</v>
       </c>
-      <c r="AD26" s="16" t="n">
+      <c r="AD26" s="18" t="n">
         <v>63.71</v>
       </c>
-      <c r="AE26" s="16" t="n">
+      <c r="AE26" s="18" t="n">
         <v>64.67</v>
       </c>
+      <c r="AG26" s="18" t="n">
+        <v>3.82</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>2-bromobenzo[b]thiophene</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="18" t="inlineStr">
         <is>
           <t>BrC1=CC2=CC=CC=C2S1</t>
         </is>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="18" t="n">
         <v>60.5</v>
       </c>
-      <c r="G27" s="16" t="n">
+      <c r="G27" s="18" t="n">
         <v>35.47</v>
       </c>
-      <c r="H27" s="16" t="n">
+      <c r="H27" s="18" t="n">
         <v>20.64</v>
       </c>
-      <c r="J27" s="16" t="n">
+      <c r="J27" s="18" t="n">
         <v>141.31</v>
       </c>
-      <c r="K27" s="16" t="n">
+      <c r="K27" s="18" t="n">
         <v>1.71</v>
       </c>
-      <c r="L27" s="16" t="n">
+      <c r="L27" s="18" t="n">
         <v>4.6</v>
       </c>
-      <c r="M27" s="16" t="n">
+      <c r="M27" s="18" t="n">
         <v>4.53</v>
       </c>
-      <c r="O27" s="16" t="n">
+      <c r="O27" s="18" t="n">
         <v>64.56</v>
       </c>
-      <c r="P27" s="16" t="n">
+      <c r="P27" s="18" t="n">
         <v>-1.62</v>
       </c>
-      <c r="Q27" s="16" t="n">
+      <c r="Q27" s="18" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="R27" s="16" t="n">
+      <c r="R27" s="18" t="n">
         <v>30.94</v>
       </c>
-      <c r="T27" s="16" t="n">
+      <c r="T27" s="18" t="n">
         <v>4972</v>
       </c>
-      <c r="U27" s="16" t="n">
+      <c r="U27" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V27" s="16" t="n">
+      <c r="V27" s="18" t="n">
         <v>81.69</v>
       </c>
-      <c r="W27" s="16" t="n">
+      <c r="W27" s="18" t="n">
         <v>6.93</v>
       </c>
-      <c r="X27" s="16" t="n">
+      <c r="X27" s="18" t="n">
         <v>63.85</v>
       </c>
-      <c r="Y27" s="16" t="n">
+      <c r="Y27" s="18" t="n">
         <v>65</v>
       </c>
-      <c r="Z27" s="16" t="n">
+      <c r="Z27" s="18" t="n">
         <v>65.58</v>
       </c>
-      <c r="AA27" s="16" t="n">
+      <c r="AA27" s="18" t="n">
         <v>66.66</v>
       </c>
-      <c r="AB27" s="16" t="n">
+      <c r="AB27" s="18" t="n">
         <v>63.76</v>
       </c>
-      <c r="AC27" s="16" t="n">
+      <c r="AC27" s="18" t="n">
         <v>64.88</v>
       </c>
-      <c r="AD27" s="16" t="n">
+      <c r="AD27" s="18" t="n">
         <v>65.47</v>
       </c>
-      <c r="AE27" s="16" t="n">
+      <c r="AE27" s="18" t="n">
         <v>66.54000000000001</v>
       </c>
+      <c r="AG27" s="18" t="n">
+        <v>3.19</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>2-bromobenzofuran</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="18" t="inlineStr">
         <is>
           <t>BrC1=CC2=CC=CC=C2O1</t>
         </is>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="18" t="n">
         <v>59.92</v>
       </c>
-      <c r="G28" s="16" t="n">
+      <c r="G28" s="18" t="n">
         <v>36.37</v>
       </c>
-      <c r="H28" s="16" t="n">
+      <c r="H28" s="18" t="n">
         <v>25.68</v>
       </c>
-      <c r="J28" s="16" t="n">
+      <c r="J28" s="18" t="n">
         <v>140.85</v>
       </c>
-      <c r="K28" s="16" t="n">
+      <c r="K28" s="18" t="n">
         <v>1.69</v>
       </c>
-      <c r="L28" s="16" t="n">
+      <c r="L28" s="18" t="n">
         <v>5.07</v>
       </c>
-      <c r="M28" s="16" t="n">
+      <c r="M28" s="18" t="n">
         <v>5.17</v>
       </c>
-      <c r="O28" s="16" t="n">
+      <c r="O28" s="18" t="n">
         <v>62.18</v>
       </c>
-      <c r="P28" s="16" t="n">
+      <c r="P28" s="18" t="n">
         <v>-1.72</v>
       </c>
-      <c r="Q28" s="16" t="n">
+      <c r="Q28" s="18" t="n">
         <v>73.45999999999999</v>
       </c>
-      <c r="R28" s="16" t="n">
+      <c r="R28" s="18" t="n">
         <v>32.62</v>
       </c>
-      <c r="T28" s="16" t="n">
+      <c r="T28" s="18" t="n">
         <v>4960</v>
       </c>
-      <c r="U28" s="16" t="n">
+      <c r="U28" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V28" s="16" t="n">
+      <c r="V28" s="18" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="W28" s="16" t="n">
+      <c r="W28" s="18" t="n">
         <v>6.81</v>
       </c>
-      <c r="X28" s="16" t="n">
+      <c r="X28" s="18" t="n">
         <v>67.55</v>
       </c>
-      <c r="Y28" s="16" t="n">
+      <c r="Y28" s="18" t="n">
         <v>68.69</v>
       </c>
-      <c r="Z28" s="16" t="n">
+      <c r="Z28" s="18" t="n">
         <v>69.25</v>
       </c>
-      <c r="AA28" s="16" t="n">
+      <c r="AA28" s="18" t="n">
         <v>70.31999999999999</v>
       </c>
-      <c r="AB28" s="16" t="n">
+      <c r="AB28" s="18" t="n">
         <v>67.12</v>
       </c>
-      <c r="AC28" s="16" t="n">
+      <c r="AC28" s="18" t="n">
         <v>68.08</v>
       </c>
-      <c r="AD28" s="16" t="n">
+      <c r="AD28" s="18" t="n">
         <v>68.56999999999999</v>
       </c>
-      <c r="AE28" s="16" t="n">
+      <c r="AE28" s="18" t="n">
         <v>69.58</v>
       </c>
+      <c r="AG28" s="18" t="n">
+        <v>3.12</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>2,5-dibromothiophene</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>BrC1=CC=C(Br)S1</t>
         </is>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="18" t="n">
         <v>58.55</v>
       </c>
-      <c r="G29" s="16" t="n">
+      <c r="G29" s="18" t="n">
         <v>36.22</v>
       </c>
-      <c r="H29" s="16" t="n">
+      <c r="H29" s="18" t="n">
         <v>19.78</v>
       </c>
-      <c r="J29" s="16" t="n">
+      <c r="J29" s="18" t="n">
         <v>144.19</v>
       </c>
-      <c r="K29" s="16" t="n">
+      <c r="K29" s="18" t="n">
         <v>1.83</v>
       </c>
-      <c r="L29" s="16" t="n">
+      <c r="L29" s="18" t="n">
         <v>5.29</v>
       </c>
-      <c r="M29" s="16" t="n">
+      <c r="M29" s="18" t="n">
         <v>5.4</v>
       </c>
-      <c r="O29" s="16" t="n">
+      <c r="O29" s="18" t="n">
         <v>65.28</v>
       </c>
-      <c r="P29" s="16" t="n">
+      <c r="P29" s="18" t="n">
         <v>-1.59</v>
       </c>
-      <c r="Q29" s="16" t="n">
+      <c r="Q29" s="18" t="n">
         <v>67.98</v>
       </c>
-      <c r="R29" s="16" t="n">
+      <c r="R29" s="18" t="n">
         <v>29.98</v>
       </c>
-      <c r="T29" s="16" t="n">
+      <c r="T29" s="18" t="n">
         <v>4982</v>
       </c>
-      <c r="U29" s="16" t="n">
+      <c r="U29" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V29" s="16" t="n">
+      <c r="V29" s="18" t="n">
         <v>81.88</v>
       </c>
-      <c r="W29" s="16" t="n">
+      <c r="W29" s="18" t="n">
         <v>7.56</v>
       </c>
-      <c r="X29" s="16" t="n">
+      <c r="X29" s="18" t="n">
         <v>62.4</v>
       </c>
-      <c r="Y29" s="16" t="n">
+      <c r="Y29" s="18" t="n">
         <v>63.66</v>
       </c>
-      <c r="Z29" s="16" t="n">
+      <c r="Z29" s="18" t="n">
         <v>64.29000000000001</v>
       </c>
-      <c r="AA29" s="16" t="n">
+      <c r="AA29" s="18" t="n">
         <v>65.47</v>
       </c>
-      <c r="AB29" s="16" t="n">
+      <c r="AB29" s="18" t="n">
         <v>64.83</v>
       </c>
-      <c r="AC29" s="16" t="n">
+      <c r="AC29" s="18" t="n">
         <v>65.61</v>
       </c>
-      <c r="AD29" s="16" t="n">
+      <c r="AD29" s="18" t="n">
         <v>66.01000000000001</v>
       </c>
-      <c r="AE29" s="16" t="n">
+      <c r="AE29" s="18" t="n">
         <v>66.79000000000001</v>
       </c>
+      <c r="AG29" s="18" t="n">
+        <v>2.98</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>2-benzoylthiazole</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="18" t="inlineStr">
         <is>
           <t>O=C(C1=CC=CC=C1)C2=NC=CS2</t>
         </is>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="18" t="n">
         <v>58.22</v>
       </c>
-      <c r="G30" s="16" t="n">
+      <c r="G30" s="18" t="n">
         <v>12.57</v>
       </c>
-      <c r="H30" s="16" t="n">
+      <c r="H30" s="18" t="n">
         <v>13.84</v>
       </c>
-      <c r="J30" s="16" t="n">
+      <c r="J30" s="18" t="n">
         <v>159.27</v>
       </c>
-      <c r="K30" s="16" t="n">
+      <c r="K30" s="18" t="n">
         <v>2.49</v>
       </c>
-      <c r="L30" s="16" t="n">
+      <c r="L30" s="18" t="n">
         <v>6.3</v>
       </c>
-      <c r="M30" s="16" t="n">
+      <c r="M30" s="18" t="n">
         <v>5.94</v>
       </c>
-      <c r="O30" s="16" t="n">
+      <c r="O30" s="18" t="n">
         <v>71.04000000000001</v>
       </c>
-      <c r="P30" s="16" t="n">
+      <c r="P30" s="18" t="n">
         <v>-1.34</v>
       </c>
-      <c r="Q30" s="16" t="n">
+      <c r="Q30" s="18" t="n">
         <v>6.6</v>
       </c>
-      <c r="R30" s="16" t="n">
+      <c r="R30" s="18" t="n">
         <v>7.2</v>
       </c>
-      <c r="T30" s="16" t="n">
+      <c r="T30" s="18" t="n">
         <v>4938</v>
       </c>
-      <c r="U30" s="16" t="n">
+      <c r="U30" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V30" s="16" t="n">
+      <c r="V30" s="18" t="n">
         <v>74.91</v>
       </c>
-      <c r="W30" s="16" t="n">
+      <c r="W30" s="18" t="n">
         <v>6.72</v>
       </c>
-      <c r="X30" s="16" t="n">
+      <c r="X30" s="18" t="n">
         <v>57.59</v>
       </c>
-      <c r="Y30" s="16" t="n">
+      <c r="Y30" s="18" t="n">
         <v>58.71</v>
       </c>
-      <c r="Z30" s="16" t="n">
+      <c r="Z30" s="18" t="n">
         <v>59.27</v>
       </c>
-      <c r="AA30" s="16" t="n">
+      <c r="AA30" s="18" t="n">
         <v>60.32</v>
       </c>
-      <c r="AB30" s="16" t="n">
+      <c r="AB30" s="18" t="n">
         <v>58.03</v>
       </c>
-      <c r="AC30" s="16" t="n">
+      <c r="AC30" s="18" t="n">
         <v>59.05</v>
       </c>
-      <c r="AD30" s="16" t="n">
+      <c r="AD30" s="18" t="n">
         <v>59.56</v>
       </c>
-      <c r="AE30" s="16" t="n">
+      <c r="AE30" s="18" t="n">
         <v>60.53</v>
       </c>
+      <c r="AG30" s="18" t="n">
+        <v>3.37</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>4,4-dimethyl-3-phenylisoxazol-5(4H)-one</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>O=C1C(C)(C)C(C2=CC=CC=C2)=NO1</t>
         </is>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="18" t="n">
         <v>58.98</v>
       </c>
-      <c r="G31" s="16" t="n">
+      <c r="G31" s="18" t="n">
         <v>23.26</v>
       </c>
-      <c r="H31" s="16" t="n">
+      <c r="H31" s="18" t="n">
         <v>21.47</v>
       </c>
-      <c r="J31" s="16" t="n">
+      <c r="J31" s="18" t="n">
         <v>154.89</v>
       </c>
-      <c r="K31" s="16" t="n">
+      <c r="K31" s="18" t="n">
         <v>2.3</v>
       </c>
-      <c r="L31" s="16" t="n">
+      <c r="L31" s="18" t="n">
         <v>7.87</v>
       </c>
-      <c r="M31" s="16" t="n">
+      <c r="M31" s="18" t="n">
         <v>6.24</v>
       </c>
-      <c r="O31" s="16" t="n">
+      <c r="O31" s="18" t="n">
         <v>55.05</v>
       </c>
-      <c r="P31" s="16" t="n">
+      <c r="P31" s="18" t="n">
         <v>-2.03</v>
       </c>
-      <c r="Q31" s="16" t="n">
+      <c r="Q31" s="18" t="n">
         <v>7.05</v>
       </c>
-      <c r="R31" s="16" t="n">
+      <c r="R31" s="18" t="n">
         <v>6.71</v>
       </c>
-      <c r="T31" s="16" t="n">
+      <c r="T31" s="18" t="n">
         <v>4936</v>
       </c>
-      <c r="U31" s="16" t="n">
+      <c r="U31" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V31" s="16" t="n">
+      <c r="V31" s="18" t="n">
         <v>82.48999999999999</v>
       </c>
-      <c r="W31" s="16" t="n">
+      <c r="W31" s="18" t="n">
         <v>8.19</v>
       </c>
-      <c r="X31" s="16" t="n">
+      <c r="X31" s="18" t="n">
         <v>61.39</v>
       </c>
-      <c r="Y31" s="16" t="n">
+      <c r="Y31" s="18" t="n">
         <v>62.75</v>
       </c>
-      <c r="Z31" s="16" t="n">
+      <c r="Z31" s="18" t="n">
         <v>63.43</v>
       </c>
-      <c r="AA31" s="16" t="n">
+      <c r="AA31" s="18" t="n">
         <v>64.70999999999999</v>
       </c>
-      <c r="AB31" s="16" t="n">
+      <c r="AB31" s="18" t="n">
         <v>60.24</v>
       </c>
-      <c r="AC31" s="16" t="n">
+      <c r="AC31" s="18" t="n">
         <v>61.71</v>
       </c>
-      <c r="AD31" s="16" t="n">
+      <c r="AD31" s="18" t="n">
         <v>62.4</v>
       </c>
-      <c r="AE31" s="16" t="n">
+      <c r="AE31" s="18" t="n">
         <v>63.77</v>
       </c>
+      <c r="AG31" s="18" t="n">
+        <v>3.46</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>Q30</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>(E)-stilbene</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="18" t="inlineStr">
         <is>
           <t>C1(/C=C/C2=CC=CC=C2)=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="18" t="n">
         <v>42.79</v>
       </c>
-      <c r="G32" s="16" t="n">
+      <c r="G32" s="18" t="n">
         <v>70.41</v>
       </c>
-      <c r="H32" s="16" t="n">
+      <c r="H32" s="18" t="n">
         <v>22.09</v>
       </c>
-      <c r="J32" s="16" t="n">
+      <c r="J32" s="18" t="n">
         <v>132.59</v>
       </c>
-      <c r="K32" s="16" t="n">
+      <c r="K32" s="18" t="n">
         <v>1.33</v>
       </c>
-      <c r="L32" s="16" t="n">
+      <c r="L32" s="18" t="n">
         <v>4.8</v>
       </c>
-      <c r="M32" s="16" t="n">
+      <c r="M32" s="18" t="n">
         <v>4.73</v>
       </c>
-      <c r="O32" s="16" t="n">
+      <c r="O32" s="18" t="n">
         <v>49.29</v>
       </c>
-      <c r="P32" s="16" t="n">
+      <c r="P32" s="18" t="n">
         <v>-2.28</v>
       </c>
-      <c r="Q32" s="16" t="n">
+      <c r="Q32" s="18" t="n">
         <v>5.41</v>
       </c>
-      <c r="R32" s="16" t="n">
+      <c r="R32" s="18" t="n">
         <v>5.06</v>
       </c>
-      <c r="T32" s="16" t="n">
+      <c r="T32" s="18" t="n">
         <v>4948</v>
       </c>
-      <c r="U32" s="16" t="n">
+      <c r="U32" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V32" s="16" t="n">
+      <c r="V32" s="18" t="n">
         <v>70.63</v>
       </c>
-      <c r="W32" s="16" t="n">
+      <c r="W32" s="18" t="n">
         <v>9.09</v>
       </c>
-      <c r="X32" s="16" t="n">
+      <c r="X32" s="18" t="n">
         <v>47.22</v>
       </c>
-      <c r="Y32" s="16" t="n">
+      <c r="Y32" s="18" t="n">
         <v>48.73</v>
       </c>
-      <c r="Z32" s="16" t="n">
+      <c r="Z32" s="18" t="n">
         <v>49.49</v>
       </c>
-      <c r="AA32" s="16" t="n">
+      <c r="AA32" s="18" t="n">
         <v>50.91</v>
       </c>
-      <c r="AB32" s="16" t="n">
+      <c r="AB32" s="18" t="n">
         <v>46.76</v>
       </c>
-      <c r="AC32" s="16" t="n">
+      <c r="AC32" s="18" t="n">
         <v>48.14</v>
       </c>
-      <c r="AD32" s="16" t="n">
+      <c r="AD32" s="18" t="n">
         <v>48.91</v>
       </c>
-      <c r="AE32" s="16" t="n">
+      <c r="AE32" s="18" t="n">
         <v>50.47</v>
       </c>
+      <c r="AG32" s="18" t="n">
+        <v>3.52</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>Q31</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>6-phenyl-5-oxa-6-azaspiro[2.4]heptane-4,7-dione</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>O=C1N(C2=CC=CC=C2)OC(C13CC3)=O</t>
         </is>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="18" t="n">
         <v>76.37</v>
       </c>
-      <c r="G33" s="16" t="n">
+      <c r="G33" s="18" t="n">
         <v>36.98</v>
       </c>
-      <c r="H33" s="16" t="n">
+      <c r="H33" s="18" t="n">
         <v>15.04</v>
       </c>
-      <c r="J33" s="16" t="n">
+      <c r="J33" s="18" t="n">
         <v>142.42</v>
       </c>
-      <c r="K33" s="16" t="n">
+      <c r="K33" s="18" t="n">
         <v>1.76</v>
       </c>
-      <c r="L33" s="16" t="n">
+      <c r="L33" s="18" t="n">
         <v>7.44</v>
       </c>
-      <c r="M33" s="16" t="n">
+      <c r="M33" s="18" t="n">
         <v>9.34</v>
       </c>
-      <c r="O33" s="16" t="n">
+      <c r="O33" s="18" t="n">
         <v>40.2</v>
       </c>
-      <c r="P33" s="16" t="n">
+      <c r="P33" s="18" t="n">
         <v>-2.68</v>
       </c>
-      <c r="Q33" s="16" t="n">
+      <c r="Q33" s="18" t="n">
         <v>27.22</v>
       </c>
-      <c r="R33" s="16" t="n">
+      <c r="R33" s="18" t="n">
         <v>11.8</v>
       </c>
-      <c r="T33" s="16" t="n">
+      <c r="T33" s="18" t="n">
         <v>4939</v>
       </c>
-      <c r="U33" s="16" t="n">
+      <c r="U33" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V33" s="16" t="n">
+      <c r="V33" s="18" t="n">
         <v>89.22</v>
       </c>
-      <c r="W33" s="16" t="n">
+      <c r="W33" s="18" t="n">
         <v>6.19</v>
       </c>
-      <c r="X33" s="16" t="n">
+      <c r="X33" s="18" t="n">
         <v>73.27</v>
       </c>
-      <c r="Y33" s="16" t="n">
+      <c r="Y33" s="18" t="n">
         <v>74.3</v>
       </c>
-      <c r="Z33" s="16" t="n">
+      <c r="Z33" s="18" t="n">
         <v>74.81</v>
       </c>
-      <c r="AA33" s="16" t="n">
+      <c r="AA33" s="18" t="n">
         <v>75.78</v>
       </c>
-      <c r="AB33" s="16" t="n">
+      <c r="AB33" s="18" t="n">
         <v>71.7</v>
       </c>
-      <c r="AC33" s="16" t="n">
+      <c r="AC33" s="18" t="n">
         <v>73.15000000000001</v>
       </c>
-      <c r="AD33" s="16" t="n">
+      <c r="AD33" s="18" t="n">
         <v>73.83</v>
       </c>
-      <c r="AE33" s="16" t="n">
+      <c r="AE33" s="18" t="n">
         <v>75</v>
       </c>
+      <c r="AG33" s="18" t="n">
+        <v>3.46</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>Q32</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>1-(thiobenzoyl)pyrrolidine</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="18" t="inlineStr">
         <is>
           <t>S=C(N1CCCC1)C2=CC=CC=C2</t>
         </is>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="F34" s="18" t="n">
         <v>54.73</v>
       </c>
-      <c r="G34" s="16" t="n">
+      <c r="G34" s="18" t="n">
         <v>41.85</v>
       </c>
-      <c r="H34" s="16" t="n">
+      <c r="H34" s="18" t="n">
         <v>18.79</v>
       </c>
-      <c r="J34" s="16" t="n">
+      <c r="J34" s="18" t="n">
         <v>134.05</v>
       </c>
-      <c r="K34" s="16" t="n">
+      <c r="K34" s="18" t="n">
         <v>1.39</v>
       </c>
-      <c r="L34" s="16" t="n">
+      <c r="L34" s="18" t="n">
         <v>2.48</v>
       </c>
-      <c r="M34" s="16" t="n">
+      <c r="M34" s="18" t="n">
         <v>2.17</v>
       </c>
-      <c r="O34" s="16" t="n">
+      <c r="O34" s="18" t="n">
         <v>53.76</v>
       </c>
-      <c r="P34" s="16" t="n">
+      <c r="P34" s="18" t="n">
         <v>-2.09</v>
       </c>
-      <c r="Q34" s="16" t="n">
+      <c r="Q34" s="18" t="n">
         <v>21.08</v>
       </c>
-      <c r="R34" s="16" t="n">
+      <c r="R34" s="18" t="n">
         <v>17.08</v>
       </c>
-      <c r="T34" s="16" t="n">
+      <c r="T34" s="18" t="n">
         <v>4941</v>
       </c>
-      <c r="U34" s="16" t="n">
+      <c r="U34" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V34" s="16" t="n">
+      <c r="V34" s="18" t="n">
         <v>73.5</v>
       </c>
-      <c r="W34" s="16" t="n">
+      <c r="W34" s="18" t="n">
         <v>5.38</v>
       </c>
-      <c r="X34" s="16" t="n">
+      <c r="X34" s="18" t="n">
         <v>59.64</v>
       </c>
-      <c r="Y34" s="16" t="n">
+      <c r="Y34" s="18" t="n">
         <v>60.54</v>
       </c>
-      <c r="Z34" s="16" t="n">
+      <c r="Z34" s="18" t="n">
         <v>60.98</v>
       </c>
-      <c r="AA34" s="16" t="n">
+      <c r="AA34" s="18" t="n">
         <v>61.82</v>
       </c>
-      <c r="AB34" s="16" t="n">
+      <c r="AB34" s="18" t="n">
         <v>59.88</v>
       </c>
-      <c r="AC34" s="16" t="n">
+      <c r="AC34" s="18" t="n">
         <v>60.72</v>
       </c>
-      <c r="AD34" s="16" t="n">
+      <c r="AD34" s="18" t="n">
         <v>61.16</v>
       </c>
-      <c r="AE34" s="16" t="n">
+      <c r="AE34" s="18" t="n">
         <v>62</v>
       </c>
+      <c r="AG34" s="18" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n">
+      <c r="A35" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>Q33</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>N-methyl-N-phenylpropanethioamide</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="18" t="inlineStr">
         <is>
           <t>S=C(N(C1=CC=CC=C1)C)CC</t>
         </is>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="F35" s="18" t="n">
         <v>58.66</v>
       </c>
-      <c r="G35" s="16" t="n">
+      <c r="G35" s="18" t="n">
         <v>32.93</v>
       </c>
-      <c r="H35" s="16" t="n">
+      <c r="H35" s="18" t="n">
         <v>16.79</v>
       </c>
-      <c r="J35" s="16" t="n">
+      <c r="J35" s="18" t="n">
         <v>133.46</v>
       </c>
-      <c r="K35" s="16" t="n">
+      <c r="K35" s="18" t="n">
         <v>1.37</v>
       </c>
-      <c r="L35" s="16" t="n">
+      <c r="L35" s="18" t="n">
         <v>7.24</v>
       </c>
-      <c r="M35" s="16" t="n">
+      <c r="M35" s="18" t="n">
         <v>3.15</v>
       </c>
-      <c r="O35" s="16" t="n">
+      <c r="O35" s="18" t="n">
         <v>51.25</v>
       </c>
-      <c r="P35" s="16" t="n">
+      <c r="P35" s="18" t="n">
         <v>-2.2</v>
       </c>
-      <c r="Q35" s="16" t="n">
+      <c r="Q35" s="18" t="n">
         <v>23.49</v>
       </c>
-      <c r="R35" s="16" t="n">
+      <c r="R35" s="18" t="n">
         <v>26.85</v>
       </c>
-      <c r="T35" s="16" t="n">
+      <c r="T35" s="18" t="n">
         <v>4922</v>
       </c>
-      <c r="U35" s="16" t="n">
+      <c r="U35" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V35" s="16" t="n">
+      <c r="V35" s="18" t="n">
         <v>75.20999999999999</v>
       </c>
-      <c r="W35" s="16" t="n">
+      <c r="W35" s="18" t="n">
         <v>4.85</v>
       </c>
-      <c r="X35" s="16" t="n">
+      <c r="X35" s="18" t="n">
         <v>62.71</v>
       </c>
-      <c r="Y35" s="16" t="n">
+      <c r="Y35" s="18" t="n">
         <v>63.52</v>
       </c>
-      <c r="Z35" s="16" t="n">
+      <c r="Z35" s="18" t="n">
         <v>63.92</v>
       </c>
-      <c r="AA35" s="16" t="n">
+      <c r="AA35" s="18" t="n">
         <v>64.68000000000001</v>
       </c>
-      <c r="AB35" s="16" t="n">
+      <c r="AB35" s="18" t="n">
         <v>62.25</v>
       </c>
-      <c r="AC35" s="16" t="n">
+      <c r="AC35" s="18" t="n">
         <v>63.26</v>
       </c>
-      <c r="AD35" s="16" t="n">
+      <c r="AD35" s="18" t="n">
         <v>63.73</v>
       </c>
-      <c r="AE35" s="16" t="n">
+      <c r="AE35" s="18" t="n">
         <v>64.55</v>
       </c>
+      <c r="AG35" s="18" t="n">
+        <v>3.46</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n">
+      <c r="A36" s="18" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>Q34</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>(Z)-3,4-dihydronaphthalen-1(2H)-one O-methyl oxime</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="18" t="inlineStr">
         <is>
           <t>CO/N=C1CCCC2=CC=CC=C2/1</t>
         </is>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="F36" s="18" t="n">
         <v>42.19</v>
       </c>
-      <c r="G36" s="16" t="n">
+      <c r="G36" s="18" t="n">
         <v>71.38</v>
       </c>
-      <c r="H36" s="16" t="n">
+      <c r="H36" s="18" t="n">
         <v>40.48</v>
       </c>
-      <c r="J36" s="16" t="n">
+      <c r="J36" s="18" t="n">
         <v>139.76</v>
       </c>
-      <c r="K36" s="16" t="n">
+      <c r="K36" s="18" t="n">
         <v>1.64</v>
       </c>
-      <c r="L36" s="16" t="n">
+      <c r="L36" s="18" t="n">
         <v>13.59</v>
       </c>
-      <c r="M36" s="16" t="n">
+      <c r="M36" s="18" t="n">
         <v>10.13</v>
       </c>
-      <c r="O36" s="16" t="n">
+      <c r="O36" s="18" t="n">
         <v>44</v>
       </c>
-      <c r="P36" s="16" t="n">
+      <c r="P36" s="18" t="n">
         <v>-2.51</v>
       </c>
-      <c r="Q36" s="16" t="n">
+      <c r="Q36" s="18" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="R36" s="16" t="n">
+      <c r="R36" s="18" t="n">
         <v>8.9</v>
       </c>
-      <c r="T36" s="16" t="n">
+      <c r="T36" s="18" t="n">
         <v>4936</v>
       </c>
-      <c r="U36" s="16" t="n">
+      <c r="U36" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V36" s="16" t="n">
+      <c r="V36" s="18" t="n">
         <v>81.95</v>
       </c>
-      <c r="W36" s="16" t="n">
+      <c r="W36" s="18" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="X36" s="16" t="n">
+      <c r="X36" s="18" t="n">
         <v>60.78</v>
       </c>
-      <c r="Y36" s="16" t="n">
+      <c r="Y36" s="18" t="n">
         <v>62.15</v>
       </c>
-      <c r="Z36" s="16" t="n">
+      <c r="Z36" s="18" t="n">
         <v>62.83</v>
       </c>
-      <c r="AA36" s="16" t="n">
+      <c r="AA36" s="18" t="n">
         <v>64.12</v>
       </c>
-      <c r="AB36" s="16" t="n">
+      <c r="AB36" s="18" t="n">
         <v>60.84</v>
       </c>
-      <c r="AC36" s="16" t="n">
+      <c r="AC36" s="18" t="n">
         <v>62.04</v>
       </c>
-      <c r="AD36" s="16" t="n">
+      <c r="AD36" s="18" t="n">
         <v>62.63</v>
       </c>
-      <c r="AE36" s="16" t="n">
+      <c r="AE36" s="18" t="n">
         <v>63.77</v>
       </c>
+      <c r="AG36" s="18" t="n">
+        <v>3.44</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n">
+      <c r="A37" s="18" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>Q35</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>(Z)-stilbene</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>C1(/C=C\C2=CC=CC=C2)=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="18" t="n">
         <v>39.19</v>
       </c>
-      <c r="G37" s="16" t="n">
+      <c r="G37" s="18" t="n">
         <v>66.36</v>
       </c>
-      <c r="H37" s="16" t="n">
+      <c r="H37" s="18" t="n">
         <v>40.38</v>
       </c>
-      <c r="J37" s="16" t="n">
+      <c r="J37" s="18" t="n">
         <v>135.62</v>
       </c>
-      <c r="K37" s="16" t="n">
+      <c r="K37" s="18" t="n">
         <v>1.46</v>
       </c>
-      <c r="L37" s="16" t="n">
+      <c r="L37" s="18" t="n">
         <v>8.6</v>
       </c>
-      <c r="M37" s="16" t="n">
+      <c r="M37" s="18" t="n">
         <v>9.19</v>
       </c>
-      <c r="O37" s="16" t="n">
+      <c r="O37" s="18" t="n">
         <v>46.63</v>
       </c>
-      <c r="P37" s="16" t="n">
+      <c r="P37" s="18" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q37" s="16" t="n">
+      <c r="Q37" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="R37" s="16" t="n">
+      <c r="R37" s="18" t="n">
         <v>12.28</v>
       </c>
-      <c r="T37" s="16" t="n">
+      <c r="T37" s="18" t="n">
         <v>4952</v>
       </c>
-      <c r="U37" s="16" t="n">
+      <c r="U37" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V37" s="16" t="n">
+      <c r="V37" s="18" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="W37" s="16" t="n">
+      <c r="W37" s="18" t="n">
         <v>8.58</v>
       </c>
-      <c r="X37" s="16" t="n">
+      <c r="X37" s="18" t="n">
         <v>55.58</v>
       </c>
-      <c r="Y37" s="16" t="n">
+      <c r="Y37" s="18" t="n">
         <v>57.01</v>
       </c>
-      <c r="Z37" s="16" t="n">
+      <c r="Z37" s="18" t="n">
         <v>57.72</v>
       </c>
-      <c r="AA37" s="16" t="n">
+      <c r="AA37" s="18" t="n">
         <v>59.06</v>
       </c>
-      <c r="AB37" s="16" t="n">
+      <c r="AB37" s="18" t="n">
         <v>54.74</v>
       </c>
-      <c r="AC37" s="16" t="n">
+      <c r="AC37" s="18" t="n">
         <v>56.04</v>
       </c>
-      <c r="AD37" s="16" t="n">
+      <c r="AD37" s="18" t="n">
         <v>56.69</v>
       </c>
-      <c r="AE37" s="16" t="n">
+      <c r="AE37" s="18" t="n">
         <v>57.96</v>
       </c>
+      <c r="AG37" s="18" t="n">
+        <v>3.52</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="n">
+      <c r="A38" s="18" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>2-acetyl-1-methylpyrrole</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="18" t="inlineStr">
         <is>
           <t>CN1C(C(C)=O)=CC=C1</t>
         </is>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="F38" s="18" t="n">
         <v>64.89</v>
       </c>
-      <c r="G38" s="16" t="n">
+      <c r="G38" s="18" t="n">
         <v>9.59</v>
       </c>
-      <c r="H38" s="16" t="n">
+      <c r="H38" s="18" t="n">
         <v>8.83</v>
       </c>
-      <c r="J38" s="16" t="n">
+      <c r="J38" s="18" t="n">
         <v>138.43</v>
       </c>
-      <c r="K38" s="16" t="n">
+      <c r="K38" s="18" t="n">
         <v>1.58</v>
       </c>
-      <c r="L38" s="16" t="n">
+      <c r="L38" s="18" t="n">
         <v>4.55</v>
       </c>
-      <c r="M38" s="16" t="n">
+      <c r="M38" s="18" t="n">
         <v>4.57</v>
       </c>
-      <c r="O38" s="16" t="n">
+      <c r="O38" s="18" t="n">
         <v>44.85</v>
       </c>
-      <c r="P38" s="16" t="n">
+      <c r="P38" s="18" t="n">
         <v>-2.48</v>
       </c>
-      <c r="Q38" s="16" t="n">
+      <c r="Q38" s="18" t="n">
         <v>6.89</v>
       </c>
-      <c r="R38" s="16" t="n">
+      <c r="R38" s="18" t="n">
         <v>6.19</v>
       </c>
-      <c r="T38" s="16" t="n">
+      <c r="T38" s="18" t="n">
         <v>4970</v>
       </c>
-      <c r="U38" s="16" t="n">
+      <c r="U38" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V38" s="16" t="n">
+      <c r="V38" s="18" t="n">
         <v>78.45</v>
       </c>
-      <c r="W38" s="16" t="n">
+      <c r="W38" s="18" t="n">
         <v>5.9</v>
       </c>
-      <c r="X38" s="16" t="n">
+      <c r="X38" s="18" t="n">
         <v>63.25</v>
       </c>
-      <c r="Y38" s="16" t="n">
+      <c r="Y38" s="18" t="n">
         <v>64.23</v>
       </c>
-      <c r="Z38" s="16" t="n">
+      <c r="Z38" s="18" t="n">
         <v>64.72</v>
       </c>
-      <c r="AA38" s="16" t="n">
+      <c r="AA38" s="18" t="n">
         <v>65.64</v>
       </c>
-      <c r="AB38" s="16" t="n">
+      <c r="AB38" s="18" t="n">
         <v>63.08</v>
       </c>
-      <c r="AC38" s="16" t="n">
+      <c r="AC38" s="18" t="n">
         <v>64.06999999999999</v>
       </c>
-      <c r="AD38" s="16" t="n">
+      <c r="AD38" s="18" t="n">
         <v>64.54000000000001</v>
       </c>
-      <c r="AE38" s="16" t="n">
+      <c r="AE38" s="18" t="n">
         <v>65.43000000000001</v>
       </c>
+      <c r="AG38" s="18" t="n">
+        <v>3.07</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="n">
+      <c r="A39" s="18" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>Q37</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>1-bromo-4-(2,2-difluorovinyl)benzene</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="18" t="inlineStr">
         <is>
           <t>F/C(F)=C/C1=CC=C(Br)C=C1</t>
         </is>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="F39" s="18" t="n">
         <v>48.43</v>
       </c>
-      <c r="G39" s="16" t="n">
+      <c r="G39" s="18" t="n">
         <v>85.31999999999999</v>
       </c>
-      <c r="H39" s="16" t="n">
+      <c r="H39" s="18" t="n">
         <v>32.55</v>
       </c>
-      <c r="J39" s="16" t="n">
+      <c r="J39" s="18" t="n">
         <v>143.11</v>
       </c>
-      <c r="K39" s="16" t="n">
+      <c r="K39" s="18" t="n">
         <v>1.79</v>
       </c>
-      <c r="L39" s="16" t="n">
+      <c r="L39" s="18" t="n">
         <v>5.98</v>
       </c>
-      <c r="M39" s="16" t="n">
+      <c r="M39" s="18" t="n">
         <v>6.1</v>
       </c>
-      <c r="O39" s="16" t="n">
+      <c r="O39" s="18" t="n">
         <v>44.68</v>
       </c>
-      <c r="P39" s="16" t="n">
+      <c r="P39" s="18" t="n">
         <v>-2.48</v>
       </c>
-      <c r="Q39" s="16" t="n">
+      <c r="Q39" s="18" t="n">
         <v>26.9</v>
       </c>
-      <c r="R39" s="16" t="n">
+      <c r="R39" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="T39" s="16" t="n">
+      <c r="T39" s="18" t="n">
         <v>4952</v>
       </c>
-      <c r="U39" s="16" t="n">
+      <c r="U39" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V39" s="16" t="n">
+      <c r="V39" s="18" t="n">
         <v>82.68000000000001</v>
       </c>
-      <c r="W39" s="16" t="n">
+      <c r="W39" s="18" t="n">
         <v>7.89</v>
       </c>
-      <c r="X39" s="16" t="n">
+      <c r="X39" s="18" t="n">
         <v>62.35</v>
       </c>
-      <c r="Y39" s="16" t="n">
+      <c r="Y39" s="18" t="n">
         <v>63.67</v>
       </c>
-      <c r="Z39" s="16" t="n">
+      <c r="Z39" s="18" t="n">
         <v>64.31999999999999</v>
       </c>
-      <c r="AA39" s="16" t="n">
+      <c r="AA39" s="18" t="n">
         <v>65.55</v>
       </c>
-      <c r="AB39" s="16" t="n">
+      <c r="AB39" s="18" t="n">
         <v>60.18</v>
       </c>
-      <c r="AC39" s="16" t="n">
+      <c r="AC39" s="18" t="n">
         <v>61.67</v>
       </c>
-      <c r="AD39" s="16" t="n">
+      <c r="AD39" s="18" t="n">
         <v>62.42</v>
       </c>
-      <c r="AE39" s="16" t="n">
+      <c r="AE39" s="18" t="n">
         <v>63.84</v>
       </c>
+      <c r="AG39" s="18" t="n">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="n">
+      <c r="A40" s="18" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>Q38</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>1,3-butadiene</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="18" t="inlineStr">
         <is>
           <t>C=CC=C</t>
         </is>
       </c>
-      <c r="F40" s="16" t="n">
+      <c r="F40" s="18" t="n">
         <v>50.55</v>
       </c>
-      <c r="G40" s="16" t="n">
+      <c r="G40" s="18" t="n">
         <v>87.06</v>
       </c>
-      <c r="H40" s="16" t="n">
+      <c r="H40" s="18" t="n">
         <v>25.79</v>
       </c>
-      <c r="J40" s="16" t="n">
+      <c r="J40" s="18" t="n">
         <v>145.58</v>
       </c>
-      <c r="K40" s="16" t="n">
+      <c r="K40" s="18" t="n">
         <v>1.89</v>
       </c>
-      <c r="L40" s="16" t="n">
+      <c r="L40" s="18" t="n">
         <v>4.55</v>
       </c>
-      <c r="M40" s="16" t="n">
+      <c r="M40" s="18" t="n">
         <v>4.54</v>
       </c>
-      <c r="O40" s="16" t="n">
+      <c r="O40" s="18" t="n">
         <v>41.61</v>
       </c>
-      <c r="P40" s="16" t="n">
+      <c r="P40" s="18" t="n">
         <v>-2.62</v>
       </c>
-      <c r="Q40" s="16" t="n">
+      <c r="Q40" s="18" t="n">
         <v>8.93</v>
       </c>
-      <c r="R40" s="16" t="n">
+      <c r="R40" s="18" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="T40" s="16" t="n">
+      <c r="T40" s="18" t="n">
         <v>4985</v>
       </c>
-      <c r="U40" s="16" t="n">
+      <c r="U40" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V40" s="16" t="n">
+      <c r="V40" s="18" t="n">
         <v>77.78</v>
       </c>
-      <c r="W40" s="16" t="n">
+      <c r="W40" s="18" t="n">
         <v>10.82</v>
       </c>
-      <c r="X40" s="16" t="n">
+      <c r="X40" s="18" t="n">
         <v>49.91</v>
       </c>
-      <c r="Y40" s="16" t="n">
+      <c r="Y40" s="18" t="n">
         <v>51.72</v>
       </c>
-      <c r="Z40" s="16" t="n">
+      <c r="Z40" s="18" t="n">
         <v>52.61</v>
       </c>
-      <c r="AA40" s="16" t="n">
+      <c r="AA40" s="18" t="n">
         <v>54.3</v>
       </c>
-      <c r="AB40" s="16" t="n">
+      <c r="AB40" s="18" t="n">
         <v>50.97</v>
       </c>
-      <c r="AC40" s="16" t="n">
+      <c r="AC40" s="18" t="n">
         <v>52.55</v>
       </c>
-      <c r="AD40" s="16" t="n">
+      <c r="AD40" s="18" t="n">
         <v>53.33</v>
       </c>
-      <c r="AE40" s="16" t="n">
+      <c r="AE40" s="18" t="n">
         <v>54.8</v>
       </c>
+      <c r="AG40" s="18" t="n">
+        <v>2.52</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="n">
+      <c r="A41" s="18" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>Q39</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>4-methyl-2-phenylthiazole</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="18" t="inlineStr">
         <is>
           <t>CC1=CSC(=N1)C2=CC=CC=C2</t>
         </is>
       </c>
-      <c r="F41" s="16" t="n">
+      <c r="F41" s="18" t="n">
         <v>55.25</v>
       </c>
-      <c r="G41" s="16" t="n">
+      <c r="G41" s="18" t="n">
         <v>17.54</v>
       </c>
-      <c r="H41" s="16" t="n">
+      <c r="H41" s="18" t="n">
         <v>19.28</v>
       </c>
-      <c r="J41" s="16" t="n">
+      <c r="J41" s="18" t="n">
         <v>139.03</v>
       </c>
-      <c r="K41" s="16" t="n">
+      <c r="K41" s="18" t="n">
         <v>1.61</v>
       </c>
-      <c r="L41" s="16" t="n">
+      <c r="L41" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="M41" s="16" t="n">
+      <c r="M41" s="18" t="n">
         <v>6.66</v>
       </c>
-      <c r="O41" s="16" t="n">
+      <c r="O41" s="18" t="n">
         <v>49.9</v>
       </c>
-      <c r="P41" s="16" t="n">
+      <c r="P41" s="18" t="n">
         <v>-2.26</v>
       </c>
-      <c r="Q41" s="16" t="n">
+      <c r="Q41" s="18" t="n">
         <v>5.55</v>
       </c>
-      <c r="R41" s="16" t="n">
+      <c r="R41" s="18" t="n">
         <v>6.66</v>
       </c>
-      <c r="T41" s="16" t="n">
+      <c r="T41" s="18" t="n">
         <v>4946</v>
       </c>
-      <c r="U41" s="16" t="n">
+      <c r="U41" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V41" s="16" t="n">
+      <c r="V41" s="18" t="n">
         <v>76.29000000000001</v>
       </c>
-      <c r="W41" s="16" t="n">
+      <c r="W41" s="18" t="n">
         <v>8.08</v>
       </c>
-      <c r="X41" s="16" t="n">
+      <c r="X41" s="18" t="n">
         <v>55.48</v>
       </c>
-      <c r="Y41" s="16" t="n">
+      <c r="Y41" s="18" t="n">
         <v>56.83</v>
       </c>
-      <c r="Z41" s="16" t="n">
+      <c r="Z41" s="18" t="n">
         <v>57.5</v>
       </c>
-      <c r="AA41" s="16" t="n">
+      <c r="AA41" s="18" t="n">
         <v>58.76</v>
       </c>
-      <c r="AB41" s="16" t="n">
+      <c r="AB41" s="18" t="n">
         <v>55.89</v>
       </c>
-      <c r="AC41" s="16" t="n">
+      <c r="AC41" s="18" t="n">
         <v>56.98</v>
       </c>
-      <c r="AD41" s="16" t="n">
+      <c r="AD41" s="18" t="n">
         <v>57.51</v>
       </c>
-      <c r="AE41" s="16" t="n">
+      <c r="AE41" s="18" t="n">
         <v>58.55</v>
       </c>
+      <c r="AG41" s="18" t="n">
+        <v>3.35</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n">
+      <c r="A42" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B42" s="18" t="inlineStr">
         <is>
           <t>Q40</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="C42" s="18" t="inlineStr">
         <is>
           <t>2-phenyloxazole</t>
         </is>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D42" s="18" t="inlineStr">
         <is>
           <t>C1(C2=CC=CC=C2)=NC=CO1</t>
         </is>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="F42" s="18" t="n">
         <v>62.71</v>
       </c>
-      <c r="G42" s="16" t="n">
+      <c r="G42" s="18" t="n">
         <v>18.65</v>
       </c>
-      <c r="H42" s="16" t="n">
+      <c r="H42" s="18" t="n">
         <v>19.3</v>
       </c>
-      <c r="J42" s="16" t="n">
+      <c r="J42" s="18" t="n">
         <v>143.96</v>
       </c>
-      <c r="K42" s="16" t="n">
+      <c r="K42" s="18" t="n">
         <v>1.82</v>
       </c>
-      <c r="L42" s="16" t="n">
+      <c r="L42" s="18" t="n">
         <v>6.46</v>
       </c>
-      <c r="M42" s="16" t="n">
+      <c r="M42" s="18" t="n">
         <v>6.49</v>
       </c>
-      <c r="O42" s="16" t="n">
+      <c r="O42" s="18" t="n">
         <v>45.72</v>
       </c>
-      <c r="P42" s="16" t="n">
+      <c r="P42" s="18" t="n">
         <v>-2.44</v>
       </c>
-      <c r="Q42" s="16" t="n">
+      <c r="Q42" s="18" t="n">
         <v>5.79</v>
       </c>
-      <c r="R42" s="16" t="n">
+      <c r="R42" s="18" t="n">
         <v>5.49</v>
       </c>
-      <c r="T42" s="16" t="n">
+      <c r="T42" s="18" t="n">
         <v>4931</v>
       </c>
-      <c r="U42" s="16" t="n">
+      <c r="U42" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V42" s="16" t="n">
+      <c r="V42" s="18" t="n">
         <v>81.55</v>
       </c>
-      <c r="W42" s="16" t="n">
+      <c r="W42" s="18" t="n">
         <v>7.92</v>
       </c>
-      <c r="X42" s="16" t="n">
+      <c r="X42" s="18" t="n">
         <v>61.14</v>
       </c>
-      <c r="Y42" s="16" t="n">
+      <c r="Y42" s="18" t="n">
         <v>62.46</v>
       </c>
-      <c r="Z42" s="16" t="n">
+      <c r="Z42" s="18" t="n">
         <v>63.11</v>
       </c>
-      <c r="AA42" s="16" t="n">
+      <c r="AA42" s="18" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="AB42" s="16" t="n">
+      <c r="AB42" s="18" t="n">
         <v>60.93</v>
       </c>
-      <c r="AC42" s="16" t="n">
+      <c r="AC42" s="18" t="n">
         <v>62.17</v>
       </c>
-      <c r="AD42" s="16" t="n">
+      <c r="AD42" s="18" t="n">
         <v>62.77</v>
       </c>
-      <c r="AE42" s="16" t="n">
+      <c r="AE42" s="18" t="n">
         <v>63.9</v>
       </c>
+      <c r="AG42" s="18" t="n">
+        <v>3.16</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n">
+      <c r="A43" s="18" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B43" s="18" t="inlineStr">
         <is>
           <t>Q41</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>alpha-methylstyrene</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D43" s="18" t="inlineStr">
         <is>
           <t>C=C(C)C1=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="F43" s="18" t="n">
         <v>51.45</v>
       </c>
-      <c r="G43" s="16" t="n">
+      <c r="G43" s="18" t="n">
         <v>85.22</v>
       </c>
-      <c r="H43" s="16" t="n">
+      <c r="H43" s="18" t="n">
         <v>33.4</v>
       </c>
-      <c r="J43" s="16" t="n">
+      <c r="J43" s="18" t="n">
         <v>141.34</v>
       </c>
-      <c r="K43" s="16" t="n">
+      <c r="K43" s="18" t="n">
         <v>1.71</v>
       </c>
-      <c r="L43" s="16" t="n">
+      <c r="L43" s="18" t="n">
         <v>5.07</v>
       </c>
-      <c r="M43" s="16" t="n">
+      <c r="M43" s="18" t="n">
         <v>6.48</v>
       </c>
-      <c r="O43" s="16" t="n">
+      <c r="O43" s="18" t="n">
         <v>39.49</v>
       </c>
-      <c r="P43" s="16" t="n">
+      <c r="P43" s="18" t="n">
         <v>-2.71</v>
       </c>
-      <c r="Q43" s="16" t="n">
+      <c r="Q43" s="18" t="n">
         <v>6.11</v>
       </c>
-      <c r="R43" s="16" t="n">
+      <c r="R43" s="18" t="n">
         <v>9.83</v>
       </c>
-      <c r="T43" s="16" t="n">
+      <c r="T43" s="18" t="n">
         <v>4909</v>
       </c>
-      <c r="U43" s="16" t="n">
+      <c r="U43" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V43" s="16" t="n">
+      <c r="V43" s="18" t="n">
         <v>83.95</v>
       </c>
-      <c r="W43" s="16" t="n">
+      <c r="W43" s="18" t="n">
         <v>9.1</v>
       </c>
-      <c r="X43" s="16" t="n">
+      <c r="X43" s="18" t="n">
         <v>60.51</v>
       </c>
-      <c r="Y43" s="16" t="n">
+      <c r="Y43" s="18" t="n">
         <v>62.03</v>
       </c>
-      <c r="Z43" s="16" t="n">
+      <c r="Z43" s="18" t="n">
         <v>62.78</v>
       </c>
-      <c r="AA43" s="16" t="n">
+      <c r="AA43" s="18" t="n">
         <v>64.2</v>
       </c>
-      <c r="AB43" s="16" t="n">
+      <c r="AB43" s="18" t="n">
         <v>58.54</v>
       </c>
-      <c r="AC43" s="16" t="n">
+      <c r="AC43" s="18" t="n">
         <v>60.08</v>
       </c>
-      <c r="AD43" s="16" t="n">
+      <c r="AD43" s="18" t="n">
         <v>60.87</v>
       </c>
-      <c r="AE43" s="16" t="n">
+      <c r="AE43" s="18" t="n">
         <v>62.44</v>
       </c>
+      <c r="AG43" s="18" t="n">
+        <v>3.12</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n">
+      <c r="A44" s="18" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B44" s="18" t="inlineStr">
         <is>
           <t>Q42</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C44" s="18" t="inlineStr">
         <is>
           <t>2-benzoylfuran</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D44" s="18" t="inlineStr">
         <is>
           <t>O=C(C1=CC=CC=C1)C2=CC=CO2</t>
         </is>
       </c>
-      <c r="F44" s="16" t="n">
+      <c r="F44" s="18" t="n">
         <v>58.67</v>
       </c>
-      <c r="G44" s="16" t="n">
+      <c r="G44" s="18" t="n">
         <v>12.21</v>
       </c>
-      <c r="H44" s="16" t="n">
+      <c r="H44" s="18" t="n">
         <v>11.87</v>
       </c>
-      <c r="J44" s="16" t="n">
+      <c r="J44" s="18" t="n">
         <v>150.87</v>
       </c>
-      <c r="K44" s="16" t="n">
+      <c r="K44" s="18" t="n">
         <v>2.12</v>
       </c>
-      <c r="L44" s="16" t="n">
+      <c r="L44" s="18" t="n">
         <v>7.07</v>
       </c>
-      <c r="M44" s="16" t="n">
+      <c r="M44" s="18" t="n">
         <v>5.56</v>
       </c>
-      <c r="O44" s="16" t="n">
+      <c r="O44" s="18" t="n">
         <v>61.43</v>
       </c>
-      <c r="P44" s="16" t="n">
+      <c r="P44" s="18" t="n">
         <v>-1.76</v>
       </c>
-      <c r="Q44" s="16" t="n">
+      <c r="Q44" s="18" t="n">
         <v>6.99</v>
       </c>
-      <c r="R44" s="16" t="n">
+      <c r="R44" s="18" t="n">
         <v>6.77</v>
       </c>
-      <c r="T44" s="16" t="n">
+      <c r="T44" s="18" t="n">
         <v>4909</v>
       </c>
-      <c r="U44" s="16" t="n">
+      <c r="U44" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V44" s="16" t="n">
+      <c r="V44" s="18" t="n">
         <v>73.09</v>
       </c>
-      <c r="W44" s="16" t="n">
+      <c r="W44" s="18" t="n">
         <v>6.7</v>
       </c>
-      <c r="X44" s="16" t="n">
+      <c r="X44" s="18" t="n">
         <v>55.83</v>
       </c>
-      <c r="Y44" s="16" t="n">
+      <c r="Y44" s="18" t="n">
         <v>56.95</v>
       </c>
-      <c r="Z44" s="16" t="n">
+      <c r="Z44" s="18" t="n">
         <v>57.5</v>
       </c>
-      <c r="AA44" s="16" t="n">
+      <c r="AA44" s="18" t="n">
         <v>58.55</v>
       </c>
-      <c r="AB44" s="16" t="n">
+      <c r="AB44" s="18" t="n">
         <v>56.21</v>
       </c>
-      <c r="AC44" s="16" t="n">
+      <c r="AC44" s="18" t="n">
         <v>57.23</v>
       </c>
-      <c r="AD44" s="16" t="n">
+      <c r="AD44" s="18" t="n">
         <v>57.73</v>
       </c>
-      <c r="AE44" s="16" t="n">
+      <c r="AE44" s="18" t="n">
         <v>58.69</v>
       </c>
+      <c r="AG44" s="18" t="n">
+        <v>3.34</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n">
+      <c r="A45" s="18" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B45" s="18" t="inlineStr">
         <is>
           <t>Q43</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C45" s="18" t="inlineStr">
         <is>
           <t>2-acetyl-4-methylthiophene</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="18" t="inlineStr">
         <is>
           <t>O=C(C)C1=CC(C)=CS1</t>
         </is>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="F45" s="18" t="n">
         <v>58.44</v>
       </c>
-      <c r="G45" s="16" t="n">
+      <c r="G45" s="18" t="n">
         <v>11.89</v>
       </c>
-      <c r="H45" s="16" t="n">
+      <c r="H45" s="18" t="n">
         <v>12.88</v>
       </c>
-      <c r="J45" s="16" t="n">
+      <c r="J45" s="18" t="n">
         <v>147.29</v>
       </c>
-      <c r="K45" s="16" t="n">
+      <c r="K45" s="18" t="n">
         <v>1.97</v>
       </c>
-      <c r="L45" s="16" t="n">
+      <c r="L45" s="18" t="n">
         <v>6.03</v>
       </c>
-      <c r="M45" s="16" t="n">
+      <c r="M45" s="18" t="n">
         <v>5.56</v>
       </c>
-      <c r="O45" s="16" t="n">
+      <c r="O45" s="18" t="n">
         <v>57.07</v>
       </c>
-      <c r="P45" s="16" t="n">
+      <c r="P45" s="18" t="n">
         <v>-1.95</v>
       </c>
-      <c r="Q45" s="16" t="n">
+      <c r="Q45" s="18" t="n">
         <v>6.87</v>
       </c>
-      <c r="R45" s="16" t="n">
+      <c r="R45" s="18" t="n">
         <v>6.45</v>
       </c>
-      <c r="T45" s="16" t="n">
+      <c r="T45" s="18" t="n">
         <v>4938</v>
       </c>
-      <c r="U45" s="16" t="n">
+      <c r="U45" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V45" s="16" t="n">
+      <c r="V45" s="18" t="n">
         <v>74.39</v>
       </c>
-      <c r="W45" s="16" t="n">
+      <c r="W45" s="18" t="n">
         <v>6.44</v>
       </c>
-      <c r="X45" s="16" t="n">
+      <c r="X45" s="18" t="n">
         <v>57.8</v>
       </c>
-      <c r="Y45" s="16" t="n">
+      <c r="Y45" s="18" t="n">
         <v>58.87</v>
       </c>
-      <c r="Z45" s="16" t="n">
+      <c r="Z45" s="18" t="n">
         <v>59.4</v>
       </c>
-      <c r="AA45" s="16" t="n">
+      <c r="AA45" s="18" t="n">
         <v>60.41</v>
       </c>
-      <c r="AB45" s="16" t="n">
+      <c r="AB45" s="18" t="n">
         <v>58.32</v>
       </c>
-      <c r="AC45" s="16" t="n">
+      <c r="AC45" s="18" t="n">
         <v>59.33</v>
       </c>
-      <c r="AD45" s="16" t="n">
+      <c r="AD45" s="18" t="n">
         <v>59.82</v>
       </c>
-      <c r="AE45" s="16" t="n">
+      <c r="AE45" s="18" t="n">
         <v>60.73</v>
       </c>
+      <c r="AG45" s="18" t="n">
+        <v>3.12</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n">
+      <c r="A46" s="18" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B46" s="18" t="inlineStr">
         <is>
           <t>Q44</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>2-acetylpyridine</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D46" s="18" t="inlineStr">
         <is>
           <t>CC(C1=NC=CC=C1)=O</t>
         </is>
       </c>
-      <c r="F46" s="16" t="n">
+      <c r="F46" s="18" t="n">
         <v>67.73</v>
       </c>
-      <c r="G46" s="16" t="n">
+      <c r="G46" s="18" t="n">
         <v>11.44</v>
       </c>
-      <c r="H46" s="16" t="n">
+      <c r="H46" s="18" t="n">
         <v>7.7</v>
       </c>
-      <c r="J46" s="16" t="n">
+      <c r="J46" s="18" t="n">
         <v>161.41</v>
       </c>
-      <c r="K46" s="16" t="n">
+      <c r="K46" s="18" t="n">
         <v>2.58</v>
       </c>
-      <c r="L46" s="16" t="n">
+      <c r="L46" s="18" t="n">
         <v>11.35</v>
       </c>
-      <c r="M46" s="16" t="n">
+      <c r="M46" s="18" t="n">
         <v>10.25</v>
       </c>
-      <c r="O46" s="16" t="n">
+      <c r="O46" s="18" t="n">
         <v>60.11</v>
       </c>
-      <c r="P46" s="16" t="n">
+      <c r="P46" s="18" t="n">
         <v>-1.81</v>
       </c>
-      <c r="Q46" s="16" t="n">
+      <c r="Q46" s="18" t="n">
         <v>7.77</v>
       </c>
-      <c r="R46" s="16" t="n">
+      <c r="R46" s="18" t="n">
         <v>7.65</v>
       </c>
-      <c r="T46" s="16" t="n">
+      <c r="T46" s="18" t="n">
         <v>4940</v>
       </c>
-      <c r="U46" s="16" t="n">
+      <c r="U46" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V46" s="16" t="n">
+      <c r="V46" s="18" t="n">
         <v>81.17</v>
       </c>
-      <c r="W46" s="16" t="n">
+      <c r="W46" s="18" t="n">
         <v>5.52</v>
       </c>
-      <c r="X46" s="16" t="n">
+      <c r="X46" s="18" t="n">
         <v>66.95999999999999</v>
       </c>
-      <c r="Y46" s="16" t="n">
+      <c r="Y46" s="18" t="n">
         <v>67.88</v>
       </c>
-      <c r="Z46" s="16" t="n">
+      <c r="Z46" s="18" t="n">
         <v>68.33</v>
       </c>
-      <c r="AA46" s="16" t="n">
+      <c r="AA46" s="18" t="n">
         <v>69.19</v>
       </c>
-      <c r="AB46" s="16" t="n">
+      <c r="AB46" s="18" t="n">
         <v>66.75</v>
       </c>
-      <c r="AC46" s="16" t="n">
+      <c r="AC46" s="18" t="n">
         <v>67.73</v>
       </c>
-      <c r="AD46" s="16" t="n">
+      <c r="AD46" s="18" t="n">
         <v>68.2</v>
       </c>
-      <c r="AE46" s="16" t="n">
+      <c r="AE46" s="18" t="n">
         <v>69.06999999999999</v>
       </c>
+      <c r="AG46" s="18" t="n">
+        <v>3.01</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n">
+      <c r="A47" s="18" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="18" t="inlineStr">
         <is>
           <t>Q45</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C47" s="18" t="inlineStr">
         <is>
           <t>phenyl vinyl selenoxide</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D47" s="18" t="inlineStr">
         <is>
           <t>O=[Se](C=C)C1=CC=CC=C1</t>
         </is>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="F47" s="18" t="n">
         <v>48.31</v>
       </c>
-      <c r="G47" s="16" t="n">
+      <c r="G47" s="18" t="n">
         <v>104.82</v>
       </c>
-      <c r="H47" s="16" t="n">
+      <c r="H47" s="18" t="n">
         <v>51.64</v>
       </c>
-      <c r="J47" s="16" t="n">
+      <c r="J47" s="18" t="n">
         <v>152.61</v>
       </c>
-      <c r="K47" s="16" t="n">
+      <c r="K47" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="L47" s="16" t="n">
+      <c r="L47" s="18" t="n">
         <v>5.98</v>
       </c>
-      <c r="M47" s="16" t="n">
+      <c r="M47" s="18" t="n">
         <v>4.19</v>
       </c>
-      <c r="O47" s="16" t="n">
+      <c r="O47" s="18" t="n">
         <v>46.38</v>
       </c>
-      <c r="P47" s="16" t="n">
+      <c r="P47" s="18" t="n">
         <v>-2.41</v>
       </c>
-      <c r="Q47" s="16" t="n">
+      <c r="Q47" s="18" t="n">
         <v>12.18</v>
       </c>
-      <c r="R47" s="16" t="n">
+      <c r="R47" s="18" t="n">
         <v>14.06</v>
       </c>
-      <c r="T47" s="16" t="n">
+      <c r="T47" s="18" t="n">
         <v>4890</v>
       </c>
-      <c r="U47" s="16" t="n">
+      <c r="U47" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V47" s="16" t="n">
+      <c r="V47" s="18" t="n">
         <v>91.7</v>
       </c>
-      <c r="W47" s="16" t="n">
+      <c r="W47" s="18" t="n">
         <v>7.23</v>
       </c>
-      <c r="X47" s="16" t="n">
+      <c r="X47" s="18" t="n">
         <v>73.06999999999999</v>
       </c>
-      <c r="Y47" s="16" t="n">
+      <c r="Y47" s="18" t="n">
         <v>74.27</v>
       </c>
-      <c r="Z47" s="16" t="n">
+      <c r="Z47" s="18" t="n">
         <v>74.87</v>
       </c>
-      <c r="AA47" s="16" t="n">
+      <c r="AA47" s="18" t="n">
         <v>76</v>
       </c>
-      <c r="AB47" s="16" t="n">
+      <c r="AB47" s="18" t="n">
         <v>71.61</v>
       </c>
-      <c r="AC47" s="16" t="n">
+      <c r="AC47" s="18" t="n">
         <v>72.98</v>
       </c>
-      <c r="AD47" s="16" t="n">
+      <c r="AD47" s="18" t="n">
         <v>73.62</v>
       </c>
-      <c r="AE47" s="16" t="n">
+      <c r="AE47" s="18" t="n">
         <v>74.81999999999999</v>
       </c>
+      <c r="AG47" s="18" t="n">
+        <v>3.24</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n">
+      <c r="A48" s="18" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>Q46</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C48" s="18" t="inlineStr">
         <is>
           <t>2,2-dimethyl-3-phenyl-2H-azirine</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D48" s="18" t="inlineStr">
         <is>
           <t>CC1(C)C(C2=CC=CC=C2)=N1</t>
         </is>
       </c>
-      <c r="F48" s="16" t="n">
+      <c r="F48" s="18" t="n">
         <v>62.47</v>
       </c>
-      <c r="G48" s="16" t="n">
+      <c r="G48" s="18" t="n">
         <v>34.18</v>
       </c>
-      <c r="H48" s="16" t="n">
+      <c r="H48" s="18" t="n">
         <v>24.49</v>
       </c>
-      <c r="J48" s="16" t="n">
+      <c r="J48" s="18" t="n">
         <v>145.35</v>
       </c>
-      <c r="K48" s="16" t="n">
+      <c r="K48" s="18" t="n">
         <v>1.88</v>
       </c>
-      <c r="L48" s="16" t="n">
+      <c r="L48" s="18" t="n">
         <v>31.14</v>
       </c>
-      <c r="M48" s="16" t="n">
+      <c r="M48" s="18" t="n">
         <v>16.3</v>
       </c>
-      <c r="O48" s="16" t="n">
+      <c r="O48" s="18" t="n">
         <v>51.66</v>
       </c>
-      <c r="P48" s="16" t="n">
+      <c r="P48" s="18" t="n">
         <v>-2.18</v>
       </c>
-      <c r="Q48" s="16" t="n">
+      <c r="Q48" s="18" t="n">
         <v>6.13</v>
       </c>
-      <c r="R48" s="16" t="n">
+      <c r="R48" s="18" t="n">
         <v>5.78</v>
       </c>
-      <c r="T48" s="16" t="n">
+      <c r="T48" s="18" t="n">
         <v>4935</v>
       </c>
-      <c r="U48" s="16" t="n">
+      <c r="U48" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V48" s="16" t="n">
+      <c r="V48" s="18" t="n">
         <v>82.20999999999999</v>
       </c>
-      <c r="W48" s="16" t="n">
+      <c r="W48" s="18" t="n">
         <v>6.97</v>
       </c>
-      <c r="X48" s="16" t="n">
+      <c r="X48" s="18" t="n">
         <v>64.26000000000001</v>
       </c>
-      <c r="Y48" s="16" t="n">
+      <c r="Y48" s="18" t="n">
         <v>65.42</v>
       </c>
-      <c r="Z48" s="16" t="n">
+      <c r="Z48" s="18" t="n">
         <v>66</v>
       </c>
-      <c r="AA48" s="16" t="n">
+      <c r="AA48" s="18" t="n">
         <v>67.09</v>
       </c>
-      <c r="AB48" s="16" t="n">
+      <c r="AB48" s="18" t="n">
         <v>63.98</v>
       </c>
-      <c r="AC48" s="16" t="n">
+      <c r="AC48" s="18" t="n">
         <v>65.06999999999999</v>
       </c>
-      <c r="AD48" s="16" t="n">
+      <c r="AD48" s="18" t="n">
         <v>65.59999999999999</v>
       </c>
-      <c r="AE48" s="16" t="n">
+      <c r="AE48" s="18" t="n">
         <v>66.62</v>
       </c>
+      <c r="AG48" s="18" t="n">
+        <v>3.29</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n">
+      <c r="A49" s="18" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B49" s="18" t="inlineStr">
         <is>
           <t>Q47</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>methyl quinoline-8-carboxylate</t>
         </is>
       </c>
-      <c r="D49" s="16" t="inlineStr">
+      <c r="D49" s="18" t="inlineStr">
         <is>
           <t>O=C(C1=CC=CC2=CC=CN=C21)OC</t>
         </is>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="F49" s="18" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="G49" s="16" t="n">
+      <c r="G49" s="18" t="n">
         <v>25.7</v>
       </c>
-      <c r="H49" s="16" t="n">
+      <c r="H49" s="18" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="J49" s="16" t="n">
+      <c r="J49" s="18" t="n">
         <v>152.71</v>
       </c>
-      <c r="K49" s="16" t="n">
+      <c r="K49" s="18" t="n">
         <v>2.2</v>
       </c>
-      <c r="L49" s="16" t="n">
+      <c r="L49" s="18" t="n">
         <v>25.61</v>
       </c>
-      <c r="M49" s="16" t="n">
+      <c r="M49" s="18" t="n">
         <v>4.69</v>
       </c>
-      <c r="O49" s="16" t="n">
+      <c r="O49" s="18" t="n">
         <v>58.25</v>
       </c>
-      <c r="P49" s="16" t="n">
+      <c r="P49" s="18" t="n">
         <v>-1.89</v>
       </c>
-      <c r="Q49" s="16" t="n">
+      <c r="Q49" s="18" t="n">
         <v>7.8</v>
       </c>
-      <c r="R49" s="16" t="n">
+      <c r="R49" s="18" t="n">
         <v>7.91</v>
       </c>
-      <c r="T49" s="16" t="n">
+      <c r="T49" s="18" t="n">
         <v>4934</v>
       </c>
-      <c r="U49" s="16" t="n">
+      <c r="U49" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V49" s="16" t="n">
+      <c r="V49" s="18" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="W49" s="16" t="n">
+      <c r="W49" s="18" t="n">
         <v>7.07</v>
       </c>
-      <c r="X49" s="16" t="n">
+      <c r="X49" s="18" t="n">
         <v>57.4</v>
       </c>
-      <c r="Y49" s="16" t="n">
+      <c r="Y49" s="18" t="n">
         <v>58.58</v>
       </c>
-      <c r="Z49" s="16" t="n">
+      <c r="Z49" s="18" t="n">
         <v>59.17</v>
       </c>
-      <c r="AA49" s="16" t="n">
+      <c r="AA49" s="18" t="n">
         <v>60.27</v>
       </c>
-      <c r="AB49" s="16" t="n">
+      <c r="AB49" s="18" t="n">
         <v>57.58</v>
       </c>
-      <c r="AC49" s="16" t="n">
+      <c r="AC49" s="18" t="n">
         <v>58.71</v>
       </c>
-      <c r="AD49" s="16" t="n">
+      <c r="AD49" s="18" t="n">
         <v>59.23</v>
       </c>
-      <c r="AE49" s="16" t="n">
+      <c r="AE49" s="18" t="n">
         <v>60.19</v>
       </c>
+      <c r="AG49" s="18" t="n">
+        <v>3.41</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n">
+      <c r="A50" s="18" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="18" t="inlineStr">
         <is>
           <t>Q48</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>cyclohex-2-en-1-one</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="18" t="inlineStr">
         <is>
           <t>O=C1C=CCCC1</t>
         </is>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="F50" s="18" t="n">
         <v>68.42</v>
       </c>
-      <c r="G50" s="16" t="n">
+      <c r="G50" s="18" t="n">
         <v>10.44</v>
       </c>
-      <c r="H50" s="16" t="n">
+      <c r="H50" s="18" t="n">
         <v>7.55</v>
       </c>
-      <c r="J50" s="16" t="n">
+      <c r="J50" s="18" t="n">
         <v>158.86</v>
       </c>
-      <c r="K50" s="16" t="n">
+      <c r="K50" s="18" t="n">
         <v>2.47</v>
       </c>
-      <c r="L50" s="16" t="n">
+      <c r="L50" s="18" t="n">
         <v>4.04</v>
       </c>
-      <c r="M50" s="16" t="n">
+      <c r="M50" s="18" t="n">
         <v>2.48</v>
       </c>
-      <c r="O50" s="16" t="n">
+      <c r="O50" s="18" t="n">
         <v>51.91</v>
       </c>
-      <c r="P50" s="16" t="n">
+      <c r="P50" s="18" t="n">
         <v>-2.17</v>
       </c>
-      <c r="Q50" s="16" t="n">
+      <c r="Q50" s="18" t="n">
         <v>8.66</v>
       </c>
-      <c r="R50" s="16" t="n">
+      <c r="R50" s="18" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="T50" s="16" t="n">
+      <c r="T50" s="18" t="n">
         <v>4959</v>
       </c>
-      <c r="U50" s="16" t="n">
+      <c r="U50" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="V50" s="16" t="n">
+      <c r="V50" s="18" t="n">
         <v>79.77</v>
       </c>
-      <c r="W50" s="16" t="n">
+      <c r="W50" s="18" t="n">
         <v>5.26</v>
       </c>
-      <c r="X50" s="16" t="n">
+      <c r="X50" s="18" t="n">
         <v>66.2</v>
       </c>
-      <c r="Y50" s="16" t="n">
+      <c r="Y50" s="18" t="n">
         <v>67.08</v>
       </c>
-      <c r="Z50" s="16" t="n">
+      <c r="Z50" s="18" t="n">
         <v>67.52</v>
       </c>
-      <c r="AA50" s="16" t="n">
+      <c r="AA50" s="18" t="n">
         <v>68.34</v>
       </c>
-      <c r="AB50" s="16" t="n">
+      <c r="AB50" s="18" t="n">
         <v>64.34999999999999</v>
       </c>
-      <c r="AC50" s="16" t="n">
+      <c r="AC50" s="18" t="n">
         <v>65.53</v>
       </c>
-      <c r="AD50" s="16" t="n">
+      <c r="AD50" s="18" t="n">
         <v>66.17</v>
       </c>
-      <c r="AE50" s="16" t="n">
+      <c r="AE50" s="18" t="n">
         <v>67.42</v>
+      </c>
+      <c r="AG50" s="18" t="n">
+        <v>2.86</v>
       </c>
     </row>
   </sheetData>
@@ -4992,7 +5159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5003,798 +5170,825 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Block</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="19" t="inlineStr">
         <is>
           <t>Taken from</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>quencher_id</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr"/>
-      <c r="D2" s="19" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr"/>
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>Quencher number.</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: quencher_id</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>quencher_name</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr"/>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>Label used throughout, Q&lt;n&gt;.</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>compound_identification.xlsx: Quenchers/quencher_id</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>compound</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr"/>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>Name derived from the SMILES, as in the experimental workbook.</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>compound_identification.xlsx: Quenchers/name</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>smiles</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr"/>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Structure.</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>compound_identification.xlsx: Quenchers/smiles</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Triplet state, adiabatic DFT / kcal mol-1</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>E_T / kcal mol-1</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>Adiabatic triplet energy, Gibbs-corrected, lowest conformer of each state.</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: E_T</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Triplet state, adiabatic DFT / kcal mol-1</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>lambda_S0_T1 / kcal mol-1</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>S0 surface: E_S0 at the T1 geometry minus E_S0 at its own.</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S0_T1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Triplet state, adiabatic DFT / kcal mol-1</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>lambda_T1_S0 / kcal mol-1</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>T1 surface: E_T1 at the S0 geometry minus E_T1 at its own.</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_T1_S0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Oxidation, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>dG_Ox / kcal mol-1</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>Free energy of Q -&gt; Q+.</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: dG_Ox</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Oxidation, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>E_Ox_vs_SCE_calc / V</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>dG_Ox / F - 4.42 V.</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: E_Ox_vs_SCE_calc</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Oxidation, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>lambda_S0_Dplus / kcal mol-1</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>S0 surface: E_S0 at the Dplus (radical cation) geometry minus E_S0 at its own.</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S0_Dplus</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Oxidation, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>lambda_Dplus_S0 / kcal mol-1</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>Dplus surface: E_Dplus at the S0 geometry minus E_Dplus at its own.</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_Dplus_S0</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Reduction, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>dG_Red / kcal mol-1</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>Free energy released by Q -&gt; Q-.</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: dG_Red</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Reduction, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>E_Red_vs_SCE_calc / V</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>dG_Red / F - 4.42 V.</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: E_Red_vs_SCE_calc</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Reduction, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>lambda_S0_Dminus / kcal mol-1</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>S0 surface: E_S0 at the Dminus (radical anion) geometry minus E_S0 at its own.</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S0_Dminus</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Reduction, adiabatic DFT</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>lambda_Dminus_S0 / kcal mol-1</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>Dminus surface: E_Dminus at the S0 geometry minus E_Dminus at its own.</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_Dminus_S0</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>n_samples</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr"/>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr"/>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>Sampled geometries with both single points.</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: n_samples</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>n_trajectories</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr"/>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>MD trajectories sampled.</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: n_trajectories</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>dvte_mu / kcal mol-1</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>Mean vertical singlet-triplet gap.</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_mu</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>dvte_std / kcal mol-1</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>Standard deviation of the gaps.</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_std</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>dvte_0.005 / kcal mol-1</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>0.005 quantile of a normal distribution with that mean and deviation.</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.005</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>dvte_0.008 / kcal mol-1</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>0.008 quantile of a normal distribution with that mean and deviation.</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.008</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>dvte_0.01 / kcal mol-1</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>0.01 quantile of a normal distribution with that mean and deviation.</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.01</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>dvte_0.015 / kcal mol-1</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>0.015 quantile of a normal distribution with that mean and deviation.</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.015</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>dvte_0.005_kde / kcal mol-1</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>0.005 quantile of a kernel density estimate of the samples (Scott's rule).</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.005_kde</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>dvte_0.008_kde / kcal mol-1</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>0.008 quantile of a kernel density estimate of the samples (Scott's rule).</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.008_kde</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>dvte_0.01_kde / kcal mol-1</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>0.01 quantile of a kernel density estimate of the samples (Scott's rule).</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.01_kde</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Vertical triplet energy distribution, DvTE / kcal mol-1</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>dvte_0.015_kde / kcal mol-1</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>kcal mol-1</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>0.015 quantile of a kernel density estimate of the samples (Scott's rule).</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.015_kde</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n"/>
-      <c r="B29" s="18" t="n"/>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="18" t="n"/>
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>Molecular size, DFT / A</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>radius_S0 / A</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>Radius of the sphere with the van der Waals volume of the optimised S0 geometry: union of atomic spheres with Bondi radii (Ir and Ru 2.00 A), counted on a 0.1 A grid. r_PC + r_Q is the contact distance of a pair in the benchmark.</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: radius_S0</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>One row per quencher. DFT values are rounded to 2 decimals in kcal/mol and V.</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="n"/>
-      <c r="C30" s="18" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="18" t="n"/>
+      <c r="A30" s="20" t="n"/>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="20" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>One row per quencher. DFT values are rounded to 2 decimals in kcal/mol, V and A.</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="21" t="n"/>
+      <c r="E31" s="20" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>The energies behind each value are in the deposited ORCA outputs under</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="18" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="B32" s="20" t="n"/>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="20" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DFT/Q&lt;n&gt;/&lt;state&gt;/, and every sampled gap in</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n"/>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="18" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="20" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte_samples.csv.gz.</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n"/>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="18" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="20" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Read with pandas as: pd.read_excel(path, header=1), then drop the 'Unnamed' columns.</t>
         </is>
       </c>
-      <c r="B34" s="18" t="n"/>
-      <c r="C34" s="18" t="n"/>
-      <c r="D34" s="19" t="n"/>
-      <c r="E34" s="18" t="n"/>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="21" t="n"/>
+      <c r="E35" s="20" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/computational_data_processed/quencher_properties_calc.xlsx
+++ b/data/computational_data_processed/quencher_properties_calc.xlsx
@@ -782,7 +782,7 @@
         <v>4.14</v>
       </c>
       <c r="O3" s="18" t="n">
-        <v>49.93</v>
+        <v>-49.93</v>
       </c>
       <c r="P3" s="18" t="n">
         <v>-2.25</v>
@@ -874,7 +874,7 @@
         <v>4.39</v>
       </c>
       <c r="O4" s="18" t="n">
-        <v>41.41</v>
+        <v>-41.41</v>
       </c>
       <c r="P4" s="18" t="n">
         <v>-2.62</v>
@@ -966,7 +966,7 @@
         <v>11</v>
       </c>
       <c r="O5" s="18" t="n">
-        <v>73.03</v>
+        <v>-73.03</v>
       </c>
       <c r="P5" s="18" t="n">
         <v>-1.25</v>
@@ -1058,7 +1058,7 @@
         <v>3.58</v>
       </c>
       <c r="O6" s="18" t="n">
-        <v>35.44</v>
+        <v>-35.44</v>
       </c>
       <c r="P6" s="18" t="n">
         <v>-2.88</v>
@@ -1150,7 +1150,7 @@
         <v>3.49</v>
       </c>
       <c r="O7" s="18" t="n">
-        <v>63.87</v>
+        <v>-63.87</v>
       </c>
       <c r="P7" s="18" t="n">
         <v>-1.65</v>
@@ -1242,7 +1242,7 @@
         <v>3.5</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>49.56</v>
+        <v>-49.56</v>
       </c>
       <c r="P8" s="18" t="n">
         <v>-2.27</v>
@@ -1334,7 +1334,7 @@
         <v>3.83</v>
       </c>
       <c r="O9" s="18" t="n">
-        <v>60.27</v>
+        <v>-60.27</v>
       </c>
       <c r="P9" s="18" t="n">
         <v>-1.81</v>
@@ -1426,7 +1426,7 @@
         <v>5.93</v>
       </c>
       <c r="O10" s="18" t="n">
-        <v>54.84</v>
+        <v>-54.84</v>
       </c>
       <c r="P10" s="18" t="n">
         <v>-2.04</v>
@@ -1518,7 +1518,7 @@
         <v>6.87</v>
       </c>
       <c r="O11" s="18" t="n">
-        <v>39.09</v>
+        <v>-39.09</v>
       </c>
       <c r="P11" s="18" t="n">
         <v>-2.73</v>
@@ -1778,7 +1778,7 @@
         <v>4.57</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>44.5</v>
+        <v>-44.5</v>
       </c>
       <c r="P14" s="18" t="n">
         <v>-2.49</v>
@@ -1870,7 +1870,7 @@
         <v>6.92</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>76.12</v>
+        <v>-76.12</v>
       </c>
       <c r="P15" s="18" t="n">
         <v>-1.12</v>
@@ -1962,7 +1962,7 @@
         <v>7.49</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>48</v>
+        <v>-48</v>
       </c>
       <c r="P16" s="18" t="n">
         <v>-2.34</v>
@@ -2054,7 +2054,7 @@
         <v>4.37</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>32.73</v>
+        <v>-32.73</v>
       </c>
       <c r="P17" s="18" t="n">
         <v>-3</v>
@@ -2146,7 +2146,7 @@
         <v>4.35</v>
       </c>
       <c r="O18" s="18" t="n">
-        <v>45.51</v>
+        <v>-45.51</v>
       </c>
       <c r="P18" s="18" t="n">
         <v>-2.45</v>
@@ -2238,7 +2238,7 @@
         <v>13.69</v>
       </c>
       <c r="O19" s="18" t="n">
-        <v>54.16</v>
+        <v>-54.16</v>
       </c>
       <c r="P19" s="18" t="n">
         <v>-2.07</v>
@@ -2330,7 +2330,7 @@
         <v>13.82</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>43.96</v>
+        <v>-43.96</v>
       </c>
       <c r="P20" s="18" t="n">
         <v>-2.51</v>
@@ -2422,7 +2422,7 @@
         <v>4.64</v>
       </c>
       <c r="O21" s="18" t="n">
-        <v>57.15</v>
+        <v>-57.15</v>
       </c>
       <c r="P21" s="18" t="n">
         <v>-1.94</v>
@@ -2514,7 +2514,7 @@
         <v>3.03</v>
       </c>
       <c r="O22" s="18" t="n">
-        <v>41.8</v>
+        <v>-41.8</v>
       </c>
       <c r="P22" s="18" t="n">
         <v>-2.61</v>
@@ -2606,7 +2606,7 @@
         <v>5.32</v>
       </c>
       <c r="O23" s="18" t="n">
-        <v>56.74</v>
+        <v>-56.74</v>
       </c>
       <c r="P23" s="18" t="n">
         <v>-1.96</v>
@@ -2698,7 +2698,7 @@
         <v>7.13</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>57.17</v>
+        <v>-57.17</v>
       </c>
       <c r="P24" s="18" t="n">
         <v>-1.94</v>
@@ -2790,7 +2790,7 @@
         <v>3.43</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>45.49</v>
+        <v>-45.49</v>
       </c>
       <c r="P25" s="18" t="n">
         <v>-2.45</v>
@@ -2882,7 +2882,7 @@
         <v>5.4</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>42.69</v>
+        <v>-42.69</v>
       </c>
       <c r="P26" s="18" t="n">
         <v>-2.57</v>
@@ -2974,7 +2974,7 @@
         <v>4.53</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>64.56</v>
+        <v>-64.56</v>
       </c>
       <c r="P27" s="18" t="n">
         <v>-1.62</v>
@@ -3066,7 +3066,7 @@
         <v>5.17</v>
       </c>
       <c r="O28" s="18" t="n">
-        <v>62.18</v>
+        <v>-62.18</v>
       </c>
       <c r="P28" s="18" t="n">
         <v>-1.72</v>
@@ -3158,7 +3158,7 @@
         <v>5.4</v>
       </c>
       <c r="O29" s="18" t="n">
-        <v>65.28</v>
+        <v>-65.28</v>
       </c>
       <c r="P29" s="18" t="n">
         <v>-1.59</v>
@@ -3250,7 +3250,7 @@
         <v>5.94</v>
       </c>
       <c r="O30" s="18" t="n">
-        <v>71.04000000000001</v>
+        <v>-71.04000000000001</v>
       </c>
       <c r="P30" s="18" t="n">
         <v>-1.34</v>
@@ -3342,7 +3342,7 @@
         <v>6.24</v>
       </c>
       <c r="O31" s="18" t="n">
-        <v>55.05</v>
+        <v>-55.05</v>
       </c>
       <c r="P31" s="18" t="n">
         <v>-2.03</v>
@@ -3434,7 +3434,7 @@
         <v>4.73</v>
       </c>
       <c r="O32" s="18" t="n">
-        <v>49.29</v>
+        <v>-49.29</v>
       </c>
       <c r="P32" s="18" t="n">
         <v>-2.28</v>
@@ -3526,7 +3526,7 @@
         <v>9.34</v>
       </c>
       <c r="O33" s="18" t="n">
-        <v>40.2</v>
+        <v>-40.2</v>
       </c>
       <c r="P33" s="18" t="n">
         <v>-2.68</v>
@@ -3618,7 +3618,7 @@
         <v>2.17</v>
       </c>
       <c r="O34" s="18" t="n">
-        <v>53.76</v>
+        <v>-53.76</v>
       </c>
       <c r="P34" s="18" t="n">
         <v>-2.09</v>
@@ -3710,7 +3710,7 @@
         <v>3.15</v>
       </c>
       <c r="O35" s="18" t="n">
-        <v>51.25</v>
+        <v>-51.25</v>
       </c>
       <c r="P35" s="18" t="n">
         <v>-2.2</v>
@@ -3802,7 +3802,7 @@
         <v>10.13</v>
       </c>
       <c r="O36" s="18" t="n">
-        <v>44</v>
+        <v>-44</v>
       </c>
       <c r="P36" s="18" t="n">
         <v>-2.51</v>
@@ -3894,7 +3894,7 @@
         <v>9.19</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>46.63</v>
+        <v>-46.63</v>
       </c>
       <c r="P37" s="18" t="n">
         <v>-2.4</v>
@@ -3986,7 +3986,7 @@
         <v>4.57</v>
       </c>
       <c r="O38" s="18" t="n">
-        <v>44.85</v>
+        <v>-44.85</v>
       </c>
       <c r="P38" s="18" t="n">
         <v>-2.48</v>
@@ -4078,7 +4078,7 @@
         <v>6.1</v>
       </c>
       <c r="O39" s="18" t="n">
-        <v>44.68</v>
+        <v>-44.68</v>
       </c>
       <c r="P39" s="18" t="n">
         <v>-2.48</v>
@@ -4170,7 +4170,7 @@
         <v>4.54</v>
       </c>
       <c r="O40" s="18" t="n">
-        <v>41.61</v>
+        <v>-41.61</v>
       </c>
       <c r="P40" s="18" t="n">
         <v>-2.62</v>
@@ -4262,7 +4262,7 @@
         <v>6.66</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>49.9</v>
+        <v>-49.9</v>
       </c>
       <c r="P41" s="18" t="n">
         <v>-2.26</v>
@@ -4354,7 +4354,7 @@
         <v>6.49</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>45.72</v>
+        <v>-45.72</v>
       </c>
       <c r="P42" s="18" t="n">
         <v>-2.44</v>
@@ -4446,7 +4446,7 @@
         <v>6.48</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>39.49</v>
+        <v>-39.49</v>
       </c>
       <c r="P43" s="18" t="n">
         <v>-2.71</v>
@@ -4538,7 +4538,7 @@
         <v>5.56</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>61.43</v>
+        <v>-61.43</v>
       </c>
       <c r="P44" s="18" t="n">
         <v>-1.76</v>
@@ -4630,7 +4630,7 @@
         <v>5.56</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>57.07</v>
+        <v>-57.07</v>
       </c>
       <c r="P45" s="18" t="n">
         <v>-1.95</v>
@@ -4722,7 +4722,7 @@
         <v>10.25</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>60.11</v>
+        <v>-60.11</v>
       </c>
       <c r="P46" s="18" t="n">
         <v>-1.81</v>
@@ -4814,7 +4814,7 @@
         <v>4.19</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>46.38</v>
+        <v>-46.38</v>
       </c>
       <c r="P47" s="18" t="n">
         <v>-2.41</v>
@@ -4906,7 +4906,7 @@
         <v>16.3</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>51.66</v>
+        <v>-51.66</v>
       </c>
       <c r="P48" s="18" t="n">
         <v>-2.18</v>
@@ -4998,7 +4998,7 @@
         <v>4.69</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>58.25</v>
+        <v>-58.25</v>
       </c>
       <c r="P49" s="18" t="n">
         <v>-1.89</v>
@@ -5090,7 +5090,7 @@
         <v>2.48</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>51.91</v>
+        <v>-51.91</v>
       </c>
       <c r="P50" s="18" t="n">
         <v>-2.17</v>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>Free energy released by Q -&gt; Q-.</t>
+          <t>Free energy of Q -&gt; Q-.</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>dG_Red / F - 4.42 V.</t>
+          <t>-dG_Red / F - 4.42 V.</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">

--- a/data/computational_data_processed/quencher_properties_calc.xlsx
+++ b/data/computational_data_processed/quencher_properties_calc.xlsx
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E2" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: quencher_id</t>
+          <t>computational_data_processed/quencher_dft.csv: quencher_id</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: E_T</t>
+          <t>computational_data_processed/quencher_dft.csv: E_T</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S0_T1</t>
+          <t>computational_data_processed/quencher_dft.csv: lambda_S0_T1</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_T1_S0</t>
+          <t>computational_data_processed/quencher_dft.csv: lambda_T1_S0</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: dG_Ox</t>
+          <t>computational_data_processed/quencher_dft.csv: dG_Ox</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: E_Ox_vs_SCE_calc</t>
+          <t>computational_data_processed/quencher_dft.csv: E_Ox_vs_SCE_calc</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S0_Dplus</t>
+          <t>computational_data_processed/quencher_dft.csv: lambda_S0_Dplus</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_Dplus_S0</t>
+          <t>computational_data_processed/quencher_dft.csv: lambda_Dplus_S0</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: dG_Red</t>
+          <t>computational_data_processed/quencher_dft.csv: dG_Red</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: E_Red_vs_SCE_calc</t>
+          <t>computational_data_processed/quencher_dft.csv: E_Red_vs_SCE_calc</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_S0_Dminus</t>
+          <t>computational_data_processed/quencher_dft.csv: lambda_S0_Dminus</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: lambda_Dminus_S0</t>
+          <t>computational_data_processed/quencher_dft.csv: lambda_Dminus_S0</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: n_samples</t>
+          <t>computational_data_processed/quencher_dvte.csv: n_samples</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: n_trajectories</t>
+          <t>computational_data_processed/quencher_dvte.csv: n_trajectories</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_mu</t>
+          <t>computational_data_processed/quencher_dvte.csv: dvte_mu</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_std</t>
+          <t>computational_data_processed/quencher_dvte.csv: dvte_std</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.005</t>
+          <t>computational_data_processed/quencher_dvte.csv: dvte_0.005</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.008</t>
+          <t>computational_data_processed/quencher_dvte.csv: dvte_0.008</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.01</t>
+          <t>computational_data_processed/quencher_dvte.csv: dvte_0.01</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.015</t>
+          <t>computational_data_processed/quencher_dvte.csv: dvte_0.015</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.005_kde</t>
+          <t>computational_data_processed/quencher_dvte.csv: dvte_0.005_kde</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.008_kde</t>
+          <t>computational_data_processed/quencher_dvte.csv: dvte_0.008_kde</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.01_kde</t>
+          <t>computational_data_processed/quencher_dvte.csv: dvte_0.01_kde</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte.csv: dvte_0.015_kde</t>
+          <t>computational_data_processed/quencher_dvte.csv: dvte_0.015_kde</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DFT/quencher_dft.csv: radius_S0</t>
+          <t>computational_data_processed/quencher_dft.csv: radius_S0</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>computational_data_raw/quencher_adiabatic_DvTE/quencher_dvte_samples.csv.gz.</t>
+          <t>computational_data_processed/quencher_dvte_samples.csv.gz.</t>
         </is>
       </c>
       <c r="B34" s="20" t="n"/>
